--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F96134-290B-4032-A72C-CD88A7496F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFDA538-8DCC-4860-A625-522A51E418E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1215" windowWidth="24240" windowHeight="13920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -12148,7 +12148,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>624</v>
+        <v>714.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -12171,7 +12171,7 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>624</v>
+        <v>714.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -13229,7 +13229,7 @@
         <v>9</v>
       </c>
       <c r="G49">
-        <v>805</v>
+        <v>918.5</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -13252,7 +13252,7 @@
         <v>13</v>
       </c>
       <c r="G50">
-        <v>357</v>
+        <v>407</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -13275,7 +13275,7 @@
         <v>9</v>
       </c>
       <c r="G51">
-        <v>805</v>
+        <v>918.5</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -13298,7 +13298,7 @@
         <v>13</v>
       </c>
       <c r="G52">
-        <v>377</v>
+        <v>407</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -13321,7 +13321,7 @@
         <v>9</v>
       </c>
       <c r="G53">
-        <v>805</v>
+        <v>918.5</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -13344,7 +13344,7 @@
         <v>9</v>
       </c>
       <c r="G54">
-        <v>1610</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -13367,7 +13367,7 @@
         <v>13</v>
       </c>
       <c r="G55">
-        <v>377</v>
+        <v>407</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -13390,7 +13390,7 @@
         <v>9</v>
       </c>
       <c r="G56">
-        <v>805</v>
+        <v>918.5</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -13413,7 +13413,7 @@
         <v>9</v>
       </c>
       <c r="G57">
-        <v>1610</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -13436,7 +13436,7 @@
         <v>13</v>
       </c>
       <c r="G58">
-        <v>357</v>
+        <v>407</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFDA538-8DCC-4860-A625-522A51E418E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF26B1DA-46EA-43C1-8D54-6FE737EB8526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -13574,7 +13574,7 @@
         <v>13</v>
       </c>
       <c r="G64">
-        <v>642</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -13597,7 +13597,7 @@
         <v>9</v>
       </c>
       <c r="G65">
-        <v>2560</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -13620,7 +13620,7 @@
         <v>9</v>
       </c>
       <c r="G66">
-        <v>1560</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -13643,7 +13643,7 @@
         <v>13</v>
       </c>
       <c r="G67">
-        <v>404</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -21065,7 +21065,7 @@
         <v>32</v>
       </c>
       <c r="G27">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -21088,7 +21088,7 @@
         <v>32</v>
       </c>
       <c r="G28">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -21111,7 +21111,7 @@
         <v>32</v>
       </c>
       <c r="G29">
-        <v>146.5</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -21134,7 +21134,7 @@
         <v>32</v>
       </c>
       <c r="G30">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -21157,7 +21157,7 @@
         <v>32</v>
       </c>
       <c r="G31">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -21180,7 +21180,7 @@
         <v>32</v>
       </c>
       <c r="G32">
-        <v>146.5</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF26B1DA-46EA-43C1-8D54-6FE737EB8526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14D8423-DC7B-45B1-ACFC-2A1656BD6568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="630" yWindow="1500" windowWidth="24240" windowHeight="13920" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3530" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3526" uniqueCount="1089">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -5114,7 +5114,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5766,7 +5766,7 @@
         <v>32</v>
       </c>
       <c r="G28">
-        <v>540</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5777,10 +5777,10 @@
         <v>667</v>
       </c>
       <c r="C29">
-        <v>3487</v>
+        <v>4488</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -5789,18 +5789,18 @@
         <v>13</v>
       </c>
       <c r="G29">
-        <v>163</v>
+        <v>299.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B30" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C30">
-        <v>4488</v>
+        <v>4333</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -5812,18 +5812,18 @@
         <v>13</v>
       </c>
       <c r="G30">
-        <v>272</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B31" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C31">
-        <v>4333</v>
+        <v>4388</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -5835,18 +5835,18 @@
         <v>13</v>
       </c>
       <c r="G31">
-        <v>259.5</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B32" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C32">
-        <v>4388</v>
+        <v>4389</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -5858,30 +5858,30 @@
         <v>13</v>
       </c>
       <c r="G32">
-        <v>145</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B33" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C33">
-        <v>4389</v>
+        <v>3488</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G33">
-        <v>102</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5892,33 +5892,33 @@
         <v>675</v>
       </c>
       <c r="C34">
-        <v>3488</v>
+        <v>3400</v>
       </c>
       <c r="D34">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G34">
-        <v>220</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B35" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C35">
-        <v>3400</v>
+        <v>2257</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -5927,7 +5927,7 @@
         <v>13</v>
       </c>
       <c r="G35">
-        <v>57</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -5938,53 +5938,53 @@
         <v>677</v>
       </c>
       <c r="C36">
-        <v>2257</v>
+        <v>565</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G36">
-        <v>16</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B37" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C37">
-        <v>565</v>
+        <v>4474</v>
       </c>
       <c r="D37">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G37">
-        <v>123</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B38" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C38">
-        <v>4474</v>
+        <v>4473</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B39" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C39">
-        <v>4473</v>
+        <v>2658</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -6024,13 +6024,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B40" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C40">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -6047,16 +6047,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B41" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C41">
         <v>2657</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -6065,18 +6065,18 @@
         <v>13</v>
       </c>
       <c r="G41">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B42" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C42">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -6093,48 +6093,48 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B43" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C43">
-        <v>2658</v>
+        <v>3537</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>1057</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G43">
-        <v>65</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B44" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C44">
-        <v>3537</v>
+        <v>2732</v>
       </c>
       <c r="D44">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>1057</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44">
-        <v>162</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -6145,42 +6145,42 @@
         <v>691</v>
       </c>
       <c r="C45">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G45">
-        <v>175</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B46" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C46">
-        <v>2733</v>
+        <v>2584</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G46">
-        <v>87.5</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -6191,42 +6191,42 @@
         <v>693</v>
       </c>
       <c r="C47">
-        <v>2584</v>
+        <v>2677</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G47">
-        <v>205</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B48" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C48">
-        <v>2677</v>
+        <v>2495</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G48">
-        <v>104.5</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -6237,65 +6237,65 @@
         <v>695</v>
       </c>
       <c r="C49">
-        <v>2495</v>
+        <v>2678</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G49">
-        <v>197</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B50" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C50">
-        <v>2678</v>
+        <v>4498</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>1057</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G50">
-        <v>100.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B51" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C51">
-        <v>4498</v>
+        <v>4253</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>1057</v>
+        <v>8</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
       </c>
       <c r="G51">
-        <v>240</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -6306,10 +6306,10 @@
         <v>699</v>
       </c>
       <c r="C52">
-        <v>4253</v>
+        <v>4500</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -6318,7 +6318,7 @@
         <v>233</v>
       </c>
       <c r="G52">
-        <v>112</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -6329,19 +6329,19 @@
         <v>699</v>
       </c>
       <c r="C53">
-        <v>4500</v>
+        <v>4249</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>8</v>
+        <v>1057</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
       </c>
       <c r="G53">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -6352,10 +6352,10 @@
         <v>699</v>
       </c>
       <c r="C54">
-        <v>4249</v>
+        <v>3724</v>
       </c>
       <c r="D54">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>1057</v>
@@ -6364,99 +6364,99 @@
         <v>233</v>
       </c>
       <c r="G54">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B55" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C55">
-        <v>3724</v>
+        <v>3736</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
         <v>1057</v>
       </c>
       <c r="F55" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G55">
-        <v>224</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B56" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C56">
-        <v>3736</v>
+        <v>4499</v>
       </c>
       <c r="D56">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>1057</v>
       </c>
       <c r="F56" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="G56">
-        <v>162</v>
+        <v>240</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B57" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C57">
-        <v>4499</v>
+        <v>3536</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
         <v>1057</v>
       </c>
       <c r="F57" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G57">
-        <v>240</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B58" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C58">
-        <v>3536</v>
+        <v>2494</v>
       </c>
       <c r="D58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>1057</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
       </c>
       <c r="G58">
-        <v>162</v>
+        <v>188.5</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -6467,134 +6467,134 @@
         <v>707</v>
       </c>
       <c r="C59">
-        <v>2494</v>
+        <v>2679</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G59">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B60" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C60">
-        <v>2679</v>
+        <v>4497</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
+        <v>1057</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G60">
-        <v>87</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B61" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C61">
-        <v>4497</v>
+        <v>2493</v>
       </c>
       <c r="D61">
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>1057</v>
+        <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G61">
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B62" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C62">
-        <v>2493</v>
+        <v>3535</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>8</v>
+        <v>1057</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
       </c>
       <c r="G62">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B63" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C63">
-        <v>3535</v>
+        <v>2498</v>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E63" t="s">
-        <v>1057</v>
+        <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G63">
-        <v>162</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B64" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C64">
-        <v>2498</v>
+        <v>2806</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G64">
-        <v>87</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -6605,42 +6605,42 @@
         <v>715</v>
       </c>
       <c r="C65">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G65">
-        <v>472.5</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B66" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C66">
-        <v>2807</v>
+        <v>4556</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G66">
-        <v>159.5</v>
+        <v>900</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -6651,33 +6651,33 @@
         <v>717</v>
       </c>
       <c r="C67">
-        <v>4556</v>
+        <v>4557</v>
       </c>
       <c r="D67">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G67">
-        <v>900</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B68" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C68">
-        <v>4557</v>
+        <v>4018</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -6686,7 +6686,7 @@
         <v>13</v>
       </c>
       <c r="G68">
-        <v>182</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -6697,10 +6697,10 @@
         <v>719</v>
       </c>
       <c r="C69">
-        <v>4018</v>
+        <v>2652</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -6709,21 +6709,21 @@
         <v>13</v>
       </c>
       <c r="G69">
-        <v>230</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B70" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C70">
-        <v>2652</v>
+        <v>4049</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -6732,7 +6732,7 @@
         <v>13</v>
       </c>
       <c r="G70">
-        <v>117</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -6743,10 +6743,10 @@
         <v>721</v>
       </c>
       <c r="C71">
-        <v>4049</v>
+        <v>3737</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -6755,21 +6755,21 @@
         <v>13</v>
       </c>
       <c r="G71">
-        <v>210</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B72" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C72">
-        <v>3737</v>
+        <v>4301</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -6778,21 +6778,21 @@
         <v>13</v>
       </c>
       <c r="G72">
-        <v>107</v>
+        <v>235</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B73" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C73">
-        <v>4301</v>
+        <v>4334</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -6801,30 +6801,30 @@
         <v>13</v>
       </c>
       <c r="G73">
-        <v>235</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B74" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C74">
-        <v>4334</v>
+        <v>195</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G74">
-        <v>376.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -6835,42 +6835,42 @@
         <v>727</v>
       </c>
       <c r="C75">
-        <v>195</v>
+        <v>54</v>
       </c>
       <c r="D75">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G75">
-        <v>255</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B76" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C76">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G76">
-        <v>53</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -6881,42 +6881,42 @@
         <v>729</v>
       </c>
       <c r="C77">
-        <v>63</v>
+        <v>2483</v>
       </c>
       <c r="D77">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G77">
-        <v>237.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B78" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C78">
-        <v>2483</v>
+        <v>2974</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G78">
-        <v>49.5</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -6927,33 +6927,33 @@
         <v>731</v>
       </c>
       <c r="C79">
-        <v>2974</v>
+        <v>2831</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G79">
-        <v>250</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B80" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C80">
-        <v>2831</v>
+        <v>4137</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -6962,18 +6962,18 @@
         <v>13</v>
       </c>
       <c r="G80">
-        <v>127</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B81" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C81">
-        <v>4137</v>
+        <v>4380</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -6990,16 +6990,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B82" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C82">
-        <v>4380</v>
+        <v>4566</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -7008,18 +7008,18 @@
         <v>13</v>
       </c>
       <c r="G82">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B83" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C83">
-        <v>4566</v>
+        <v>4567</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -7036,16 +7036,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B84" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C84">
-        <v>4567</v>
+        <v>4204</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -7054,7 +7054,7 @@
         <v>13</v>
       </c>
       <c r="G84">
-        <v>240</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -7065,19 +7065,19 @@
         <v>741</v>
       </c>
       <c r="C85">
-        <v>4204</v>
+        <v>4205</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G85">
-        <v>145.5</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -7088,42 +7088,42 @@
         <v>741</v>
       </c>
       <c r="C86">
-        <v>4205</v>
+        <v>4225</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G86">
-        <v>360</v>
+        <v>900</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B87" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C87">
-        <v>4225</v>
+        <v>4378</v>
       </c>
       <c r="D87">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G87">
-        <v>900</v>
+        <v>430</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -7134,10 +7134,10 @@
         <v>743</v>
       </c>
       <c r="C88">
-        <v>4378</v>
+        <v>4379</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -7146,30 +7146,30 @@
         <v>32</v>
       </c>
       <c r="G88">
-        <v>430</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B89" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C89">
-        <v>4379</v>
+        <v>3524</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>32</v>
+        <v>746</v>
       </c>
       <c r="G89">
-        <v>43</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -7180,10 +7180,10 @@
         <v>745</v>
       </c>
       <c r="C90">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D90">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -7192,30 +7192,30 @@
         <v>746</v>
       </c>
       <c r="G90">
-        <v>350</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B91" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C91">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>8</v>
+        <v>1084</v>
       </c>
       <c r="F91" t="s">
-        <v>746</v>
+        <v>9</v>
       </c>
       <c r="G91">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -7226,53 +7226,53 @@
         <v>748</v>
       </c>
       <c r="C92">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="D92">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
       </c>
       <c r="G92">
-        <v>158</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B93" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C93">
-        <v>3522</v>
+        <v>64</v>
       </c>
       <c r="D93">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>1075</v>
+        <v>1057</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
       </c>
       <c r="G93">
-        <v>216.5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B94" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C94">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D94">
         <v>8</v>
@@ -7289,25 +7289,25 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B95" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C95">
-        <v>90</v>
+        <v>3637</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E95" t="s">
-        <v>1057</v>
+        <v>8</v>
       </c>
       <c r="F95" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G95">
-        <v>132</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -7318,10 +7318,10 @@
         <v>754</v>
       </c>
       <c r="C96">
-        <v>3637</v>
+        <v>2805</v>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -7330,7 +7330,7 @@
         <v>32</v>
       </c>
       <c r="G96">
-        <v>375</v>
+        <v>150</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -7341,42 +7341,42 @@
         <v>754</v>
       </c>
       <c r="C97">
-        <v>2805</v>
+        <v>2427</v>
       </c>
       <c r="D97">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G97">
-        <v>150</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B98" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C98">
-        <v>2427</v>
+        <v>3437</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G98">
-        <v>46</v>
+        <v>390</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -7387,53 +7387,53 @@
         <v>756</v>
       </c>
       <c r="C99">
-        <v>3437</v>
+        <v>3396</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
       </c>
       <c r="F99" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G99">
-        <v>390</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B100" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C100">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>8</v>
+        <v>1060</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G100">
-        <v>197</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B101" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C101">
-        <v>3395</v>
+        <v>3490</v>
       </c>
       <c r="D101">
         <v>12</v>
@@ -7445,41 +7445,41 @@
         <v>9</v>
       </c>
       <c r="G101">
-        <v>54</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B102" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C102">
-        <v>3490</v>
+        <v>458</v>
       </c>
       <c r="D102">
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F102" t="s">
         <v>9</v>
       </c>
       <c r="G102">
-        <v>169</v>
+        <v>269.5</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B103" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C103">
-        <v>458</v>
+        <v>2641</v>
       </c>
       <c r="D103">
         <v>12</v>
@@ -7491,18 +7491,18 @@
         <v>9</v>
       </c>
       <c r="G103">
-        <v>269.5</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B104" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C104">
-        <v>2641</v>
+        <v>4293</v>
       </c>
       <c r="D104">
         <v>12</v>
@@ -7514,30 +7514,30 @@
         <v>9</v>
       </c>
       <c r="G104">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B105" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C105">
-        <v>4293</v>
+        <v>2396</v>
       </c>
       <c r="D105">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E105" t="s">
-        <v>1061</v>
+        <v>8</v>
       </c>
       <c r="F105" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G105">
-        <v>210</v>
+        <v>675</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -7548,33 +7548,33 @@
         <v>768</v>
       </c>
       <c r="C106">
-        <v>2396</v>
+        <v>2426</v>
       </c>
       <c r="D106">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G106">
-        <v>675</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B107" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C107">
-        <v>2426</v>
+        <v>4335</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -7583,21 +7583,21 @@
         <v>13</v>
       </c>
       <c r="G107">
-        <v>137</v>
+        <v>424.5</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B108" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C108">
-        <v>4335</v>
+        <v>4477</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -7606,18 +7606,18 @@
         <v>13</v>
       </c>
       <c r="G108">
-        <v>424.5</v>
+        <v>244.5</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B109" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C109">
-        <v>4477</v>
+        <v>4479</v>
       </c>
       <c r="D109">
         <v>5</v>
@@ -7634,13 +7634,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B110" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C110">
-        <v>4479</v>
+        <v>4478</v>
       </c>
       <c r="D110">
         <v>5</v>
@@ -7657,25 +7657,25 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B111" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C111">
-        <v>4478</v>
+        <v>2646</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>8</v>
+        <v>1062</v>
       </c>
       <c r="F111" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G111">
-        <v>244.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -7686,19 +7686,19 @@
         <v>778</v>
       </c>
       <c r="C112">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="D112">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F112" t="s">
         <v>233</v>
       </c>
       <c r="G112">
-        <v>50.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -7709,110 +7709,87 @@
         <v>778</v>
       </c>
       <c r="C113">
-        <v>2645</v>
+        <v>2638</v>
       </c>
       <c r="D113">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F113" t="s">
         <v>233</v>
       </c>
       <c r="G113">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B114" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C114">
-        <v>2638</v>
+        <v>4294</v>
       </c>
       <c r="D114">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E114" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F114" t="s">
         <v>233</v>
       </c>
       <c r="G114">
-        <v>65</v>
+        <v>150</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B115" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C115">
-        <v>4294</v>
+        <v>4314</v>
       </c>
       <c r="D115">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E115" t="s">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="F115" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G115">
-        <v>150</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B116" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C116">
-        <v>4314</v>
+        <v>4315</v>
       </c>
       <c r="D116">
         <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="F116" t="s">
         <v>9</v>
       </c>
       <c r="G116">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>783</v>
-      </c>
-      <c r="B117" t="s">
-        <v>784</v>
-      </c>
-      <c r="C117">
-        <v>4315</v>
-      </c>
-      <c r="D117">
-        <v>15</v>
-      </c>
-      <c r="E117" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F117" t="s">
-        <v>9</v>
-      </c>
-      <c r="G117">
         <v>450</v>
       </c>
     </row>
@@ -20904,7 +20881,7 @@
         <v>32</v>
       </c>
       <c r="G20">
-        <v>500</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -20927,7 +20904,7 @@
         <v>13</v>
       </c>
       <c r="G21">
-        <v>252</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14D8423-DC7B-45B1-ACFC-2A1656BD6568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBA6095-CE8D-4108-9698-BE58195B08A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="1500" windowWidth="24240" windowHeight="13920" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -3711,7 +3711,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBA6095-CE8D-4108-9698-BE58195B08A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0768C037-F321-4AAF-A8EA-43DEEA94BEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -9035,7 +9035,7 @@
         <v>13</v>
       </c>
       <c r="G24">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -10778,7 +10778,7 @@
         <v>970</v>
       </c>
       <c r="G75">
-        <v>24</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0768C037-F321-4AAF-A8EA-43DEEA94BEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE04920-086B-495F-B988-B3FE3A6DD7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="1365" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -6870,7 +6870,7 @@
         <v>32</v>
       </c>
       <c r="G76">
-        <v>237.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -6893,7 +6893,7 @@
         <v>13</v>
       </c>
       <c r="G77">
-        <v>49.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -7583,7 +7583,7 @@
         <v>13</v>
       </c>
       <c r="G107">
-        <v>424.5</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -7597,7 +7597,7 @@
         <v>4477</v>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -7606,7 +7606,7 @@
         <v>13</v>
       </c>
       <c r="G108">
-        <v>244.5</v>
+        <v>252</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -7620,7 +7620,7 @@
         <v>4479</v>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -7629,7 +7629,7 @@
         <v>13</v>
       </c>
       <c r="G109">
-        <v>244.5</v>
+        <v>252</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -7643,7 +7643,7 @@
         <v>4478</v>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -7652,7 +7652,7 @@
         <v>13</v>
       </c>
       <c r="G110">
-        <v>244.5</v>
+        <v>252</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE04920-086B-495F-B988-B3FE3A6DD7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C054B39-0725-4D80-9196-A2A2FB93863A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="1365" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="1365" windowWidth="27300" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3526" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="1087">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -1153,12 +1153,6 @@
   </si>
   <si>
     <t>AMIDO DE MILHO INTEGRADA</t>
-  </si>
-  <si>
-    <t>amido-de-milho-bv-foods</t>
-  </si>
-  <si>
-    <t>AMIDO DE MILHO BV FOODS</t>
   </si>
   <si>
     <t>fecula-de-batata</t>
@@ -3656,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C8D572-3175-4532-9898-FEC58E78606B}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -3693,10 +3687,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C2">
         <v>2229</v>
@@ -3712,6 +3706,190 @@
       </c>
       <c r="G2">
         <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>724</v>
+      </c>
+      <c r="B3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C3">
+        <v>195</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>652</v>
+      </c>
+      <c r="B4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C4">
+        <v>569</v>
+      </c>
+      <c r="D4">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>648</v>
+      </c>
+      <c r="B5" t="s">
+        <v>649</v>
+      </c>
+      <c r="C5">
+        <v>282</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6">
+        <v>564</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>674</v>
+      </c>
+      <c r="B7" t="s">
+        <v>675</v>
+      </c>
+      <c r="C7">
+        <v>565</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>109</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9">
+        <v>3110</v>
+      </c>
+      <c r="D9">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3757,10 +3935,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C2">
         <v>3051</v>
@@ -3780,10 +3958,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C3">
         <v>2675</v>
@@ -3803,10 +3981,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C4">
         <v>2791</v>
@@ -3826,10 +4004,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C5">
         <v>3090</v>
@@ -3849,10 +4027,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C6">
         <v>2414</v>
@@ -3872,10 +4050,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B7" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C7">
         <v>2418</v>
@@ -3895,10 +4073,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B8" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C8">
         <v>2272</v>
@@ -3918,10 +4096,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C9">
         <v>3651</v>
@@ -3941,10 +4119,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B10" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C10">
         <v>4206</v>
@@ -3964,10 +4142,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B11" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C11">
         <v>3652</v>
@@ -3987,10 +4165,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B12" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C12">
         <v>4136</v>
@@ -4010,10 +4188,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B13" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C13">
         <v>4585</v>
@@ -4022,7 +4200,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -4033,10 +4211,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B14" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C14">
         <v>4584</v>
@@ -4056,10 +4234,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B15" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C15">
         <v>2756</v>
@@ -4068,7 +4246,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -4079,10 +4257,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B16" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C16">
         <v>2757</v>
@@ -4102,10 +4280,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B17" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C17">
         <v>4491</v>
@@ -4114,7 +4292,7 @@
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -4125,10 +4303,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B18" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C18">
         <v>4492</v>
@@ -4148,10 +4326,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C19">
         <v>2350</v>
@@ -4171,10 +4349,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B20" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C20">
         <v>2362</v>
@@ -4194,10 +4372,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B21" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C21">
         <v>4403</v>
@@ -4217,10 +4395,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B22" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C22">
         <v>2406</v>
@@ -4240,10 +4418,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B23" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C23">
         <v>2229</v>
@@ -4304,10 +4482,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C2">
         <v>189</v>
@@ -4327,10 +4505,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C3">
         <v>9</v>
@@ -4350,10 +4528,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C4">
         <v>2553</v>
@@ -4373,10 +4551,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C5">
         <v>521</v>
@@ -4396,10 +4574,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C6">
         <v>99</v>
@@ -4419,10 +4597,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B7" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C7">
         <v>2613</v>
@@ -4442,10 +4620,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B8" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C8">
         <v>3365</v>
@@ -4465,10 +4643,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B9" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C9">
         <v>2556</v>
@@ -4488,10 +4666,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B10" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C10">
         <v>2555</v>
@@ -4511,10 +4689,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B11" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C11">
         <v>4045</v>
@@ -4534,10 +4712,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B12" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C12">
         <v>3669</v>
@@ -4557,10 +4735,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C13">
         <v>38</v>
@@ -4580,10 +4758,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B14" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C14">
         <v>2479</v>
@@ -4603,10 +4781,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C15">
         <v>105</v>
@@ -4626,10 +4804,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B16" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C16">
         <v>212</v>
@@ -4649,10 +4827,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B17" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C17">
         <v>2848</v>
@@ -4672,10 +4850,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B18" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C18">
         <v>2851</v>
@@ -4695,10 +4873,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C19">
         <v>4202</v>
@@ -4718,10 +4896,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B20" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C20">
         <v>4201</v>
@@ -4730,7 +4908,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -4741,10 +4919,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B21" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C21">
         <v>653</v>
@@ -4764,10 +4942,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B22" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C22">
         <v>2484</v>
@@ -4787,10 +4965,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B23" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C23">
         <v>3417</v>
@@ -4810,10 +4988,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B24" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C24">
         <v>2716</v>
@@ -4833,10 +5011,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B25" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C25">
         <v>2478</v>
@@ -4856,10 +5034,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B26" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C26">
         <v>2606</v>
@@ -4879,10 +5057,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B27" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C27">
         <v>2338</v>
@@ -4902,10 +5080,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B28" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C28">
         <v>2425</v>
@@ -4925,10 +5103,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B29" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C29">
         <v>2579</v>
@@ -4948,10 +5126,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B30" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C30">
         <v>2243</v>
@@ -4971,10 +5149,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B31" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C31">
         <v>4400</v>
@@ -4994,10 +5172,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B32" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C32">
         <v>2680</v>
@@ -5017,10 +5195,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B33" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C33">
         <v>2676</v>
@@ -5040,10 +5218,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B34" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C34">
         <v>571</v>
@@ -5063,10 +5241,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B35" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C35">
         <v>2245</v>
@@ -5086,10 +5264,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B36" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C36">
         <v>3754</v>
@@ -5150,10 +5328,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C2">
         <v>4336</v>
@@ -5173,10 +5351,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C3">
         <v>2618</v>
@@ -5196,10 +5374,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C4">
         <v>2398</v>
@@ -5219,10 +5397,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C5">
         <v>2297</v>
@@ -5231,7 +5409,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -5242,10 +5420,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B6" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C6">
         <v>3653</v>
@@ -5265,10 +5443,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B7" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C7">
         <v>2339</v>
@@ -5277,7 +5455,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -5288,10 +5466,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B8" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C8">
         <v>2223</v>
@@ -5300,7 +5478,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -5311,10 +5489,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B9" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C9">
         <v>3707</v>
@@ -5323,7 +5501,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -5334,10 +5512,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B10" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C10">
         <v>4090</v>
@@ -5357,10 +5535,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B11" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C11">
         <v>4279</v>
@@ -5380,10 +5558,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C12">
         <v>2259</v>
@@ -5403,10 +5581,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B13" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C13">
         <v>3540</v>
@@ -5426,10 +5604,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B14" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C14">
         <v>3541</v>
@@ -5449,10 +5627,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C15">
         <v>2422</v>
@@ -5472,10 +5650,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C16">
         <v>569</v>
@@ -5495,10 +5673,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B17" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C17">
         <v>282</v>
@@ -5518,10 +5696,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B18" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C18">
         <v>2336</v>
@@ -5541,10 +5719,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B19" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C19">
         <v>2421</v>
@@ -5564,10 +5742,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B20" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C20">
         <v>2568</v>
@@ -5587,10 +5765,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B21" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C21">
         <v>3009</v>
@@ -5610,10 +5788,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B22" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C22">
         <v>2778</v>
@@ -5633,10 +5811,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B23" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C23">
         <v>3106</v>
@@ -5656,10 +5834,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B24" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C24">
         <v>3489</v>
@@ -5679,10 +5857,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B25" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C25">
         <v>3696</v>
@@ -5702,10 +5880,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B26" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C26">
         <v>2783</v>
@@ -5725,10 +5903,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B27" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C27">
         <v>3755</v>
@@ -5748,10 +5926,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B28" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C28">
         <v>3486</v>
@@ -5771,10 +5949,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B29" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C29">
         <v>4488</v>
@@ -5794,10 +5972,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B30" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C30">
         <v>4333</v>
@@ -5817,10 +5995,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B31" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C31">
         <v>4388</v>
@@ -5840,10 +6018,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B32" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C32">
         <v>4389</v>
@@ -5863,10 +6041,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B33" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C33">
         <v>3488</v>
@@ -5886,10 +6064,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B34" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C34">
         <v>3400</v>
@@ -5909,10 +6087,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B35" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C35">
         <v>2257</v>
@@ -5932,10 +6110,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B36" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C36">
         <v>565</v>
@@ -5955,10 +6133,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B37" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C37">
         <v>4474</v>
@@ -5978,10 +6156,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B38" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C38">
         <v>4473</v>
@@ -6001,10 +6179,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B39" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C39">
         <v>2658</v>
@@ -6024,10 +6202,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B40" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C40">
         <v>2657</v>
@@ -6047,10 +6225,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B41" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C41">
         <v>2657</v>
@@ -6070,10 +6248,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B42" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C42">
         <v>2658</v>
@@ -6093,10 +6271,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B43" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C43">
         <v>3537</v>
@@ -6105,7 +6283,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
@@ -6116,10 +6294,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B44" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C44">
         <v>2732</v>
@@ -6139,10 +6317,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B45" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C45">
         <v>2733</v>
@@ -6162,10 +6340,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B46" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C46">
         <v>2584</v>
@@ -6185,10 +6363,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B47" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C47">
         <v>2677</v>
@@ -6208,10 +6386,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B48" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C48">
         <v>2495</v>
@@ -6231,10 +6409,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B49" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C49">
         <v>2678</v>
@@ -6254,10 +6432,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B50" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C50">
         <v>4498</v>
@@ -6266,7 +6444,7 @@
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -6277,10 +6455,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B51" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C51">
         <v>4253</v>
@@ -6300,10 +6478,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B52" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C52">
         <v>4500</v>
@@ -6323,10 +6501,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B53" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C53">
         <v>4249</v>
@@ -6335,7 +6513,7 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
@@ -6346,10 +6524,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B54" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C54">
         <v>3724</v>
@@ -6358,7 +6536,7 @@
         <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F54" t="s">
         <v>233</v>
@@ -6369,10 +6547,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B55" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C55">
         <v>3736</v>
@@ -6381,7 +6559,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
@@ -6392,10 +6570,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B56" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C56">
         <v>4499</v>
@@ -6404,7 +6582,7 @@
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F56" t="s">
         <v>233</v>
@@ -6415,10 +6593,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B57" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C57">
         <v>3536</v>
@@ -6427,7 +6605,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F57" t="s">
         <v>9</v>
@@ -6438,10 +6616,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B58" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C58">
         <v>2494</v>
@@ -6461,10 +6639,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B59" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C59">
         <v>2679</v>
@@ -6484,10 +6662,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B60" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C60">
         <v>4497</v>
@@ -6496,7 +6674,7 @@
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F60" t="s">
         <v>233</v>
@@ -6507,10 +6685,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B61" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C61">
         <v>2493</v>
@@ -6530,10 +6708,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B62" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C62">
         <v>3535</v>
@@ -6542,7 +6720,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
@@ -6553,10 +6731,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B63" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C63">
         <v>2498</v>
@@ -6576,10 +6754,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B64" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C64">
         <v>2806</v>
@@ -6599,10 +6777,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B65" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C65">
         <v>2807</v>
@@ -6622,10 +6800,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B66" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C66">
         <v>4556</v>
@@ -6645,10 +6823,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B67" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C67">
         <v>4557</v>
@@ -6668,10 +6846,10 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B68" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C68">
         <v>4018</v>
@@ -6691,10 +6869,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B69" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C69">
         <v>2652</v>
@@ -6714,10 +6892,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B70" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C70">
         <v>4049</v>
@@ -6737,10 +6915,10 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B71" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C71">
         <v>3737</v>
@@ -6760,10 +6938,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B72" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C72">
         <v>4301</v>
@@ -6783,10 +6961,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B73" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C73">
         <v>4334</v>
@@ -6806,10 +6984,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B74" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C74">
         <v>195</v>
@@ -6829,10 +7007,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B75" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C75">
         <v>54</v>
@@ -6852,10 +7030,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B76" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C76">
         <v>63</v>
@@ -6875,10 +7053,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B77" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C77">
         <v>2483</v>
@@ -6898,10 +7076,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B78" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C78">
         <v>2974</v>
@@ -6921,10 +7099,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B79" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C79">
         <v>2831</v>
@@ -6944,10 +7122,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B80" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C80">
         <v>4137</v>
@@ -6967,10 +7145,10 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B81" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C81">
         <v>4380</v>
@@ -6990,10 +7168,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B82" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C82">
         <v>4566</v>
@@ -7013,10 +7191,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B83" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C83">
         <v>4567</v>
@@ -7036,10 +7214,10 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B84" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C84">
         <v>4204</v>
@@ -7059,10 +7237,10 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B85" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C85">
         <v>4205</v>
@@ -7082,10 +7260,10 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B86" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C86">
         <v>4225</v>
@@ -7105,10 +7283,10 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B87" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C87">
         <v>4378</v>
@@ -7128,10 +7306,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B88" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C88">
         <v>4379</v>
@@ -7151,10 +7329,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B89" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C89">
         <v>3524</v>
@@ -7166,7 +7344,7 @@
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G89">
         <v>350</v>
@@ -7174,10 +7352,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B90" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C90">
         <v>3523</v>
@@ -7189,7 +7367,7 @@
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G90">
         <v>72</v>
@@ -7197,10 +7375,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B91" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C91">
         <v>3521</v>
@@ -7209,7 +7387,7 @@
         <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="F91" t="s">
         <v>9</v>
@@ -7220,10 +7398,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B92" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C92">
         <v>3522</v>
@@ -7232,7 +7410,7 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -7243,10 +7421,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B93" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C93">
         <v>64</v>
@@ -7255,7 +7433,7 @@
         <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -7266,10 +7444,10 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B94" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C94">
         <v>90</v>
@@ -7278,7 +7456,7 @@
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -7289,10 +7467,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B95" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C95">
         <v>3637</v>
@@ -7312,10 +7490,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B96" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C96">
         <v>2805</v>
@@ -7335,10 +7513,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B97" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C97">
         <v>2427</v>
@@ -7358,10 +7536,10 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B98" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C98">
         <v>3437</v>
@@ -7381,10 +7559,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B99" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C99">
         <v>3396</v>
@@ -7404,10 +7582,10 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B100" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C100">
         <v>3395</v>
@@ -7416,7 +7594,7 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F100" t="s">
         <v>9</v>
@@ -7427,10 +7605,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B101" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C101">
         <v>3490</v>
@@ -7439,7 +7617,7 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F101" t="s">
         <v>9</v>
@@ -7450,10 +7628,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B102" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C102">
         <v>458</v>
@@ -7462,7 +7640,7 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F102" t="s">
         <v>9</v>
@@ -7473,10 +7651,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B103" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C103">
         <v>2641</v>
@@ -7485,7 +7663,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F103" t="s">
         <v>9</v>
@@ -7496,10 +7674,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B104" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C104">
         <v>4293</v>
@@ -7508,7 +7686,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F104" t="s">
         <v>9</v>
@@ -7519,10 +7697,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B105" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C105">
         <v>2396</v>
@@ -7542,10 +7720,10 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B106" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C106">
         <v>2426</v>
@@ -7565,10 +7743,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B107" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C107">
         <v>4335</v>
@@ -7588,10 +7766,10 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B108" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C108">
         <v>4477</v>
@@ -7611,10 +7789,10 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B109" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C109">
         <v>4479</v>
@@ -7634,10 +7812,10 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B110" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C110">
         <v>4478</v>
@@ -7657,10 +7835,10 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B111" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C111">
         <v>2646</v>
@@ -7669,7 +7847,7 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F111" t="s">
         <v>233</v>
@@ -7680,10 +7858,10 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B112" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C112">
         <v>2645</v>
@@ -7692,7 +7870,7 @@
         <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F112" t="s">
         <v>233</v>
@@ -7703,10 +7881,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B113" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C113">
         <v>2638</v>
@@ -7715,7 +7893,7 @@
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F113" t="s">
         <v>233</v>
@@ -7726,10 +7904,10 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B114" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C114">
         <v>4294</v>
@@ -7738,7 +7916,7 @@
         <v>18</v>
       </c>
       <c r="E114" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F114" t="s">
         <v>233</v>
@@ -7749,10 +7927,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B115" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C115">
         <v>4314</v>
@@ -7761,7 +7939,7 @@
         <v>15</v>
       </c>
       <c r="E115" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F115" t="s">
         <v>9</v>
@@ -7772,10 +7950,10 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B116" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C116">
         <v>4315</v>
@@ -7784,7 +7962,7 @@
         <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F116" t="s">
         <v>9</v>
@@ -7836,10 +8014,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C2">
         <v>3402</v>
@@ -7848,7 +8026,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F2" t="s">
         <v>233</v>
@@ -7859,10 +8037,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C3">
         <v>3401</v>
@@ -7871,7 +8049,7 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="F3" t="s">
         <v>233</v>
@@ -7882,10 +8060,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C4">
         <v>3403</v>
@@ -7894,7 +8072,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F4" t="s">
         <v>233</v>
@@ -7905,10 +8083,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B5" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C5">
         <v>4032</v>
@@ -7917,7 +8095,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -7928,10 +8106,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C6">
         <v>4460</v>
@@ -7940,7 +8118,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -7951,10 +8129,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B7" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C7">
         <v>4260</v>
@@ -7963,7 +8141,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -7974,10 +8152,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B8" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C8">
         <v>2551</v>
@@ -7986,7 +8164,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -7997,10 +8175,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B9" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C9">
         <v>2550</v>
@@ -8009,7 +8187,7 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -8020,10 +8198,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B10" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C10">
         <v>4383</v>
@@ -8032,7 +8210,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -8084,10 +8262,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C2">
         <v>3644</v>
@@ -8096,7 +8274,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F2" t="s">
         <v>233</v>
@@ -8107,10 +8285,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C3">
         <v>3644</v>
@@ -8119,7 +8297,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F3" t="s">
         <v>233</v>
@@ -8130,10 +8308,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B4" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C4">
         <v>3641</v>
@@ -8142,7 +8320,7 @@
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F4" t="s">
         <v>233</v>
@@ -8153,10 +8331,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C5">
         <v>3645</v>
@@ -8165,7 +8343,7 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -8176,10 +8354,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B6" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C6">
         <v>3852</v>
@@ -8188,7 +8366,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -8199,10 +8377,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B7" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C7">
         <v>3647</v>
@@ -8211,7 +8389,7 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -8222,10 +8400,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B8" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C8">
         <v>3648</v>
@@ -8234,7 +8412,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -8286,10 +8464,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C2">
         <v>3056</v>
@@ -8298,7 +8476,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F2" t="s">
         <v>233</v>
@@ -8309,10 +8487,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B3" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C3">
         <v>3083</v>
@@ -8321,7 +8499,7 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F3" t="s">
         <v>233</v>
@@ -8332,10 +8510,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B4" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C4">
         <v>2264</v>
@@ -8344,7 +8522,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -8355,10 +8533,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B5" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C5">
         <v>2355</v>
@@ -8367,7 +8545,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -8378,10 +8556,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C6">
         <v>573</v>
@@ -8390,7 +8568,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -8401,10 +8579,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B7" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C7">
         <v>572</v>
@@ -8413,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -8424,10 +8602,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B8" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C8">
         <v>4411</v>
@@ -8436,7 +8614,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -8447,10 +8625,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B9" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C9">
         <v>4410</v>
@@ -8459,7 +8637,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -8511,10 +8689,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C2">
         <v>4044</v>
@@ -8523,7 +8701,7 @@
         <v>500</v>
       </c>
       <c r="E2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
@@ -8534,10 +8712,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C3">
         <v>4043</v>
@@ -8557,10 +8735,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C4">
         <v>3531</v>
@@ -8580,10 +8758,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C5">
         <v>3974</v>
@@ -8603,10 +8781,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B6" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C6">
         <v>3530</v>
@@ -8626,10 +8804,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C7">
         <v>4282</v>
@@ -8649,10 +8827,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B8" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C8">
         <v>3870</v>
@@ -8661,7 +8839,7 @@
         <v>500</v>
       </c>
       <c r="E8" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
@@ -8672,10 +8850,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B9" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C9">
         <v>3701</v>
@@ -8684,7 +8862,7 @@
         <v>500</v>
       </c>
       <c r="E9" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -8695,10 +8873,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B10" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C10">
         <v>3800</v>
@@ -8707,7 +8885,7 @@
         <v>500</v>
       </c>
       <c r="E10" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -8718,10 +8896,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B11" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C11">
         <v>3725</v>
@@ -8730,7 +8908,7 @@
         <v>500</v>
       </c>
       <c r="E11" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -8741,10 +8919,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B12" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C12">
         <v>3871</v>
@@ -8753,7 +8931,7 @@
         <v>500</v>
       </c>
       <c r="E12" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -8764,10 +8942,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B13" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C13">
         <v>2825</v>
@@ -8787,10 +8965,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B14" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C14">
         <v>2828</v>
@@ -8810,10 +8988,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B15" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C15">
         <v>2826</v>
@@ -8833,10 +9011,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B16" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C16">
         <v>3058</v>
@@ -8856,10 +9034,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B17" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C17">
         <v>3059</v>
@@ -8879,10 +9057,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B18" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C18">
         <v>2829</v>
@@ -8902,10 +9080,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C19">
         <v>4126</v>
@@ -8925,10 +9103,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B20" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C20">
         <v>2827</v>
@@ -8948,10 +9126,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B21" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C21">
         <v>3801</v>
@@ -8960,7 +9138,7 @@
         <v>500</v>
       </c>
       <c r="E21" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -8971,10 +9149,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B22" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C22">
         <v>3833</v>
@@ -8983,7 +9161,7 @@
         <v>500</v>
       </c>
       <c r="E22" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -8994,10 +9172,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B23" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C23">
         <v>3897</v>
@@ -9017,10 +9195,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B24" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C24">
         <v>3764</v>
@@ -9081,10 +9259,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C2">
         <v>3438</v>
@@ -9104,10 +9282,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C3">
         <v>3434</v>
@@ -9127,10 +9305,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B4" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C4">
         <v>3443</v>
@@ -9150,10 +9328,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B5" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C5">
         <v>3019</v>
@@ -9173,10 +9351,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B6" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C6">
         <v>4489</v>
@@ -9196,10 +9374,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B7" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C7">
         <v>4490</v>
@@ -9219,10 +9397,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B8" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C8">
         <v>3476</v>
@@ -9242,10 +9420,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B9" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C9">
         <v>3477</v>
@@ -9265,10 +9443,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B10" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C10">
         <v>4344</v>
@@ -9277,7 +9455,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -9288,10 +9466,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B11" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C11">
         <v>3123</v>
@@ -9311,10 +9489,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B12" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C12">
         <v>2674</v>
@@ -9334,10 +9512,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B13" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C13">
         <v>3719</v>
@@ -9357,10 +9535,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B14" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C14">
         <v>3720</v>
@@ -9380,10 +9558,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B15" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C15">
         <v>3765</v>
@@ -9403,10 +9581,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B16" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C16">
         <v>3766</v>
@@ -9426,10 +9604,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B17" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C17">
         <v>3126</v>
@@ -9449,10 +9627,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B18" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C18">
         <v>3127</v>
@@ -9472,10 +9650,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B19" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C19">
         <v>3435</v>
@@ -9495,10 +9673,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B20" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C20">
         <v>3436</v>
@@ -9518,10 +9696,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B21" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C21">
         <v>3128</v>
@@ -9541,10 +9719,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C22">
         <v>3129</v>
@@ -9564,10 +9742,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B23" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C23">
         <v>4158</v>
@@ -9587,10 +9765,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B24" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C24">
         <v>4159</v>
@@ -9610,10 +9788,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B25" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C25">
         <v>4561</v>
@@ -9633,10 +9811,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B26" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C26">
         <v>4562</v>
@@ -9656,10 +9834,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B27" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C27">
         <v>3124</v>
@@ -9679,10 +9857,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B28" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C28">
         <v>2824</v>
@@ -9702,10 +9880,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B29" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C29">
         <v>3130</v>
@@ -9725,10 +9903,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B30" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C30">
         <v>3131</v>
@@ -9748,10 +9926,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B31" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C31">
         <v>4346</v>
@@ -9760,7 +9938,7 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -9771,10 +9949,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B32" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C32">
         <v>4345</v>
@@ -9783,7 +9961,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -9794,10 +9972,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B33" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C33">
         <v>4347</v>
@@ -9806,7 +9984,7 @@
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -9817,10 +9995,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B34" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C34">
         <v>4446</v>
@@ -9829,7 +10007,7 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -9840,10 +10018,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B35" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C35">
         <v>4476</v>
@@ -9855,7 +10033,7 @@
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G35">
         <v>33.5</v>
@@ -9863,10 +10041,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B36" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C36">
         <v>4348</v>
@@ -9875,7 +10053,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
@@ -9886,10 +10064,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B37" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C37">
         <v>4456</v>
@@ -9898,7 +10076,7 @@
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -9909,10 +10087,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B38" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C38">
         <v>4051</v>
@@ -9932,10 +10110,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B39" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C39">
         <v>4408</v>
@@ -9955,10 +10133,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B40" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C40">
         <v>4341</v>
@@ -9978,10 +10156,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B41" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C41">
         <v>4265</v>
@@ -10001,10 +10179,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B42" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C42">
         <v>4266</v>
@@ -10024,10 +10202,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B43" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C43">
         <v>4269</v>
@@ -10047,10 +10225,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B44" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C44">
         <v>4273</v>
@@ -10070,10 +10248,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B45" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C45">
         <v>4405</v>
@@ -10093,10 +10271,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B46" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C46">
         <v>4406</v>
@@ -10116,10 +10294,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B47" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C47">
         <v>4267</v>
@@ -10139,10 +10317,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B48" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C48">
         <v>4271</v>
@@ -10162,10 +10340,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B49" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C49">
         <v>4276</v>
@@ -10185,10 +10363,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B50" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C50">
         <v>4342</v>
@@ -10208,10 +10386,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B51" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C51">
         <v>4398</v>
@@ -10231,10 +10409,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B52" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C52">
         <v>4270</v>
@@ -10254,10 +10432,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B53" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C53">
         <v>4275</v>
@@ -10277,10 +10455,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B54" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C54">
         <v>4274</v>
@@ -10300,10 +10478,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B55" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C55">
         <v>4399</v>
@@ -10323,10 +10501,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B56" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C56">
         <v>4404</v>
@@ -10346,10 +10524,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B57" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C57">
         <v>4262</v>
@@ -10369,10 +10547,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B58" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C58">
         <v>4263</v>
@@ -10392,10 +10570,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B59" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C59">
         <v>4264</v>
@@ -10415,10 +10593,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B60" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C60">
         <v>4407</v>
@@ -10438,10 +10616,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B61" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C61">
         <v>4397</v>
@@ -10461,10 +10639,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B62" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C62">
         <v>4343</v>
@@ -10484,10 +10662,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B63" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C63">
         <v>4268</v>
@@ -10507,10 +10685,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B64" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C64">
         <v>2833</v>
@@ -10530,10 +10708,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B65" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C65">
         <v>3125</v>
@@ -10553,10 +10731,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B66" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C66">
         <v>3752</v>
@@ -10576,10 +10754,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B67" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C67">
         <v>3753</v>
@@ -10599,10 +10777,10 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B68" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C68">
         <v>2511</v>
@@ -10622,10 +10800,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B69" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C69">
         <v>4311</v>
@@ -10645,10 +10823,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B70" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C70">
         <v>4046</v>
@@ -10668,10 +10846,10 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B71" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C71">
         <v>4047</v>
@@ -10691,10 +10869,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B72" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C72">
         <v>4312</v>
@@ -10714,10 +10892,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B73" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C73">
         <v>4310</v>
@@ -10737,10 +10915,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B74" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C74">
         <v>4074</v>
@@ -10749,7 +10927,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
@@ -10760,10 +10938,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B75" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C75">
         <v>4076</v>
@@ -10772,10 +10950,10 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F75" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G75">
         <v>32.5</v>
@@ -10783,10 +10961,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B76" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C76">
         <v>4133</v>
@@ -10795,10 +10973,10 @@
         <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F76" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G76">
         <v>72</v>
@@ -10806,10 +10984,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B77" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C77">
         <v>3068</v>
@@ -10829,10 +11007,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B78" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C78">
         <v>3087</v>
@@ -10852,10 +11030,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B79" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C79">
         <v>4560</v>
@@ -10875,10 +11053,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B80" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C80">
         <v>4531</v>
@@ -10887,7 +11065,7 @@
         <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F80" t="s">
         <v>32</v>
@@ -10898,10 +11076,10 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B81" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C81">
         <v>4532</v>
@@ -10921,10 +11099,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B82" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C82">
         <v>4559</v>
@@ -10933,7 +11111,7 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
@@ -10944,10 +11122,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B83" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C83">
         <v>4493</v>
@@ -10967,10 +11145,10 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B84" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C84">
         <v>4102</v>
@@ -10979,7 +11157,7 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
@@ -10990,10 +11168,10 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B85" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C85">
         <v>4103</v>
@@ -11002,7 +11180,7 @@
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F85" t="s">
         <v>233</v>
@@ -11013,10 +11191,10 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B86" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C86">
         <v>4547</v>
@@ -11025,7 +11203,7 @@
         <v>10</v>
       </c>
       <c r="E86" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F86" t="s">
         <v>233</v>
@@ -11036,10 +11214,10 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B87" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C87">
         <v>4104</v>
@@ -11048,7 +11226,7 @@
         <v>10</v>
       </c>
       <c r="E87" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F87" t="s">
         <v>233</v>
@@ -11059,10 +11237,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B88" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C88">
         <v>4101</v>
@@ -11071,7 +11249,7 @@
         <v>10</v>
       </c>
       <c r="E88" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F88" t="s">
         <v>233</v>
@@ -11082,10 +11260,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B89" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C89">
         <v>4105</v>
@@ -11094,7 +11272,7 @@
         <v>10</v>
       </c>
       <c r="E89" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F89" t="s">
         <v>233</v>
@@ -11105,10 +11283,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B90" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C90">
         <v>3705</v>
@@ -11117,7 +11295,7 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F90" t="s">
         <v>233</v>
@@ -11128,10 +11306,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B91" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C91">
         <v>3823</v>
@@ -11140,7 +11318,7 @@
         <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F91" t="s">
         <v>9</v>
@@ -11151,10 +11329,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B92" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C92">
         <v>4583</v>
@@ -11163,7 +11341,7 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F92" t="s">
         <v>233</v>
@@ -11174,10 +11352,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B93" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C93">
         <v>4308</v>
@@ -11186,7 +11364,7 @@
         <v>10</v>
       </c>
       <c r="E93" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
@@ -11197,10 +11375,10 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B94" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C94">
         <v>4309</v>
@@ -11209,10 +11387,10 @@
         <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F94" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G94">
         <v>68.5</v>
@@ -11220,10 +11398,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B95" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C95">
         <v>4412</v>
@@ -11235,7 +11413,7 @@
         <v>8</v>
       </c>
       <c r="F95" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G95">
         <v>71.5</v>
@@ -11243,10 +11421,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B96" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C96">
         <v>4413</v>
@@ -11266,10 +11444,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B97" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C97">
         <v>4414</v>
@@ -11289,10 +11467,10 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B98" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C98">
         <v>4415</v>
@@ -11312,10 +11490,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B99" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C99">
         <v>4416</v>
@@ -11335,10 +11513,10 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B100" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C100">
         <v>4475</v>
@@ -11347,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
@@ -11358,10 +11536,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B101" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C101">
         <v>4354</v>
@@ -11370,10 +11548,10 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F101" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G101">
         <v>79.5</v>
@@ -11381,10 +11559,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B102" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C102">
         <v>4445</v>
@@ -11393,7 +11571,7 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F102" t="s">
         <v>9</v>
@@ -11404,10 +11582,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B103" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C103">
         <v>4353</v>
@@ -11416,7 +11594,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F103" t="s">
         <v>9</v>
@@ -11427,10 +11605,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B104" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C104">
         <v>4350</v>
@@ -11439,7 +11617,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F104" t="s">
         <v>9</v>
@@ -11450,10 +11628,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B105" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C105">
         <v>4352</v>
@@ -11462,7 +11640,7 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F105" t="s">
         <v>9</v>
@@ -11473,10 +11651,10 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B106" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C106">
         <v>4349</v>
@@ -11485,7 +11663,7 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F106" t="s">
         <v>9</v>
@@ -11496,10 +11674,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B107" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C107">
         <v>4351</v>
@@ -11508,7 +11686,7 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F107" t="s">
         <v>9</v>
@@ -11519,10 +11697,10 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B108" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C108">
         <v>4581</v>
@@ -11531,7 +11709,7 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F108" t="s">
         <v>9</v>
@@ -11542,10 +11720,10 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B109" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C109">
         <v>4096</v>
@@ -11565,10 +11743,10 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B110" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C110">
         <v>4123</v>
@@ -11577,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="E110" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F110" t="s">
         <v>13</v>
@@ -11588,10 +11766,10 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B111" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C111">
         <v>4306</v>
@@ -11600,10 +11778,10 @@
         <v>10</v>
       </c>
       <c r="E111" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F111" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G111">
         <v>81</v>
@@ -11611,10 +11789,10 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B112" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C112">
         <v>4307</v>
@@ -11623,10 +11801,10 @@
         <v>10</v>
       </c>
       <c r="E112" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F112" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G112">
         <v>81</v>
@@ -11634,10 +11812,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B113" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C113">
         <v>2659</v>
@@ -11646,7 +11824,7 @@
         <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="F113" t="s">
         <v>233</v>
@@ -11657,10 +11835,10 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B114" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C114">
         <v>2621</v>
@@ -11669,7 +11847,7 @@
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="F114" t="s">
         <v>233</v>
@@ -11680,10 +11858,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B115" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C115">
         <v>3656</v>
@@ -11692,7 +11870,7 @@
         <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F115" t="s">
         <v>233</v>
@@ -11744,10 +11922,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B2" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C2">
         <v>3459</v>
@@ -11756,7 +11934,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
@@ -11767,10 +11945,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C3">
         <v>3803</v>
@@ -11779,7 +11957,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
@@ -11790,10 +11968,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B4" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C4">
         <v>3425</v>
@@ -11802,10 +11980,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G4">
         <v>29</v>
@@ -11813,10 +11991,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B5" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C5">
         <v>3426</v>
@@ -11825,7 +12003,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -11836,10 +12014,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B6" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C6">
         <v>3427</v>
@@ -11848,10 +12026,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F6" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G6">
         <v>62.5</v>
@@ -11859,10 +12037,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B7" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C7">
         <v>3428</v>
@@ -11871,7 +12049,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -11882,10 +12060,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B8" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C8">
         <v>3429</v>
@@ -11894,10 +12072,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G8">
         <v>76.5</v>
@@ -11905,10 +12083,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B9" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C9">
         <v>3430</v>
@@ -11917,7 +12095,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -11928,10 +12106,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C10">
         <v>3913</v>
@@ -11940,10 +12118,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F10" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G10">
         <v>68</v>
@@ -11951,10 +12129,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B11" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C11">
         <v>3872</v>
@@ -11963,7 +12141,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -11974,10 +12152,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B12" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C12">
         <v>3422</v>
@@ -11986,10 +12164,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F12" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G12">
         <v>20</v>
@@ -11997,10 +12175,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B13" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C13">
         <v>3423</v>
@@ -12009,7 +12187,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -12020,10 +12198,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B14" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C14">
         <v>3431</v>
@@ -12032,10 +12210,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F14" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G14">
         <v>115</v>
@@ -12043,10 +12221,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B15" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C15">
         <v>3432</v>
@@ -12055,7 +12233,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -12110,7 +12288,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C2">
         <v>585</v>
@@ -12133,7 +12311,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C3">
         <v>467</v>
@@ -13142,7 +13320,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B47" t="s">
         <v>59</v>
@@ -17021,7 +17199,7 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -17090,7 +17268,7 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -17849,7 +18027,7 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
@@ -17918,7 +18096,7 @@
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F56" t="s">
         <v>233</v>
@@ -18125,7 +18303,7 @@
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F65" t="s">
         <v>233</v>
@@ -20413,7 +20591,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -20478,7 +20656,7 @@
         <v>373</v>
       </c>
       <c r="C3">
-        <v>3864</v>
+        <v>2391</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -20490,30 +20668,30 @@
         <v>32</v>
       </c>
       <c r="G3">
-        <v>93</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C4">
-        <v>2391</v>
+        <v>2529</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>195</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -20524,19 +20702,19 @@
         <v>375</v>
       </c>
       <c r="C5">
-        <v>2529</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>41</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -20547,7 +20725,7 @@
         <v>377</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>2255</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -20559,7 +20737,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -20570,10 +20748,10 @@
         <v>379</v>
       </c>
       <c r="C7">
-        <v>2255</v>
+        <v>3649</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -20582,30 +20760,30 @@
         <v>32</v>
       </c>
       <c r="G7">
-        <v>96</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C8">
-        <v>3649</v>
+        <v>3650</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>350</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -20616,19 +20794,19 @@
         <v>381</v>
       </c>
       <c r="C9">
-        <v>3650</v>
+        <v>3386</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G9">
-        <v>177</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -20639,10 +20817,10 @@
         <v>383</v>
       </c>
       <c r="C10">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -20651,7 +20829,7 @@
         <v>32</v>
       </c>
       <c r="G10">
-        <v>51.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -20662,10 +20840,10 @@
         <v>385</v>
       </c>
       <c r="C11">
-        <v>3385</v>
+        <v>460</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -20674,30 +20852,30 @@
         <v>32</v>
       </c>
       <c r="G11">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C12">
-        <v>460</v>
+        <v>2473</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>78</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -20708,42 +20886,42 @@
         <v>387</v>
       </c>
       <c r="C13">
-        <v>2473</v>
+        <v>128</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G13">
-        <v>18</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C14">
-        <v>128</v>
+        <v>2474</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>67</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -20754,42 +20932,42 @@
         <v>389</v>
       </c>
       <c r="C15">
-        <v>2474</v>
+        <v>3085</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G15">
-        <v>15.5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B16" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C16">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>102</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -20800,19 +20978,19 @@
         <v>391</v>
       </c>
       <c r="C17">
-        <v>3086</v>
+        <v>4558</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>1073</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G17">
-        <v>22.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -20823,19 +21001,19 @@
         <v>393</v>
       </c>
       <c r="C18">
-        <v>4558</v>
+        <v>4048</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
       </c>
       <c r="G18">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -20846,42 +21024,42 @@
         <v>395</v>
       </c>
       <c r="C19">
-        <v>4048</v>
+        <v>2519</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>1075</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>233</v>
+        <v>32</v>
       </c>
       <c r="G19">
-        <v>55</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C20">
-        <v>2519</v>
+        <v>2525</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>530</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -20892,42 +21070,42 @@
         <v>397</v>
       </c>
       <c r="C21">
-        <v>2525</v>
+        <v>3433</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G21">
-        <v>267</v>
+        <v>940</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B22" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C22">
-        <v>3433</v>
+        <v>3394</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>940</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -20938,19 +21116,19 @@
         <v>399</v>
       </c>
       <c r="C23">
-        <v>3394</v>
+        <v>47</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G23">
-        <v>237</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -20961,7 +21139,7 @@
         <v>401</v>
       </c>
       <c r="C24">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <v>25</v>
@@ -20984,10 +21162,10 @@
         <v>403</v>
       </c>
       <c r="C25">
-        <v>46</v>
+        <v>3100</v>
       </c>
       <c r="D25">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -20996,7 +21174,7 @@
         <v>32</v>
       </c>
       <c r="G25">
-        <v>125</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -21007,10 +21185,10 @@
         <v>405</v>
       </c>
       <c r="C26">
-        <v>3100</v>
+        <v>3746</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -21019,7 +21197,7 @@
         <v>32</v>
       </c>
       <c r="G26">
-        <v>209</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -21030,7 +21208,7 @@
         <v>407</v>
       </c>
       <c r="C27">
-        <v>3746</v>
+        <v>3639</v>
       </c>
       <c r="D27">
         <v>15</v>
@@ -21053,10 +21231,10 @@
         <v>409</v>
       </c>
       <c r="C28">
-        <v>3639</v>
+        <v>2415</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -21065,7 +21243,7 @@
         <v>32</v>
       </c>
       <c r="G28">
-        <v>115</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -21076,10 +21254,10 @@
         <v>411</v>
       </c>
       <c r="C29">
-        <v>2415</v>
+        <v>3747</v>
       </c>
       <c r="D29">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -21088,7 +21266,7 @@
         <v>32</v>
       </c>
       <c r="G29">
-        <v>153.5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -21099,7 +21277,7 @@
         <v>413</v>
       </c>
       <c r="C30">
-        <v>3747</v>
+        <v>3640</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -21122,10 +21300,10 @@
         <v>415</v>
       </c>
       <c r="C31">
-        <v>3640</v>
+        <v>2416</v>
       </c>
       <c r="D31">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -21134,7 +21312,7 @@
         <v>32</v>
       </c>
       <c r="G31">
-        <v>115</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -21145,10 +21323,10 @@
         <v>417</v>
       </c>
       <c r="C32">
-        <v>2416</v>
+        <v>50</v>
       </c>
       <c r="D32">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -21157,30 +21335,30 @@
         <v>32</v>
       </c>
       <c r="G32">
-        <v>153.5</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B33" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C33">
-        <v>50</v>
+        <v>2533</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G33">
-        <v>165</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -21191,42 +21369,42 @@
         <v>419</v>
       </c>
       <c r="C34">
-        <v>2533</v>
+        <v>52</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G34">
-        <v>36</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B35" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C35">
-        <v>52</v>
+        <v>2470</v>
       </c>
       <c r="D35">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G35">
-        <v>155</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -21237,64 +21415,41 @@
         <v>421</v>
       </c>
       <c r="C36">
-        <v>2470</v>
+        <v>53</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G36">
-        <v>33</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B37" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C37">
-        <v>53</v>
+        <v>2435</v>
       </c>
       <c r="D37">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G37">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>422</v>
-      </c>
-      <c r="B38" t="s">
-        <v>423</v>
-      </c>
-      <c r="C38">
-        <v>2435</v>
-      </c>
-      <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38">
         <v>25.5</v>
       </c>
     </row>
@@ -21341,10 +21496,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C2">
         <v>4139</v>
@@ -21364,10 +21519,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C3">
         <v>3383</v>
@@ -21387,10 +21542,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C4">
         <v>4520</v>
@@ -21410,10 +21565,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C5">
         <v>3381</v>
@@ -21433,10 +21588,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C6">
         <v>3498</v>
@@ -21456,10 +21611,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C7">
         <v>4112</v>
@@ -21479,10 +21634,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C8">
         <v>4116</v>
@@ -21502,10 +21657,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C9">
         <v>4107</v>
@@ -21525,10 +21680,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C10">
         <v>2222</v>
@@ -21548,10 +21703,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C11">
         <v>3572</v>
@@ -21571,10 +21726,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C12">
         <v>2522</v>
@@ -21594,10 +21749,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B13" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C13">
         <v>2521</v>
@@ -21617,10 +21772,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B14" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C14">
         <v>2571</v>
@@ -21640,10 +21795,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B15" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C15">
         <v>4108</v>
@@ -21663,10 +21818,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B16" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C16">
         <v>4111</v>
@@ -21686,10 +21841,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B17" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C17">
         <v>3499</v>
@@ -21709,10 +21864,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B18" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C18">
         <v>2616</v>
@@ -21732,10 +21887,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B19" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C19">
         <v>2615</v>
@@ -21755,10 +21910,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B20" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C20">
         <v>4283</v>
@@ -21778,10 +21933,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B21" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C21">
         <v>4114</v>
@@ -21801,10 +21956,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B22" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C22">
         <v>3493</v>
@@ -21824,10 +21979,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B23" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C23">
         <v>4395</v>
@@ -21847,10 +22002,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B24" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C24">
         <v>4394</v>
@@ -21870,10 +22025,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B25" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C25">
         <v>4115</v>
@@ -21893,10 +22048,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B26" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C26">
         <v>3497</v>
@@ -21916,10 +22071,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C27">
         <v>2492</v>
@@ -21939,10 +22094,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C28">
         <v>2499</v>
@@ -21962,10 +22117,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B29" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C29">
         <v>3101</v>
@@ -21985,10 +22140,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B30" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C30">
         <v>580</v>
@@ -22008,10 +22163,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B31" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C31">
         <v>581</v>
@@ -22031,10 +22186,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B32" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C32">
         <v>4029</v>
@@ -22043,7 +22198,7 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -22054,10 +22209,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B33" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C33">
         <v>4203</v>
@@ -22066,7 +22221,7 @@
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -22077,10 +22232,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B34" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C34">
         <v>3936</v>
@@ -22089,7 +22244,7 @@
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -22100,10 +22255,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B35" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C35">
         <v>4302</v>
@@ -22112,7 +22267,7 @@
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
@@ -22123,10 +22278,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B36" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C36">
         <v>3027</v>
@@ -22146,10 +22301,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B37" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C37">
         <v>3026</v>
@@ -22158,7 +22313,7 @@
         <v>30</v>
       </c>
       <c r="E37" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -22169,10 +22324,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B38" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C38">
         <v>3514</v>
@@ -22192,10 +22347,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B39" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C39">
         <v>3515</v>
@@ -22204,7 +22359,7 @@
         <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -22215,10 +22370,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B40" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C40">
         <v>3139</v>
@@ -22238,10 +22393,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B41" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C41">
         <v>3138</v>
@@ -22261,10 +22416,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B42" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C42">
         <v>2592</v>
@@ -22284,10 +22439,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B43" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C43">
         <v>2591</v>
@@ -22307,10 +22462,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B44" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C44">
         <v>2597</v>
@@ -22330,10 +22485,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C45">
         <v>4174</v>
@@ -22353,10 +22508,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B46" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C46">
         <v>4176</v>
@@ -22376,10 +22531,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B47" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C47">
         <v>2686</v>
@@ -22399,10 +22554,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B48" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C48">
         <v>2687</v>
@@ -22422,10 +22577,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B49" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C49">
         <v>4496</v>
@@ -22445,10 +22600,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B50" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C50">
         <v>4061</v>
@@ -22468,10 +22623,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B51" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C51">
         <v>4166</v>
@@ -22491,10 +22646,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B52" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C52">
         <v>2681</v>
@@ -22514,10 +22669,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C53">
         <v>2682</v>
@@ -22537,10 +22692,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C54">
         <v>2683</v>
@@ -22560,10 +22715,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B55" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C55">
         <v>2600</v>
@@ -22583,10 +22738,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C56">
         <v>4167</v>
@@ -22606,10 +22761,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C57">
         <v>2595</v>
@@ -22629,10 +22784,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B58" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C58">
         <v>4062</v>
@@ -22652,10 +22807,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C59">
         <v>2707</v>
@@ -22675,10 +22830,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B60" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C60">
         <v>3605</v>
@@ -22698,10 +22853,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B61" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C61">
         <v>3606</v>
@@ -22721,10 +22876,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C62">
         <v>4402</v>
@@ -22744,10 +22899,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C63">
         <v>4401</v>
@@ -22767,10 +22922,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B64" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C64">
         <v>2684</v>
@@ -22790,10 +22945,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B65" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C65">
         <v>2723</v>
@@ -22813,10 +22968,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B66" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C66">
         <v>2734</v>
@@ -22825,7 +22980,7 @@
         <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -22836,10 +22991,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B67" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C67">
         <v>4168</v>
@@ -22859,10 +23014,10 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B68" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C68">
         <v>2718</v>
@@ -22882,10 +23037,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C69">
         <v>2719</v>
@@ -22905,10 +23060,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C70">
         <v>3094</v>
@@ -22928,10 +23083,10 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C71">
         <v>4169</v>
@@ -22951,10 +23106,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C72">
         <v>2685</v>
@@ -22974,10 +23129,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B73" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C73">
         <v>4113</v>
@@ -22997,10 +23152,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C74">
         <v>4106</v>
@@ -23020,10 +23175,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B75" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C75">
         <v>2596</v>
@@ -23043,10 +23198,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C76">
         <v>4457</v>
@@ -23066,10 +23221,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B77" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C77">
         <v>4458</v>
@@ -23089,10 +23244,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C78">
         <v>2602</v>
@@ -23112,10 +23267,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B79" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C79">
         <v>2605</v>
@@ -23135,10 +23290,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B80" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C80">
         <v>3894</v>
@@ -23158,10 +23313,10 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B81" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C81">
         <v>4109</v>
@@ -23181,10 +23336,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C82">
         <v>4110</v>
@@ -23204,10 +23359,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C83">
         <v>4171</v>
@@ -23227,10 +23382,10 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B84" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C84">
         <v>2653</v>
@@ -23250,10 +23405,10 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C85">
         <v>3675</v>
@@ -23273,10 +23428,10 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B86" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C86">
         <v>2417</v>
@@ -23296,10 +23451,10 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B87" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C87">
         <v>3109</v>
@@ -23319,10 +23474,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B88" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C88">
         <v>2777</v>
@@ -23342,10 +23497,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C89">
         <v>2776</v>
@@ -23365,10 +23520,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B90" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C90">
         <v>4173</v>
@@ -23388,10 +23543,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B91" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C91">
         <v>2689</v>
@@ -23411,10 +23566,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B92" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C92">
         <v>4170</v>
@@ -23434,10 +23589,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B93" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C93">
         <v>4494</v>
@@ -23457,10 +23612,10 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B94" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C94">
         <v>4495</v>
@@ -23480,10 +23635,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B95" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C95">
         <v>2785</v>
@@ -23503,10 +23658,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B96" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C96">
         <v>2784</v>
@@ -23526,10 +23681,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B97" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C97">
         <v>2788</v>
@@ -23549,10 +23704,10 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B98" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C98">
         <v>2789</v>
@@ -23572,10 +23727,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B99" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C99">
         <v>4539</v>
@@ -23595,10 +23750,10 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B100" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C100">
         <v>3495</v>
@@ -23618,10 +23773,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B101" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C101">
         <v>2786</v>
@@ -23641,10 +23796,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C102">
         <v>2787</v>
@@ -23664,10 +23819,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C103">
         <v>2598</v>
@@ -23687,10 +23842,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B104" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C104">
         <v>4060</v>
@@ -23710,10 +23865,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C105">
         <v>2690</v>
@@ -23733,10 +23888,10 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B106" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C106">
         <v>3355</v>
@@ -23756,10 +23911,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B107" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C107">
         <v>3066</v>
@@ -23779,10 +23934,10 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B108" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C108">
         <v>1515</v>
@@ -23802,10 +23957,10 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C109">
         <v>2552</v>
@@ -23825,10 +23980,10 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B110" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C110">
         <v>3092</v>
@@ -23848,10 +24003,10 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B111" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C111">
         <v>2589</v>
@@ -23871,10 +24026,10 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B112" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C112">
         <v>2588</v>
@@ -23894,10 +24049,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B113" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C113">
         <v>2688</v>
@@ -23917,10 +24072,10 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B114" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C114">
         <v>2599</v>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C054B39-0725-4D80-9196-A2A2FB93863A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7751E334-E905-4AFF-96B4-5DAC0C6A5034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="1365" windowWidth="27300" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3562" uniqueCount="1089">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3298,6 +3298,12 @@
   </si>
   <si>
     <t>castanha-de-caju-caramelizada-açai</t>
+  </si>
+  <si>
+    <t>ch-hortela</t>
+  </si>
+  <si>
+    <t>CHÁ DE HORTELÃ</t>
   </si>
 </sst>
 </file>
@@ -3345,9 +3351,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4298,7 +4306,7 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>435</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4321,7 +4329,7 @@
         <v>13</v>
       </c>
       <c r="G18">
-        <v>217.5</v>
+        <v>227.5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4344,7 +4352,7 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4367,7 +4375,7 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4891,7 +4899,7 @@
         <v>13</v>
       </c>
       <c r="G19">
-        <v>152.5</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4914,7 +4922,7 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>305</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8960,7 +8968,7 @@
         <v>13</v>
       </c>
       <c r="G13">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8983,7 +8991,7 @@
         <v>13</v>
       </c>
       <c r="G14">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9006,7 +9014,7 @@
         <v>13</v>
       </c>
       <c r="G15">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9029,7 +9037,7 @@
         <v>13</v>
       </c>
       <c r="G16">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9052,7 +9060,7 @@
         <v>13</v>
       </c>
       <c r="G17">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -9075,7 +9083,7 @@
         <v>13</v>
       </c>
       <c r="G18">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9098,7 +9106,7 @@
         <v>13</v>
       </c>
       <c r="G19">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9121,7 +9129,7 @@
         <v>13</v>
       </c>
       <c r="G20">
-        <v>23.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -15109,7 +15117,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -16203,39 +16211,39 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>189</v>
+        <v>1087</v>
       </c>
       <c r="B48" t="s">
-        <v>190</v>
+        <v>1088</v>
       </c>
       <c r="C48">
-        <v>4318</v>
+        <v>2466</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G48">
-        <v>250</v>
+        <v>775</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>189</v>
+        <v>1087</v>
       </c>
       <c r="B49" t="s">
-        <v>190</v>
+        <v>1088</v>
       </c>
       <c r="C49">
-        <v>4319</v>
+        <v>2465</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -16244,18 +16252,18 @@
         <v>13</v>
       </c>
       <c r="G49">
-        <v>127</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C50">
-        <v>4254</v>
+        <v>4318</v>
       </c>
       <c r="D50">
         <v>10</v>
@@ -16267,21 +16275,21 @@
         <v>13</v>
       </c>
       <c r="G50">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C51">
-        <v>2563</v>
+        <v>4319</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -16290,18 +16298,18 @@
         <v>13</v>
       </c>
       <c r="G51">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C52">
-        <v>2725</v>
+        <v>4254</v>
       </c>
       <c r="D52">
         <v>10</v>
@@ -16310,21 +16318,21 @@
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G52">
-        <v>600</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C53">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -16336,21 +16344,21 @@
         <v>13</v>
       </c>
       <c r="G53">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C54">
-        <v>2782</v>
+        <v>2725</v>
       </c>
       <c r="D54">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -16359,18 +16367,18 @@
         <v>32</v>
       </c>
       <c r="G54">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C55">
-        <v>2745</v>
+        <v>2562</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -16382,21 +16390,21 @@
         <v>13</v>
       </c>
       <c r="G55">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B56" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C56">
-        <v>4207</v>
+        <v>2782</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -16410,16 +16418,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C57">
-        <v>3769</v>
+        <v>2745</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -16428,90 +16436,90 @@
         <v>13</v>
       </c>
       <c r="G57">
-        <v>190</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C58">
-        <v>3034</v>
+        <v>4207</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G58">
-        <v>30</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C59">
-        <v>3039</v>
+        <v>3769</v>
       </c>
       <c r="D59">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G59">
-        <v>750</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C60">
-        <v>3421</v>
+        <v>3034</v>
       </c>
       <c r="D60">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G60">
-        <v>420</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C61">
-        <v>2748</v>
+        <v>3039</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -16520,7 +16528,7 @@
         <v>32</v>
       </c>
       <c r="G61">
-        <v>210</v>
+        <v>750</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -16531,88 +16539,88 @@
         <v>202</v>
       </c>
       <c r="C62">
-        <v>2576</v>
+        <v>3421</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G62">
-        <v>21</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B63" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C63">
-        <v>3032</v>
+        <v>2748</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G63">
-        <v>19</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B64" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C64">
-        <v>2740</v>
+        <v>2576</v>
       </c>
       <c r="D64">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G64">
-        <v>780</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C65">
-        <v>3098</v>
+        <v>3032</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G65">
-        <v>390</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -16623,33 +16631,33 @@
         <v>206</v>
       </c>
       <c r="C66">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G66">
-        <v>39</v>
+        <v>780</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B67" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C67">
-        <v>3360</v>
+        <v>3098</v>
       </c>
       <c r="D67">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -16658,30 +16666,30 @@
         <v>32</v>
       </c>
       <c r="G67">
-        <v>300</v>
+        <v>390</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B68" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C68">
-        <v>2611</v>
+        <v>2743</v>
       </c>
       <c r="D68">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G68">
-        <v>600</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -16692,56 +16700,56 @@
         <v>208</v>
       </c>
       <c r="C69">
-        <v>2558</v>
+        <v>3360</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G69">
-        <v>24</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B70" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C70">
-        <v>3042</v>
+        <v>2611</v>
       </c>
       <c r="D70">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G70">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B71" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C71">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -16750,21 +16758,21 @@
         <v>13</v>
       </c>
       <c r="G71">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C72">
-        <v>4226</v>
+        <v>3042</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -16773,29 +16781,75 @@
         <v>13</v>
       </c>
       <c r="G72">
-        <v>35</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" t="s">
+        <v>210</v>
+      </c>
+      <c r="C73">
+        <v>2561</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>211</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>212</v>
       </c>
-      <c r="C73">
+      <c r="C74">
+        <v>4226</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>211</v>
+      </c>
+      <c r="B75" t="s">
+        <v>212</v>
+      </c>
+      <c r="C75">
         <v>4227</v>
       </c>
-      <c r="D73">
+      <c r="D75">
         <v>10</v>
       </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>32</v>
-      </c>
-      <c r="G73">
+      <c r="E75" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" t="s">
+        <v>32</v>
+      </c>
+      <c r="G75">
         <v>350</v>
       </c>
     </row>
@@ -17067,7 +17121,7 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>430</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -17090,7 +17144,7 @@
         <v>13</v>
       </c>
       <c r="G12">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -21468,7 +21522,7 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21490,7 +21544,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -21513,7 +21567,7 @@
       <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>380</v>
       </c>
     </row>
@@ -21536,7 +21590,7 @@
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>57</v>
       </c>
     </row>
@@ -21559,7 +21613,7 @@
       <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>350</v>
       </c>
     </row>
@@ -21582,7 +21636,7 @@
       <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>53.5</v>
       </c>
     </row>
@@ -21605,7 +21659,7 @@
       <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>73</v>
       </c>
     </row>
@@ -21628,7 +21682,7 @@
       <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>146</v>
       </c>
     </row>
@@ -21651,7 +21705,7 @@
       <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3">
         <v>60</v>
       </c>
     </row>
@@ -21674,7 +21728,7 @@
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3">
         <v>32</v>
       </c>
     </row>
@@ -21697,7 +21751,7 @@
       <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="3">
         <v>132.5</v>
       </c>
     </row>
@@ -21720,7 +21774,7 @@
       <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="3">
         <v>128</v>
       </c>
     </row>
@@ -21743,7 +21797,7 @@
       <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <v>39</v>
       </c>
     </row>
@@ -21766,7 +21820,7 @@
       <c r="F13" t="s">
         <v>9</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <v>390</v>
       </c>
     </row>
@@ -21789,7 +21843,7 @@
       <c r="F14" t="s">
         <v>32</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="3">
         <v>185</v>
       </c>
     </row>
@@ -21812,7 +21866,7 @@
       <c r="F15" t="s">
         <v>13</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>94.5</v>
       </c>
     </row>
@@ -21835,7 +21889,7 @@
       <c r="F16" t="s">
         <v>32</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="3">
         <v>180</v>
       </c>
     </row>
@@ -21858,7 +21912,7 @@
       <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="3">
         <v>92</v>
       </c>
     </row>
@@ -21881,7 +21935,7 @@
       <c r="F18" t="s">
         <v>32</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="3">
         <v>1450</v>
       </c>
     </row>
@@ -21904,7 +21958,7 @@
       <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="3">
         <v>290</v>
       </c>
     </row>
@@ -21927,7 +21981,7 @@
       <c r="F20" t="s">
         <v>13</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>170</v>
       </c>
     </row>
@@ -21950,7 +22004,7 @@
       <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="3">
         <v>62.5</v>
       </c>
     </row>
@@ -21973,7 +22027,7 @@
       <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="3">
         <v>33</v>
       </c>
     </row>
@@ -21996,7 +22050,7 @@
       <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="3">
         <v>320</v>
       </c>
     </row>
@@ -22019,7 +22073,7 @@
       <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="3">
         <v>97</v>
       </c>
     </row>
@@ -22042,7 +22096,7 @@
       <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="3">
         <v>240</v>
       </c>
     </row>
@@ -22065,7 +22119,7 @@
       <c r="F26" t="s">
         <v>13</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <v>122</v>
       </c>
     </row>
@@ -22088,7 +22142,7 @@
       <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <v>348</v>
       </c>
     </row>
@@ -22111,7 +22165,7 @@
       <c r="F28" t="s">
         <v>13</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <v>29</v>
       </c>
     </row>
@@ -22134,7 +22188,7 @@
       <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <v>112.5</v>
       </c>
     </row>
@@ -22157,7 +22211,7 @@
       <c r="F30" t="s">
         <v>32</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <v>45</v>
       </c>
     </row>
@@ -22180,7 +22234,7 @@
       <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <v>125</v>
       </c>
     </row>
@@ -22203,7 +22257,7 @@
       <c r="F32" t="s">
         <v>9</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <v>122</v>
       </c>
     </row>
@@ -22226,7 +22280,7 @@
       <c r="F33" t="s">
         <v>233</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <v>86</v>
       </c>
     </row>
@@ -22249,7 +22303,7 @@
       <c r="F34" t="s">
         <v>9</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <v>192</v>
       </c>
     </row>
@@ -22272,7 +22326,7 @@
       <c r="F35" t="s">
         <v>9</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <v>103.5</v>
       </c>
     </row>
@@ -22295,7 +22349,7 @@
       <c r="F36" t="s">
         <v>32</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <v>28.5</v>
       </c>
     </row>
@@ -22318,7 +22372,7 @@
       <c r="F37" t="s">
         <v>233</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <v>40</v>
       </c>
     </row>
@@ -22341,7 +22395,7 @@
       <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <v>30.5</v>
       </c>
     </row>
@@ -22364,7 +22418,7 @@
       <c r="F39" t="s">
         <v>233</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <v>42.5</v>
       </c>
     </row>
@@ -22387,7 +22441,7 @@
       <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <v>63</v>
       </c>
     </row>
@@ -22410,7 +22464,7 @@
       <c r="F41" t="s">
         <v>32</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
     </row>
@@ -22433,7 +22487,7 @@
       <c r="F42" t="s">
         <v>13</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <v>27.5</v>
       </c>
     </row>
@@ -22456,7 +22510,7 @@
       <c r="F43" t="s">
         <v>32</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <v>337.5</v>
       </c>
     </row>
@@ -22479,7 +22533,7 @@
       <c r="F44" t="s">
         <v>13</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <v>90</v>
       </c>
     </row>
@@ -22502,7 +22556,7 @@
       <c r="F45" t="s">
         <v>13</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <v>125</v>
       </c>
     </row>
@@ -22525,7 +22579,7 @@
       <c r="F46" t="s">
         <v>13</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <v>140</v>
       </c>
     </row>
@@ -22548,7 +22602,7 @@
       <c r="F47" t="s">
         <v>13</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <v>64.5</v>
       </c>
     </row>
@@ -22571,7 +22625,7 @@
       <c r="F48" t="s">
         <v>13</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="3">
         <v>64.5</v>
       </c>
     </row>
@@ -22594,7 +22648,7 @@
       <c r="F49" t="s">
         <v>13</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="3">
         <v>115</v>
       </c>
     </row>
@@ -22617,7 +22671,7 @@
       <c r="F50" t="s">
         <v>13</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <v>125</v>
       </c>
     </row>
@@ -22640,7 +22694,7 @@
       <c r="F51" t="s">
         <v>13</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <v>125</v>
       </c>
     </row>
@@ -22663,7 +22717,7 @@
       <c r="F52" t="s">
         <v>13</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <v>42</v>
       </c>
     </row>
@@ -22686,7 +22740,7 @@
       <c r="F53" t="s">
         <v>13</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <v>37</v>
       </c>
     </row>
@@ -22709,7 +22763,7 @@
       <c r="F54" t="s">
         <v>13</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <v>37</v>
       </c>
     </row>
@@ -22732,7 +22786,7 @@
       <c r="F55" t="s">
         <v>13</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <v>120</v>
       </c>
     </row>
@@ -22755,7 +22809,7 @@
       <c r="F56" t="s">
         <v>13</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <v>125</v>
       </c>
     </row>
@@ -22778,7 +22832,7 @@
       <c r="F57" t="s">
         <v>13</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <v>140</v>
       </c>
     </row>
@@ -22801,7 +22855,7 @@
       <c r="F58" t="s">
         <v>13</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="3">
         <v>140</v>
       </c>
     </row>
@@ -22824,7 +22878,7 @@
       <c r="F59" t="s">
         <v>13</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <v>140</v>
       </c>
     </row>
@@ -22847,7 +22901,7 @@
       <c r="F60" t="s">
         <v>32</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <v>212.5</v>
       </c>
     </row>
@@ -22870,7 +22924,7 @@
       <c r="F61" t="s">
         <v>13</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <v>27</v>
       </c>
     </row>
@@ -22893,7 +22947,7 @@
       <c r="F62" t="s">
         <v>13</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <v>160</v>
       </c>
     </row>
@@ -22916,7 +22970,7 @@
       <c r="F63" t="s">
         <v>13</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <v>82</v>
       </c>
     </row>
@@ -22939,7 +22993,7 @@
       <c r="F64" t="s">
         <v>13</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <v>50.5</v>
       </c>
     </row>
@@ -22962,7 +23016,7 @@
       <c r="F65" t="s">
         <v>13</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="3">
         <v>105</v>
       </c>
     </row>
@@ -22985,7 +23039,7 @@
       <c r="F66" t="s">
         <v>13</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <v>630</v>
       </c>
     </row>
@@ -23008,7 +23062,7 @@
       <c r="F67" t="s">
         <v>13</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <v>125</v>
       </c>
     </row>
@@ -23031,8 +23085,8 @@
       <c r="F68" t="s">
         <v>32</v>
       </c>
-      <c r="G68">
-        <v>575</v>
+      <c r="G68" s="3">
+        <v>750</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -23054,8 +23108,8 @@
       <c r="F69" t="s">
         <v>13</v>
       </c>
-      <c r="G69">
-        <v>117</v>
+      <c r="G69" s="3">
+        <v>172.5</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -23077,7 +23131,7 @@
       <c r="F70" t="s">
         <v>13</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="3">
         <v>64</v>
       </c>
     </row>
@@ -23100,7 +23154,7 @@
       <c r="F71" t="s">
         <v>13</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="3">
         <v>140</v>
       </c>
     </row>
@@ -23123,7 +23177,7 @@
       <c r="F72" t="s">
         <v>13</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="3">
         <v>72</v>
       </c>
     </row>
@@ -23146,7 +23200,7 @@
       <c r="F73" t="s">
         <v>32</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="3">
         <v>189</v>
       </c>
     </row>
@@ -23169,7 +23223,7 @@
       <c r="F74" t="s">
         <v>13</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="3">
         <v>96</v>
       </c>
     </row>
@@ -23192,7 +23246,7 @@
       <c r="F75" t="s">
         <v>13</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="3">
         <v>125</v>
       </c>
     </row>
@@ -23215,7 +23269,7 @@
       <c r="F76" t="s">
         <v>13</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="3">
         <v>224</v>
       </c>
     </row>
@@ -23238,7 +23292,7 @@
       <c r="F77" t="s">
         <v>13</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="3">
         <v>114</v>
       </c>
     </row>
@@ -23261,7 +23315,7 @@
       <c r="F78" t="s">
         <v>32</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="3">
         <v>330</v>
       </c>
     </row>
@@ -23284,7 +23338,7 @@
       <c r="F79" t="s">
         <v>13</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="3">
         <v>33</v>
       </c>
     </row>
@@ -23307,7 +23361,7 @@
       <c r="F80" t="s">
         <v>32</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="3">
         <v>825</v>
       </c>
     </row>
@@ -23330,7 +23384,7 @@
       <c r="F81" t="s">
         <v>32</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="3">
         <v>148</v>
       </c>
     </row>
@@ -23353,7 +23407,7 @@
       <c r="F82" t="s">
         <v>32</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="3">
         <v>76</v>
       </c>
     </row>
@@ -23376,7 +23430,7 @@
       <c r="F83" t="s">
         <v>13</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="3">
         <v>125</v>
       </c>
     </row>
@@ -23399,7 +23453,7 @@
       <c r="F84" t="s">
         <v>13</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="3">
         <v>160</v>
       </c>
     </row>
@@ -23422,7 +23476,7 @@
       <c r="F85" t="s">
         <v>13</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="3">
         <v>132</v>
       </c>
     </row>
@@ -23445,7 +23499,7 @@
       <c r="F86" t="s">
         <v>32</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="3">
         <v>182</v>
       </c>
     </row>
@@ -23468,7 +23522,7 @@
       <c r="F87" t="s">
         <v>13</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="3">
         <v>38.5</v>
       </c>
     </row>
@@ -23491,7 +23545,7 @@
       <c r="F88" t="s">
         <v>13</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="3">
         <v>200</v>
       </c>
     </row>
@@ -23514,7 +23568,7 @@
       <c r="F89" t="s">
         <v>13</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="3">
         <v>102</v>
       </c>
     </row>
@@ -23537,7 +23591,7 @@
       <c r="F90" t="s">
         <v>13</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="3">
         <v>105</v>
       </c>
     </row>
@@ -23560,7 +23614,7 @@
       <c r="F91" t="s">
         <v>13</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="3">
         <v>85</v>
       </c>
     </row>
@@ -23583,7 +23637,7 @@
       <c r="F92" t="s">
         <v>13</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="3">
         <v>125</v>
       </c>
     </row>
@@ -23606,7 +23660,7 @@
       <c r="F93" t="s">
         <v>32</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="3">
         <v>300</v>
       </c>
     </row>
@@ -23629,7 +23683,7 @@
       <c r="F94" t="s">
         <v>13</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="3">
         <v>150</v>
       </c>
     </row>
@@ -23652,7 +23706,7 @@
       <c r="F95" t="s">
         <v>13</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="3">
         <v>47.5</v>
       </c>
     </row>
@@ -23675,7 +23729,7 @@
       <c r="F96" t="s">
         <v>32</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="3">
         <v>95</v>
       </c>
     </row>
@@ -23698,7 +23752,7 @@
       <c r="F97" t="s">
         <v>32</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="3">
         <v>90</v>
       </c>
     </row>
@@ -23721,7 +23775,7 @@
       <c r="F98" t="s">
         <v>13</v>
       </c>
-      <c r="G98">
+      <c r="G98" s="3">
         <v>45</v>
       </c>
     </row>
@@ -23744,7 +23798,7 @@
       <c r="F99" t="s">
         <v>32</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="3">
         <v>95</v>
       </c>
     </row>
@@ -23767,7 +23821,7 @@
       <c r="F100" t="s">
         <v>13</v>
       </c>
-      <c r="G100">
+      <c r="G100" s="3">
         <v>47.5</v>
       </c>
     </row>
@@ -23790,7 +23844,7 @@
       <c r="F101" t="s">
         <v>32</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="3">
         <v>90</v>
       </c>
     </row>
@@ -23813,7 +23867,7 @@
       <c r="F102" t="s">
         <v>13</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="3">
         <v>45</v>
       </c>
     </row>
@@ -23836,7 +23890,7 @@
       <c r="F103" t="s">
         <v>13</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="3">
         <v>130</v>
       </c>
     </row>
@@ -23859,7 +23913,7 @@
       <c r="F104" t="s">
         <v>13</v>
       </c>
-      <c r="G104">
+      <c r="G104" s="3">
         <v>145</v>
       </c>
     </row>
@@ -23882,7 +23936,7 @@
       <c r="F105" t="s">
         <v>13</v>
       </c>
-      <c r="G105">
+      <c r="G105" s="3">
         <v>135</v>
       </c>
     </row>
@@ -23905,7 +23959,7 @@
       <c r="F106" t="s">
         <v>32</v>
       </c>
-      <c r="G106">
+      <c r="G106" s="3">
         <v>315</v>
       </c>
     </row>
@@ -23928,7 +23982,7 @@
       <c r="F107" t="s">
         <v>13</v>
       </c>
-      <c r="G107">
+      <c r="G107" s="3">
         <v>65</v>
       </c>
     </row>
@@ -23951,7 +24005,7 @@
       <c r="F108" t="s">
         <v>32</v>
       </c>
-      <c r="G108">
+      <c r="G108" s="3">
         <v>1175</v>
       </c>
     </row>
@@ -23974,7 +24028,7 @@
       <c r="F109" t="s">
         <v>13</v>
       </c>
-      <c r="G109">
+      <c r="G109" s="3">
         <v>235</v>
       </c>
     </row>
@@ -23997,7 +24051,7 @@
       <c r="F110" t="s">
         <v>13</v>
       </c>
-      <c r="G110">
+      <c r="G110" s="3">
         <v>73.5</v>
       </c>
     </row>
@@ -24020,7 +24074,7 @@
       <c r="F111" t="s">
         <v>13</v>
       </c>
-      <c r="G111">
+      <c r="G111" s="3">
         <v>200</v>
       </c>
     </row>
@@ -24043,7 +24097,7 @@
       <c r="F112" t="s">
         <v>13</v>
       </c>
-      <c r="G112">
+      <c r="G112" s="3">
         <v>20</v>
       </c>
     </row>
@@ -24066,7 +24120,7 @@
       <c r="F113" t="s">
         <v>13</v>
       </c>
-      <c r="G113">
+      <c r="G113" s="3">
         <v>90</v>
       </c>
     </row>
@@ -24089,7 +24143,7 @@
       <c r="F114" t="s">
         <v>13</v>
       </c>
-      <c r="G114">
+      <c r="G114" s="3">
         <v>84</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7751E334-E905-4AFF-96B4-5DAC0C6A5034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88A5FA7-59B6-4013-8C64-F032FCF965BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -3351,11 +3351,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17834,7 +17832,7 @@
         <v>13</v>
       </c>
       <c r="G42">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -19393,7 +19391,7 @@
         <v>32</v>
       </c>
       <c r="G38">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -19416,7 +19414,7 @@
         <v>13</v>
       </c>
       <c r="G39">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -20014,7 +20012,7 @@
         <v>32</v>
       </c>
       <c r="G65">
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -20037,7 +20035,7 @@
         <v>32</v>
       </c>
       <c r="G66">
-        <v>212.5</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -20060,7 +20058,7 @@
         <v>13</v>
       </c>
       <c r="G67">
-        <v>44.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -21522,7 +21520,7 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="15" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21544,7 +21542,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -21567,7 +21565,7 @@
       <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <v>380</v>
       </c>
     </row>
@@ -21590,7 +21588,7 @@
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>57</v>
       </c>
     </row>
@@ -21613,7 +21611,7 @@
       <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>350</v>
       </c>
     </row>
@@ -21636,7 +21634,7 @@
       <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>53.5</v>
       </c>
     </row>
@@ -21659,7 +21657,7 @@
       <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>73</v>
       </c>
     </row>
@@ -21682,7 +21680,7 @@
       <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>146</v>
       </c>
     </row>
@@ -21705,7 +21703,7 @@
       <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>60</v>
       </c>
     </row>
@@ -21728,7 +21726,7 @@
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>32</v>
       </c>
     </row>
@@ -21751,7 +21749,7 @@
       <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10">
         <v>132.5</v>
       </c>
     </row>
@@ -21774,7 +21772,7 @@
       <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>128</v>
       </c>
     </row>
@@ -21797,7 +21795,7 @@
       <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>39</v>
       </c>
     </row>
@@ -21820,7 +21818,7 @@
       <c r="F13" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>390</v>
       </c>
     </row>
@@ -21843,7 +21841,7 @@
       <c r="F14" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14">
         <v>185</v>
       </c>
     </row>
@@ -21866,7 +21864,7 @@
       <c r="F15" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>94.5</v>
       </c>
     </row>
@@ -21889,7 +21887,7 @@
       <c r="F16" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16">
         <v>180</v>
       </c>
     </row>
@@ -21912,7 +21910,7 @@
       <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>92</v>
       </c>
     </row>
@@ -21935,7 +21933,7 @@
       <c r="F18" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18">
         <v>1450</v>
       </c>
     </row>
@@ -21958,7 +21956,7 @@
       <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>290</v>
       </c>
     </row>
@@ -21981,7 +21979,7 @@
       <c r="F20" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20">
         <v>170</v>
       </c>
     </row>
@@ -22004,7 +22002,7 @@
       <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>62.5</v>
       </c>
     </row>
@@ -22027,7 +22025,7 @@
       <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>33</v>
       </c>
     </row>
@@ -22050,7 +22048,7 @@
       <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>320</v>
       </c>
     </row>
@@ -22073,7 +22071,7 @@
       <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>97</v>
       </c>
     </row>
@@ -22096,7 +22094,7 @@
       <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>240</v>
       </c>
     </row>
@@ -22119,7 +22117,7 @@
       <c r="F26" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>122</v>
       </c>
     </row>
@@ -22142,7 +22140,7 @@
       <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27">
         <v>348</v>
       </c>
     </row>
@@ -22165,7 +22163,7 @@
       <c r="F28" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28">
         <v>29</v>
       </c>
     </row>
@@ -22188,7 +22186,7 @@
       <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29">
         <v>112.5</v>
       </c>
     </row>
@@ -22211,7 +22209,7 @@
       <c r="F30" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30">
         <v>45</v>
       </c>
     </row>
@@ -22234,7 +22232,7 @@
       <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31">
         <v>125</v>
       </c>
     </row>
@@ -22257,7 +22255,7 @@
       <c r="F32" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32">
         <v>122</v>
       </c>
     </row>
@@ -22280,7 +22278,7 @@
       <c r="F33" t="s">
         <v>233</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33">
         <v>86</v>
       </c>
     </row>
@@ -22303,7 +22301,7 @@
       <c r="F34" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34">
         <v>192</v>
       </c>
     </row>
@@ -22326,7 +22324,7 @@
       <c r="F35" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35">
         <v>103.5</v>
       </c>
     </row>
@@ -22349,7 +22347,7 @@
       <c r="F36" t="s">
         <v>32</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36">
         <v>28.5</v>
       </c>
     </row>
@@ -22372,7 +22370,7 @@
       <c r="F37" t="s">
         <v>233</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37">
         <v>40</v>
       </c>
     </row>
@@ -22395,7 +22393,7 @@
       <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38">
         <v>30.5</v>
       </c>
     </row>
@@ -22418,7 +22416,7 @@
       <c r="F39" t="s">
         <v>233</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39">
         <v>42.5</v>
       </c>
     </row>
@@ -22441,7 +22439,7 @@
       <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40">
         <v>63</v>
       </c>
     </row>
@@ -22464,7 +22462,7 @@
       <c r="F41" t="s">
         <v>32</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41">
         <v>300</v>
       </c>
     </row>
@@ -22487,7 +22485,7 @@
       <c r="F42" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42">
         <v>27.5</v>
       </c>
     </row>
@@ -22510,7 +22508,7 @@
       <c r="F43" t="s">
         <v>32</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43">
         <v>337.5</v>
       </c>
     </row>
@@ -22533,7 +22531,7 @@
       <c r="F44" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44">
         <v>90</v>
       </c>
     </row>
@@ -22556,7 +22554,7 @@
       <c r="F45" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45">
         <v>125</v>
       </c>
     </row>
@@ -22579,7 +22577,7 @@
       <c r="F46" t="s">
         <v>13</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46">
         <v>140</v>
       </c>
     </row>
@@ -22602,7 +22600,7 @@
       <c r="F47" t="s">
         <v>13</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47">
         <v>64.5</v>
       </c>
     </row>
@@ -22625,7 +22623,7 @@
       <c r="F48" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48">
         <v>64.5</v>
       </c>
     </row>
@@ -22648,7 +22646,7 @@
       <c r="F49" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49">
         <v>115</v>
       </c>
     </row>
@@ -22671,7 +22669,7 @@
       <c r="F50" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50">
         <v>125</v>
       </c>
     </row>
@@ -22694,7 +22692,7 @@
       <c r="F51" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51">
         <v>125</v>
       </c>
     </row>
@@ -22717,7 +22715,7 @@
       <c r="F52" t="s">
         <v>13</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52">
         <v>42</v>
       </c>
     </row>
@@ -22740,7 +22738,7 @@
       <c r="F53" t="s">
         <v>13</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53">
         <v>37</v>
       </c>
     </row>
@@ -22763,7 +22761,7 @@
       <c r="F54" t="s">
         <v>13</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54">
         <v>37</v>
       </c>
     </row>
@@ -22786,7 +22784,7 @@
       <c r="F55" t="s">
         <v>13</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55">
         <v>120</v>
       </c>
     </row>
@@ -22809,7 +22807,7 @@
       <c r="F56" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56">
         <v>125</v>
       </c>
     </row>
@@ -22832,7 +22830,7 @@
       <c r="F57" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57">
         <v>140</v>
       </c>
     </row>
@@ -22855,7 +22853,7 @@
       <c r="F58" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58">
         <v>140</v>
       </c>
     </row>
@@ -22878,7 +22876,7 @@
       <c r="F59" t="s">
         <v>13</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59">
         <v>140</v>
       </c>
     </row>
@@ -22901,7 +22899,7 @@
       <c r="F60" t="s">
         <v>32</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60">
         <v>212.5</v>
       </c>
     </row>
@@ -22924,7 +22922,7 @@
       <c r="F61" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61">
         <v>27</v>
       </c>
     </row>
@@ -22947,7 +22945,7 @@
       <c r="F62" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62">
         <v>160</v>
       </c>
     </row>
@@ -22970,7 +22968,7 @@
       <c r="F63" t="s">
         <v>13</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63">
         <v>82</v>
       </c>
     </row>
@@ -22993,7 +22991,7 @@
       <c r="F64" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64">
         <v>50.5</v>
       </c>
     </row>
@@ -23016,7 +23014,7 @@
       <c r="F65" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65">
         <v>105</v>
       </c>
     </row>
@@ -23039,7 +23037,7 @@
       <c r="F66" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66">
         <v>630</v>
       </c>
     </row>
@@ -23062,7 +23060,7 @@
       <c r="F67" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67">
         <v>125</v>
       </c>
     </row>
@@ -23085,7 +23083,7 @@
       <c r="F68" t="s">
         <v>32</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68">
         <v>750</v>
       </c>
     </row>
@@ -23108,7 +23106,7 @@
       <c r="F69" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69">
         <v>172.5</v>
       </c>
     </row>
@@ -23131,7 +23129,7 @@
       <c r="F70" t="s">
         <v>13</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70">
         <v>64</v>
       </c>
     </row>
@@ -23154,7 +23152,7 @@
       <c r="F71" t="s">
         <v>13</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71">
         <v>140</v>
       </c>
     </row>
@@ -23177,7 +23175,7 @@
       <c r="F72" t="s">
         <v>13</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72">
         <v>72</v>
       </c>
     </row>
@@ -23200,7 +23198,7 @@
       <c r="F73" t="s">
         <v>32</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73">
         <v>189</v>
       </c>
     </row>
@@ -23223,7 +23221,7 @@
       <c r="F74" t="s">
         <v>13</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74">
         <v>96</v>
       </c>
     </row>
@@ -23246,7 +23244,7 @@
       <c r="F75" t="s">
         <v>13</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75">
         <v>125</v>
       </c>
     </row>
@@ -23269,7 +23267,7 @@
       <c r="F76" t="s">
         <v>13</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76">
         <v>224</v>
       </c>
     </row>
@@ -23292,7 +23290,7 @@
       <c r="F77" t="s">
         <v>13</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77">
         <v>114</v>
       </c>
     </row>
@@ -23315,7 +23313,7 @@
       <c r="F78" t="s">
         <v>32</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78">
         <v>330</v>
       </c>
     </row>
@@ -23338,7 +23336,7 @@
       <c r="F79" t="s">
         <v>13</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79">
         <v>33</v>
       </c>
     </row>
@@ -23361,7 +23359,7 @@
       <c r="F80" t="s">
         <v>32</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80">
         <v>825</v>
       </c>
     </row>
@@ -23384,7 +23382,7 @@
       <c r="F81" t="s">
         <v>32</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81">
         <v>148</v>
       </c>
     </row>
@@ -23407,7 +23405,7 @@
       <c r="F82" t="s">
         <v>32</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82">
         <v>76</v>
       </c>
     </row>
@@ -23430,7 +23428,7 @@
       <c r="F83" t="s">
         <v>13</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83">
         <v>125</v>
       </c>
     </row>
@@ -23453,7 +23451,7 @@
       <c r="F84" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84">
         <v>160</v>
       </c>
     </row>
@@ -23476,7 +23474,7 @@
       <c r="F85" t="s">
         <v>13</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85">
         <v>132</v>
       </c>
     </row>
@@ -23499,7 +23497,7 @@
       <c r="F86" t="s">
         <v>32</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G86">
         <v>182</v>
       </c>
     </row>
@@ -23522,7 +23520,7 @@
       <c r="F87" t="s">
         <v>13</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87">
         <v>38.5</v>
       </c>
     </row>
@@ -23545,7 +23543,7 @@
       <c r="F88" t="s">
         <v>13</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G88">
         <v>200</v>
       </c>
     </row>
@@ -23568,7 +23566,7 @@
       <c r="F89" t="s">
         <v>13</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89">
         <v>102</v>
       </c>
     </row>
@@ -23591,7 +23589,7 @@
       <c r="F90" t="s">
         <v>13</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90">
         <v>105</v>
       </c>
     </row>
@@ -23614,7 +23612,7 @@
       <c r="F91" t="s">
         <v>13</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91">
         <v>85</v>
       </c>
     </row>
@@ -23637,7 +23635,7 @@
       <c r="F92" t="s">
         <v>13</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92">
         <v>125</v>
       </c>
     </row>
@@ -23660,7 +23658,7 @@
       <c r="F93" t="s">
         <v>32</v>
       </c>
-      <c r="G93" s="3">
+      <c r="G93">
         <v>300</v>
       </c>
     </row>
@@ -23683,7 +23681,7 @@
       <c r="F94" t="s">
         <v>13</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94">
         <v>150</v>
       </c>
     </row>
@@ -23706,7 +23704,7 @@
       <c r="F95" t="s">
         <v>13</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G95">
         <v>47.5</v>
       </c>
     </row>
@@ -23729,7 +23727,7 @@
       <c r="F96" t="s">
         <v>32</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96">
         <v>95</v>
       </c>
     </row>
@@ -23752,7 +23750,7 @@
       <c r="F97" t="s">
         <v>32</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97">
         <v>90</v>
       </c>
     </row>
@@ -23775,7 +23773,7 @@
       <c r="F98" t="s">
         <v>13</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G98">
         <v>45</v>
       </c>
     </row>
@@ -23798,7 +23796,7 @@
       <c r="F99" t="s">
         <v>32</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99">
         <v>95</v>
       </c>
     </row>
@@ -23821,7 +23819,7 @@
       <c r="F100" t="s">
         <v>13</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100">
         <v>47.5</v>
       </c>
     </row>
@@ -23844,7 +23842,7 @@
       <c r="F101" t="s">
         <v>32</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101">
         <v>90</v>
       </c>
     </row>
@@ -23867,7 +23865,7 @@
       <c r="F102" t="s">
         <v>13</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102">
         <v>45</v>
       </c>
     </row>
@@ -23890,7 +23888,7 @@
       <c r="F103" t="s">
         <v>13</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103">
         <v>130</v>
       </c>
     </row>
@@ -23913,7 +23911,7 @@
       <c r="F104" t="s">
         <v>13</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104">
         <v>145</v>
       </c>
     </row>
@@ -23936,7 +23934,7 @@
       <c r="F105" t="s">
         <v>13</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105">
         <v>135</v>
       </c>
     </row>
@@ -23959,7 +23957,7 @@
       <c r="F106" t="s">
         <v>32</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106">
         <v>315</v>
       </c>
     </row>
@@ -23982,7 +23980,7 @@
       <c r="F107" t="s">
         <v>13</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107">
         <v>65</v>
       </c>
     </row>
@@ -24005,7 +24003,7 @@
       <c r="F108" t="s">
         <v>32</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108">
         <v>1175</v>
       </c>
     </row>
@@ -24028,7 +24026,7 @@
       <c r="F109" t="s">
         <v>13</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109">
         <v>235</v>
       </c>
     </row>
@@ -24051,7 +24049,7 @@
       <c r="F110" t="s">
         <v>13</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110">
         <v>73.5</v>
       </c>
     </row>
@@ -24074,7 +24072,7 @@
       <c r="F111" t="s">
         <v>13</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111">
         <v>200</v>
       </c>
     </row>
@@ -24097,7 +24095,7 @@
       <c r="F112" t="s">
         <v>13</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112">
         <v>20</v>
       </c>
     </row>
@@ -24120,7 +24118,7 @@
       <c r="F113" t="s">
         <v>13</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G113">
         <v>90</v>
       </c>
     </row>
@@ -24143,7 +24141,7 @@
       <c r="F114" t="s">
         <v>13</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114">
         <v>84</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88A5FA7-59B6-4013-8C64-F032FCF965BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327C41BC-5FE6-4316-8AA1-428E209C121D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -12309,7 +12309,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>714.5</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -12332,7 +12332,7 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>714.5</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -13390,7 +13390,7 @@
         <v>9</v>
       </c>
       <c r="G49">
-        <v>918.5</v>
+        <v>850.5</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -13413,7 +13413,7 @@
         <v>13</v>
       </c>
       <c r="G50">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -13436,7 +13436,7 @@
         <v>9</v>
       </c>
       <c r="G51">
-        <v>918.5</v>
+        <v>850.5</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -13459,7 +13459,7 @@
         <v>13</v>
       </c>
       <c r="G52">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -13482,7 +13482,7 @@
         <v>9</v>
       </c>
       <c r="G53">
-        <v>918.5</v>
+        <v>850.5</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -13505,7 +13505,7 @@
         <v>9</v>
       </c>
       <c r="G54">
-        <v>1837</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -13528,7 +13528,7 @@
         <v>13</v>
       </c>
       <c r="G55">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -13551,7 +13551,7 @@
         <v>9</v>
       </c>
       <c r="G56">
-        <v>918.5</v>
+        <v>850.5</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -13574,7 +13574,7 @@
         <v>9</v>
       </c>
       <c r="G57">
-        <v>1837</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -13597,7 +13597,7 @@
         <v>13</v>
       </c>
       <c r="G58">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -20858,7 +20858,7 @@
         <v>32</v>
       </c>
       <c r="G9">
-        <v>51.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327C41BC-5FE6-4316-8AA1-428E209C121D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46D7A7E-755E-4141-964D-418547CDBC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3562" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="1107">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3304,6 +3304,60 @@
   </si>
   <si>
     <t>CHÁ DE HORTELÃ</t>
+  </si>
+  <si>
+    <t>doce-brigadeiro</t>
+  </si>
+  <si>
+    <t>doce-geleia-de-mocoto</t>
+  </si>
+  <si>
+    <t>doce-palha-italiana</t>
+  </si>
+  <si>
+    <t>doce-pingo-bel</t>
+  </si>
+  <si>
+    <t>doce-de-leite-souvenir</t>
+  </si>
+  <si>
+    <t>doce-de-leite-c-cocosouvenir</t>
+  </si>
+  <si>
+    <t>DOCE DE BRIGADEIRO</t>
+  </si>
+  <si>
+    <t>DOCE GELEIA DE MOCOTO</t>
+  </si>
+  <si>
+    <t>DOCE PALHA ITALIANA</t>
+  </si>
+  <si>
+    <t>DOCE PINGO BEL</t>
+  </si>
+  <si>
+    <t>DOCE DE LEITE SOUVENIR</t>
+  </si>
+  <si>
+    <t>DOCE DE LEITE C/COCOSUVENIR</t>
+  </si>
+  <si>
+    <t>X50G</t>
+  </si>
+  <si>
+    <t>X55G</t>
+  </si>
+  <si>
+    <t>X37,5G</t>
+  </si>
+  <si>
+    <t>X400g</t>
+  </si>
+  <si>
+    <t>doce-de-leite-docura-fazenda</t>
+  </si>
+  <si>
+    <t>DOCE DE LEITE DOÇURA FAZENDA</t>
   </si>
 </sst>
 </file>
@@ -9229,7 +9283,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11220,128 +11274,128 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>987</v>
+        <v>1089</v>
       </c>
       <c r="B87" t="s">
-        <v>988</v>
+        <v>1095</v>
       </c>
       <c r="C87">
-        <v>4104</v>
+        <v>4624</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>1078</v>
+        <v>1101</v>
       </c>
       <c r="F87" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G87">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>989</v>
+        <v>1105</v>
       </c>
       <c r="B88" t="s">
-        <v>990</v>
+        <v>1106</v>
       </c>
       <c r="C88">
-        <v>4101</v>
+        <v>4627</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E88" t="s">
-        <v>1078</v>
+        <v>1102</v>
       </c>
       <c r="F88" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G88">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>991</v>
+        <v>1090</v>
       </c>
       <c r="B89" t="s">
-        <v>992</v>
+        <v>1096</v>
       </c>
       <c r="C89">
-        <v>4105</v>
+        <v>4628</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
-        <v>1078</v>
+        <v>1103</v>
       </c>
       <c r="F89" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G89">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>993</v>
+        <v>1091</v>
       </c>
       <c r="B90" t="s">
-        <v>994</v>
+        <v>1097</v>
       </c>
       <c r="C90">
-        <v>3705</v>
+        <v>4625</v>
       </c>
       <c r="D90">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E90" t="s">
-        <v>1076</v>
+        <v>1101</v>
       </c>
       <c r="F90" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G90">
-        <v>123.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>995</v>
+        <v>1092</v>
       </c>
       <c r="B91" t="s">
-        <v>996</v>
+        <v>1098</v>
       </c>
       <c r="C91">
-        <v>3823</v>
+        <v>4626</v>
       </c>
       <c r="D91">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>1078</v>
+        <v>1101</v>
       </c>
       <c r="F91" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G91">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>997</v>
+        <v>1093</v>
       </c>
       <c r="B92" t="s">
-        <v>998</v>
+        <v>1099</v>
       </c>
       <c r="C92">
-        <v>4583</v>
+        <v>4629</v>
       </c>
       <c r="D92">
         <v>12</v>
@@ -11350,366 +11404,366 @@
         <v>1078</v>
       </c>
       <c r="F92" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G92">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>999</v>
+        <v>1094</v>
       </c>
       <c r="B93" t="s">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="C93">
-        <v>4308</v>
+        <v>4630</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>1077</v>
+        <v>1104</v>
       </c>
       <c r="F93" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G93">
-        <v>68.5</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="B94" t="s">
-        <v>1002</v>
+        <v>988</v>
       </c>
       <c r="C94">
-        <v>4309</v>
+        <v>4104</v>
       </c>
       <c r="D94">
         <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F94" t="s">
-        <v>968</v>
+        <v>233</v>
       </c>
       <c r="G94">
-        <v>68.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1003</v>
+        <v>989</v>
       </c>
       <c r="B95" t="s">
-        <v>1004</v>
+        <v>990</v>
       </c>
       <c r="C95">
-        <v>4412</v>
+        <v>4101</v>
       </c>
       <c r="D95">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
-        <v>8</v>
+        <v>1078</v>
       </c>
       <c r="F95" t="s">
-        <v>968</v>
+        <v>233</v>
       </c>
       <c r="G95">
-        <v>71.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1005</v>
+        <v>991</v>
       </c>
       <c r="B96" t="s">
-        <v>1006</v>
+        <v>992</v>
       </c>
       <c r="C96">
-        <v>4413</v>
+        <v>4105</v>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>8</v>
+        <v>1078</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G96">
-        <v>496</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="B97" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="C97">
-        <v>4414</v>
+        <v>3705</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>8</v>
+        <v>1076</v>
       </c>
       <c r="F97" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G97">
-        <v>101</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="B98" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="C98">
-        <v>4415</v>
+        <v>3823</v>
       </c>
       <c r="D98">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
-        <v>8</v>
+        <v>1078</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G98">
-        <v>414</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
       <c r="B99" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="C99">
-        <v>4416</v>
+        <v>4583</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>8</v>
+        <v>1078</v>
       </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G99">
-        <v>85</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
       <c r="B100" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="C100">
-        <v>4475</v>
+        <v>4308</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
       </c>
       <c r="G100">
-        <v>9</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1011</v>
+        <v>1001</v>
       </c>
       <c r="B101" t="s">
-        <v>1012</v>
+        <v>1002</v>
       </c>
       <c r="C101">
-        <v>4354</v>
+        <v>4309</v>
       </c>
       <c r="D101">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="F101" t="s">
-        <v>744</v>
+        <v>968</v>
       </c>
       <c r="G101">
-        <v>79.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="B102" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
       <c r="C102">
-        <v>4445</v>
+        <v>4412</v>
       </c>
       <c r="D102">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="E102" t="s">
-        <v>1083</v>
+        <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>9</v>
+        <v>968</v>
       </c>
       <c r="G102">
-        <v>79.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
       <c r="B103" t="s">
-        <v>1016</v>
+        <v>1006</v>
       </c>
       <c r="C103">
-        <v>4353</v>
+        <v>4413</v>
       </c>
       <c r="D103">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>1083</v>
+        <v>8</v>
       </c>
       <c r="F103" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G103">
-        <v>79.5</v>
+        <v>496</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="B104" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="C104">
-        <v>4350</v>
+        <v>4414</v>
       </c>
       <c r="D104">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E104" t="s">
-        <v>1083</v>
+        <v>8</v>
       </c>
       <c r="F104" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G104">
-        <v>79.5</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="B105" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="C105">
-        <v>4352</v>
+        <v>4415</v>
       </c>
       <c r="D105">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E105" t="s">
-        <v>1083</v>
+        <v>8</v>
       </c>
       <c r="F105" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G105">
-        <v>79.5</v>
+        <v>414</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="B106" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="C106">
-        <v>4349</v>
+        <v>4416</v>
       </c>
       <c r="D106">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>1083</v>
+        <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G106">
-        <v>79.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1023</v>
+        <v>1009</v>
       </c>
       <c r="B107" t="s">
-        <v>1024</v>
+        <v>1010</v>
       </c>
       <c r="C107">
-        <v>4351</v>
+        <v>4475</v>
       </c>
       <c r="D107">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E107" t="s">
         <v>1083</v>
       </c>
       <c r="F107" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107">
         <v>9</v>
-      </c>
-      <c r="G107">
-        <v>79.5</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1025</v>
+        <v>1011</v>
       </c>
       <c r="B108" t="s">
-        <v>1026</v>
+        <v>1012</v>
       </c>
       <c r="C108">
-        <v>4581</v>
+        <v>4354</v>
       </c>
       <c r="D108">
         <v>12</v>
@@ -11718,7 +11772,7 @@
         <v>1083</v>
       </c>
       <c r="F108" t="s">
-        <v>9</v>
+        <v>744</v>
       </c>
       <c r="G108">
         <v>79.5</v>
@@ -11726,162 +11780,323 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
       <c r="B109" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="C109">
-        <v>4096</v>
+        <v>4445</v>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>8</v>
+        <v>1083</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G109">
-        <v>79</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="B110" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="C110">
-        <v>4123</v>
+        <v>4353</v>
       </c>
       <c r="D110">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G110">
-        <v>60</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="B111" t="s">
-        <v>1032</v>
+        <v>1018</v>
       </c>
       <c r="C111">
-        <v>4306</v>
+        <v>4350</v>
       </c>
       <c r="D111">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="F111" t="s">
-        <v>968</v>
+        <v>9</v>
       </c>
       <c r="G111">
-        <v>81</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="B112" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
       <c r="C112">
-        <v>4307</v>
+        <v>4352</v>
       </c>
       <c r="D112">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="F112" t="s">
-        <v>968</v>
+        <v>9</v>
       </c>
       <c r="G112">
-        <v>81</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="B113" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="C113">
-        <v>2659</v>
+        <v>4349</v>
       </c>
       <c r="D113">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="F113" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G113">
-        <v>27.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="B114" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="C114">
-        <v>2621</v>
+        <v>4351</v>
       </c>
       <c r="D114">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="F114" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G114">
-        <v>24.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C115">
+        <v>4581</v>
+      </c>
+      <c r="D115">
+        <v>12</v>
+      </c>
+      <c r="E115" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F115" t="s">
+        <v>9</v>
+      </c>
+      <c r="G115">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C116">
+        <v>4096</v>
+      </c>
+      <c r="D116">
+        <v>5</v>
+      </c>
+      <c r="E116" t="s">
+        <v>8</v>
+      </c>
+      <c r="F116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C117">
+        <v>4123</v>
+      </c>
+      <c r="D117">
+        <v>10</v>
+      </c>
+      <c r="E117" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C118">
+        <v>4306</v>
+      </c>
+      <c r="D118">
+        <v>10</v>
+      </c>
+      <c r="E118" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F118" t="s">
+        <v>968</v>
+      </c>
+      <c r="G118">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C119">
+        <v>4307</v>
+      </c>
+      <c r="D119">
+        <v>10</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F119" t="s">
+        <v>968</v>
+      </c>
+      <c r="G119">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C120">
+        <v>2659</v>
+      </c>
+      <c r="D120">
+        <v>20</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F120" t="s">
+        <v>233</v>
+      </c>
+      <c r="G120">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C121">
+        <v>2621</v>
+      </c>
+      <c r="D121">
+        <v>5</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F121" t="s">
+        <v>233</v>
+      </c>
+      <c r="G121">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>1037</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B122" t="s">
         <v>1038</v>
       </c>
-      <c r="C115">
+      <c r="C122">
         <v>3656</v>
       </c>
-      <c r="D115">
-        <v>5</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="D122">
+        <v>5</v>
+      </c>
+      <c r="E122" t="s">
         <v>1078</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F122" t="s">
         <v>233</v>
       </c>
-      <c r="G115">
+      <c r="G122">
         <v>27</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46D7A7E-755E-4141-964D-418547CDBC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9C33E3-851A-44B5-9B12-F5FC2576BA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2709,18 +2709,6 @@
     <t>BALA GELATINA BEIJO</t>
   </si>
   <si>
-    <t>bala-geatina-cobrinha-citrica</t>
-  </si>
-  <si>
-    <t>BALA GEATINA COBRINHA CITRICA</t>
-  </si>
-  <si>
-    <t>bala-geatina-diversas</t>
-  </si>
-  <si>
-    <t>BALA GEATINA DIVERSAS</t>
-  </si>
-  <si>
     <t>bala-gelatina-mix-formatos</t>
   </si>
   <si>
@@ -3358,6 +3346,18 @@
   </si>
   <si>
     <t>DOCE DE LEITE DOÇURA FAZENDA</t>
+  </si>
+  <si>
+    <t>bala-gelatina-cobrinha-citrica</t>
+  </si>
+  <si>
+    <t>bala-gelatina-diversas</t>
+  </si>
+  <si>
+    <t>BALA GELATINA DIVERSAS</t>
+  </si>
+  <si>
+    <t>BALA GELATINA COBRINHA CITRICA</t>
   </si>
 </sst>
 </file>
@@ -4260,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -4306,7 +4306,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -4352,7 +4352,7 @@
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -4968,7 +4968,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -5469,7 +5469,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -5515,7 +5515,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -5538,7 +5538,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -5561,7 +5561,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6343,7 +6343,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F43" t="s">
         <v>9</v>
@@ -6504,7 +6504,7 @@
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -6573,7 +6573,7 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
@@ -6596,7 +6596,7 @@
         <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F54" t="s">
         <v>233</v>
@@ -6619,7 +6619,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F55" t="s">
         <v>9</v>
@@ -6642,7 +6642,7 @@
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F56" t="s">
         <v>233</v>
@@ -6665,7 +6665,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F57" t="s">
         <v>9</v>
@@ -6734,7 +6734,7 @@
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F60" t="s">
         <v>233</v>
@@ -6780,7 +6780,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F62" t="s">
         <v>9</v>
@@ -7447,7 +7447,7 @@
         <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="F91" t="s">
         <v>9</v>
@@ -7470,7 +7470,7 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -7493,7 +7493,7 @@
         <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -7516,7 +7516,7 @@
         <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -7654,7 +7654,7 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="F100" t="s">
         <v>9</v>
@@ -7677,7 +7677,7 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="F101" t="s">
         <v>9</v>
@@ -7700,7 +7700,7 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F102" t="s">
         <v>9</v>
@@ -7723,7 +7723,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F103" t="s">
         <v>9</v>
@@ -7746,7 +7746,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F104" t="s">
         <v>9</v>
@@ -7907,7 +7907,7 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="F111" t="s">
         <v>233</v>
@@ -7930,7 +7930,7 @@
         <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="F112" t="s">
         <v>233</v>
@@ -7953,7 +7953,7 @@
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F113" t="s">
         <v>233</v>
@@ -7976,7 +7976,7 @@
         <v>18</v>
       </c>
       <c r="E114" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="F114" t="s">
         <v>233</v>
@@ -7999,7 +7999,7 @@
         <v>15</v>
       </c>
       <c r="E115" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F115" t="s">
         <v>9</v>
@@ -8022,7 +8022,7 @@
         <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="F116" t="s">
         <v>9</v>
@@ -8086,7 +8086,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="F2" t="s">
         <v>233</v>
@@ -8109,7 +8109,7 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="F3" t="s">
         <v>233</v>
@@ -8132,7 +8132,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="F4" t="s">
         <v>233</v>
@@ -8155,7 +8155,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -8178,7 +8178,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -8201,7 +8201,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -8224,7 +8224,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -8247,7 +8247,7 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -8270,7 +8270,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -8334,7 +8334,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="F2" t="s">
         <v>233</v>
@@ -8357,7 +8357,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F3" t="s">
         <v>233</v>
@@ -8380,7 +8380,7 @@
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="F4" t="s">
         <v>233</v>
@@ -8403,7 +8403,7 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -8426,7 +8426,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -8449,7 +8449,7 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -8472,7 +8472,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -8536,7 +8536,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F2" t="s">
         <v>233</v>
@@ -8559,7 +8559,7 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F3" t="s">
         <v>233</v>
@@ -8582,7 +8582,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -8605,7 +8605,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -8628,7 +8628,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -8651,7 +8651,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -8674,7 +8674,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -8697,7 +8697,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -9515,7 +9515,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -9998,7 +9998,7 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -10021,7 +10021,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -10044,7 +10044,7 @@
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F33" t="s">
         <v>9</v>
@@ -10055,10 +10055,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>890</v>
+        <v>1103</v>
       </c>
       <c r="B34" t="s">
-        <v>891</v>
+        <v>1106</v>
       </c>
       <c r="C34">
         <v>4446</v>
@@ -10067,7 +10067,7 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -10078,10 +10078,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>892</v>
+        <v>1104</v>
       </c>
       <c r="B35" t="s">
-        <v>893</v>
+        <v>1105</v>
       </c>
       <c r="C35">
         <v>4476</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B36" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C36">
         <v>4348</v>
@@ -10113,7 +10113,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F36" t="s">
         <v>9</v>
@@ -10124,10 +10124,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B37" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="C37">
         <v>4456</v>
@@ -10136,7 +10136,7 @@
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -10147,10 +10147,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B38" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="C38">
         <v>4051</v>
@@ -10170,10 +10170,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B39" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="C39">
         <v>4408</v>
@@ -10193,10 +10193,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B40" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="C40">
         <v>4341</v>
@@ -10216,10 +10216,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B41" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C41">
         <v>4265</v>
@@ -10239,10 +10239,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B42" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C42">
         <v>4266</v>
@@ -10262,10 +10262,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B43" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C43">
         <v>4269</v>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B44" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C44">
         <v>4273</v>
@@ -10308,10 +10308,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B45" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C45">
         <v>4405</v>
@@ -10331,10 +10331,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B46" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C46">
         <v>4406</v>
@@ -10354,10 +10354,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B47" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C47">
         <v>4267</v>
@@ -10377,10 +10377,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B48" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C48">
         <v>4271</v>
@@ -10400,10 +10400,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B49" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C49">
         <v>4276</v>
@@ -10423,10 +10423,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B50" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C50">
         <v>4342</v>
@@ -10446,10 +10446,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B51" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C51">
         <v>4398</v>
@@ -10469,10 +10469,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B52" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C52">
         <v>4270</v>
@@ -10492,10 +10492,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B53" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C53">
         <v>4275</v>
@@ -10515,10 +10515,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B54" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="C54">
         <v>4274</v>
@@ -10538,10 +10538,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B55" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="C55">
         <v>4399</v>
@@ -10561,10 +10561,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B56" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="C56">
         <v>4404</v>
@@ -10584,10 +10584,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B57" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C57">
         <v>4262</v>
@@ -10607,10 +10607,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B58" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C58">
         <v>4263</v>
@@ -10630,10 +10630,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B59" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C59">
         <v>4264</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B60" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C60">
         <v>4407</v>
@@ -10676,10 +10676,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B61" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="C61">
         <v>4397</v>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B62" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="C62">
         <v>4343</v>
@@ -10722,10 +10722,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B63" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C63">
         <v>4268</v>
@@ -10745,10 +10745,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B64" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C64">
         <v>2833</v>
@@ -10768,10 +10768,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B65" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C65">
         <v>3125</v>
@@ -10791,10 +10791,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B66" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C66">
         <v>3752</v>
@@ -10814,10 +10814,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B67" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C67">
         <v>3753</v>
@@ -10837,10 +10837,10 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B68" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C68">
         <v>2511</v>
@@ -10860,10 +10860,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B69" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C69">
         <v>4311</v>
@@ -10883,10 +10883,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B70" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C70">
         <v>4046</v>
@@ -10906,10 +10906,10 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B71" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C71">
         <v>4047</v>
@@ -10929,10 +10929,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B72" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="C72">
         <v>4312</v>
@@ -10952,10 +10952,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B73" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C73">
         <v>4310</v>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B74" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C74">
         <v>4074</v>
@@ -10987,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
@@ -10998,10 +10998,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B75" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C75">
         <v>4076</v>
@@ -11010,10 +11010,10 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="F75" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G75">
         <v>32.5</v>
@@ -11021,10 +11021,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B76" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C76">
         <v>4133</v>
@@ -11033,10 +11033,10 @@
         <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F76" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G76">
         <v>72</v>
@@ -11044,10 +11044,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B77" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C77">
         <v>3068</v>
@@ -11067,10 +11067,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B78" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C78">
         <v>3087</v>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B79" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C79">
         <v>4560</v>
@@ -11113,10 +11113,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B80" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="C80">
         <v>4531</v>
@@ -11125,7 +11125,7 @@
         <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F80" t="s">
         <v>32</v>
@@ -11136,10 +11136,10 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B81" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="C81">
         <v>4532</v>
@@ -11159,10 +11159,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B82" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C82">
         <v>4559</v>
@@ -11171,7 +11171,7 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
@@ -11182,10 +11182,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B83" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="C83">
         <v>4493</v>
@@ -11205,10 +11205,10 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B84" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C84">
         <v>4102</v>
@@ -11217,7 +11217,7 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
@@ -11228,10 +11228,10 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B85" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C85">
         <v>4103</v>
@@ -11240,7 +11240,7 @@
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F85" t="s">
         <v>233</v>
@@ -11251,10 +11251,10 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B86" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C86">
         <v>4547</v>
@@ -11263,7 +11263,7 @@
         <v>10</v>
       </c>
       <c r="E86" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F86" t="s">
         <v>233</v>
@@ -11274,10 +11274,10 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="B87" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="C87">
         <v>4624</v>
@@ -11286,7 +11286,7 @@
         <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
@@ -11297,10 +11297,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="B88" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="C88">
         <v>4627</v>
@@ -11309,7 +11309,7 @@
         <v>25</v>
       </c>
       <c r="E88" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="F88" t="s">
         <v>13</v>
@@ -11320,10 +11320,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="B89" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="C89">
         <v>4628</v>
@@ -11332,7 +11332,7 @@
         <v>15</v>
       </c>
       <c r="E89" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="F89" t="s">
         <v>13</v>
@@ -11343,10 +11343,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="B90" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="C90">
         <v>4625</v>
@@ -11355,7 +11355,7 @@
         <v>21</v>
       </c>
       <c r="E90" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
@@ -11366,10 +11366,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="B91" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C91">
         <v>4626</v>
@@ -11378,7 +11378,7 @@
         <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="F91" t="s">
         <v>13</v>
@@ -11389,10 +11389,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B92" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="C92">
         <v>4629</v>
@@ -11401,7 +11401,7 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F92" t="s">
         <v>9</v>
@@ -11412,10 +11412,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="B93" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="C93">
         <v>4630</v>
@@ -11424,7 +11424,7 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="F93" t="s">
         <v>9</v>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B94" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="C94">
         <v>4104</v>
@@ -11447,7 +11447,7 @@
         <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F94" t="s">
         <v>233</v>
@@ -11458,10 +11458,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B95" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C95">
         <v>4101</v>
@@ -11470,7 +11470,7 @@
         <v>10</v>
       </c>
       <c r="E95" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F95" t="s">
         <v>233</v>
@@ -11481,10 +11481,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B96" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="C96">
         <v>4105</v>
@@ -11493,7 +11493,7 @@
         <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F96" t="s">
         <v>233</v>
@@ -11504,10 +11504,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B97" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C97">
         <v>3705</v>
@@ -11516,7 +11516,7 @@
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="F97" t="s">
         <v>233</v>
@@ -11527,10 +11527,10 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B98" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C98">
         <v>3823</v>
@@ -11539,7 +11539,7 @@
         <v>10</v>
       </c>
       <c r="E98" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F98" t="s">
         <v>9</v>
@@ -11550,10 +11550,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B99" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C99">
         <v>4583</v>
@@ -11562,7 +11562,7 @@
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F99" t="s">
         <v>233</v>
@@ -11573,10 +11573,10 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B100" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C100">
         <v>4308</v>
@@ -11585,7 +11585,7 @@
         <v>10</v>
       </c>
       <c r="E100" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
@@ -11596,10 +11596,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B101" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C101">
         <v>4309</v>
@@ -11608,10 +11608,10 @@
         <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="F101" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G101">
         <v>68.5</v>
@@ -11619,10 +11619,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B102" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C102">
         <v>4412</v>
@@ -11634,7 +11634,7 @@
         <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G102">
         <v>71.5</v>
@@ -11642,10 +11642,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B103" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C103">
         <v>4413</v>
@@ -11665,10 +11665,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B104" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C104">
         <v>4414</v>
@@ -11688,10 +11688,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B105" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C105">
         <v>4415</v>
@@ -11711,10 +11711,10 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B106" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C106">
         <v>4416</v>
@@ -11734,10 +11734,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="B107" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="C107">
         <v>4475</v>
@@ -11746,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F107" t="s">
         <v>13</v>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B108" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C108">
         <v>4354</v>
@@ -11769,7 +11769,7 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F108" t="s">
         <v>744</v>
@@ -11780,10 +11780,10 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B109" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C109">
         <v>4445</v>
@@ -11792,7 +11792,7 @@
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F109" t="s">
         <v>9</v>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="B110" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C110">
         <v>4353</v>
@@ -11815,7 +11815,7 @@
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F110" t="s">
         <v>9</v>
@@ -11826,10 +11826,10 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B111" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C111">
         <v>4350</v>
@@ -11838,7 +11838,7 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F111" t="s">
         <v>9</v>
@@ -11849,10 +11849,10 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="B112" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="C112">
         <v>4352</v>
@@ -11861,7 +11861,7 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F112" t="s">
         <v>9</v>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="B113" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C113">
         <v>4349</v>
@@ -11884,7 +11884,7 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F113" t="s">
         <v>9</v>
@@ -11895,10 +11895,10 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B114" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="C114">
         <v>4351</v>
@@ -11907,7 +11907,7 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F114" t="s">
         <v>9</v>
@@ -11918,10 +11918,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B115" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C115">
         <v>4581</v>
@@ -11930,7 +11930,7 @@
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F115" t="s">
         <v>9</v>
@@ -11941,10 +11941,10 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B116" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C116">
         <v>4096</v>
@@ -11964,10 +11964,10 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B117" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C117">
         <v>4123</v>
@@ -11976,7 +11976,7 @@
         <v>10</v>
       </c>
       <c r="E117" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="F117" t="s">
         <v>13</v>
@@ -11987,10 +11987,10 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B118" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C118">
         <v>4306</v>
@@ -11999,10 +11999,10 @@
         <v>10</v>
       </c>
       <c r="E118" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F118" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G118">
         <v>81</v>
@@ -12010,10 +12010,10 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B119" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C119">
         <v>4307</v>
@@ -12022,10 +12022,10 @@
         <v>10</v>
       </c>
       <c r="E119" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F119" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G119">
         <v>81</v>
@@ -12033,10 +12033,10 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B120" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C120">
         <v>2659</v>
@@ -12045,7 +12045,7 @@
         <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="F120" t="s">
         <v>233</v>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B121" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C121">
         <v>2621</v>
@@ -12068,7 +12068,7 @@
         <v>5</v>
       </c>
       <c r="E121" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="F121" t="s">
         <v>233</v>
@@ -12079,10 +12079,10 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="B122" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C122">
         <v>3656</v>
@@ -12091,7 +12091,7 @@
         <v>5</v>
       </c>
       <c r="E122" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F122" t="s">
         <v>233</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="B2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="C2">
         <v>3459</v>
@@ -12166,10 +12166,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="B3" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="C3">
         <v>3803</v>
@@ -12189,10 +12189,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="B4" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C4">
         <v>3425</v>
@@ -12212,10 +12212,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="B5" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C5">
         <v>3426</v>
@@ -12235,10 +12235,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="B6" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C6">
         <v>3427</v>
@@ -12258,10 +12258,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="B7" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C7">
         <v>3428</v>
@@ -12281,10 +12281,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="B8" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="C8">
         <v>3429</v>
@@ -12304,10 +12304,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="B9" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="C9">
         <v>3430</v>
@@ -12327,10 +12327,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="B10" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C10">
         <v>3913</v>
@@ -12350,10 +12350,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="B11" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C11">
         <v>3872</v>
@@ -12373,10 +12373,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B12" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="C12">
         <v>3422</v>
@@ -12396,10 +12396,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B13" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="C13">
         <v>3423</v>
@@ -12408,7 +12408,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -12419,10 +12419,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B14" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C14">
         <v>3431</v>
@@ -12442,10 +12442,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C15">
         <v>3432</v>
@@ -12509,7 +12509,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C2">
         <v>585</v>
@@ -12532,7 +12532,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="C3">
         <v>467</v>
@@ -13541,7 +13541,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="B47" t="s">
         <v>59</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="B48" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="C48">
         <v>2466</v>
@@ -16447,10 +16447,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="B49" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="C49">
         <v>2465</v>
@@ -17466,7 +17466,7 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -17535,7 +17535,7 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -18294,7 +18294,7 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="F53" t="s">
         <v>233</v>
@@ -18363,7 +18363,7 @@
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="F56" t="s">
         <v>233</v>
@@ -18570,7 +18570,7 @@
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F65" t="s">
         <v>233</v>
@@ -21251,7 +21251,7 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -21274,7 +21274,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -22465,7 +22465,7 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F32" t="s">
         <v>9</v>
@@ -22488,7 +22488,7 @@
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -22511,7 +22511,7 @@
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F34" t="s">
         <v>9</v>
@@ -22534,7 +22534,7 @@
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F35" t="s">
         <v>9</v>
@@ -22580,7 +22580,7 @@
         <v>30</v>
       </c>
       <c r="E37" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -22626,7 +22626,7 @@
         <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -23247,7 +23247,7 @@
         <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9C33E3-851A-44B5-9B12-F5FC2576BA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E48348-D186-4370-81E1-91703B074A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -22563,7 +22563,7 @@
         <v>32</v>
       </c>
       <c r="G36">
-        <v>28.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -22586,7 +22586,7 @@
         <v>233</v>
       </c>
       <c r="G37">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -22609,7 +22609,7 @@
         <v>32</v>
       </c>
       <c r="G38">
-        <v>30.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -22632,7 +22632,7 @@
         <v>233</v>
       </c>
       <c r="G39">
-        <v>42.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E48348-D186-4370-81E1-91703B074A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F2E9D9-8B07-40F2-8BE4-9131FB929469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="1109">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3358,6 +3358,12 @@
   </si>
   <si>
     <t>BALA GELATINA COBRINHA CITRICA</t>
+  </si>
+  <si>
+    <t>gota-chocolate-branco</t>
+  </si>
+  <si>
+    <t>GOTA CHOCOLATE BRANCO</t>
   </si>
 </sst>
 </file>
@@ -9283,7 +9289,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11619,48 +11625,48 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>999</v>
+        <v>1107</v>
       </c>
       <c r="B102" t="s">
-        <v>1000</v>
+        <v>1108</v>
       </c>
       <c r="C102">
-        <v>4412</v>
+        <v>4635</v>
       </c>
       <c r="D102">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
-        <v>8</v>
+        <v>1069</v>
       </c>
       <c r="F102" t="s">
         <v>964</v>
       </c>
       <c r="G102">
-        <v>71.5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B103" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C103">
-        <v>4413</v>
+        <v>4412</v>
       </c>
       <c r="D103">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>964</v>
       </c>
       <c r="G103">
-        <v>496</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -11671,10 +11677,10 @@
         <v>1002</v>
       </c>
       <c r="C104">
-        <v>4414</v>
+        <v>4413</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -11683,21 +11689,21 @@
         <v>13</v>
       </c>
       <c r="G104">
-        <v>101</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B105" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C105">
-        <v>4415</v>
+        <v>4414</v>
       </c>
       <c r="D105">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -11706,7 +11712,7 @@
         <v>13</v>
       </c>
       <c r="G105">
-        <v>414</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -11717,10 +11723,10 @@
         <v>1004</v>
       </c>
       <c r="C106">
-        <v>4416</v>
+        <v>4415</v>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -11729,64 +11735,64 @@
         <v>13</v>
       </c>
       <c r="G106">
-        <v>85</v>
+        <v>414</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B107" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C107">
-        <v>4475</v>
+        <v>4416</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E107" t="s">
-        <v>1079</v>
+        <v>8</v>
       </c>
       <c r="F107" t="s">
         <v>13</v>
       </c>
       <c r="G107">
-        <v>9</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B108" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C108">
-        <v>4354</v>
+        <v>4475</v>
       </c>
       <c r="D108">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E108" t="s">
         <v>1079</v>
       </c>
       <c r="F108" t="s">
-        <v>744</v>
+        <v>13</v>
       </c>
       <c r="G108">
-        <v>79.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B109" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C109">
-        <v>4445</v>
+        <v>4354</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -11795,7 +11801,7 @@
         <v>1079</v>
       </c>
       <c r="F109" t="s">
-        <v>9</v>
+        <v>744</v>
       </c>
       <c r="G109">
         <v>79.5</v>
@@ -11803,13 +11809,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B110" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C110">
-        <v>4353</v>
+        <v>4445</v>
       </c>
       <c r="D110">
         <v>12</v>
@@ -11826,13 +11832,13 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B111" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C111">
-        <v>4350</v>
+        <v>4353</v>
       </c>
       <c r="D111">
         <v>12</v>
@@ -11849,13 +11855,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B112" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C112">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="D112">
         <v>12</v>
@@ -11872,13 +11878,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B113" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C113">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="D113">
         <v>12</v>
@@ -11895,13 +11901,13 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B114" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C114">
-        <v>4351</v>
+        <v>4349</v>
       </c>
       <c r="D114">
         <v>12</v>
@@ -11918,13 +11924,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B115" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C115">
-        <v>4581</v>
+        <v>4351</v>
       </c>
       <c r="D115">
         <v>12</v>
@@ -11941,82 +11947,82 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B116" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C116">
-        <v>4096</v>
+        <v>4581</v>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>8</v>
+        <v>1079</v>
       </c>
       <c r="F116" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G116">
-        <v>79</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B117" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C117">
-        <v>4123</v>
+        <v>4096</v>
       </c>
       <c r="D117">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E117" t="s">
-        <v>1072</v>
+        <v>8</v>
       </c>
       <c r="F117" t="s">
         <v>13</v>
       </c>
       <c r="G117">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B118" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C118">
-        <v>4306</v>
+        <v>4123</v>
       </c>
       <c r="D118">
         <v>10</v>
       </c>
       <c r="E118" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F118" t="s">
-        <v>964</v>
+        <v>13</v>
       </c>
       <c r="G118">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B119" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C119">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D119">
         <v>10</v>
@@ -12033,25 +12039,25 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B120" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C120">
-        <v>2659</v>
+        <v>4307</v>
       </c>
       <c r="D120">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F120" t="s">
-        <v>233</v>
+        <v>964</v>
       </c>
       <c r="G120">
-        <v>27.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -12062,41 +12068,64 @@
         <v>1032</v>
       </c>
       <c r="C121">
-        <v>2621</v>
+        <v>2659</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E121" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F121" t="s">
         <v>233</v>
       </c>
       <c r="G121">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B122" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C122">
-        <v>3656</v>
+        <v>2621</v>
       </c>
       <c r="D122">
         <v>5</v>
       </c>
       <c r="E122" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="F122" t="s">
         <v>233</v>
       </c>
       <c r="G122">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C123">
+        <v>3656</v>
+      </c>
+      <c r="D123">
+        <v>5</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F123" t="s">
+        <v>233</v>
+      </c>
+      <c r="G123">
         <v>27</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F2E9D9-8B07-40F2-8BE4-9131FB929469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6882F4-80E7-4F65-8F01-737765A93534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="1109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="1109">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -12499,7 +12499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -13864,7 +13864,7 @@
         <v>13</v>
       </c>
       <c r="G59">
-        <v>652</v>
+        <v>457</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -13875,30 +13875,30 @@
         <v>69</v>
       </c>
       <c r="C60">
-        <v>3520</v>
+        <v>2291</v>
       </c>
       <c r="D60">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G60">
-        <v>1300</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C61">
-        <v>2291</v>
+        <v>3534</v>
       </c>
       <c r="D61">
         <v>20</v>
@@ -13910,7 +13910,7 @@
         <v>9</v>
       </c>
       <c r="G61">
-        <v>2600</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -13921,30 +13921,30 @@
         <v>71</v>
       </c>
       <c r="C62">
-        <v>3534</v>
+        <v>2250</v>
       </c>
       <c r="D62">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G62">
-        <v>1700</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C63">
-        <v>2250</v>
+        <v>2340</v>
       </c>
       <c r="D63">
         <v>5</v>
@@ -13956,7 +13956,7 @@
         <v>13</v>
       </c>
       <c r="G63">
-        <v>427</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -13967,30 +13967,30 @@
         <v>73</v>
       </c>
       <c r="C64">
-        <v>2340</v>
+        <v>3533</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G64">
-        <v>417</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C65">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D65">
         <v>20</v>
@@ -14002,7 +14002,7 @@
         <v>9</v>
       </c>
       <c r="G65">
-        <v>1660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -14013,33 +14013,33 @@
         <v>75</v>
       </c>
       <c r="C66">
-        <v>3532</v>
+        <v>2251</v>
       </c>
       <c r="D66">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G66">
-        <v>1440</v>
+        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C67">
-        <v>2251</v>
+        <v>3081</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -14048,7 +14048,7 @@
         <v>13</v>
       </c>
       <c r="G67">
-        <v>362</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -14059,10 +14059,10 @@
         <v>77</v>
       </c>
       <c r="C68">
-        <v>3081</v>
+        <v>3818</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -14071,18 +14071,18 @@
         <v>13</v>
       </c>
       <c r="G68">
-        <v>135</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C69">
-        <v>3818</v>
+        <v>2534</v>
       </c>
       <c r="D69">
         <v>5</v>
@@ -14105,10 +14105,10 @@
         <v>79</v>
       </c>
       <c r="C70">
-        <v>2534</v>
+        <v>2234</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -14117,18 +14117,18 @@
         <v>13</v>
       </c>
       <c r="G70">
-        <v>69.5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C71">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="D71">
         <v>10</v>
@@ -14148,13 +14148,13 @@
         <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C72">
-        <v>2238</v>
+        <v>2535</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -14163,21 +14163,21 @@
         <v>13</v>
       </c>
       <c r="G72">
-        <v>135</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C73">
-        <v>2535</v>
+        <v>2512</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -14186,7 +14186,7 @@
         <v>13</v>
       </c>
       <c r="G73">
-        <v>69.5</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -14197,10 +14197,10 @@
         <v>84</v>
       </c>
       <c r="C74">
-        <v>2512</v>
+        <v>2537</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -14209,21 +14209,21 @@
         <v>13</v>
       </c>
       <c r="G74">
-        <v>166</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C75">
-        <v>2537</v>
+        <v>2236</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -14232,7 +14232,7 @@
         <v>13</v>
       </c>
       <c r="G75">
-        <v>83</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -14243,10 +14243,10 @@
         <v>86</v>
       </c>
       <c r="C76">
-        <v>2236</v>
+        <v>2546</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -14255,21 +14255,21 @@
         <v>13</v>
       </c>
       <c r="G76">
-        <v>135</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C77">
-        <v>2546</v>
+        <v>2232</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -14278,7 +14278,7 @@
         <v>13</v>
       </c>
       <c r="G77">
-        <v>69.5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14289,10 +14289,10 @@
         <v>88</v>
       </c>
       <c r="C78">
-        <v>2232</v>
+        <v>2536</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -14301,41 +14301,41 @@
         <v>13</v>
       </c>
       <c r="G78">
-        <v>135</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C79">
-        <v>2536</v>
+        <v>3815</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G79">
-        <v>69.5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C80">
-        <v>3815</v>
+        <v>3713</v>
       </c>
       <c r="D80">
         <v>10</v>
@@ -14344,7 +14344,7 @@
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G80">
         <v>125</v>
@@ -14352,13 +14352,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C81">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="D81">
         <v>10</v>
@@ -14367,7 +14367,7 @@
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G81">
         <v>125</v>
@@ -14375,13 +14375,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C82">
-        <v>3712</v>
+        <v>3714</v>
       </c>
       <c r="D82">
         <v>10</v>
@@ -14390,7 +14390,7 @@
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G82">
         <v>125</v>
@@ -14398,13 +14398,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C83">
-        <v>3714</v>
+        <v>3715</v>
       </c>
       <c r="D83">
         <v>10</v>
@@ -14413,7 +14413,7 @@
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G83">
         <v>125</v>
@@ -14421,22 +14421,22 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C84">
-        <v>3715</v>
+        <v>4021</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G84">
         <v>125</v>
@@ -14450,42 +14450,42 @@
         <v>100</v>
       </c>
       <c r="C85">
-        <v>4021</v>
+        <v>4135</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G85">
-        <v>125</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C86">
-        <v>4135</v>
+        <v>2852</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G86">
-        <v>1250</v>
+        <v>325</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -14496,10 +14496,10 @@
         <v>102</v>
       </c>
       <c r="C87">
-        <v>2852</v>
+        <v>3601</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -14508,30 +14508,30 @@
         <v>13</v>
       </c>
       <c r="G87">
-        <v>325</v>
+        <v>650</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C88">
-        <v>3601</v>
+        <v>3093</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G88">
-        <v>650</v>
+        <v>693</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -14542,42 +14542,42 @@
         <v>104</v>
       </c>
       <c r="C89">
-        <v>3093</v>
+        <v>2632</v>
       </c>
       <c r="D89">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G89">
-        <v>693</v>
+        <v>317</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C90">
-        <v>2632</v>
+        <v>4179</v>
       </c>
       <c r="D90">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G90">
-        <v>317</v>
+        <v>572</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -14588,10 +14588,10 @@
         <v>106</v>
       </c>
       <c r="C91">
-        <v>4179</v>
+        <v>2330</v>
       </c>
       <c r="D91">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -14600,7 +14600,7 @@
         <v>9</v>
       </c>
       <c r="G91">
-        <v>572</v>
+        <v>520</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -14611,42 +14611,42 @@
         <v>106</v>
       </c>
       <c r="C92">
-        <v>2330</v>
+        <v>2385</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G92">
-        <v>520</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C93">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G93">
-        <v>262</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -14657,19 +14657,19 @@
         <v>108</v>
       </c>
       <c r="C94">
-        <v>2384</v>
+        <v>3851</v>
       </c>
       <c r="D94">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G94">
-        <v>187.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -14680,41 +14680,18 @@
         <v>108</v>
       </c>
       <c r="C95">
-        <v>3851</v>
+        <v>2424</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
       </c>
       <c r="F95" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G95">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>107</v>
-      </c>
-      <c r="B96" t="s">
-        <v>108</v>
-      </c>
-      <c r="C96">
-        <v>2424</v>
-      </c>
-      <c r="D96">
-        <v>5</v>
-      </c>
-      <c r="E96" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96">
         <v>39.5</v>
       </c>
     </row>
@@ -15413,7 +15390,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -15436,7 +15413,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -20003,7 +19980,7 @@
         <v>32</v>
       </c>
       <c r="G54">
-        <v>270</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -20026,7 +20003,7 @@
         <v>32</v>
       </c>
       <c r="G55">
-        <v>135</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -20049,7 +20026,7 @@
         <v>13</v>
       </c>
       <c r="G56">
-        <v>24.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6882F4-80E7-4F65-8F01-737765A93534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F583BD-A60C-4DAD-BC6E-905FC1C3107E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -4410,7 +4410,7 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F583BD-A60C-4DAD-BC6E-905FC1C3107E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B73CEB-260B-4B6F-9A2C-3F9C500AFC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="1109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3602" uniqueCount="1113">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3364,6 +3364,18 @@
   </si>
   <si>
     <t>GOTA CHOCOLATE BRANCO</t>
+  </si>
+  <si>
+    <t>flocos-de-arroz</t>
+  </si>
+  <si>
+    <t>FLOCOS DE ARROZ</t>
+  </si>
+  <si>
+    <t>ameixa-em-po</t>
+  </si>
+  <si>
+    <t>AMEIXA EM PÓ</t>
   </si>
 </sst>
 </file>
@@ -5358,7 +5370,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5550,7 +5562,7 @@
         <v>233</v>
       </c>
       <c r="G8">
-        <v>57.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5573,7 +5585,7 @@
         <v>233</v>
       </c>
       <c r="G9">
-        <v>65</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5596,7 +5608,7 @@
         <v>233</v>
       </c>
       <c r="G10">
-        <v>141.5</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5762,25 +5774,25 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>654</v>
+        <v>1111</v>
       </c>
       <c r="B18" t="s">
-        <v>655</v>
+        <v>1112</v>
       </c>
       <c r="C18">
-        <v>2336</v>
+        <v>4639</v>
       </c>
       <c r="D18">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>750</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5791,42 +5803,42 @@
         <v>655</v>
       </c>
       <c r="C19">
-        <v>2421</v>
+        <v>2336</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G19">
-        <v>91</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B20" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C20">
-        <v>2568</v>
+        <v>2421</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>260</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5837,53 +5849,53 @@
         <v>657</v>
       </c>
       <c r="C21">
-        <v>3009</v>
+        <v>2568</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G21">
-        <v>78</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B22" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C22">
-        <v>2778</v>
+        <v>3009</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>180</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B23" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C23">
-        <v>3106</v>
+        <v>2778</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -5892,33 +5904,33 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G23">
-        <v>260</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B24" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C24">
-        <v>3489</v>
+        <v>3106</v>
       </c>
       <c r="D24">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>700</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -5929,10 +5941,10 @@
         <v>663</v>
       </c>
       <c r="C25">
-        <v>3696</v>
+        <v>3489</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -5941,7 +5953,7 @@
         <v>32</v>
       </c>
       <c r="G25">
-        <v>280</v>
+        <v>700</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5952,19 +5964,19 @@
         <v>663</v>
       </c>
       <c r="C26">
-        <v>2783</v>
+        <v>3696</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G26">
-        <v>142</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5975,10 +5987,10 @@
         <v>663</v>
       </c>
       <c r="C27">
-        <v>3755</v>
+        <v>2783</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -5987,30 +5999,30 @@
         <v>13</v>
       </c>
       <c r="G27">
-        <v>85</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B28" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C28">
-        <v>3486</v>
+        <v>3755</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G28">
-        <v>595</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -6021,33 +6033,33 @@
         <v>665</v>
       </c>
       <c r="C29">
-        <v>4488</v>
+        <v>3486</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G29">
-        <v>299.5</v>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B30" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C30">
-        <v>4333</v>
+        <v>3487</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -6056,18 +6068,18 @@
         <v>13</v>
       </c>
       <c r="G30">
-        <v>259.5</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B31" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C31">
-        <v>4388</v>
+        <v>4488</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -6079,18 +6091,18 @@
         <v>13</v>
       </c>
       <c r="G31">
-        <v>145</v>
+        <v>299.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B32" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C32">
-        <v>4389</v>
+        <v>4333</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -6102,41 +6114,41 @@
         <v>13</v>
       </c>
       <c r="G32">
-        <v>102</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B33" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C33">
-        <v>3488</v>
+        <v>4388</v>
       </c>
       <c r="D33">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G33">
-        <v>220</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B34" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C34">
-        <v>3400</v>
+        <v>4389</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -6148,64 +6160,64 @@
         <v>13</v>
       </c>
       <c r="G34">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B35" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C35">
-        <v>2257</v>
+        <v>3488</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G35">
-        <v>16</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B36" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C36">
-        <v>565</v>
+        <v>3400</v>
       </c>
       <c r="D36">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G36">
-        <v>123</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B37" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C37">
-        <v>4474</v>
+        <v>2257</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -6217,41 +6229,41 @@
         <v>13</v>
       </c>
       <c r="G37">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B38" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C38">
-        <v>4473</v>
+        <v>565</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G38">
-        <v>39</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B39" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C39">
-        <v>2658</v>
+        <v>4474</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -6268,13 +6280,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B40" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C40">
-        <v>2657</v>
+        <v>4473</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -6291,16 +6303,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B41" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C41">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -6309,21 +6321,21 @@
         <v>13</v>
       </c>
       <c r="G41">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B42" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C42">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -6332,251 +6344,251 @@
         <v>13</v>
       </c>
       <c r="G42">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B43" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C43">
-        <v>3537</v>
+        <v>2657</v>
       </c>
       <c r="D43">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>1051</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G43">
-        <v>162</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="B44" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="C44">
-        <v>2732</v>
+        <v>2658</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G44">
-        <v>189</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>688</v>
+        <v>1109</v>
       </c>
       <c r="B45" t="s">
-        <v>689</v>
+        <v>1110</v>
       </c>
       <c r="C45">
-        <v>2733</v>
+        <v>4640</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F45" t="s">
         <v>13</v>
       </c>
       <c r="G45">
-        <v>96.5</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B46" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C46">
-        <v>2584</v>
+        <v>3537</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F46" t="s">
         <v>9</v>
       </c>
       <c r="G46">
-        <v>223</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B47" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C47">
-        <v>2677</v>
+        <v>2732</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G47">
-        <v>113.5</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B48" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C48">
-        <v>2495</v>
+        <v>2733</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G48">
-        <v>220</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B49" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C49">
-        <v>2678</v>
+        <v>2584</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G49">
-        <v>112</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B50" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C50">
-        <v>4498</v>
+        <v>2677</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>1051</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G50">
-        <v>240</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B51" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C51">
-        <v>4253</v>
+        <v>2495</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G51">
-        <v>112</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B52" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C52">
-        <v>4500</v>
+        <v>2678</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G52">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B53" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C53">
-        <v>4249</v>
+        <v>4498</v>
       </c>
       <c r="D53">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>1051</v>
@@ -6585,7 +6597,7 @@
         <v>233</v>
       </c>
       <c r="G53">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -6596,56 +6608,56 @@
         <v>697</v>
       </c>
       <c r="C54">
-        <v>3724</v>
+        <v>4253</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>1051</v>
+        <v>8</v>
       </c>
       <c r="F54" t="s">
         <v>233</v>
       </c>
       <c r="G54">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B55" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C55">
-        <v>3736</v>
+        <v>4500</v>
       </c>
       <c r="D55">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>1051</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="G55">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B56" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C56">
-        <v>4499</v>
+        <v>4249</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>1051</v>
@@ -6654,110 +6666,110 @@
         <v>233</v>
       </c>
       <c r="G56">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="B57" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C57">
-        <v>3536</v>
+        <v>3724</v>
       </c>
       <c r="D57">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E57" t="s">
         <v>1051</v>
       </c>
       <c r="F57" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="G57">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B58" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C58">
-        <v>2494</v>
+        <v>3736</v>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F58" t="s">
         <v>9</v>
       </c>
       <c r="G58">
-        <v>188.5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B59" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C59">
-        <v>2679</v>
+        <v>4499</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G59">
-        <v>96</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B60" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C60">
-        <v>4497</v>
+        <v>3536</v>
       </c>
       <c r="D60">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E60" t="s">
         <v>1051</v>
       </c>
       <c r="F60" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G60">
-        <v>240</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B61" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C61">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="D61">
         <v>10</v>
@@ -6769,205 +6781,205 @@
         <v>9</v>
       </c>
       <c r="G61">
-        <v>180</v>
+        <v>188.5</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B62" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C62">
-        <v>3535</v>
+        <v>2679</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>1051</v>
+        <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G62">
-        <v>162</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B63" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C63">
-        <v>2498</v>
+        <v>4497</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G63">
-        <v>92</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B64" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C64">
-        <v>2806</v>
+        <v>2493</v>
       </c>
       <c r="D64">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G64">
-        <v>472.5</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B65" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C65">
-        <v>2807</v>
+        <v>3535</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
       </c>
       <c r="G65">
-        <v>159.5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="B66" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="C66">
-        <v>4556</v>
+        <v>2498</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G66">
-        <v>900</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B67" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C67">
-        <v>4557</v>
+        <v>2806</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="G67">
-        <v>182</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B68" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C68">
-        <v>4018</v>
+        <v>2807</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G68">
-        <v>230</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B69" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C69">
-        <v>2652</v>
+        <v>4556</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G69">
-        <v>117</v>
+        <v>900</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B70" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C70">
-        <v>4049</v>
+        <v>4557</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -6976,21 +6988,21 @@
         <v>13</v>
       </c>
       <c r="G70">
-        <v>210</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B71" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C71">
-        <v>3737</v>
+        <v>4018</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -6999,21 +7011,21 @@
         <v>13</v>
       </c>
       <c r="G71">
-        <v>107</v>
+        <v>230</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B72" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C72">
-        <v>4301</v>
+        <v>2652</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -7022,21 +7034,21 @@
         <v>13</v>
       </c>
       <c r="G72">
-        <v>235</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B73" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C73">
-        <v>4334</v>
+        <v>4049</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -7045,44 +7057,44 @@
         <v>13</v>
       </c>
       <c r="G73">
-        <v>376.5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="B74" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C74">
-        <v>195</v>
+        <v>3737</v>
       </c>
       <c r="D74">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G74">
-        <v>255</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B75" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C75">
-        <v>54</v>
+        <v>4301</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -7091,113 +7103,113 @@
         <v>13</v>
       </c>
       <c r="G75">
-        <v>53</v>
+        <v>235</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B76" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C76">
-        <v>63</v>
+        <v>4334</v>
       </c>
       <c r="D76">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G76">
-        <v>255</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B77" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C77">
-        <v>2483</v>
+        <v>195</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G77">
-        <v>53</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B78" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C78">
-        <v>2974</v>
+        <v>54</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G78">
-        <v>250</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B79" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C79">
-        <v>2831</v>
+        <v>63</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G79">
-        <v>127</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B80" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="C80">
-        <v>4137</v>
+        <v>2483</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -7206,41 +7218,41 @@
         <v>13</v>
       </c>
       <c r="G80">
-        <v>270</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B81" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C81">
-        <v>4380</v>
+        <v>2974</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G81">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B82" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C82">
-        <v>4566</v>
+        <v>2831</v>
       </c>
       <c r="D82">
         <v>5</v>
@@ -7252,21 +7264,21 @@
         <v>13</v>
       </c>
       <c r="G82">
-        <v>240</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="B83" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C83">
-        <v>4567</v>
+        <v>4137</v>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -7275,21 +7287,21 @@
         <v>13</v>
       </c>
       <c r="G83">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B84" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C84">
-        <v>4204</v>
+        <v>4380</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -7298,44 +7310,44 @@
         <v>13</v>
       </c>
       <c r="G84">
-        <v>145.5</v>
+        <v>270</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B85" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C85">
-        <v>4205</v>
+        <v>4566</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G85">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B86" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C86">
-        <v>4225</v>
+        <v>4567</v>
       </c>
       <c r="D86">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -7344,44 +7356,44 @@
         <v>13</v>
       </c>
       <c r="G86">
-        <v>900</v>
+        <v>240</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B87" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C87">
-        <v>4378</v>
+        <v>4204</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G87">
-        <v>430</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B88" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C88">
-        <v>4379</v>
+        <v>4205</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -7390,228 +7402,228 @@
         <v>32</v>
       </c>
       <c r="G88">
-        <v>43</v>
+        <v>360</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B89" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C89">
-        <v>3524</v>
+        <v>4225</v>
       </c>
       <c r="D89">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>744</v>
+        <v>13</v>
       </c>
       <c r="G89">
-        <v>350</v>
+        <v>900</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B90" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C90">
-        <v>3523</v>
+        <v>4378</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>744</v>
+        <v>32</v>
       </c>
       <c r="G90">
-        <v>72</v>
+        <v>430</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B91" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C91">
-        <v>3521</v>
+        <v>4379</v>
       </c>
       <c r="D91">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>1078</v>
+        <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G91">
-        <v>158</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B92" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C92">
-        <v>3522</v>
+        <v>3524</v>
       </c>
       <c r="D92">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E92" t="s">
-        <v>1069</v>
+        <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>9</v>
+        <v>744</v>
       </c>
       <c r="G92">
-        <v>216.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B93" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C93">
-        <v>64</v>
+        <v>3523</v>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E93" t="s">
-        <v>1051</v>
+        <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>9</v>
+        <v>744</v>
       </c>
       <c r="G93">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B94" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C94">
-        <v>90</v>
+        <v>3521</v>
       </c>
       <c r="D94">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E94" t="s">
-        <v>1051</v>
+        <v>1078</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
       </c>
       <c r="G94">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="B95" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C95">
-        <v>3637</v>
+        <v>3522</v>
       </c>
       <c r="D95">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>8</v>
+        <v>1069</v>
       </c>
       <c r="F95" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G95">
-        <v>375</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B96" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C96">
-        <v>2805</v>
+        <v>64</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F96" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G96">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B97" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C97">
-        <v>2427</v>
+        <v>90</v>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>8</v>
+        <v>1051</v>
       </c>
       <c r="F97" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G97">
-        <v>46</v>
+        <v>132</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B98" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C98">
-        <v>3437</v>
+        <v>3637</v>
       </c>
       <c r="D98">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -7620,251 +7632,251 @@
         <v>32</v>
       </c>
       <c r="G98">
-        <v>390</v>
+        <v>375</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B99" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C99">
-        <v>3396</v>
+        <v>2805</v>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
       </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G99">
-        <v>197</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B100" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C100">
-        <v>3395</v>
+        <v>2427</v>
       </c>
       <c r="D100">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E100" t="s">
-        <v>1054</v>
+        <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G100">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B101" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C101">
-        <v>3490</v>
+        <v>3437</v>
       </c>
       <c r="D101">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>1054</v>
+        <v>8</v>
       </c>
       <c r="F101" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G101">
-        <v>169</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="B102" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C102">
-        <v>458</v>
+        <v>3396</v>
       </c>
       <c r="D102">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E102" t="s">
-        <v>1055</v>
+        <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G102">
-        <v>269.5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B103" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C103">
-        <v>2641</v>
+        <v>3395</v>
       </c>
       <c r="D103">
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F103" t="s">
         <v>9</v>
       </c>
       <c r="G103">
-        <v>222</v>
+        <v>54</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B104" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C104">
-        <v>4293</v>
+        <v>3490</v>
       </c>
       <c r="D104">
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F104" t="s">
         <v>9</v>
       </c>
       <c r="G104">
-        <v>210</v>
+        <v>169</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B105" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C105">
-        <v>2396</v>
+        <v>458</v>
       </c>
       <c r="D105">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>8</v>
+        <v>1055</v>
       </c>
       <c r="F105" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G105">
-        <v>675</v>
+        <v>269.5</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B106" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C106">
-        <v>2426</v>
+        <v>2641</v>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>8</v>
+        <v>1055</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G106">
-        <v>137</v>
+        <v>222</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B107" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C107">
-        <v>4335</v>
+        <v>4293</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>8</v>
+        <v>1055</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G107">
-        <v>440</v>
+        <v>210</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B108" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C108">
-        <v>4477</v>
+        <v>2396</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G108">
-        <v>252</v>
+        <v>675</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B109" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C109">
-        <v>4479</v>
+        <v>2426</v>
       </c>
       <c r="D109">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -7873,18 +7885,18 @@
         <v>13</v>
       </c>
       <c r="G109">
-        <v>252</v>
+        <v>137</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B110" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="C110">
-        <v>4478</v>
+        <v>4335</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -7896,144 +7908,213 @@
         <v>13</v>
       </c>
       <c r="G110">
-        <v>252</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="B111" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="C111">
-        <v>2646</v>
+        <v>4477</v>
       </c>
       <c r="D111">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E111" t="s">
-        <v>1056</v>
+        <v>8</v>
       </c>
       <c r="F111" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G111">
-        <v>50.5</v>
+        <v>252</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B112" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C112">
-        <v>2645</v>
+        <v>4479</v>
       </c>
       <c r="D112">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E112" t="s">
-        <v>1057</v>
+        <v>8</v>
       </c>
       <c r="F112" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G112">
-        <v>78</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B113" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C113">
-        <v>2638</v>
+        <v>4478</v>
       </c>
       <c r="D113">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E113" t="s">
-        <v>1058</v>
+        <v>8</v>
       </c>
       <c r="F113" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G113">
-        <v>65</v>
+        <v>252</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B114" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C114">
-        <v>4294</v>
+        <v>2646</v>
       </c>
       <c r="D114">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="F114" t="s">
         <v>233</v>
       </c>
       <c r="G114">
-        <v>150</v>
+        <v>53</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B115" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C115">
-        <v>4314</v>
+        <v>2645</v>
       </c>
       <c r="D115">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E115" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="F115" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="G115">
-        <v>252</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>775</v>
+      </c>
+      <c r="B116" t="s">
+        <v>776</v>
+      </c>
+      <c r="C116">
+        <v>2638</v>
+      </c>
+      <c r="D116">
+        <v>9</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F116" t="s">
+        <v>233</v>
+      </c>
+      <c r="G116">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>777</v>
+      </c>
+      <c r="B117" t="s">
+        <v>778</v>
+      </c>
+      <c r="C117">
+        <v>4294</v>
+      </c>
+      <c r="D117">
+        <v>18</v>
+      </c>
+      <c r="E117" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F117" t="s">
+        <v>233</v>
+      </c>
+      <c r="G117">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>779</v>
+      </c>
+      <c r="B118" t="s">
+        <v>780</v>
+      </c>
+      <c r="C118">
+        <v>4314</v>
+      </c>
+      <c r="D118">
+        <v>15</v>
+      </c>
+      <c r="E118" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F118" t="s">
+        <v>9</v>
+      </c>
+      <c r="G118">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>781</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B119" t="s">
         <v>782</v>
       </c>
-      <c r="C116">
+      <c r="C119">
         <v>4315</v>
       </c>
-      <c r="D116">
+      <c r="D119">
         <v>15</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E119" t="s">
         <v>1060</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F119" t="s">
         <v>9</v>
       </c>
-      <c r="G116">
+      <c r="G119">
         <v>450</v>
       </c>
     </row>
@@ -12080,7 +12161,7 @@
         <v>233</v>
       </c>
       <c r="G121">
-        <v>27.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -12103,7 +12184,7 @@
         <v>233</v>
       </c>
       <c r="G122">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B73CEB-260B-4B6F-9A2C-3F9C500AFC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4264EEB-64F0-4D88-AEEA-69FF97D773BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3602" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3606" uniqueCount="1116">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3376,6 +3376,15 @@
   </si>
   <si>
     <t>AMEIXA EM PÓ</t>
+  </si>
+  <si>
+    <t>pacoca-de-amendoim-espeto</t>
+  </si>
+  <si>
+    <t>PAÇOCA DE AMENDOIM ESPETO</t>
+  </si>
+  <si>
+    <t>X90G</t>
   </si>
 </sst>
 </file>
@@ -9370,7 +9379,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11747,7 +11756,7 @@
         <v>964</v>
       </c>
       <c r="G103">
-        <v>71.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -12074,59 +12083,59 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1025</v>
+        <v>1113</v>
       </c>
       <c r="B118" t="s">
-        <v>1026</v>
+        <v>1114</v>
       </c>
       <c r="C118">
-        <v>4123</v>
+        <v>4582</v>
       </c>
       <c r="D118">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E118" t="s">
-        <v>1072</v>
+        <v>1115</v>
       </c>
       <c r="F118" t="s">
         <v>13</v>
       </c>
       <c r="G118">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B119" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C119">
-        <v>4306</v>
+        <v>4123</v>
       </c>
       <c r="D119">
         <v>10</v>
       </c>
       <c r="E119" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F119" t="s">
-        <v>964</v>
+        <v>13</v>
       </c>
       <c r="G119">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B120" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C120">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D120">
         <v>10</v>
@@ -12143,25 +12152,25 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B121" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C121">
-        <v>2659</v>
+        <v>4307</v>
       </c>
       <c r="D121">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E121" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F121" t="s">
-        <v>233</v>
+        <v>964</v>
       </c>
       <c r="G121">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -12172,41 +12181,64 @@
         <v>1032</v>
       </c>
       <c r="C122">
-        <v>2621</v>
+        <v>2659</v>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E122" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F122" t="s">
         <v>233</v>
       </c>
       <c r="G122">
-        <v>25.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B123" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C123">
-        <v>3656</v>
+        <v>2621</v>
       </c>
       <c r="D123">
         <v>5</v>
       </c>
       <c r="E123" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="F123" t="s">
         <v>233</v>
       </c>
       <c r="G123">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C124">
+        <v>3656</v>
+      </c>
+      <c r="D124">
+        <v>5</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F124" t="s">
+        <v>233</v>
+      </c>
+      <c r="G124">
         <v>27</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4264EEB-64F0-4D88-AEEA-69FF97D773BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB07649-0675-4EE3-A393-F7209E896800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3606" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3618" uniqueCount="1119">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3339,9 +3339,6 @@
     <t>X37,5G</t>
   </si>
   <si>
-    <t>X400g</t>
-  </si>
-  <si>
     <t>doce-de-leite-docura-fazenda</t>
   </si>
   <si>
@@ -3385,6 +3382,18 @@
   </si>
   <si>
     <t>X90G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCE DE LEITE C/CACAUSOUVENIR </t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCE ABÓBORA C/ COCO </t>
+  </si>
+  <si>
+    <t>doce-de-leite-c-cacausouvenir</t>
   </si>
 </sst>
 </file>
@@ -5783,10 +5792,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B18" t="s">
         <v>1111</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1112</v>
       </c>
       <c r="C18">
         <v>4639</v>
@@ -6404,10 +6413,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B45" t="s">
         <v>1109</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1110</v>
       </c>
       <c r="C45">
         <v>4640</v>
@@ -9379,7 +9388,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10151,10 +10160,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B34" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C34">
         <v>4446</v>
@@ -10174,10 +10183,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B35" t="s">
         <v>1104</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1105</v>
       </c>
       <c r="C35">
         <v>4476</v>
@@ -11393,10 +11402,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B88" t="s">
         <v>1101</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1102</v>
       </c>
       <c r="C88">
         <v>4627</v>
@@ -11508,82 +11517,82 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B93" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C93">
-        <v>4630</v>
+        <v>4643</v>
       </c>
       <c r="D93">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E93" t="s">
-        <v>1100</v>
+        <v>1074</v>
       </c>
       <c r="F93" t="s">
-        <v>9</v>
+        <v>1116</v>
       </c>
       <c r="G93">
-        <v>127.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>983</v>
+        <v>1090</v>
       </c>
       <c r="B94" t="s">
-        <v>984</v>
+        <v>1096</v>
       </c>
       <c r="C94">
-        <v>4104</v>
+        <v>4630</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
         <v>1074</v>
       </c>
       <c r="F94" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="G94">
-        <v>77</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>985</v>
+        <v>1118</v>
       </c>
       <c r="B95" t="s">
-        <v>986</v>
+        <v>1115</v>
       </c>
       <c r="C95">
-        <v>4101</v>
+        <v>4644</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
         <v>1074</v>
       </c>
       <c r="F95" t="s">
-        <v>233</v>
+        <v>964</v>
       </c>
       <c r="G95">
-        <v>77</v>
+        <v>113</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B96" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="C96">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D96">
         <v>10</v>
@@ -11600,36 +11609,36 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B97" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C97">
-        <v>3705</v>
+        <v>4101</v>
       </c>
       <c r="D97">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="F97" t="s">
         <v>233</v>
       </c>
       <c r="G97">
-        <v>123.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B98" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="C98">
-        <v>3823</v>
+        <v>4105</v>
       </c>
       <c r="D98">
         <v>10</v>
@@ -11638,7 +11647,7 @@
         <v>1074</v>
       </c>
       <c r="F98" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="G98">
         <v>77</v>
@@ -11646,200 +11655,200 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B99" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C99">
-        <v>4583</v>
+        <v>3705</v>
       </c>
       <c r="D99">
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F99" t="s">
         <v>233</v>
       </c>
       <c r="G99">
-        <v>144</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B100" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C100">
-        <v>4308</v>
+        <v>3823</v>
       </c>
       <c r="D100">
         <v>10</v>
       </c>
       <c r="E100" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G100">
-        <v>68.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B101" t="s">
-        <v>998</v>
+        <v>1117</v>
       </c>
       <c r="C101">
-        <v>4309</v>
+        <v>4641</v>
       </c>
       <c r="D101">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E101" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F101" t="s">
-        <v>964</v>
+        <v>13</v>
       </c>
       <c r="G101">
-        <v>68.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1107</v>
+        <v>993</v>
       </c>
       <c r="B102" t="s">
-        <v>1108</v>
+        <v>994</v>
       </c>
       <c r="C102">
-        <v>4635</v>
+        <v>4583</v>
       </c>
       <c r="D102">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="F102" t="s">
-        <v>964</v>
+        <v>233</v>
       </c>
       <c r="G102">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B103" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C103">
-        <v>4412</v>
+        <v>4308</v>
       </c>
       <c r="D103">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="E103" t="s">
-        <v>8</v>
+        <v>1073</v>
       </c>
       <c r="F103" t="s">
-        <v>964</v>
+        <v>13</v>
       </c>
       <c r="G103">
-        <v>75.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B104" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C104">
-        <v>4413</v>
+        <v>4309</v>
       </c>
       <c r="D104">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E104" t="s">
-        <v>8</v>
+        <v>1073</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>964</v>
       </c>
       <c r="G104">
-        <v>496</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1001</v>
+        <v>1106</v>
       </c>
       <c r="B105" t="s">
-        <v>1002</v>
+        <v>1107</v>
       </c>
       <c r="C105">
-        <v>4414</v>
+        <v>4635</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>8</v>
+        <v>1069</v>
       </c>
       <c r="F105" t="s">
-        <v>13</v>
+        <v>964</v>
       </c>
       <c r="G105">
-        <v>101</v>
+        <v>167</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B106" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C106">
-        <v>4415</v>
+        <v>4412</v>
       </c>
       <c r="D106">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>964</v>
       </c>
       <c r="G106">
-        <v>414</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B107" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C107">
-        <v>4416</v>
+        <v>4413</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -11848,110 +11857,110 @@
         <v>13</v>
       </c>
       <c r="G107">
-        <v>85</v>
+        <v>496</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B108" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C108">
-        <v>4475</v>
+        <v>4414</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
-        <v>1079</v>
+        <v>8</v>
       </c>
       <c r="F108" t="s">
         <v>13</v>
       </c>
       <c r="G108">
-        <v>9</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B109" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C109">
-        <v>4354</v>
+        <v>4415</v>
       </c>
       <c r="D109">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E109" t="s">
-        <v>1079</v>
+        <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>744</v>
+        <v>13</v>
       </c>
       <c r="G109">
-        <v>79.5</v>
+        <v>414</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="B110" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="C110">
-        <v>4445</v>
+        <v>4416</v>
       </c>
       <c r="D110">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E110" t="s">
-        <v>1079</v>
+        <v>8</v>
       </c>
       <c r="F110" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G110">
-        <v>79.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B111" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C111">
-        <v>4353</v>
+        <v>4475</v>
       </c>
       <c r="D111">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E111" t="s">
         <v>1079</v>
       </c>
       <c r="F111" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111">
         <v>9</v>
-      </c>
-      <c r="G111">
-        <v>79.5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B112" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C112">
-        <v>4350</v>
+        <v>4354</v>
       </c>
       <c r="D112">
         <v>12</v>
@@ -11960,7 +11969,7 @@
         <v>1079</v>
       </c>
       <c r="F112" t="s">
-        <v>9</v>
+        <v>744</v>
       </c>
       <c r="G112">
         <v>79.5</v>
@@ -11968,13 +11977,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B113" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C113">
-        <v>4352</v>
+        <v>4445</v>
       </c>
       <c r="D113">
         <v>12</v>
@@ -11991,13 +12000,13 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B114" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C114">
-        <v>4349</v>
+        <v>4353</v>
       </c>
       <c r="D114">
         <v>12</v>
@@ -12014,13 +12023,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="B115" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="C115">
-        <v>4351</v>
+        <v>4350</v>
       </c>
       <c r="D115">
         <v>12</v>
@@ -12037,13 +12046,13 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B116" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C116">
-        <v>4581</v>
+        <v>4352</v>
       </c>
       <c r="D116">
         <v>12</v>
@@ -12060,185 +12069,254 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="B117" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="C117">
-        <v>4096</v>
+        <v>4349</v>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>8</v>
+        <v>1079</v>
       </c>
       <c r="F117" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G117">
-        <v>79</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1113</v>
+        <v>1019</v>
       </c>
       <c r="B118" t="s">
-        <v>1114</v>
+        <v>1020</v>
       </c>
       <c r="C118">
-        <v>4582</v>
+        <v>4351</v>
       </c>
       <c r="D118">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>1115</v>
+        <v>1079</v>
       </c>
       <c r="F118" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G118">
-        <v>45</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B119" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C119">
-        <v>4123</v>
+        <v>4581</v>
       </c>
       <c r="D119">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="F119" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G119">
-        <v>60</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B120" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C120">
-        <v>4306</v>
+        <v>4096</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E120" t="s">
-        <v>1074</v>
+        <v>8</v>
       </c>
       <c r="F120" t="s">
-        <v>964</v>
+        <v>13</v>
       </c>
       <c r="G120">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1029</v>
+        <v>1112</v>
       </c>
       <c r="B121" t="s">
-        <v>1030</v>
+        <v>1113</v>
       </c>
       <c r="C121">
-        <v>4307</v>
+        <v>4582</v>
       </c>
       <c r="D121">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E121" t="s">
-        <v>1074</v>
+        <v>1114</v>
       </c>
       <c r="F121" t="s">
-        <v>964</v>
+        <v>13</v>
       </c>
       <c r="G121">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="B122" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C122">
-        <v>2659</v>
+        <v>4123</v>
       </c>
       <c r="D122">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="F122" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="G122">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B123" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C123">
-        <v>2621</v>
+        <v>4306</v>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E123" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="F123" t="s">
-        <v>233</v>
+        <v>964</v>
       </c>
       <c r="G123">
-        <v>25.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B124" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C124">
-        <v>3656</v>
+        <v>4307</v>
       </c>
       <c r="D124">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E124" t="s">
         <v>1074</v>
       </c>
       <c r="F124" t="s">
+        <v>964</v>
+      </c>
+      <c r="G124">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C125">
+        <v>2659</v>
+      </c>
+      <c r="D125">
+        <v>20</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F125" t="s">
         <v>233</v>
       </c>
-      <c r="G124">
+      <c r="G125">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C126">
+        <v>2621</v>
+      </c>
+      <c r="D126">
+        <v>5</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F126" t="s">
+        <v>233</v>
+      </c>
+      <c r="G126">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C127">
+        <v>3656</v>
+      </c>
+      <c r="D127">
+        <v>5</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F127" t="s">
+        <v>233</v>
+      </c>
+      <c r="G127">
         <v>27</v>
       </c>
     </row>
@@ -19725,7 +19803,7 @@
         <v>32</v>
       </c>
       <c r="G38">
-        <v>280</v>
+        <v>360</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -19748,7 +19826,7 @@
         <v>13</v>
       </c>
       <c r="G39">
-        <v>48.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -20093,7 +20171,7 @@
         <v>32</v>
       </c>
       <c r="G54">
-        <v>315</v>
+        <v>375</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -20116,7 +20194,7 @@
         <v>32</v>
       </c>
       <c r="G55">
-        <v>157.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -20139,7 +20217,7 @@
         <v>13</v>
       </c>
       <c r="G56">
-        <v>28.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB07649-0675-4EE3-A393-F7209E896800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC35461A-D801-48D5-BCE7-69B1A4D1B711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -4440,7 +4440,7 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -14733,42 +14733,42 @@
         <v>104</v>
       </c>
       <c r="C89">
-        <v>2632</v>
+        <v>263</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G89">
-        <v>317</v>
+        <v>630</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B90" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C90">
-        <v>4179</v>
+        <v>2632</v>
       </c>
       <c r="D90">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G90">
-        <v>572</v>
+        <v>317</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -20240,7 +20240,7 @@
         <v>32</v>
       </c>
       <c r="G57">
-        <v>212.5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -20263,7 +20263,7 @@
         <v>13</v>
       </c>
       <c r="G58">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC35461A-D801-48D5-BCE7-69B1A4D1B711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F05C7E5-534A-42BD-A62F-B4940DB4B2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -16409,7 +16409,7 @@
         <v>32</v>
       </c>
       <c r="G38">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -16432,7 +16432,7 @@
         <v>13</v>
       </c>
       <c r="G39">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F05C7E5-534A-42BD-A62F-B4940DB4B2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B94C428-723C-4D08-809B-644DB9503F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3618" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3642" uniqueCount="1119">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3746,11 +3746,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C8D572-3175-4532-9898-FEC58E78606B}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -3783,36 +3783,36 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>604</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>605</v>
+        <v>44</v>
       </c>
       <c r="C2">
-        <v>2229</v>
+        <v>109</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>724</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>725</v>
+        <v>52</v>
       </c>
       <c r="C3">
-        <v>195</v>
+        <v>103</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -3824,18 +3824,18 @@
         <v>32</v>
       </c>
       <c r="G3">
-        <v>245</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>652</v>
+        <v>360</v>
       </c>
       <c r="B4" t="s">
-        <v>653</v>
+        <v>361</v>
       </c>
       <c r="C4">
-        <v>569</v>
+        <v>3110</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -3847,21 +3847,21 @@
         <v>32</v>
       </c>
       <c r="G4">
-        <v>117</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>648</v>
+        <v>286</v>
       </c>
       <c r="B5" t="s">
-        <v>649</v>
+        <v>287</v>
       </c>
       <c r="C5">
-        <v>282</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -3870,21 +3870,21 @@
         <v>32</v>
       </c>
       <c r="G5">
-        <v>117</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="C6">
-        <v>564</v>
+        <v>3472</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -3893,21 +3893,21 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>117</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>674</v>
+        <v>266</v>
       </c>
       <c r="B7" t="s">
-        <v>675</v>
+        <v>267</v>
       </c>
       <c r="C7">
-        <v>565</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -3916,21 +3916,21 @@
         <v>32</v>
       </c>
       <c r="G7">
-        <v>121</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>268</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>269</v>
       </c>
       <c r="C8">
-        <v>109</v>
+        <v>221</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -3939,18 +3939,18 @@
         <v>32</v>
       </c>
       <c r="G8">
-        <v>155</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="B9" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C9">
-        <v>3110</v>
+        <v>460</v>
       </c>
       <c r="D9">
         <v>25</v>
@@ -3962,18 +3962,18 @@
         <v>32</v>
       </c>
       <c r="G9">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B10" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="D10">
         <v>25</v>
@@ -3985,7 +3985,145 @@
         <v>32</v>
       </c>
       <c r="G10">
-        <v>88</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>436</v>
+      </c>
+      <c r="B11" t="s">
+        <v>437</v>
+      </c>
+      <c r="C11">
+        <v>2571</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>434</v>
+      </c>
+      <c r="B12" t="s">
+        <v>435</v>
+      </c>
+      <c r="C12">
+        <v>2522</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B13" t="s">
+        <v>441</v>
+      </c>
+      <c r="C13">
+        <v>2615</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14">
+        <v>150</v>
+      </c>
+      <c r="D14">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16">
+        <v>3851</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B94C428-723C-4D08-809B-644DB9503F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3367692A-CF80-40CF-8BAA-3FB3AC60BD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -8583,7 +8583,7 @@
         <v>233</v>
       </c>
       <c r="G2">
-        <v>162</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8606,7 +8606,7 @@
         <v>233</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8629,7 +8629,7 @@
         <v>233</v>
       </c>
       <c r="G4">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -8652,7 +8652,7 @@
         <v>233</v>
       </c>
       <c r="G5">
-        <v>162</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8675,7 +8675,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8698,7 +8698,7 @@
         <v>233</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8721,7 +8721,7 @@
         <v>233</v>
       </c>
       <c r="G8">
-        <v>33</v>
+        <v>35.5</v>
       </c>
     </row>
   </sheetData>
@@ -8923,7 +8923,7 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8946,7 +8946,7 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -23197,7 +23197,7 @@
         <v>13</v>
       </c>
       <c r="G49">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3367692A-CF80-40CF-8BAA-3FB3AC60BD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75E656F-CD4F-4653-B3EC-FC0FC3B35C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3642" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="1119">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3847,7 +3847,7 @@
         <v>32</v>
       </c>
       <c r="G4">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3870,7 +3870,7 @@
         <v>32</v>
       </c>
       <c r="G5">
-        <v>78.5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>112.5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4054,7 +4054,7 @@
         <v>13</v>
       </c>
       <c r="G13">
-        <v>290</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4803,7 +4803,7 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>72</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4826,7 +4826,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>350</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4987,7 +4987,7 @@
         <v>13</v>
       </c>
       <c r="G13">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,7 +5171,7 @@
         <v>32</v>
       </c>
       <c r="G21">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5470,7 +5470,7 @@
         <v>13</v>
       </c>
       <c r="G34">
-        <v>525</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,7 +5493,7 @@
         <v>32</v>
       </c>
       <c r="G35">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -14860,7 +14860,7 @@
         <v>9</v>
       </c>
       <c r="G88">
-        <v>693</v>
+        <v>583</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -14883,7 +14883,7 @@
         <v>9</v>
       </c>
       <c r="G89">
-        <v>630</v>
+        <v>530</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -14906,7 +14906,7 @@
         <v>13</v>
       </c>
       <c r="G90">
-        <v>317</v>
+        <v>267</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -14929,7 +14929,7 @@
         <v>9</v>
       </c>
       <c r="G91">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -14952,7 +14952,7 @@
         <v>13</v>
       </c>
       <c r="G92">
-        <v>262</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -18428,7 +18428,7 @@
         <v>32</v>
       </c>
       <c r="G44">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -18451,7 +18451,7 @@
         <v>13</v>
       </c>
       <c r="G45">
-        <v>18</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -18474,7 +18474,7 @@
         <v>32</v>
       </c>
       <c r="G46">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -18497,7 +18497,7 @@
         <v>13</v>
       </c>
       <c r="G47">
-        <v>11</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -18773,7 +18773,7 @@
         <v>32</v>
       </c>
       <c r="G59">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -19059,7 +19059,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -19113,7 +19113,7 @@
         <v>32</v>
       </c>
       <c r="G2">
-        <v>78.5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -19136,7 +19136,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -19159,7 +19159,7 @@
         <v>32</v>
       </c>
       <c r="G4">
-        <v>112.5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -19504,7 +19504,7 @@
         <v>32</v>
       </c>
       <c r="G19">
-        <v>660</v>
+        <v>590</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -19527,7 +19527,7 @@
         <v>13</v>
       </c>
       <c r="G20">
-        <v>112</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -19550,7 +19550,7 @@
         <v>32</v>
       </c>
       <c r="G21">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -19573,7 +19573,7 @@
         <v>13</v>
       </c>
       <c r="G22">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -19596,7 +19596,7 @@
         <v>13</v>
       </c>
       <c r="G23">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -19619,7 +19619,7 @@
         <v>32</v>
       </c>
       <c r="G24">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -19642,7 +19642,7 @@
         <v>32</v>
       </c>
       <c r="G25">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -19665,7 +19665,7 @@
         <v>13</v>
       </c>
       <c r="G26">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -19688,7 +19688,7 @@
         <v>32</v>
       </c>
       <c r="G27">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -19711,7 +19711,7 @@
         <v>13</v>
       </c>
       <c r="G28">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -19987,7 +19987,7 @@
         <v>13</v>
       </c>
       <c r="G40">
-        <v>26</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -20010,7 +20010,7 @@
         <v>32</v>
       </c>
       <c r="G41">
-        <v>142.5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -20033,7 +20033,7 @@
         <v>32</v>
       </c>
       <c r="G42">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -20044,10 +20044,10 @@
         <v>325</v>
       </c>
       <c r="C43">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D43">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -20056,7 +20056,7 @@
         <v>32</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -20067,10 +20067,10 @@
         <v>325</v>
       </c>
       <c r="C44">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -20079,21 +20079,21 @@
         <v>32</v>
       </c>
       <c r="G44">
-        <v>22</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C45">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D45">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -20102,7 +20102,7 @@
         <v>32</v>
       </c>
       <c r="G45">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -20113,42 +20113,42 @@
         <v>327</v>
       </c>
       <c r="C46">
-        <v>2543</v>
+        <v>3025</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G46">
-        <v>35.5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C47">
-        <v>98</v>
+        <v>2543</v>
       </c>
       <c r="D47">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G47">
-        <v>338</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -20159,10 +20159,10 @@
         <v>329</v>
       </c>
       <c r="C48">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -20171,21 +20171,21 @@
         <v>32</v>
       </c>
       <c r="G48">
-        <v>58.5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C49">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D49">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -20194,7 +20194,7 @@
         <v>32</v>
       </c>
       <c r="G49">
-        <v>362.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -20205,42 +20205,42 @@
         <v>331</v>
       </c>
       <c r="C50">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G50">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C51">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D51">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G51">
-        <v>255</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -20251,10 +20251,10 @@
         <v>333</v>
       </c>
       <c r="C52">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D52">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -20263,7 +20263,7 @@
         <v>32</v>
       </c>
       <c r="G52">
-        <v>212.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -20274,42 +20274,42 @@
         <v>333</v>
       </c>
       <c r="C53">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G53">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B54" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C54">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D54">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G54">
-        <v>375</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -20320,10 +20320,10 @@
         <v>335</v>
       </c>
       <c r="C55">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D55">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -20332,7 +20332,7 @@
         <v>32</v>
       </c>
       <c r="G55">
-        <v>187.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -20343,42 +20343,42 @@
         <v>335</v>
       </c>
       <c r="C56">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G56">
-        <v>33.5</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B57" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C57">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D57">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G57">
-        <v>275</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -20389,42 +20389,42 @@
         <v>337</v>
       </c>
       <c r="C58">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G58">
-        <v>57</v>
+        <v>275</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B59" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C59">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D59">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G59">
-        <v>240</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -20435,10 +20435,10 @@
         <v>339</v>
       </c>
       <c r="C60">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -20447,21 +20447,21 @@
         <v>32</v>
       </c>
       <c r="G60">
-        <v>42</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B61" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C61">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D61">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -20470,7 +20470,7 @@
         <v>32</v>
       </c>
       <c r="G61">
-        <v>375</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -20481,42 +20481,42 @@
         <v>341</v>
       </c>
       <c r="C62">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G62">
-        <v>64.5</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B63" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C63">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D63">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G63">
-        <v>330</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -20527,42 +20527,42 @@
         <v>343</v>
       </c>
       <c r="C64">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G64">
-        <v>57</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B65" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C65">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D65">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G65">
-        <v>285</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -20573,10 +20573,10 @@
         <v>345</v>
       </c>
       <c r="C66">
-        <v>3740</v>
+        <v>3670</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -20585,7 +20585,7 @@
         <v>32</v>
       </c>
       <c r="G66">
-        <v>237.5</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -20596,42 +20596,42 @@
         <v>345</v>
       </c>
       <c r="C67">
-        <v>2469</v>
+        <v>3740</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G67">
-        <v>49.5</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B68" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C68">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D68">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G68">
-        <v>312.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -20642,42 +20642,42 @@
         <v>347</v>
       </c>
       <c r="C69">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G69">
-        <v>64.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B70" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C70">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D70">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G70">
-        <v>322.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -20688,42 +20688,42 @@
         <v>349</v>
       </c>
       <c r="C71">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G71">
-        <v>66.5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B72" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C72">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D72">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G72">
-        <v>195</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -20734,42 +20734,42 @@
         <v>351</v>
       </c>
       <c r="C73">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G73">
-        <v>41</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B74" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C74">
-        <v>211</v>
+        <v>2321</v>
       </c>
       <c r="D74">
-        <v>22.68</v>
+        <v>5</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G74">
-        <v>187.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -20780,10 +20780,10 @@
         <v>353</v>
       </c>
       <c r="C75">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D75">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -20792,7 +20792,7 @@
         <v>32</v>
       </c>
       <c r="G75">
-        <v>375</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -20803,42 +20803,42 @@
         <v>353</v>
       </c>
       <c r="C76">
-        <v>2322</v>
+        <v>41</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>45.36</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G76">
-        <v>43.5</v>
+        <v>375</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B77" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C77">
-        <v>67</v>
+        <v>2322</v>
       </c>
       <c r="D77">
-        <v>45.36</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G77">
-        <v>626</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -20849,10 +20849,10 @@
         <v>355</v>
       </c>
       <c r="C78">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D78">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -20861,7 +20861,7 @@
         <v>32</v>
       </c>
       <c r="G78">
-        <v>313</v>
+        <v>626</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20872,65 +20872,65 @@
         <v>355</v>
       </c>
       <c r="C79">
-        <v>2488</v>
+        <v>2244</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G79">
-        <v>71</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B80" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C80">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D80">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G80">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B81" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C81">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G81">
-        <v>182</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -20941,19 +20941,19 @@
         <v>359</v>
       </c>
       <c r="C82">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G82">
-        <v>350</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -20964,10 +20964,10 @@
         <v>359</v>
       </c>
       <c r="C83">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D83">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -20976,7 +20976,7 @@
         <v>32</v>
       </c>
       <c r="G83">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -20987,56 +20987,56 @@
         <v>359</v>
       </c>
       <c r="C84">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G84">
-        <v>106</v>
+        <v>700</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B85" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C85">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D85">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G85">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B86" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C86">
-        <v>135</v>
+        <v>3110</v>
       </c>
       <c r="D86">
-        <v>22.68</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -21045,21 +21045,21 @@
         <v>32</v>
       </c>
       <c r="G86">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B87" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C87">
-        <v>2463</v>
+        <v>135</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -21068,21 +21068,21 @@
         <v>32</v>
       </c>
       <c r="G87">
-        <v>20</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C88">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D88">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>32</v>
       </c>
       <c r="G88">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -21102,10 +21102,10 @@
         <v>367</v>
       </c>
       <c r="C89">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -21114,7 +21114,7 @@
         <v>32</v>
       </c>
       <c r="G89">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -21125,10 +21125,10 @@
         <v>367</v>
       </c>
       <c r="C90">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -21137,21 +21137,21 @@
         <v>32</v>
       </c>
       <c r="G90">
-        <v>228</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B91" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C91">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D91">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -21160,7 +21160,7 @@
         <v>32</v>
       </c>
       <c r="G91">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -21171,18 +21171,41 @@
         <v>369</v>
       </c>
       <c r="C92">
+        <v>4223</v>
+      </c>
+      <c r="D92">
+        <v>25</v>
+      </c>
+      <c r="E92" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" t="s">
+        <v>32</v>
+      </c>
+      <c r="G92">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>368</v>
+      </c>
+      <c r="B93" t="s">
+        <v>369</v>
+      </c>
+      <c r="C93">
         <v>4224</v>
       </c>
-      <c r="D92">
-        <v>5</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92">
+      <c r="D93">
+        <v>5</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93">
         <v>27</v>
       </c>
     </row>
@@ -21270,7 +21293,7 @@
         <v>32</v>
       </c>
       <c r="G3">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -21293,7 +21316,7 @@
         <v>13</v>
       </c>
       <c r="G4">
-        <v>41</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -21339,7 +21362,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -21730,7 +21753,7 @@
         <v>32</v>
       </c>
       <c r="G23">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -21753,7 +21776,7 @@
         <v>32</v>
       </c>
       <c r="G24">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -22484,7 +22507,7 @@
         <v>32</v>
       </c>
       <c r="G18">
-        <v>1450</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -22507,7 +22530,7 @@
         <v>13</v>
       </c>
       <c r="G19">
-        <v>290</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75E656F-CD4F-4653-B3EC-FC0FC3B35C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324B2951-729C-4623-A9D7-77CA7D5D6774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -21270,7 +21270,7 @@
         <v>32</v>
       </c>
       <c r="G2">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaDeProdutosB\lista-de-produtos-b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324B2951-729C-4623-A9D7-77CA7D5D6774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B29DD-7B93-495E-B10B-ED12ADF839DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="18" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3650" uniqueCount="1121">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3394,6 +3394,12 @@
   </si>
   <si>
     <t>doce-de-leite-c-cacausouvenir</t>
+  </si>
+  <si>
+    <t>canjicao-amarelo</t>
+  </si>
+  <si>
+    <t>CANJICÃO AMARELO</t>
   </si>
 </sst>
 </file>
@@ -19059,7 +19065,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -19187,16 +19193,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>1119</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>1120</v>
       </c>
       <c r="C6">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -19205,7 +19211,7 @@
         <v>32</v>
       </c>
       <c r="G6">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -19216,42 +19222,42 @@
         <v>291</v>
       </c>
       <c r="C7">
-        <v>2637</v>
+        <v>127</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>14.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>2637</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>63</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -19262,33 +19268,33 @@
         <v>293</v>
       </c>
       <c r="C9">
-        <v>2501</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G9">
-        <v>14.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C10">
-        <v>24</v>
+        <v>2501</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -19297,7 +19303,7 @@
         <v>13</v>
       </c>
       <c r="G10">
-        <v>63</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -19308,33 +19314,33 @@
         <v>295</v>
       </c>
       <c r="C11">
-        <v>2726</v>
+        <v>24</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>14.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C12">
-        <v>4221</v>
+        <v>2726</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -19343,7 +19349,7 @@
         <v>32</v>
       </c>
       <c r="G12">
-        <v>142.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -19354,30 +19360,30 @@
         <v>297</v>
       </c>
       <c r="C13">
-        <v>4222</v>
+        <v>4221</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G13">
-        <v>30.5</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C14">
-        <v>2580</v>
+        <v>4222</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -19389,7 +19395,7 @@
         <v>13</v>
       </c>
       <c r="G14">
-        <v>38</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -19400,30 +19406,30 @@
         <v>299</v>
       </c>
       <c r="C15">
-        <v>123</v>
+        <v>2580</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>180</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C16">
-        <v>4016</v>
+        <v>123</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -19435,7 +19441,7 @@
         <v>32</v>
       </c>
       <c r="G16">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -19446,10 +19452,10 @@
         <v>301</v>
       </c>
       <c r="C17">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="D17">
-        <v>45.36</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -19458,7 +19464,7 @@
         <v>32</v>
       </c>
       <c r="G17">
-        <v>268.5</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -19469,10 +19475,10 @@
         <v>301</v>
       </c>
       <c r="C18">
-        <v>210</v>
+        <v>4017</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>45.36</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -19481,21 +19487,21 @@
         <v>32</v>
       </c>
       <c r="G18">
-        <v>31.5</v>
+        <v>268.5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C19">
-        <v>4545</v>
+        <v>210</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -19504,7 +19510,7 @@
         <v>32</v>
       </c>
       <c r="G19">
-        <v>590</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -19515,42 +19521,42 @@
         <v>303</v>
       </c>
       <c r="C20">
-        <v>3363</v>
+        <v>4545</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G20">
-        <v>100.5</v>
+        <v>590</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C21">
-        <v>2482</v>
+        <v>3363</v>
       </c>
       <c r="D21">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <v>540</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -19561,33 +19567,33 @@
         <v>305</v>
       </c>
       <c r="C22">
-        <v>34</v>
+        <v>2482</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G22">
-        <v>92</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B23" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C23">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="D23">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -19596,7 +19602,7 @@
         <v>13</v>
       </c>
       <c r="G23">
-        <v>540</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -19607,33 +19613,33 @@
         <v>307</v>
       </c>
       <c r="C24">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>92</v>
+        <v>540</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B25" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C25">
-        <v>2486</v>
+        <v>114</v>
       </c>
       <c r="D25">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -19642,7 +19648,7 @@
         <v>32</v>
       </c>
       <c r="G25">
-        <v>540</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -19653,42 +19659,42 @@
         <v>309</v>
       </c>
       <c r="C26">
-        <v>2241</v>
+        <v>2486</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G26">
-        <v>92</v>
+        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B27" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C27">
-        <v>2487</v>
+        <v>2241</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G27">
-        <v>540</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -19699,42 +19705,42 @@
         <v>311</v>
       </c>
       <c r="C28">
-        <v>23</v>
+        <v>2487</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G28">
-        <v>92</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B29" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C29">
-        <v>2260</v>
+        <v>23</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G29">
-        <v>430</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -19745,10 +19751,10 @@
         <v>313</v>
       </c>
       <c r="C30">
-        <v>214</v>
+        <v>2260</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -19757,21 +19763,21 @@
         <v>32</v>
       </c>
       <c r="G30">
-        <v>73.5</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C31">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -19780,7 +19786,7 @@
         <v>32</v>
       </c>
       <c r="G31">
-        <v>270</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -19791,30 +19797,30 @@
         <v>315</v>
       </c>
       <c r="C32">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G32">
-        <v>47</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C33">
-        <v>2302</v>
+        <v>68</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -19823,10 +19829,10 @@
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G33">
-        <v>54.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -19837,10 +19843,10 @@
         <v>317</v>
       </c>
       <c r="C34">
-        <v>320</v>
+        <v>2302</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -19849,21 +19855,21 @@
         <v>32</v>
       </c>
       <c r="G34">
-        <v>315</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C35">
-        <v>3479</v>
+        <v>320</v>
       </c>
       <c r="D35">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -19872,7 +19878,7 @@
         <v>32</v>
       </c>
       <c r="G35">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -19883,10 +19889,10 @@
         <v>319</v>
       </c>
       <c r="C36">
-        <v>130</v>
+        <v>3479</v>
       </c>
       <c r="D36">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -19895,7 +19901,7 @@
         <v>32</v>
       </c>
       <c r="G36">
-        <v>178</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -19906,42 +19912,42 @@
         <v>319</v>
       </c>
       <c r="C37">
-        <v>2464</v>
+        <v>130</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G37">
-        <v>37.5</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C38">
-        <v>101</v>
+        <v>2464</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G38">
-        <v>360</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -19952,30 +19958,30 @@
         <v>321</v>
       </c>
       <c r="C39">
-        <v>2465</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G39">
-        <v>62</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C40">
-        <v>65</v>
+        <v>2465</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -19987,7 +19993,7 @@
         <v>13</v>
       </c>
       <c r="G40">
-        <v>24.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -19998,19 +20004,19 @@
         <v>323</v>
       </c>
       <c r="C41">
-        <v>2624</v>
+        <v>65</v>
       </c>
       <c r="D41">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G41">
-        <v>135</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -20021,10 +20027,10 @@
         <v>323</v>
       </c>
       <c r="C42">
-        <v>119</v>
+        <v>2624</v>
       </c>
       <c r="D42">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -20033,21 +20039,21 @@
         <v>32</v>
       </c>
       <c r="G42">
-        <v>270</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C43">
-        <v>2834</v>
+        <v>119</v>
       </c>
       <c r="D43">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -20056,7 +20062,7 @@
         <v>32</v>
       </c>
       <c r="G43">
-        <v>123</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -20067,10 +20073,10 @@
         <v>325</v>
       </c>
       <c r="C44">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D44">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -20079,7 +20085,7 @@
         <v>32</v>
       </c>
       <c r="G44">
-        <v>102.5</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -20090,10 +20096,10 @@
         <v>325</v>
       </c>
       <c r="C45">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -20102,21 +20108,21 @@
         <v>32</v>
       </c>
       <c r="G45">
-        <v>23</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C46">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D46">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -20125,7 +20131,7 @@
         <v>32</v>
       </c>
       <c r="G46">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -20136,42 +20142,42 @@
         <v>327</v>
       </c>
       <c r="C47">
-        <v>2543</v>
+        <v>3025</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G47">
-        <v>35.5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C48">
-        <v>98</v>
+        <v>2543</v>
       </c>
       <c r="D48">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G48">
-        <v>320</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -20182,10 +20188,10 @@
         <v>329</v>
       </c>
       <c r="C49">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -20194,21 +20200,21 @@
         <v>32</v>
       </c>
       <c r="G49">
-        <v>55.5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C50">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D50">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -20217,7 +20223,7 @@
         <v>32</v>
       </c>
       <c r="G50">
-        <v>362.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -20228,42 +20234,42 @@
         <v>331</v>
       </c>
       <c r="C51">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G51">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B52" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C52">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D52">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G52">
-        <v>255</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -20274,10 +20280,10 @@
         <v>333</v>
       </c>
       <c r="C53">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D53">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -20286,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G53">
-        <v>212.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -20297,42 +20303,42 @@
         <v>333</v>
       </c>
       <c r="C54">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G54">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C55">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D55">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G55">
-        <v>350</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -20343,10 +20349,10 @@
         <v>335</v>
       </c>
       <c r="C56">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D56">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -20355,7 +20361,7 @@
         <v>32</v>
       </c>
       <c r="G56">
-        <v>175</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -20366,42 +20372,42 @@
         <v>335</v>
       </c>
       <c r="C57">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G57">
-        <v>31</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B58" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C58">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D58">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G58">
-        <v>275</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -20412,42 +20418,42 @@
         <v>337</v>
       </c>
       <c r="C59">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G59">
-        <v>57</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B60" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C60">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D60">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G60">
-        <v>280</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -20458,10 +20464,10 @@
         <v>339</v>
       </c>
       <c r="C61">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -20470,21 +20476,21 @@
         <v>32</v>
       </c>
       <c r="G61">
-        <v>48.5</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B62" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C62">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D62">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -20493,7 +20499,7 @@
         <v>32</v>
       </c>
       <c r="G62">
-        <v>375</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -20504,42 +20510,42 @@
         <v>341</v>
       </c>
       <c r="C63">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G63">
-        <v>64.5</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B64" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C64">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D64">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G64">
-        <v>330</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -20550,42 +20556,42 @@
         <v>343</v>
       </c>
       <c r="C65">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G65">
-        <v>57</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B66" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C66">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D66">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G66">
-        <v>285</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -20596,10 +20602,10 @@
         <v>345</v>
       </c>
       <c r="C67">
-        <v>3740</v>
+        <v>3670</v>
       </c>
       <c r="D67">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -20608,7 +20614,7 @@
         <v>32</v>
       </c>
       <c r="G67">
-        <v>237.5</v>
+        <v>285</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -20619,42 +20625,42 @@
         <v>345</v>
       </c>
       <c r="C68">
-        <v>2469</v>
+        <v>3740</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G68">
-        <v>49.5</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B69" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C69">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D69">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G69">
-        <v>312.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -20665,42 +20671,42 @@
         <v>347</v>
       </c>
       <c r="C70">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G70">
-        <v>64.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B71" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C71">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D71">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G71">
-        <v>300</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -20711,42 +20717,42 @@
         <v>349</v>
       </c>
       <c r="C72">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G72">
-        <v>62</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B73" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C73">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D73">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G73">
-        <v>180</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -20757,42 +20763,42 @@
         <v>351</v>
       </c>
       <c r="C74">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G74">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B75" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C75">
-        <v>211</v>
+        <v>2321</v>
       </c>
       <c r="D75">
-        <v>22.68</v>
+        <v>5</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G75">
-        <v>187.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -20803,10 +20809,10 @@
         <v>353</v>
       </c>
       <c r="C76">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D76">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -20815,7 +20821,7 @@
         <v>32</v>
       </c>
       <c r="G76">
-        <v>375</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -20826,42 +20832,42 @@
         <v>353</v>
       </c>
       <c r="C77">
-        <v>2322</v>
+        <v>41</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>45.36</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G77">
-        <v>43.5</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B78" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C78">
-        <v>67</v>
+        <v>2322</v>
       </c>
       <c r="D78">
-        <v>45.36</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G78">
-        <v>626</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20872,10 +20878,10 @@
         <v>355</v>
       </c>
       <c r="C79">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D79">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -20884,7 +20890,7 @@
         <v>32</v>
       </c>
       <c r="G79">
-        <v>313</v>
+        <v>626</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -20895,65 +20901,65 @@
         <v>355</v>
       </c>
       <c r="C80">
-        <v>2488</v>
+        <v>2244</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G80">
-        <v>71</v>
+        <v>313</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B81" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C81">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D81">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G81">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B82" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C82">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G82">
-        <v>182</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -20964,19 +20970,19 @@
         <v>359</v>
       </c>
       <c r="C83">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G83">
-        <v>350</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -20987,10 +20993,10 @@
         <v>359</v>
       </c>
       <c r="C84">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D84">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -20999,7 +21005,7 @@
         <v>32</v>
       </c>
       <c r="G84">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -21010,56 +21016,56 @@
         <v>359</v>
       </c>
       <c r="C85">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G85">
-        <v>106</v>
+        <v>700</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B86" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C86">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D86">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G86">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B87" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C87">
-        <v>135</v>
+        <v>3110</v>
       </c>
       <c r="D87">
-        <v>22.68</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -21068,21 +21074,21 @@
         <v>32</v>
       </c>
       <c r="G87">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B88" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C88">
-        <v>2463</v>
+        <v>135</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -21091,21 +21097,21 @@
         <v>32</v>
       </c>
       <c r="G88">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B89" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C89">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D89">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -21114,7 +21120,7 @@
         <v>32</v>
       </c>
       <c r="G89">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -21125,10 +21131,10 @@
         <v>367</v>
       </c>
       <c r="C90">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D90">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -21137,7 +21143,7 @@
         <v>32</v>
       </c>
       <c r="G90">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -21148,10 +21154,10 @@
         <v>367</v>
       </c>
       <c r="C91">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -21160,21 +21166,21 @@
         <v>32</v>
       </c>
       <c r="G91">
-        <v>228</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B92" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C92">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D92">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -21183,7 +21189,7 @@
         <v>32</v>
       </c>
       <c r="G92">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -21194,18 +21200,41 @@
         <v>369</v>
       </c>
       <c r="C93">
+        <v>4223</v>
+      </c>
+      <c r="D93">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>368</v>
+      </c>
+      <c r="B94" t="s">
+        <v>369</v>
+      </c>
+      <c r="C94">
         <v>4224</v>
       </c>
-      <c r="D93">
-        <v>5</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93">
+      <c r="D94">
+        <v>5</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94">
         <v>27</v>
       </c>
     </row>
@@ -24117,7 +24146,7 @@
         <v>13</v>
       </c>
       <c r="G88">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -24140,7 +24169,7 @@
         <v>13</v>
       </c>
       <c r="G89">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -3407,7 +3407,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3419,6 +3419,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFffffff"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3505,7 +3511,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -6093,7 +6099,7 @@
         <v>156</v>
       </c>
       <c r="G21" s="4">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -6107,7 +6113,7 @@
         <v>3009</v>
       </c>
       <c r="D22" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>29</v>
@@ -6116,7 +6122,7 @@
         <v>10</v>
       </c>
       <c r="G22" s="4">
-        <v>78</v>
+        <v>142.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -6142,7 +6148,7 @@
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
         <v>356</v>
       </c>
@@ -6165,7 +6171,7 @@
         <v>260</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
         <v>358</v>
       </c>
@@ -6188,7 +6194,7 @@
         <v>700</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
         <v>358</v>
       </c>
@@ -6211,7 +6217,7 @@
         <v>280</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
         <v>358</v>
       </c>
@@ -6234,7 +6240,7 @@
         <v>142</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
         <v>358</v>
       </c>
@@ -6257,7 +6263,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
         <v>360</v>
       </c>
@@ -6280,7 +6286,7 @@
         <v>595</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
         <v>360</v>
       </c>
@@ -6303,7 +6309,7 @@
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
         <v>360</v>
       </c>
@@ -6326,7 +6332,7 @@
         <v>299.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
         <v>362</v>
       </c>
@@ -6372,7 +6378,7 @@
         <v>160</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3" t="s">
         <v>366</v>
       </c>
@@ -6395,7 +6401,7 @@
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
         <v>368</v>
       </c>
@@ -6418,7 +6424,7 @@
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3" t="s">
         <v>370</v>
       </c>
@@ -6441,7 +6447,7 @@
         <v>220</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
         <v>370</v>
       </c>
@@ -6464,7 +6470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
         <v>372</v>
       </c>
@@ -6487,7 +6493,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3" t="s">
         <v>372</v>
       </c>
@@ -6510,7 +6516,7 @@
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3" t="s">
         <v>374</v>
       </c>
@@ -6533,7 +6539,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3" t="s">
         <v>376</v>
       </c>
@@ -6556,7 +6562,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3" t="s">
         <v>378</v>
       </c>
@@ -6579,7 +6585,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3" t="s">
         <v>380</v>
       </c>
@@ -6602,7 +6608,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3" t="s">
         <v>382</v>
       </c>
@@ -6625,7 +6631,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3" t="s">
         <v>378</v>
       </c>
@@ -6648,7 +6654,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3" t="s">
         <v>384</v>
       </c>
@@ -6671,7 +6677,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3" t="s">
         <v>386</v>
       </c>
@@ -6694,7 +6700,7 @@
         <v>162</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
         <v>388</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3407,7 +3407,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3425,12 +3425,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3482,7 +3476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3509,9 +3503,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -3828,7 +3819,7 @@
     <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3851,7 +3842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>1056</v>
       </c>
@@ -3874,7 +3865,7 @@
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>1064</v>
       </c>
@@ -3897,7 +3888,7 @@
         <v>215</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>834</v>
       </c>
@@ -3920,7 +3911,7 @@
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>758</v>
       </c>
@@ -3943,7 +3934,7 @@
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>760</v>
       </c>
@@ -3966,7 +3957,7 @@
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>896</v>
       </c>
@@ -3989,7 +3980,7 @@
         <v>168</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>898</v>
       </c>
@@ -4012,7 +4003,7 @@
         <v>300</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>720</v>
       </c>
@@ -4035,7 +4026,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>722</v>
       </c>
@@ -4058,7 +4049,7 @@
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>566</v>
       </c>
@@ -4081,7 +4072,7 @@
         <v>185</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>564</v>
       </c>
@@ -4104,7 +4095,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>570</v>
       </c>
@@ -4127,7 +4118,7 @@
         <v>375</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>1066</v>
       </c>
@@ -4150,7 +4141,7 @@
         <v>190</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>1068</v>
       </c>
@@ -4173,7 +4164,7 @@
         <v>190</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>1121</v>
       </c>
@@ -4858,7 +4849,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -5662,7 +5653,7 @@
         <v>10</v>
       </c>
       <c r="G2" s="5">
-        <v>329.5</v>
+        <v>333</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -5708,7 +5699,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="5">
-        <v>124.5</v>
+        <v>126</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -5869,7 +5860,7 @@
         <v>49</v>
       </c>
       <c r="G11" s="4">
-        <v>295</v>
+        <v>298.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -5892,7 +5883,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -5915,7 +5906,7 @@
         <v>156</v>
       </c>
       <c r="G13" s="5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
@@ -5961,7 +5952,7 @@
         <v>10</v>
       </c>
       <c r="G15" s="5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -6030,7 +6021,7 @@
         <v>10</v>
       </c>
       <c r="G18" s="4">
-        <v>295</v>
+        <v>298.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
@@ -6076,7 +6067,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="4">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -6362,10 +6353,10 @@
       <c r="B33" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="4">
         <v>4650</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="4">
         <v>5</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -6374,7 +6365,7 @@
       <c r="F33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="4">
         <v>160</v>
       </c>
     </row>
@@ -13084,7 +13075,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>220</v>
+        <v>223.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -13153,7 +13144,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4">
-        <v>312</v>
+        <v>313.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -13199,7 +13190,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="4">
-        <v>220</v>
+        <v>223.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -13245,7 +13236,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="4">
-        <v>342</v>
+        <v>343.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -13291,7 +13282,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="4">
-        <v>332</v>
+        <v>333.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
@@ -13360,7 +13351,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
@@ -13429,7 +13420,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -13475,7 +13466,7 @@
         <v>10</v>
       </c>
       <c r="G22" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -13521,7 +13512,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
@@ -13728,7 +13719,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="5">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
@@ -13774,7 +13765,7 @@
         <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -13866,7 +13857,7 @@
         <v>10</v>
       </c>
       <c r="G39" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
@@ -13935,7 +13926,7 @@
         <v>10</v>
       </c>
       <c r="G42" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
@@ -14004,7 +13995,7 @@
         <v>10</v>
       </c>
       <c r="G45" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
@@ -14050,7 +14041,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="4">
-        <v>200</v>
+        <v>203.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
@@ -14073,7 +14064,7 @@
         <v>10</v>
       </c>
       <c r="G48" s="4">
-        <v>200</v>
+        <v>203.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
@@ -14119,7 +14110,7 @@
         <v>10</v>
       </c>
       <c r="G50" s="4">
-        <v>377</v>
+        <v>378.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -14165,7 +14156,7 @@
         <v>10</v>
       </c>
       <c r="G52" s="4">
-        <v>377</v>
+        <v>378.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -14234,7 +14225,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="4">
-        <v>377</v>
+        <v>378.6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -14303,7 +14294,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="4">
-        <v>377</v>
+        <v>378.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -14326,7 +14317,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
@@ -14395,7 +14386,7 @@
         <v>10</v>
       </c>
       <c r="G62" s="4">
-        <v>392</v>
+        <v>393.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -14418,7 +14409,7 @@
         <v>10</v>
       </c>
       <c r="G63" s="4">
-        <v>372</v>
+        <v>373.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -14487,7 +14478,7 @@
         <v>10</v>
       </c>
       <c r="G66" s="4">
-        <v>262</v>
+        <v>263.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -15245,7 +15236,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -15291,7 +15282,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -15337,7 +15328,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5">
-        <v>83.5</v>
+        <v>84.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -15383,7 +15374,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -15429,7 +15420,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -15475,7 +15466,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="4">
-        <v>112</v>
+        <v>113.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
@@ -15521,7 +15512,7 @@
         <v>156</v>
       </c>
       <c r="G15" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -15567,7 +15558,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -15887,7 +15878,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -17611,7 +17602,7 @@
         <v>10</v>
       </c>
       <c r="G2" s="4">
-        <v>190</v>
+        <v>193.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -18071,7 +18062,7 @@
         <v>10</v>
       </c>
       <c r="G22" s="5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -19289,7 +19280,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -19335,7 +19326,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -19404,7 +19395,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -19450,7 +19441,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -19496,7 +19487,7 @@
         <v>156</v>
       </c>
       <c r="G12" s="5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -22346,7 +22337,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -22392,7 +22383,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="5">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -22415,7 +22406,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="4">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -22484,7 +22475,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="4">
-        <v>32</v>
+        <v>33.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -22622,7 +22613,7 @@
         <v>10</v>
       </c>
       <c r="G15" s="5">
-        <v>94.5</v>
+        <v>95.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -15282,7 +15282,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -8160,7 +8160,7 @@
         <v>10</v>
       </c>
       <c r="G111" s="4">
-        <v>440</v>
+        <v>510</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
@@ -15170,7 +15170,7 @@
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>1006</v>
       </c>
@@ -15216,7 +15216,7 @@
         <v>144</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>1006</v>
       </c>
@@ -15239,7 +15239,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>1008</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>190</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>1008</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>1010</v>
       </c>
@@ -15308,7 +15308,7 @@
         <v>408</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>1010</v>
       </c>
@@ -15331,7 +15331,7 @@
         <v>84.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>1012</v>
       </c>
@@ -15354,7 +15354,7 @@
         <v>260</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>1012</v>
       </c>
@@ -15377,7 +15377,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>1014</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>266</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>1014</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>1016</v>
       </c>
@@ -15446,7 +15446,7 @@
         <v>550</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>1016</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>1018</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -14501,7 +14501,7 @@
         <v>10</v>
       </c>
       <c r="G67" s="4">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -14524,7 +14524,7 @@
         <v>10</v>
       </c>
       <c r="G68" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -14547,7 +14547,7 @@
         <v>10</v>
       </c>
       <c r="G69" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -14570,7 +14570,7 @@
         <v>10</v>
       </c>
       <c r="G70" s="4">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -14593,7 +14593,7 @@
         <v>10</v>
       </c>
       <c r="G71" s="4">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
@@ -14616,7 +14616,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -14685,7 +14685,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="4">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -14708,7 +14708,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -14731,7 +14731,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="4">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -14754,7 +14754,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -5470,7 +5470,7 @@
         <v>156</v>
       </c>
       <c r="G31" s="4">
-        <v>900</v>
+        <v>1325</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -5516,7 +5516,7 @@
         <v>156</v>
       </c>
       <c r="G33" s="4">
-        <v>182</v>
+        <v>278.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
@@ -19901,7 +19901,7 @@
         <v>156</v>
       </c>
       <c r="G30" s="4">
-        <v>430</v>
+        <v>390</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -19924,7 +19924,7 @@
         <v>156</v>
       </c>
       <c r="G31" s="5">
-        <v>73.5</v>
+        <v>68</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -5536,10 +5536,10 @@
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G34" s="4">
-        <v>475</v>
+        <v>362.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -5559,10 +5559,10 @@
         <v>29</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>97</v>
+        <v>75.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -19743,7 +19743,7 @@
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
         <v>780</v>
       </c>
@@ -19766,7 +19766,7 @@
         <v>540</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
         <v>780</v>
       </c>
@@ -19789,7 +19789,7 @@
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
         <v>782</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>540</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
         <v>782</v>
       </c>
@@ -19835,7 +19835,7 @@
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
         <v>784</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>540</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
         <v>784</v>
       </c>
@@ -19881,7 +19881,7 @@
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
         <v>786</v>
       </c>
@@ -19904,7 +19904,7 @@
         <v>390</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
         <v>786</v>
       </c>
@@ -19927,7 +19927,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
         <v>788</v>
       </c>
@@ -19950,7 +19950,7 @@
         <v>270</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
         <v>788</v>
       </c>
@@ -19973,7 +19973,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3" t="s">
         <v>790</v>
       </c>
@@ -19996,7 +19996,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
         <v>790</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>315</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3" t="s">
         <v>792</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>356</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
         <v>792</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>178</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
         <v>792</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3" t="s">
         <v>794</v>
       </c>
@@ -20111,7 +20111,7 @@
         <v>360</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3" t="s">
         <v>794</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3" t="s">
         <v>796</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3" t="s">
         <v>796</v>
       </c>
@@ -20180,7 +20180,7 @@
         <v>135</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3" t="s">
         <v>796</v>
       </c>
@@ -20203,7 +20203,7 @@
         <v>270</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3" t="s">
         <v>798</v>
       </c>
@@ -20226,7 +20226,7 @@
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3" t="s">
         <v>798</v>
       </c>
@@ -20249,7 +20249,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3" t="s">
         <v>798</v>
       </c>
@@ -20272,7 +20272,7 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3" t="s">
         <v>800</v>
       </c>
@@ -20295,7 +20295,7 @@
         <v>200</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
         <v>800</v>
       </c>
@@ -22935,7 +22935,7 @@
         <v>156</v>
       </c>
       <c r="G29" s="5">
-        <v>112.5</v>
+        <v>77.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -22958,7 +22958,7 @@
         <v>156</v>
       </c>
       <c r="G30" s="4">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -22981,7 +22981,7 @@
         <v>156</v>
       </c>
       <c r="G31" s="4">
-        <v>125</v>
+        <v>112.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4643,7 +4643,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="4">
-        <v>175</v>
+        <v>250</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
@@ -22271,7 +22271,7 @@
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22294,7 +22294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>552</v>
       </c>
@@ -22317,7 +22317,7 @@
         <v>380</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>552</v>
       </c>
@@ -22340,7 +22340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>554</v>
       </c>
@@ -22363,7 +22363,7 @@
         <v>350</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>554</v>
       </c>
@@ -22386,7 +22386,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>556</v>
       </c>
@@ -22409,7 +22409,7 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>556</v>
       </c>
@@ -22432,7 +22432,7 @@
         <v>146</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>558</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>558</v>
       </c>
@@ -22478,7 +22478,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>560</v>
       </c>
@@ -22501,7 +22501,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>562</v>
       </c>
@@ -22524,7 +22524,7 @@
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>564</v>
       </c>
@@ -22547,7 +22547,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>564</v>
       </c>
@@ -22570,7 +22570,7 @@
         <v>390</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>566</v>
       </c>
@@ -22593,7 +22593,7 @@
         <v>185</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>566</v>
       </c>
@@ -22616,7 +22616,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>568</v>
       </c>
@@ -22639,7 +22639,7 @@
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>568</v>
       </c>
@@ -22662,7 +22662,7 @@
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>570</v>
       </c>
@@ -22685,7 +22685,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>570</v>
       </c>
@@ -22708,7 +22708,7 @@
         <v>375</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>572</v>
       </c>
@@ -22731,7 +22731,7 @@
         <v>170</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>574</v>
       </c>
@@ -22754,7 +22754,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>574</v>
       </c>
@@ -22777,7 +22777,7 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>576</v>
       </c>
@@ -22800,7 +22800,7 @@
         <v>320</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
         <v>576</v>
       </c>
@@ -22823,7 +22823,7 @@
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
         <v>578</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4209,7 +4209,7 @@
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>522</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>310</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>524</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>385</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>524</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>172</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>526</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>500</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>528</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>530</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>480</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>530</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>242</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>532</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>532</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>464</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>534</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>84</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>534</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>290.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>536</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>675</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>536</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>538</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>580</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>538</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>290</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>540</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>455</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>540</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>542</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>250</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>544</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>546</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>142</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>548</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>420</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>550</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5">
-        <v>34.5</v>
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -4941,7 +4941,7 @@
         <v>156</v>
       </c>
       <c r="G8" s="5">
-        <v>162.5</v>
+        <v>175</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -22544,7 +22544,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="4">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
@@ -22567,7 +22567,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="4">
-        <v>390</v>
+        <v>490</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -7401,7 +7401,7 @@
         <v>156</v>
       </c>
       <c r="G78" s="4">
-        <v>255</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
@@ -7424,7 +7424,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="4">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Documents\lista-bourached\Lista-de-Produtos-Bourached\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D579D5AC-4BA5-42C8-8252-EFAFB2673F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF3AF5A-9580-46BE-A06E-AF672E9AEAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11685" yWindow="0" windowWidth="17220" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4005" yWindow="420" windowWidth="13710" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3698" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3786" uniqueCount="1123">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3809,7 +3809,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -4030,16 +4030,16 @@
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>1060</v>
       </c>
       <c r="B10" t="s">
-        <v>275</v>
+        <v>1061</v>
       </c>
       <c r="C10" s="3">
-        <v>2825</v>
+        <v>2283</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -4048,21 +4048,21 @@
         <v>10</v>
       </c>
       <c r="G10" s="3">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>276</v>
+        <v>1062</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>1063</v>
       </c>
       <c r="C11" s="3">
-        <v>2828</v>
+        <v>4255</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -4071,21 +4071,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="3">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>1090</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>1091</v>
       </c>
       <c r="C12" s="3">
-        <v>2826</v>
+        <v>3081</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -4094,21 +4094,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="3">
-        <v>25</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>280</v>
+        <v>1090</v>
       </c>
       <c r="B13" t="s">
-        <v>281</v>
+        <v>1091</v>
       </c>
       <c r="C13" s="3">
-        <v>3058</v>
+        <v>3818</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -4116,22 +4116,22 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="3">
-        <v>25</v>
+      <c r="G13" s="4">
+        <v>72.5</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>1092</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>1093</v>
       </c>
       <c r="C14" s="3">
-        <v>3059</v>
+        <v>2534</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -4139,22 +4139,22 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
-        <v>25</v>
+      <c r="G14" s="4">
+        <v>72.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>1092</v>
       </c>
       <c r="B15" t="s">
-        <v>285</v>
+        <v>1093</v>
       </c>
       <c r="C15" s="3">
-        <v>2829</v>
+        <v>2234</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -4163,21 +4163,21 @@
         <v>10</v>
       </c>
       <c r="G15" s="3">
-        <v>25</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>286</v>
+        <v>1094</v>
       </c>
       <c r="B16" t="s">
-        <v>287</v>
+        <v>1095</v>
       </c>
       <c r="C16" s="3">
-        <v>4126</v>
+        <v>2238</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -4186,21 +4186,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="3">
-        <v>25</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>288</v>
+        <v>1094</v>
       </c>
       <c r="B17" t="s">
-        <v>289</v>
+        <v>1096</v>
       </c>
       <c r="C17" s="3">
-        <v>2827</v>
+        <v>2535</v>
       </c>
       <c r="D17" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -4208,45 +4208,45 @@
       <c r="F17" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="3">
-        <v>25</v>
+      <c r="G17" s="4">
+        <v>72.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>290</v>
+        <v>1099</v>
       </c>
       <c r="B18" t="s">
-        <v>291</v>
+        <v>1100</v>
       </c>
       <c r="C18" s="3">
-        <v>3801</v>
+        <v>2236</v>
       </c>
       <c r="D18" s="3">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="3">
-        <v>25</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>296</v>
+        <v>1099</v>
       </c>
       <c r="B19" t="s">
-        <v>297</v>
+        <v>1100</v>
       </c>
       <c r="C19" s="3">
-        <v>3764</v>
+        <v>2546</v>
       </c>
       <c r="D19" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -4254,191 +4254,697 @@
       <c r="F19" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="3">
-        <v>81</v>
+      <c r="G19" s="4">
+        <v>72.5</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>313</v>
+        <v>1101</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>1102</v>
       </c>
       <c r="C20" s="3">
-        <v>3402</v>
+        <v>2232</v>
       </c>
       <c r="D20" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>306</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="4">
-        <v>46.5</v>
+        <v>10</v>
+      </c>
+      <c r="G20" s="3">
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>313</v>
+        <v>1101</v>
       </c>
       <c r="B21" t="s">
-        <v>314</v>
+        <v>1102</v>
       </c>
       <c r="C21" s="3">
-        <v>3401</v>
+        <v>2536</v>
       </c>
       <c r="D21" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>315</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G21" s="4">
-        <v>66.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>313</v>
+        <v>1066</v>
       </c>
       <c r="B22" t="s">
-        <v>314</v>
+        <v>1067</v>
       </c>
       <c r="C22" s="3">
-        <v>3403</v>
+        <v>2452</v>
       </c>
       <c r="D22" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>308</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" s="4">
-        <v>38.5</v>
+        <v>10</v>
+      </c>
+      <c r="G22" s="3">
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>316</v>
+        <v>1066</v>
       </c>
       <c r="B23" t="s">
-        <v>317</v>
+        <v>1067</v>
       </c>
       <c r="C23" s="3">
-        <v>4032</v>
+        <v>150</v>
       </c>
       <c r="D23" s="3">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>318</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="4">
-        <v>57.5</v>
+        <v>156</v>
+      </c>
+      <c r="G23" s="3">
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>319</v>
+        <v>1066</v>
       </c>
       <c r="B24" t="s">
-        <v>320</v>
+        <v>1067</v>
       </c>
       <c r="C24" s="3">
-        <v>4460</v>
+        <v>2453</v>
       </c>
       <c r="D24" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>318</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" s="4">
-        <v>57.5</v>
+        <v>10</v>
+      </c>
+      <c r="G24" s="3">
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>324</v>
+        <v>1068</v>
       </c>
       <c r="B25" t="s">
-        <v>325</v>
+        <v>1069</v>
       </c>
       <c r="C25" s="3">
-        <v>2551</v>
+        <v>2450</v>
       </c>
       <c r="D25" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>306</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G25" s="3">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>326</v>
+        <v>1068</v>
       </c>
       <c r="B26" t="s">
-        <v>327</v>
+        <v>1069</v>
       </c>
       <c r="C26" s="3">
-        <v>2550</v>
+        <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>328</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="4">
-        <v>25.5</v>
+        <v>156</v>
+      </c>
+      <c r="G26" s="3">
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2451</v>
+      </c>
+      <c r="D27" s="3">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2643</v>
+      </c>
+      <c r="D28" s="3">
+        <v>5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2644</v>
+      </c>
+      <c r="D29" s="3">
+        <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2570</v>
+      </c>
+      <c r="D30" s="3">
+        <v>5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C31" s="3">
+        <v>3021</v>
+      </c>
+      <c r="D31" s="3">
+        <v>5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>274</v>
+      </c>
+      <c r="B32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2825</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>276</v>
+      </c>
+      <c r="B33" t="s">
+        <v>277</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2828</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" t="s">
+        <v>279</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2826</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" t="s">
+        <v>281</v>
+      </c>
+      <c r="C35" s="3">
+        <v>3058</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>282</v>
+      </c>
+      <c r="B36" t="s">
+        <v>283</v>
+      </c>
+      <c r="C36" s="3">
+        <v>3059</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>284</v>
+      </c>
+      <c r="B37" t="s">
+        <v>285</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2829</v>
+      </c>
+      <c r="D37" s="3">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>286</v>
+      </c>
+      <c r="B38" t="s">
+        <v>287</v>
+      </c>
+      <c r="C38" s="3">
+        <v>4126</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>288</v>
+      </c>
+      <c r="B39" t="s">
+        <v>289</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2827</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>290</v>
+      </c>
+      <c r="B40" t="s">
+        <v>291</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3801</v>
+      </c>
+      <c r="D40" s="3">
+        <v>500</v>
+      </c>
+      <c r="E40" t="s">
+        <v>253</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>296</v>
+      </c>
+      <c r="B41" t="s">
+        <v>297</v>
+      </c>
+      <c r="C41" s="3">
+        <v>3764</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>313</v>
+      </c>
+      <c r="B42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3402</v>
+      </c>
+      <c r="D42" s="3">
+        <v>6</v>
+      </c>
+      <c r="E42" t="s">
+        <v>306</v>
+      </c>
+      <c r="F42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>313</v>
+      </c>
+      <c r="B43" t="s">
+        <v>314</v>
+      </c>
+      <c r="C43" s="3">
+        <v>3401</v>
+      </c>
+      <c r="D43" s="3">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>315</v>
+      </c>
+      <c r="F43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" s="4">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>313</v>
+      </c>
+      <c r="B44" t="s">
+        <v>314</v>
+      </c>
+      <c r="C44" s="3">
+        <v>3403</v>
+      </c>
+      <c r="D44" s="3">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>308</v>
+      </c>
+      <c r="F44" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" s="4">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>316</v>
+      </c>
+      <c r="B45" t="s">
+        <v>317</v>
+      </c>
+      <c r="C45" s="3">
+        <v>4032</v>
+      </c>
+      <c r="D45" s="3">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>318</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" s="4">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>319</v>
+      </c>
+      <c r="B46" t="s">
+        <v>320</v>
+      </c>
+      <c r="C46" s="3">
+        <v>4460</v>
+      </c>
+      <c r="D46" s="3">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>318</v>
+      </c>
+      <c r="F46" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" s="4">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>324</v>
+      </c>
+      <c r="B47" t="s">
+        <v>325</v>
+      </c>
+      <c r="C47" s="3">
+        <v>2551</v>
+      </c>
+      <c r="D47" s="3">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>306</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>326</v>
+      </c>
+      <c r="B48" t="s">
+        <v>327</v>
+      </c>
+      <c r="C48" s="3">
+        <v>2550</v>
+      </c>
+      <c r="D48" s="3">
+        <v>6</v>
+      </c>
+      <c r="E48" t="s">
+        <v>328</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" s="4">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>329</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B49" t="s">
         <v>330</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C49" s="3">
         <v>4383</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D49" s="3">
         <v>12</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E49" t="s">
         <v>318</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F49" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G49" s="3">
         <v>53</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Documents\lista-bourached\Lista-de-Produtos-Bourached\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF3AF5A-9580-46BE-A06E-AF672E9AEAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC21806D-DB48-4492-99F4-5E691F451875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="420" windowWidth="13710" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3786" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="1125">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3406,6 +3406,12 @@
   </si>
   <si>
     <t>XEREM DE AMENDOIM</t>
+  </si>
+  <si>
+    <t>pecarbonato-jezza</t>
+  </si>
+  <si>
+    <t>PECARBONATO JEZZA</t>
   </si>
 </sst>
 </file>
@@ -15262,7 +15268,7 @@
         <v>10</v>
       </c>
       <c r="G67" s="3">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15285,7 +15291,7 @@
         <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>72.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15308,7 +15314,7 @@
         <v>10</v>
       </c>
       <c r="G69" s="4">
-        <v>72.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15331,7 +15337,7 @@
         <v>10</v>
       </c>
       <c r="G70" s="3">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15354,7 +15360,7 @@
         <v>10</v>
       </c>
       <c r="G71" s="3">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15377,7 +15383,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="4">
-        <v>72.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15446,7 +15452,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="3">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15469,7 +15475,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="4">
-        <v>72.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15492,7 +15498,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="3">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15515,7 +15521,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="4">
-        <v>72.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20064,7 +20070,7 @@
         <v>156</v>
       </c>
       <c r="G4" s="3">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20087,7 +20093,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23020,7 +23026,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
@@ -23241,36 +23247,36 @@
     </row>
     <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>560</v>
+        <v>1123</v>
       </c>
       <c r="B10" t="s">
-        <v>561</v>
+        <v>1124</v>
       </c>
       <c r="C10" s="3">
-        <v>2222</v>
+        <v>4657</v>
       </c>
       <c r="D10" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="4">
-        <v>132.5</v>
+        <v>49</v>
+      </c>
+      <c r="G10" s="3">
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B11" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C11" s="3">
-        <v>3572</v>
+        <v>2222</v>
       </c>
       <c r="D11" s="3">
         <v>25</v>
@@ -23281,31 +23287,31 @@
       <c r="F11" t="s">
         <v>156</v>
       </c>
-      <c r="G11" s="3">
-        <v>128</v>
+      <c r="G11" s="4">
+        <v>132.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B12" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C12" s="3">
-        <v>2522</v>
+        <v>3572</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G12" s="3">
-        <v>49</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23316,30 +23322,30 @@
         <v>565</v>
       </c>
       <c r="C13" s="3">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="D13" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G13" s="3">
-        <v>490</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B14" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C14" s="3">
-        <v>2571</v>
+        <v>2521</v>
       </c>
       <c r="D14" s="3">
         <v>10</v>
@@ -23348,10 +23354,10 @@
         <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="G14" s="3">
-        <v>185</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23362,42 +23368,42 @@
         <v>567</v>
       </c>
       <c r="C15" s="3">
-        <v>4108</v>
+        <v>2571</v>
       </c>
       <c r="D15" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="4">
-        <v>95.5</v>
+        <v>156</v>
+      </c>
+      <c r="G15" s="3">
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B16" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C16" s="3">
-        <v>4111</v>
+        <v>4108</v>
       </c>
       <c r="D16" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>156</v>
-      </c>
-      <c r="G16" s="3">
-        <v>180</v>
+        <v>10</v>
+      </c>
+      <c r="G16" s="4">
+        <v>95.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23408,42 +23414,42 @@
         <v>569</v>
       </c>
       <c r="C17" s="3">
-        <v>3499</v>
+        <v>4111</v>
       </c>
       <c r="D17" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G17" s="3">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C18" s="3">
-        <v>2616</v>
+        <v>3499</v>
       </c>
       <c r="D18" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G18" s="3">
-        <v>1875</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23454,30 +23460,30 @@
         <v>571</v>
       </c>
       <c r="C19" s="3">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="D19" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G19" s="3">
-        <v>375</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B20" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C20" s="3">
-        <v>4283</v>
+        <v>2615</v>
       </c>
       <c r="D20" s="3">
         <v>5</v>
@@ -23489,30 +23495,30 @@
         <v>10</v>
       </c>
       <c r="G20" s="3">
-        <v>170</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B21" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C21" s="3">
-        <v>4114</v>
+        <v>4283</v>
       </c>
       <c r="D21" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>156</v>
-      </c>
-      <c r="G21" s="4">
-        <v>62.5</v>
+        <v>10</v>
+      </c>
+      <c r="G21" s="3">
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23523,33 +23529,33 @@
         <v>575</v>
       </c>
       <c r="C22" s="3">
-        <v>3493</v>
+        <v>4114</v>
       </c>
       <c r="D22" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="3">
-        <v>33</v>
+        <v>156</v>
+      </c>
+      <c r="G22" s="4">
+        <v>62.5</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B23" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C23" s="3">
-        <v>4395</v>
+        <v>3493</v>
       </c>
       <c r="D23" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -23558,7 +23564,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="3">
-        <v>320</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23569,10 +23575,10 @@
         <v>577</v>
       </c>
       <c r="C24" s="3">
-        <v>4394</v>
+        <v>4395</v>
       </c>
       <c r="D24" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -23581,33 +23587,33 @@
         <v>10</v>
       </c>
       <c r="G24" s="3">
-        <v>97</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B25" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C25" s="3">
-        <v>4115</v>
+        <v>4394</v>
       </c>
       <c r="D25" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G25" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>578</v>
       </c>
@@ -23615,42 +23621,42 @@
         <v>579</v>
       </c>
       <c r="C26" s="3">
-        <v>3497</v>
+        <v>4115</v>
       </c>
       <c r="D26" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G26" s="3">
-        <v>122</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B27" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C27" s="3">
-        <v>2492</v>
+        <v>3497</v>
       </c>
       <c r="D27" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G27" s="3">
-        <v>348</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23661,42 +23667,42 @@
         <v>581</v>
       </c>
       <c r="C28" s="3">
-        <v>2499</v>
+        <v>2492</v>
       </c>
       <c r="D28" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G28" s="3">
-        <v>29</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B29" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C29" s="3">
-        <v>3101</v>
+        <v>2499</v>
       </c>
       <c r="D29" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>156</v>
-      </c>
-      <c r="G29" s="4">
-        <v>77.5</v>
+        <v>10</v>
+      </c>
+      <c r="G29" s="3">
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23707,10 +23713,10 @@
         <v>583</v>
       </c>
       <c r="C30" s="3">
-        <v>580</v>
+        <v>3101</v>
       </c>
       <c r="D30" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -23718,22 +23724,22 @@
       <c r="F30" t="s">
         <v>156</v>
       </c>
-      <c r="G30" s="3">
-        <v>31</v>
+      <c r="G30" s="4">
+        <v>77.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B31" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C31" s="3">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D31" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -23742,41 +23748,41 @@
         <v>156</v>
       </c>
       <c r="G31" s="3">
-        <v>112.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B32" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C32" s="3">
-        <v>4029</v>
+        <v>581</v>
       </c>
       <c r="D32" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="G32" s="3">
-        <v>122</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B33" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C33" s="3">
-        <v>4203</v>
+        <v>4029</v>
       </c>
       <c r="D33" s="3">
         <v>20</v>
@@ -23785,47 +23791,47 @@
         <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="G33" s="3">
-        <v>86</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B34" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C34" s="3">
-        <v>3936</v>
+        <v>4203</v>
       </c>
       <c r="D34" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G34" s="3">
-        <v>192</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B35" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C35" s="3">
-        <v>4302</v>
+        <v>3936</v>
       </c>
       <c r="D35" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
         <v>38</v>
@@ -23833,31 +23839,31 @@
       <c r="F35" t="s">
         <v>15</v>
       </c>
-      <c r="G35" s="4">
-        <v>103.5</v>
+      <c r="G35" s="3">
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B36" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C36" s="3">
-        <v>3027</v>
+        <v>4302</v>
       </c>
       <c r="D36" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="G36" s="4">
-        <v>31.5</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23868,42 +23874,42 @@
         <v>595</v>
       </c>
       <c r="C37" s="3">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="D37" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
-        <v>49</v>
-      </c>
-      <c r="G37" s="3">
-        <v>44</v>
+        <v>156</v>
+      </c>
+      <c r="G37" s="4">
+        <v>31.5</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B38" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C38" s="3">
-        <v>3514</v>
+        <v>3026</v>
       </c>
       <c r="D38" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="G38" s="3">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23914,42 +23920,42 @@
         <v>597</v>
       </c>
       <c r="C39" s="3">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="D39" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="G39" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B40" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C40" s="3">
-        <v>3139</v>
+        <v>3515</v>
       </c>
       <c r="D40" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="G40" s="3">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23960,10 +23966,10 @@
         <v>599</v>
       </c>
       <c r="C41" s="3">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="D41" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>29</v>
@@ -23972,30 +23978,30 @@
         <v>156</v>
       </c>
       <c r="G41" s="3">
-        <v>300</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B42" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C42" s="3">
-        <v>2592</v>
+        <v>3138</v>
       </c>
       <c r="D42" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
         <v>29</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="4">
-        <v>27.5</v>
+        <v>156</v>
+      </c>
+      <c r="G42" s="3">
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24006,53 +24012,53 @@
         <v>601</v>
       </c>
       <c r="C43" s="3">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="D43" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
         <v>29</v>
       </c>
       <c r="F43" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G43" s="4">
-        <v>337.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B44" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C44" s="3">
-        <v>2597</v>
+        <v>2591</v>
       </c>
       <c r="D44" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
         <v>29</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="3">
-        <v>90</v>
+        <v>156</v>
+      </c>
+      <c r="G44" s="4">
+        <v>337.5</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B45" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C45" s="3">
-        <v>4174</v>
+        <v>2597</v>
       </c>
       <c r="D45" s="3">
         <v>5</v>
@@ -24064,18 +24070,18 @@
         <v>10</v>
       </c>
       <c r="G45" s="3">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B46" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C46" s="3">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="D46" s="3">
         <v>5</v>
@@ -24087,18 +24093,18 @@
         <v>10</v>
       </c>
       <c r="G46" s="3">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B47" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C47" s="3">
-        <v>2686</v>
+        <v>4176</v>
       </c>
       <c r="D47" s="3">
         <v>5</v>
@@ -24109,19 +24115,19 @@
       <c r="F47" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="4">
-        <v>64.5</v>
+      <c r="G47" s="3">
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B48" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C48" s="3">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="D48" s="3">
         <v>5</v>
@@ -24138,13 +24144,13 @@
     </row>
     <row r="49" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B49" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C49" s="3">
-        <v>4496</v>
+        <v>2687</v>
       </c>
       <c r="D49" s="3">
         <v>5</v>
@@ -24155,19 +24161,19 @@
       <c r="F49" t="s">
         <v>10</v>
       </c>
-      <c r="G49" s="3">
-        <v>125</v>
+      <c r="G49" s="4">
+        <v>64.5</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B50" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C50" s="3">
-        <v>4061</v>
+        <v>4496</v>
       </c>
       <c r="D50" s="3">
         <v>5</v>
@@ -24184,13 +24190,13 @@
     </row>
     <row r="51" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B51" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C51" s="3">
-        <v>4166</v>
+        <v>4061</v>
       </c>
       <c r="D51" s="3">
         <v>5</v>
@@ -24207,13 +24213,13 @@
     </row>
     <row r="52" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B52" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C52" s="3">
-        <v>2681</v>
+        <v>4166</v>
       </c>
       <c r="D52" s="3">
         <v>5</v>
@@ -24225,18 +24231,18 @@
         <v>10</v>
       </c>
       <c r="G52" s="3">
-        <v>42</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B53" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C53" s="3">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="D53" s="3">
         <v>5</v>
@@ -24248,18 +24254,18 @@
         <v>10</v>
       </c>
       <c r="G53" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B54" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C54" s="3">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="D54" s="3">
         <v>5</v>
@@ -24276,13 +24282,13 @@
     </row>
     <row r="55" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B55" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C55" s="3">
-        <v>2600</v>
+        <v>2683</v>
       </c>
       <c r="D55" s="3">
         <v>5</v>
@@ -24294,18 +24300,18 @@
         <v>10</v>
       </c>
       <c r="G55" s="3">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C56" s="3">
-        <v>4167</v>
+        <v>2600</v>
       </c>
       <c r="D56" s="3">
         <v>5</v>
@@ -24317,18 +24323,18 @@
         <v>10</v>
       </c>
       <c r="G56" s="3">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B57" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C57" s="3">
-        <v>2595</v>
+        <v>4167</v>
       </c>
       <c r="D57" s="3">
         <v>5</v>
@@ -24340,18 +24346,18 @@
         <v>10</v>
       </c>
       <c r="G57" s="3">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B58" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C58" s="3">
-        <v>4062</v>
+        <v>2595</v>
       </c>
       <c r="D58" s="3">
         <v>5</v>
@@ -24368,13 +24374,13 @@
     </row>
     <row r="59" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B59" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C59" s="3">
-        <v>2707</v>
+        <v>4062</v>
       </c>
       <c r="D59" s="3">
         <v>5</v>
@@ -24391,25 +24397,25 @@
     </row>
     <row r="60" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B60" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C60" s="3">
-        <v>3605</v>
+        <v>2707</v>
       </c>
       <c r="D60" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>29</v>
       </c>
       <c r="F60" t="s">
-        <v>156</v>
-      </c>
-      <c r="G60" s="4">
-        <v>212.5</v>
+        <v>10</v>
+      </c>
+      <c r="G60" s="3">
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24420,33 +24426,33 @@
         <v>635</v>
       </c>
       <c r="C61" s="3">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="D61" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
         <v>29</v>
       </c>
       <c r="F61" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="3">
-        <v>27</v>
+        <v>156</v>
+      </c>
+      <c r="G61" s="4">
+        <v>212.5</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B62" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C62" s="3">
-        <v>4402</v>
+        <v>3606</v>
       </c>
       <c r="D62" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
         <v>29</v>
@@ -24455,7 +24461,7 @@
         <v>10</v>
       </c>
       <c r="G62" s="3">
-        <v>160</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24466,10 +24472,10 @@
         <v>637</v>
       </c>
       <c r="C63" s="3">
-        <v>4401</v>
+        <v>4402</v>
       </c>
       <c r="D63" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>29</v>
@@ -24478,18 +24484,18 @@
         <v>10</v>
       </c>
       <c r="G63" s="3">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B64" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C64" s="3">
-        <v>2684</v>
+        <v>4401</v>
       </c>
       <c r="D64" s="3">
         <v>5</v>
@@ -24500,19 +24506,19 @@
       <c r="F64" t="s">
         <v>10</v>
       </c>
-      <c r="G64" s="4">
-        <v>50.5</v>
+      <c r="G64" s="3">
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B65" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C65" s="3">
-        <v>2723</v>
+        <v>2684</v>
       </c>
       <c r="D65" s="3">
         <v>5</v>
@@ -24523,8 +24529,8 @@
       <c r="F65" t="s">
         <v>10</v>
       </c>
-      <c r="G65" s="3">
-        <v>105</v>
+      <c r="G65" s="4">
+        <v>50.5</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24535,65 +24541,65 @@
         <v>641</v>
       </c>
       <c r="C66" s="3">
-        <v>2734</v>
+        <v>2723</v>
       </c>
       <c r="D66" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
-        <v>337</v>
+        <v>29</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="3">
-        <v>630</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B67" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C67" s="3">
-        <v>4168</v>
+        <v>2734</v>
       </c>
       <c r="D67" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>337</v>
       </c>
       <c r="F67" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="3">
-        <v>125</v>
+        <v>630</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B68" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C68" s="3">
-        <v>2718</v>
+        <v>4168</v>
       </c>
       <c r="D68" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>29</v>
       </c>
       <c r="F68" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G68" s="3">
-        <v>750</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24604,30 +24610,30 @@
         <v>645</v>
       </c>
       <c r="C69" s="3">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="D69" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
         <v>29</v>
       </c>
       <c r="F69" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="4">
-        <v>172.5</v>
+        <v>156</v>
+      </c>
+      <c r="G69" s="3">
+        <v>750</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B70" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C70" s="3">
-        <v>3094</v>
+        <v>2719</v>
       </c>
       <c r="D70" s="3">
         <v>5</v>
@@ -24638,19 +24644,19 @@
       <c r="F70" t="s">
         <v>10</v>
       </c>
-      <c r="G70" s="3">
-        <v>64</v>
+      <c r="G70" s="4">
+        <v>172.5</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B71" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C71" s="3">
-        <v>4169</v>
+        <v>3094</v>
       </c>
       <c r="D71" s="3">
         <v>5</v>
@@ -24662,18 +24668,18 @@
         <v>10</v>
       </c>
       <c r="G71" s="3">
-        <v>140</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B72" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C72" s="3">
-        <v>2685</v>
+        <v>4169</v>
       </c>
       <c r="D72" s="3">
         <v>5</v>
@@ -24685,30 +24691,30 @@
         <v>10</v>
       </c>
       <c r="G72" s="3">
-        <v>72</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B73" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C73" s="3">
-        <v>4113</v>
+        <v>2685</v>
       </c>
       <c r="D73" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>29</v>
       </c>
       <c r="F73" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G73" s="3">
-        <v>189</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24719,30 +24725,30 @@
         <v>653</v>
       </c>
       <c r="C74" s="3">
-        <v>4106</v>
+        <v>4113</v>
       </c>
       <c r="D74" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E74" t="s">
         <v>29</v>
       </c>
       <c r="F74" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G74" s="3">
-        <v>96</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B75" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C75" s="3">
-        <v>2596</v>
+        <v>4106</v>
       </c>
       <c r="D75" s="3">
         <v>5</v>
@@ -24754,21 +24760,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="3">
-        <v>125</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B76" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C76" s="3">
-        <v>4457</v>
+        <v>2596</v>
       </c>
       <c r="D76" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E76" t="s">
         <v>29</v>
@@ -24777,7 +24783,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="3">
-        <v>224</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24788,10 +24794,10 @@
         <v>657</v>
       </c>
       <c r="C77" s="3">
-        <v>4458</v>
+        <v>4457</v>
       </c>
       <c r="D77" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E77" t="s">
         <v>29</v>
@@ -24800,30 +24806,30 @@
         <v>10</v>
       </c>
       <c r="G77" s="3">
-        <v>114</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B78" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C78" s="3">
-        <v>2602</v>
+        <v>4458</v>
       </c>
       <c r="D78" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>29</v>
       </c>
       <c r="F78" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G78" s="3">
-        <v>330</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24834,19 +24840,19 @@
         <v>659</v>
       </c>
       <c r="C79" s="3">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="D79" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>29</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G79" s="3">
-        <v>33</v>
+        <v>330</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24857,33 +24863,33 @@
         <v>659</v>
       </c>
       <c r="C80" s="3">
-        <v>3894</v>
+        <v>2605</v>
       </c>
       <c r="D80" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E80" t="s">
         <v>29</v>
       </c>
       <c r="F80" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G80" s="3">
-        <v>825</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B81" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C81" s="3">
-        <v>4109</v>
+        <v>3894</v>
       </c>
       <c r="D81" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
         <v>29</v>
@@ -24892,7 +24898,7 @@
         <v>156</v>
       </c>
       <c r="G81" s="3">
-        <v>148</v>
+        <v>825</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24903,10 +24909,10 @@
         <v>661</v>
       </c>
       <c r="C82" s="3">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D82" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>29</v>
@@ -24915,18 +24921,18 @@
         <v>156</v>
       </c>
       <c r="G82" s="3">
-        <v>76</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B83" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C83" s="3">
-        <v>4171</v>
+        <v>4110</v>
       </c>
       <c r="D83" s="3">
         <v>5</v>
@@ -24935,21 +24941,21 @@
         <v>29</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G83" s="3">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B84" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C84" s="3">
-        <v>2653</v>
+        <v>4171</v>
       </c>
       <c r="D84" s="3">
         <v>5</v>
@@ -24961,21 +24967,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="3">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B85" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C85" s="3">
-        <v>3675</v>
+        <v>2653</v>
       </c>
       <c r="D85" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E85" t="s">
         <v>29</v>
@@ -24984,30 +24990,30 @@
         <v>10</v>
       </c>
       <c r="G85" s="3">
-        <v>132</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B86" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C86" s="3">
-        <v>2417</v>
+        <v>3675</v>
       </c>
       <c r="D86" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E86" t="s">
         <v>29</v>
       </c>
       <c r="F86" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G86" s="3">
-        <v>182</v>
+        <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25018,33 +25024,33 @@
         <v>669</v>
       </c>
       <c r="C87" s="3">
-        <v>3109</v>
+        <v>2417</v>
       </c>
       <c r="D87" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
         <v>29</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" s="4">
-        <v>38.5</v>
+        <v>156</v>
+      </c>
+      <c r="G87" s="3">
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B88" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C88" s="3">
-        <v>2777</v>
+        <v>3109</v>
       </c>
       <c r="D88" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E88" t="s">
         <v>29</v>
@@ -25052,8 +25058,8 @@
       <c r="F88" t="s">
         <v>10</v>
       </c>
-      <c r="G88" s="3">
-        <v>180</v>
+      <c r="G88" s="4">
+        <v>38.5</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25064,10 +25070,10 @@
         <v>671</v>
       </c>
       <c r="C89" s="3">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="D89" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" t="s">
         <v>29</v>
@@ -25076,18 +25082,18 @@
         <v>10</v>
       </c>
       <c r="G89" s="3">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B90" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C90" s="3">
-        <v>4173</v>
+        <v>2776</v>
       </c>
       <c r="D90" s="3">
         <v>5</v>
@@ -25099,18 +25105,18 @@
         <v>10</v>
       </c>
       <c r="G90" s="3">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B91" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C91" s="3">
-        <v>2689</v>
+        <v>4173</v>
       </c>
       <c r="D91" s="3">
         <v>5</v>
@@ -25122,18 +25128,18 @@
         <v>10</v>
       </c>
       <c r="G91" s="3">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B92" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C92" s="3">
-        <v>4170</v>
+        <v>2689</v>
       </c>
       <c r="D92" s="3">
         <v>5</v>
@@ -25145,30 +25151,30 @@
         <v>10</v>
       </c>
       <c r="G92" s="3">
-        <v>125</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B93" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C93" s="3">
-        <v>4494</v>
+        <v>4170</v>
       </c>
       <c r="D93" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E93" t="s">
         <v>29</v>
       </c>
       <c r="F93" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G93" s="3">
-        <v>300</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25179,30 +25185,30 @@
         <v>679</v>
       </c>
       <c r="C94" s="3">
-        <v>4495</v>
+        <v>4494</v>
       </c>
       <c r="D94" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>29</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G94" s="3">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B95" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C95" s="3">
-        <v>2785</v>
+        <v>4495</v>
       </c>
       <c r="D95" s="3">
         <v>5</v>
@@ -25213,8 +25219,8 @@
       <c r="F95" t="s">
         <v>10</v>
       </c>
-      <c r="G95" s="4">
-        <v>47.5</v>
+      <c r="G95" s="3">
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25225,30 +25231,30 @@
         <v>681</v>
       </c>
       <c r="C96" s="3">
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="D96" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E96" t="s">
         <v>29</v>
       </c>
       <c r="F96" t="s">
-        <v>156</v>
-      </c>
-      <c r="G96" s="3">
-        <v>95</v>
+        <v>10</v>
+      </c>
+      <c r="G96" s="4">
+        <v>47.5</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B97" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C97" s="3">
-        <v>2788</v>
+        <v>2784</v>
       </c>
       <c r="D97" s="3">
         <v>10</v>
@@ -25260,7 +25266,7 @@
         <v>156</v>
       </c>
       <c r="G97" s="3">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25271,42 +25277,42 @@
         <v>683</v>
       </c>
       <c r="C98" s="3">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="D98" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
         <v>29</v>
       </c>
       <c r="F98" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G98" s="3">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B99" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C99" s="3">
-        <v>4539</v>
+        <v>2789</v>
       </c>
       <c r="D99" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E99" t="s">
         <v>29</v>
       </c>
       <c r="F99" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G99" s="3">
-        <v>95</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25317,42 +25323,42 @@
         <v>685</v>
       </c>
       <c r="C100" s="3">
-        <v>3495</v>
+        <v>4539</v>
       </c>
       <c r="D100" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
         <v>29</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="4">
-        <v>47.5</v>
+        <v>156</v>
+      </c>
+      <c r="G100" s="3">
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B101" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C101" s="3">
-        <v>2786</v>
+        <v>3495</v>
       </c>
       <c r="D101" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E101" t="s">
         <v>29</v>
       </c>
       <c r="F101" t="s">
-        <v>156</v>
-      </c>
-      <c r="G101" s="3">
-        <v>90</v>
+        <v>10</v>
+      </c>
+      <c r="G101" s="4">
+        <v>47.5</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25363,30 +25369,30 @@
         <v>687</v>
       </c>
       <c r="C102" s="3">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="D102" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
         <v>29</v>
       </c>
       <c r="F102" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G102" s="3">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B103" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C103" s="3">
-        <v>2598</v>
+        <v>2787</v>
       </c>
       <c r="D103" s="3">
         <v>5</v>
@@ -25398,18 +25404,18 @@
         <v>10</v>
       </c>
       <c r="G103" s="3">
-        <v>130</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B104" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C104" s="3">
-        <v>4060</v>
+        <v>2598</v>
       </c>
       <c r="D104" s="3">
         <v>5</v>
@@ -25421,18 +25427,18 @@
         <v>10</v>
       </c>
       <c r="G104" s="3">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B105" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C105" s="3">
-        <v>2690</v>
+        <v>4060</v>
       </c>
       <c r="D105" s="3">
         <v>5</v>
@@ -25444,30 +25450,30 @@
         <v>10</v>
       </c>
       <c r="G105" s="3">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B106" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C106" s="3">
-        <v>3355</v>
+        <v>2690</v>
       </c>
       <c r="D106" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
         <v>29</v>
       </c>
       <c r="F106" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G106" s="3">
-        <v>315</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25478,42 +25484,42 @@
         <v>695</v>
       </c>
       <c r="C107" s="3">
-        <v>3066</v>
+        <v>3355</v>
       </c>
       <c r="D107" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
         <v>29</v>
       </c>
       <c r="F107" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G107" s="3">
-        <v>65</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B108" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C108" s="3">
-        <v>1515</v>
+        <v>3066</v>
       </c>
       <c r="D108" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
         <v>29</v>
       </c>
       <c r="F108" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G108" s="3">
-        <v>1175</v>
+        <v>65</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25524,30 +25530,30 @@
         <v>697</v>
       </c>
       <c r="C109" s="3">
-        <v>2552</v>
+        <v>1515</v>
       </c>
       <c r="D109" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E109" t="s">
         <v>29</v>
       </c>
       <c r="F109" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G109" s="3">
-        <v>235</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B110" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C110" s="3">
-        <v>3092</v>
+        <v>2552</v>
       </c>
       <c r="D110" s="3">
         <v>5</v>
@@ -25558,22 +25564,22 @@
       <c r="F110" t="s">
         <v>10</v>
       </c>
-      <c r="G110" s="4">
-        <v>73.5</v>
+      <c r="G110" s="3">
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B111" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C111" s="3">
-        <v>2589</v>
+        <v>3092</v>
       </c>
       <c r="D111" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E111" t="s">
         <v>29</v>
@@ -25581,8 +25587,8 @@
       <c r="F111" t="s">
         <v>10</v>
       </c>
-      <c r="G111" s="3">
-        <v>200</v>
+      <c r="G111" s="4">
+        <v>73.5</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25593,10 +25599,10 @@
         <v>701</v>
       </c>
       <c r="C112" s="3">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="D112" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E112" t="s">
         <v>29</v>
@@ -25605,21 +25611,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="3">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B113" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C113" s="3">
-        <v>2688</v>
+        <v>2588</v>
       </c>
       <c r="D113" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" t="s">
         <v>29</v>
@@ -25628,29 +25634,52 @@
         <v>10</v>
       </c>
       <c r="G113" s="3">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>702</v>
+      </c>
+      <c r="B114" t="s">
+        <v>703</v>
+      </c>
+      <c r="C114" s="3">
+        <v>2688</v>
+      </c>
+      <c r="D114" s="3">
+        <v>5</v>
+      </c>
+      <c r="E114" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>704</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B115" t="s">
         <v>705</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C115" s="3">
         <v>2599</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D115" s="3">
         <v>3</v>
       </c>
-      <c r="E114" t="s">
-        <v>29</v>
-      </c>
-      <c r="F114" t="s">
-        <v>10</v>
-      </c>
-      <c r="G114" s="3">
+      <c r="E115" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" s="3">
         <v>84</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Documents\lista-bourached\Lista-de-Produtos-Bourached\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC21806D-DB48-4492-99F4-5E691F451875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847E6636-A384-4AA8-8C92-080B0C436CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -5479,7 +5479,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="3">
-        <v>420</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6811,7 +6811,7 @@
         <v>156</v>
       </c>
       <c r="G19" s="3">
-        <v>750</v>
+        <v>575</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6834,7 +6834,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="3">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7110,7 +7110,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="4">
-        <v>259.5</v>
+        <v>228.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8398,7 +8398,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="4">
-        <v>145.5</v>
+        <v>127</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8421,7 +8421,7 @@
         <v>156</v>
       </c>
       <c r="G89" s="3">
-        <v>360</v>
+        <v>310</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8444,7 +8444,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="3">
-        <v>900</v>
+        <v>775</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8720,7 +8720,7 @@
         <v>156</v>
       </c>
       <c r="G102" s="3">
-        <v>390</v>
+        <v>350</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8743,7 +8743,7 @@
         <v>10</v>
       </c>
       <c r="G103" s="3">
-        <v>197</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19887,7 +19887,7 @@
         <v>156</v>
       </c>
       <c r="G68" s="3">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19910,7 +19910,7 @@
         <v>10</v>
       </c>
       <c r="G69" s="3">
-        <v>150</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19933,7 +19933,7 @@
         <v>156</v>
       </c>
       <c r="G70" s="3">
-        <v>420</v>
+        <v>360</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19956,7 +19956,7 @@
         <v>156</v>
       </c>
       <c r="G71" s="3">
-        <v>210</v>
+        <v>183.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3786" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3778" uniqueCount="1125">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -5513,7 +5513,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -6235,7 +6235,7 @@
         <v>156</v>
       </c>
       <c r="G31" s="4">
-        <v>1325</v>
+        <v>1550</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -6246,33 +6246,33 @@
         <v>517</v>
       </c>
       <c r="C32" s="4">
-        <v>2680</v>
+        <v>2676</v>
       </c>
       <c r="D32" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="G32" s="4">
-        <v>720</v>
+        <v>313.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C33" s="4">
-        <v>2676</v>
+        <v>571</v>
       </c>
       <c r="D33" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>29</v>
@@ -6281,7 +6281,7 @@
         <v>156</v>
       </c>
       <c r="G33" s="4">
-        <v>278.5</v>
+        <v>287.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
@@ -6292,33 +6292,33 @@
         <v>519</v>
       </c>
       <c r="C34" s="4">
-        <v>571</v>
+        <v>2245</v>
       </c>
       <c r="D34" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>362.5</v>
+        <v>60.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C35" s="4">
-        <v>2245</v>
+        <v>3754</v>
       </c>
       <c r="D35" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>29</v>
@@ -6327,29 +6327,6 @@
         <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="C36" s="4">
-        <v>3754</v>
-      </c>
-      <c r="D36" s="4">
-        <v>3</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="4">
         <v>450</v>
       </c>
     </row>
@@ -16577,7 +16554,7 @@
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16600,7 +16577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>918</v>
       </c>
@@ -16623,7 +16600,7 @@
         <v>448</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>918</v>
       </c>
@@ -16646,7 +16623,7 @@
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>920</v>
       </c>
@@ -16669,7 +16646,7 @@
         <v>170</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>922</v>
       </c>
@@ -16692,7 +16669,7 @@
         <v>380</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>922</v>
       </c>
@@ -16715,7 +16692,7 @@
         <v>190</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>922</v>
       </c>
@@ -16738,7 +16715,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>924</v>
       </c>
@@ -16761,7 +16738,7 @@
         <v>950</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>924</v>
       </c>
@@ -16784,7 +16761,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>926</v>
       </c>
@@ -16807,7 +16784,7 @@
         <v>300</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>926</v>
       </c>
@@ -16830,7 +16807,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>928</v>
       </c>
@@ -16853,7 +16830,7 @@
         <v>320</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>928</v>
       </c>
@@ -16876,7 +16853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>930</v>
       </c>
@@ -16899,7 +16876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>930</v>
       </c>
@@ -16922,7 +16899,7 @@
         <v>170</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>932</v>
       </c>
@@ -16945,7 +16922,7 @@
         <v>225</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>932</v>
       </c>
@@ -16968,7 +16945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>934</v>
       </c>
@@ -16991,7 +16968,7 @@
         <v>340</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>934</v>
       </c>
@@ -17014,7 +16991,7 @@
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>936</v>
       </c>
@@ -17037,7 +17014,7 @@
         <v>530</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>936</v>
       </c>
@@ -17060,7 +17037,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>938</v>
       </c>
@@ -17083,7 +17060,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>940</v>
       </c>
@@ -17106,7 +17083,7 @@
         <v>300</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
         <v>940</v>
       </c>
@@ -17129,7 +17106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
         <v>942</v>
       </c>
@@ -19944,7 +19921,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -20850,7 +20827,7 @@
         <v>156</v>
       </c>
       <c r="G39" s="4">
-        <v>360</v>
+        <v>280</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
@@ -20873,7 +20850,7 @@
         <v>10</v>
       </c>
       <c r="G40" s="4">
-        <v>62</v>
+        <v>49.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
@@ -21494,7 +21471,7 @@
         <v>156</v>
       </c>
       <c r="G67" s="4">
-        <v>285</v>
+        <v>225</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -21505,42 +21482,42 @@
         <v>821</v>
       </c>
       <c r="C68" s="4">
-        <v>3740</v>
+        <v>2469</v>
       </c>
       <c r="D68" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G68" s="5">
-        <v>237.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C69" s="4">
-        <v>2469</v>
+        <v>3006</v>
       </c>
       <c r="D69" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G69" s="5">
-        <v>49.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -21551,42 +21528,42 @@
         <v>823</v>
       </c>
       <c r="C70" s="4">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="D70" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G70" s="5">
-        <v>312.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C71" s="4">
-        <v>3007</v>
+        <v>117</v>
       </c>
       <c r="D71" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G71" s="5">
-        <v>64.5</v>
+        <v>156</v>
+      </c>
+      <c r="G71" s="4">
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
@@ -21597,42 +21574,42 @@
         <v>825</v>
       </c>
       <c r="C72" s="4">
-        <v>117</v>
+        <v>2320</v>
       </c>
       <c r="D72" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G72" s="4">
-        <v>300</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C73" s="4">
-        <v>2320</v>
+        <v>60</v>
       </c>
       <c r="D73" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G73" s="4">
-        <v>62</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -21643,42 +21620,42 @@
         <v>827</v>
       </c>
       <c r="C74" s="4">
-        <v>60</v>
+        <v>2321</v>
       </c>
       <c r="D74" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G74" s="4">
-        <v>180</v>
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C75" s="4">
-        <v>2321</v>
-      </c>
-      <c r="D75" s="4">
-        <v>5</v>
+        <v>211</v>
+      </c>
+      <c r="D75" s="5">
+        <v>22.68</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="4">
-        <v>38</v>
+        <v>156</v>
+      </c>
+      <c r="G75" s="5">
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -21689,10 +21666,10 @@
         <v>829</v>
       </c>
       <c r="C76" s="4">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="D76" s="5">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>29</v>
@@ -21700,8 +21677,8 @@
       <c r="F76" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G76" s="5">
-        <v>187.5</v>
+      <c r="G76" s="4">
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -21712,42 +21689,42 @@
         <v>829</v>
       </c>
       <c r="C77" s="4">
-        <v>41</v>
-      </c>
-      <c r="D77" s="5">
-        <v>45.36</v>
+        <v>2322</v>
+      </c>
+      <c r="D77" s="4">
+        <v>5</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G77" s="4">
-        <v>375</v>
+        <v>10</v>
+      </c>
+      <c r="G77" s="5">
+        <v>43.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C78" s="4">
-        <v>2322</v>
-      </c>
-      <c r="D78" s="4">
-        <v>5</v>
+        <v>67</v>
+      </c>
+      <c r="D78" s="5">
+        <v>45.36</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="5">
-        <v>43.5</v>
+        <v>156</v>
+      </c>
+      <c r="G78" s="4">
+        <v>626</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
@@ -21758,10 +21735,10 @@
         <v>831</v>
       </c>
       <c r="C79" s="4">
-        <v>67</v>
+        <v>2244</v>
       </c>
       <c r="D79" s="5">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>29</v>
@@ -21770,7 +21747,7 @@
         <v>156</v>
       </c>
       <c r="G79" s="4">
-        <v>626</v>
+        <v>313</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
@@ -21781,65 +21758,65 @@
         <v>831</v>
       </c>
       <c r="C80" s="4">
-        <v>2244</v>
-      </c>
-      <c r="D80" s="5">
-        <v>22.68</v>
+        <v>2488</v>
+      </c>
+      <c r="D80" s="4">
+        <v>5</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G80" s="4">
-        <v>313</v>
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C81" s="4">
-        <v>2488</v>
+        <v>520</v>
       </c>
       <c r="D81" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G81" s="4">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C82" s="4">
-        <v>520</v>
+        <v>4546</v>
       </c>
       <c r="D82" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G82" s="4">
-        <v>52</v>
+        <v>182</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
@@ -21850,19 +21827,19 @@
         <v>835</v>
       </c>
       <c r="C83" s="4">
-        <v>4546</v>
+        <v>3695</v>
       </c>
       <c r="D83" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G83" s="4">
-        <v>182</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -21873,10 +21850,10 @@
         <v>835</v>
       </c>
       <c r="C84" s="4">
-        <v>3695</v>
+        <v>3097</v>
       </c>
       <c r="D84" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>29</v>
@@ -21885,7 +21862,7 @@
         <v>156</v>
       </c>
       <c r="G84" s="4">
-        <v>350</v>
+        <v>700</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -21896,56 +21873,56 @@
         <v>835</v>
       </c>
       <c r="C85" s="4">
-        <v>3097</v>
+        <v>2460</v>
       </c>
       <c r="D85" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G85" s="4">
-        <v>700</v>
+        <v>106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C86" s="4">
-        <v>2460</v>
+        <v>3110</v>
       </c>
       <c r="D86" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="G86" s="4">
-        <v>106</v>
+        <v>87</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C87" s="4">
-        <v>3110</v>
-      </c>
-      <c r="D87" s="4">
-        <v>25</v>
+        <v>135</v>
+      </c>
+      <c r="D87" s="5">
+        <v>22.68</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
@@ -21954,21 +21931,21 @@
         <v>156</v>
       </c>
       <c r="G87" s="4">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C88" s="4">
-        <v>135</v>
-      </c>
-      <c r="D88" s="5">
-        <v>22.68</v>
+        <v>2463</v>
+      </c>
+      <c r="D88" s="4">
+        <v>5</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
@@ -21977,21 +21954,21 @@
         <v>156</v>
       </c>
       <c r="G88" s="4">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C89" s="4">
-        <v>2463</v>
+        <v>55</v>
       </c>
       <c r="D89" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
@@ -22000,7 +21977,7 @@
         <v>156</v>
       </c>
       <c r="G89" s="4">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -22011,10 +21988,10 @@
         <v>843</v>
       </c>
       <c r="C90" s="4">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D90" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
@@ -22023,7 +22000,7 @@
         <v>156</v>
       </c>
       <c r="G90" s="4">
-        <v>114</v>
+        <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -22034,10 +22011,10 @@
         <v>843</v>
       </c>
       <c r="C91" s="4">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="D91" s="4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
@@ -22046,21 +22023,21 @@
         <v>156</v>
       </c>
       <c r="G91" s="4">
-        <v>27</v>
+        <v>228</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C92" s="4">
-        <v>201</v>
+        <v>4223</v>
       </c>
       <c r="D92" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
@@ -22069,7 +22046,7 @@
         <v>156</v>
       </c>
       <c r="G92" s="4">
-        <v>228</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -22080,41 +22057,18 @@
         <v>845</v>
       </c>
       <c r="C93" s="4">
-        <v>4223</v>
+        <v>4224</v>
       </c>
       <c r="D93" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G93" s="4">
-        <v>125</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>845</v>
-      </c>
-      <c r="C94" s="4">
-        <v>4224</v>
-      </c>
-      <c r="D94" s="4">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="4">
         <v>27</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -3419,7 +3419,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3437,6 +3437,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3511,7 +3517,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -5738,7 +5744,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="4">
-        <v>147</v>
+        <v>108.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -5761,7 +5767,7 @@
         <v>158</v>
       </c>
       <c r="G10" s="4">
-        <v>725</v>
+        <v>525</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -23801,7 +23807,7 @@
         <v>15</v>
       </c>
       <c r="G35" s="4">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3419,7 +3419,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3437,12 +3437,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3494,7 +3488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3515,9 +3509,6 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -6250,7 +6241,7 @@
         <v>158</v>
       </c>
       <c r="G31" s="4">
-        <v>1550</v>
+        <v>1875</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -6273,7 +6264,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>313.5</v>
+        <v>378.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -9398,7 +9389,7 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -9420,7 +9411,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -11567,10 +11558,10 @@
       <c r="B51" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="4">
         <v>2505</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="4">
         <v>2.5</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -11579,7 +11570,7 @@
       <c r="F51" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="4">
         <v>126</v>
       </c>
     </row>
@@ -13740,7 +13731,7 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -13762,7 +13753,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -20865,7 +20856,7 @@
         <v>158</v>
       </c>
       <c r="G39" s="4">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
@@ -20888,7 +20879,7 @@
         <v>10</v>
       </c>
       <c r="G40" s="4">
-        <v>49.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
@@ -20911,7 +20902,7 @@
         <v>10</v>
       </c>
       <c r="G41" s="5">
-        <v>24.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
@@ -20934,7 +20925,7 @@
         <v>158</v>
       </c>
       <c r="G42" s="4">
-        <v>135</v>
+        <v>165</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
@@ -20957,7 +20948,7 @@
         <v>158</v>
       </c>
       <c r="G43" s="4">
-        <v>270</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
@@ -22129,7 +22120,7 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -22151,7 +22142,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -23603,7 +23594,7 @@
         <v>240</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
         <v>582</v>
       </c>
@@ -23626,7 +23617,7 @@
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
         <v>584</v>
       </c>
@@ -23649,7 +23640,7 @@
         <v>348</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
         <v>584</v>
       </c>
@@ -23672,7 +23663,7 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
         <v>586</v>
       </c>
@@ -23695,7 +23686,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
         <v>586</v>
       </c>
@@ -23718,7 +23709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
         <v>588</v>
       </c>
@@ -23741,7 +23732,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
         <v>590</v>
       </c>
@@ -23764,7 +23755,7 @@
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3" t="s">
         <v>592</v>
       </c>
@@ -23787,7 +23778,7 @@
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
         <v>594</v>
       </c>
@@ -23810,7 +23801,7 @@
         <v>209</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3" t="s">
         <v>596</v>
       </c>
@@ -23833,7 +23824,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
         <v>598</v>
       </c>
@@ -23856,7 +23847,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
         <v>598</v>
       </c>
@@ -23879,7 +23870,7 @@
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3" t="s">
         <v>600</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3782" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="1128">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3412,6 +3412,9 @@
   </si>
   <si>
     <t>XEREM DE AMENDOIM</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -3488,7 +3491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3516,6 +3519,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3819,7 +3828,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="15.290714285714287" customWidth="1" bestFit="1"/>
@@ -3877,30 +3886,30 @@
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="C3" s="4">
-        <v>103</v>
+        <v>2419</v>
       </c>
       <c r="D3" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" s="4">
-        <v>215</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
         <v>838</v>
       </c>
@@ -3923,363 +3932,363 @@
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>266</v>
+        <v>1048</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>267</v>
+        <v>1049</v>
       </c>
       <c r="C5" s="4">
-        <v>3870</v>
+        <v>3821</v>
       </c>
       <c r="D5" s="4">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G5" s="4">
-        <v>22</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+        <v>140</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>268</v>
+        <v>1048</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>269</v>
+        <v>1049</v>
       </c>
       <c r="C6" s="4">
-        <v>3701</v>
-      </c>
-      <c r="D6" s="4">
-        <v>500</v>
+        <v>2263</v>
+      </c>
+      <c r="D6" s="5">
+        <v>12.5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G6" s="4">
-        <v>22</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <v>70</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>270</v>
+        <v>894</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>271</v>
+        <v>895</v>
       </c>
       <c r="C7" s="4">
-        <v>3800</v>
+        <v>92</v>
       </c>
       <c r="D7" s="4">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G7" s="4">
-        <v>22</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <v>67</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>272</v>
+        <v>894</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>273</v>
+        <v>895</v>
       </c>
       <c r="C8" s="4">
-        <v>3725</v>
+        <v>2476</v>
       </c>
       <c r="D8" s="4">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="4">
-        <v>22</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="G8" s="5">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>274</v>
+        <v>892</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>275</v>
+        <v>893</v>
       </c>
       <c r="C9" s="4">
-        <v>3871</v>
+        <v>261</v>
       </c>
       <c r="D9" s="4">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G9" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2475</v>
+      </c>
+      <c r="D10" s="4">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C11" s="4">
+        <v>564</v>
+      </c>
+      <c r="D11" s="4">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="4">
+        <v>118</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2256</v>
+      </c>
+      <c r="D12" s="4">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C13" s="4">
         <v>27</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2283</v>
-      </c>
-      <c r="D10" s="4">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4">
-        <v>61</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="3" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C11" s="4">
-        <v>4255</v>
-      </c>
-      <c r="D11" s="4">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="4">
-        <v>64</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C12" s="4">
-        <v>3081</v>
-      </c>
-      <c r="D12" s="4">
-        <v>10</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4">
-        <v>139</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C13" s="4">
-        <v>3818</v>
-      </c>
       <c r="D13" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="5">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+        <v>158</v>
+      </c>
+      <c r="G13" s="4">
+        <v>110</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>1096</v>
+        <v>716</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1097</v>
+        <v>717</v>
       </c>
       <c r="C14" s="4">
-        <v>2534</v>
+        <v>2255</v>
       </c>
       <c r="D14" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="5">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+        <v>158</v>
+      </c>
+      <c r="G14" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>1096</v>
+        <v>544</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1097</v>
+        <v>545</v>
       </c>
       <c r="C15" s="4">
-        <v>2234</v>
+        <v>2350</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G15" s="4">
-        <v>139</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+        <v>250</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>1098</v>
+        <v>552</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C16" s="4">
-        <v>2238</v>
-      </c>
-      <c r="D16" s="4">
+        <v>553</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2229</v>
+      </c>
+      <c r="D16" s="10">
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="4">
-        <v>139</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+        <v>15</v>
+      </c>
+      <c r="G16" s="10">
+        <v>140</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>1098</v>
+        <v>518</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1100</v>
+        <v>519</v>
       </c>
       <c r="C17" s="4">
-        <v>2535</v>
+        <v>4400</v>
       </c>
       <c r="D17" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="5">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+        <v>158</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1875</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>1103</v>
+        <v>518</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1104</v>
+        <v>519</v>
       </c>
       <c r="C18" s="4">
-        <v>2236</v>
+        <v>2676</v>
       </c>
       <c r="D18" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G18" s="4">
-        <v>139</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+        <v>378.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3" t="s">
-        <v>1103</v>
+        <v>520</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1104</v>
+        <v>521</v>
       </c>
       <c r="C19" s="4">
-        <v>2546</v>
+        <v>571</v>
       </c>
       <c r="D19" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="5">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+        <v>158</v>
+      </c>
+      <c r="G19" s="4">
+        <v>287.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>1105</v>
+        <v>520</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1106</v>
+        <v>521</v>
       </c>
       <c r="C20" s="4">
-        <v>2232</v>
+        <v>2245</v>
       </c>
       <c r="D20" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>29</v>
@@ -4288,21 +4297,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="4">
-        <v>139</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>1105</v>
+        <v>344</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1106</v>
+        <v>345</v>
       </c>
       <c r="C21" s="4">
-        <v>2536</v>
+        <v>2259</v>
       </c>
       <c r="D21" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>29</v>
@@ -4311,21 +4320,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="5">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>1070</v>
+        <v>348</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1071</v>
+        <v>349</v>
       </c>
       <c r="C22" s="4">
-        <v>2452</v>
+        <v>2422</v>
       </c>
       <c r="D22" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>29</v>
@@ -4333,19 +4342,19 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="4">
-        <v>76</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="G22" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>1070</v>
+        <v>348</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1071</v>
+        <v>349</v>
       </c>
       <c r="C23" s="4">
-        <v>150</v>
+        <v>569</v>
       </c>
       <c r="D23" s="4">
         <v>25</v>
@@ -4357,41 +4366,41 @@
         <v>158</v>
       </c>
       <c r="G23" s="4">
-        <v>190</v>
+        <v>118</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>1070</v>
+        <v>344</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1071</v>
+        <v>345</v>
       </c>
       <c r="C24" s="4">
-        <v>2453</v>
+        <v>282</v>
       </c>
       <c r="D24" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G24" s="4">
-        <v>41</v>
+        <v>118</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>1072</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1073</v>
+        <v>40</v>
       </c>
       <c r="C25" s="4">
-        <v>2450</v>
+        <v>3123</v>
       </c>
       <c r="D25" s="4">
         <v>10</v>
@@ -4400,67 +4409,67 @@
         <v>29</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" s="4">
-        <v>76</v>
+        <v>121</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>1072</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1073</v>
+        <v>40</v>
       </c>
       <c r="C26" s="4">
-        <v>7</v>
+        <v>2674</v>
       </c>
       <c r="D26" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G26" s="4">
-        <v>190</v>
+        <v>10</v>
+      </c>
+      <c r="G26" s="5">
+        <v>60.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="3" t="s">
-        <v>1072</v>
+        <v>56</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1073</v>
+        <v>57</v>
       </c>
       <c r="C27" s="4">
-        <v>2451</v>
+        <v>3124</v>
       </c>
       <c r="D27" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G27" s="4">
-        <v>41</v>
+        <v>161</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>1052</v>
+        <v>56</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1053</v>
+        <v>57</v>
       </c>
       <c r="C28" s="4">
-        <v>2643</v>
+        <v>2824</v>
       </c>
       <c r="D28" s="4">
         <v>5</v>
@@ -4471,42 +4480,42 @@
       <c r="F28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="4">
-        <v>68</v>
+      <c r="G28" s="5">
+        <v>80.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>1054</v>
+        <v>58</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1055</v>
+        <v>59</v>
       </c>
       <c r="C29" s="4">
-        <v>2644</v>
+        <v>3130</v>
       </c>
       <c r="D29" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G29" s="4">
-        <v>70</v>
+        <v>138</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="3" t="s">
-        <v>1056</v>
+        <v>58</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1057</v>
+        <v>59</v>
       </c>
       <c r="C30" s="4">
-        <v>2570</v>
+        <v>3131</v>
       </c>
       <c r="D30" s="4">
         <v>5</v>
@@ -4518,44 +4527,44 @@
         <v>10</v>
       </c>
       <c r="G30" s="4">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>1058</v>
+        <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1059</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4">
-        <v>3021</v>
+        <v>3438</v>
       </c>
       <c r="D31" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G31" s="4">
-        <v>63</v>
+        <v>228</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4">
-        <v>2825</v>
+        <v>3434</v>
       </c>
       <c r="D32" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -4564,399 +4573,34 @@
         <v>10</v>
       </c>
       <c r="G32" s="4">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C33" s="4">
-        <v>2828</v>
-      </c>
-      <c r="D33" s="4">
-        <v>2</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C34" s="4">
-        <v>2826</v>
-      </c>
-      <c r="D34" s="4">
-        <v>2</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C35" s="4">
-        <v>3058</v>
-      </c>
-      <c r="D35" s="4">
-        <v>2</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C36" s="4">
-        <v>3059</v>
-      </c>
-      <c r="D36" s="4">
-        <v>2</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C37" s="4">
-        <v>2829</v>
-      </c>
-      <c r="D37" s="4">
-        <v>2</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C38" s="4">
-        <v>4126</v>
-      </c>
-      <c r="D38" s="4">
-        <v>2</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C39" s="4">
-        <v>2827</v>
-      </c>
-      <c r="D39" s="4">
-        <v>2</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C40" s="4">
-        <v>3801</v>
-      </c>
-      <c r="D40" s="4">
-        <v>500</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C41" s="4">
-        <v>3764</v>
-      </c>
-      <c r="D41" s="4">
-        <v>2</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="4">
-        <v>81</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C42" s="4">
-        <v>3402</v>
-      </c>
-      <c r="D42" s="4">
-        <v>6</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G42" s="5">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C43" s="4">
-        <v>3401</v>
-      </c>
-      <c r="D43" s="4">
-        <v>6</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G43" s="5">
-        <v>66.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C44" s="4">
-        <v>3403</v>
-      </c>
-      <c r="D44" s="4">
-        <v>12</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G44" s="5">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C45" s="4">
-        <v>4032</v>
-      </c>
-      <c r="D45" s="4">
-        <v>12</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G45" s="5">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C46" s="4">
-        <v>4460</v>
-      </c>
-      <c r="D46" s="4">
-        <v>12</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G46" s="5">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C47" s="4">
-        <v>2551</v>
-      </c>
-      <c r="D47" s="4">
-        <v>12</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G47" s="4">
-        <v>82</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C48" s="4">
-        <v>2550</v>
-      </c>
-      <c r="D48" s="4">
-        <v>6</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G48" s="5">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C49" s="4">
-        <v>4383</v>
-      </c>
-      <c r="D49" s="4">
-        <v>12</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G49" s="4">
-        <v>53</v>
-      </c>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="10"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
+      <c r="A34" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G34" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5968,7 +5612,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>507</v>
       </c>
@@ -5991,7 +5635,7 @@
         <v>395</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>510</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="1129">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2409,6 +2409,12 @@
     <t>FEIJÃO ANDU</t>
   </si>
   <si>
+    <t>feijao-andu-paulista</t>
+  </si>
+  <si>
+    <t>FEIJÃO ANDU PAULISTA</t>
+  </si>
+  <si>
     <t>feijo-azuki</t>
   </si>
   <si>
@@ -3412,9 +3418,6 @@
   </si>
   <si>
     <t>XEREM DE AMENDOIM</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -3422,7 +3425,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3440,6 +3443,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3523,8 +3532,8 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3865,10 +3874,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C2" s="4">
         <v>109</v>
@@ -3888,10 +3897,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C3" s="4">
         <v>2419</v>
@@ -3911,10 +3920,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C4" s="4">
         <v>3110</v>
@@ -3934,10 +3943,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C5" s="4">
         <v>3821</v>
@@ -3957,10 +3966,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C6" s="4">
         <v>2263</v>
@@ -3980,10 +3989,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C7" s="4">
         <v>92</v>
@@ -4003,10 +4012,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C8" s="4">
         <v>2476</v>
@@ -4026,10 +4035,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C9" s="4">
         <v>261</v>
@@ -4049,10 +4058,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C10" s="4">
         <v>2475</v>
@@ -4072,10 +4081,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C11" s="4">
         <v>564</v>
@@ -4095,10 +4104,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C12" s="4">
         <v>2256</v>
@@ -4192,10 +4201,10 @@
       <c r="B16" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="11">
         <v>2229</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="11">
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4204,7 +4213,7 @@
       <c r="F16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="11">
         <v>140</v>
       </c>
     </row>
@@ -4579,27 +4588,19 @@
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="10"/>
+      <c r="G33" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
-      <c r="A34" s="11" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>1127</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="11" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>1127</v>
-      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="5"/>
     </row>
   </sheetData>
@@ -5012,7 +5013,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="4">
-        <v>455</v>
+        <v>850</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -5035,7 +5036,7 @@
         <v>10</v>
       </c>
       <c r="G18" s="5">
-        <v>227.5</v>
+        <v>425</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
@@ -5609,7 +5610,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="5">
-        <v>197.5</v>
+        <v>202.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -5632,7 +5633,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="4">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -13403,10 +13404,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C2" s="4">
         <v>585</v>
@@ -13426,10 +13427,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C3" s="4">
         <v>467</v>
@@ -13449,10 +13450,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C4" s="4">
         <v>3391</v>
@@ -13472,10 +13473,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C5" s="4">
         <v>3399</v>
@@ -13495,10 +13496,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C6" s="4">
         <v>2405</v>
@@ -13518,10 +13519,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="4">
         <v>3655</v>
@@ -13541,10 +13542,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C8" s="4">
         <v>2444</v>
@@ -13564,10 +13565,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C9" s="4">
         <v>3390</v>
@@ -13587,10 +13588,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C10" s="4">
         <v>3404</v>
@@ -13610,10 +13611,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C11" s="4">
         <v>3105</v>
@@ -13633,10 +13634,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C12" s="4">
         <v>2445</v>
@@ -13656,10 +13657,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C13" s="4">
         <v>2446</v>
@@ -13679,10 +13680,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C14" s="4">
         <v>2781</v>
@@ -13702,10 +13703,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C15" s="4">
         <v>3463</v>
@@ -13725,10 +13726,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C16" s="4">
         <v>4259</v>
@@ -13748,10 +13749,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C17" s="4">
         <v>3367</v>
@@ -13771,10 +13772,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C18" s="4">
         <v>3464</v>
@@ -13794,10 +13795,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C19" s="4">
         <v>4256</v>
@@ -13817,10 +13818,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C20" s="4">
         <v>3368</v>
@@ -13840,10 +13841,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C21" s="4">
         <v>3465</v>
@@ -13863,10 +13864,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C22" s="4">
         <v>3372</v>
@@ -13886,10 +13887,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C23" s="4">
         <v>3466</v>
@@ -13909,10 +13910,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C24" s="4">
         <v>3380</v>
@@ -13932,10 +13933,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C25" s="4">
         <v>3821</v>
@@ -13955,10 +13956,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C26" s="4">
         <v>2263</v>
@@ -13978,10 +13979,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="3" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C27" s="4">
         <v>465</v>
@@ -14001,10 +14002,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C28" s="4">
         <v>2643</v>
@@ -14024,10 +14025,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C29" s="4">
         <v>2644</v>
@@ -14047,10 +14048,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="3" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C30" s="4">
         <v>2570</v>
@@ -14070,10 +14071,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C31" s="4">
         <v>3021</v>
@@ -14093,10 +14094,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C32" s="4">
         <v>109</v>
@@ -14116,10 +14117,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C33" s="4">
         <v>2419</v>
@@ -14139,10 +14140,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C34" s="4">
         <v>3505</v>
@@ -14162,10 +14163,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C35" s="4">
         <v>2443</v>
@@ -14185,10 +14186,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C36" s="4">
         <v>2283</v>
@@ -14208,10 +14209,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C37" s="4">
         <v>4255</v>
@@ -14231,10 +14232,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C38" s="4">
         <v>103</v>
@@ -14254,10 +14255,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="3" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C39" s="4">
         <v>2629</v>
@@ -14277,10 +14278,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C40" s="4">
         <v>2452</v>
@@ -14300,10 +14301,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C41" s="4">
         <v>150</v>
@@ -14323,10 +14324,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C42" s="4">
         <v>2453</v>
@@ -14346,10 +14347,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C43" s="4">
         <v>2450</v>
@@ -14369,10 +14370,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C44" s="4">
         <v>7</v>
@@ -14392,10 +14393,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C45" s="4">
         <v>2451</v>
@@ -14415,10 +14416,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C46" s="4">
         <v>468</v>
@@ -14438,10 +14439,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="3" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C47" s="4">
         <v>4138</v>
@@ -14461,10 +14462,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C48" s="4">
         <v>2508</v>
@@ -14484,10 +14485,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C49" s="4">
         <v>2442</v>
@@ -14507,10 +14508,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C50" s="4">
         <v>2524</v>
@@ -14530,10 +14531,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C51" s="4">
         <v>3441</v>
@@ -14553,10 +14554,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C52" s="4">
         <v>2523</v>
@@ -14576,10 +14577,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C53" s="4">
         <v>3408</v>
@@ -14599,10 +14600,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C54" s="4">
         <v>2273</v>
@@ -14622,10 +14623,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C55" s="4">
         <v>2271</v>
@@ -14645,10 +14646,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C56" s="4">
         <v>3409</v>
@@ -14668,10 +14669,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C57" s="4">
         <v>459</v>
@@ -14691,10 +14692,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C58" s="4">
         <v>285</v>
@@ -14714,10 +14715,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C59" s="4">
         <v>2252</v>
@@ -14737,10 +14738,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C60" s="4">
         <v>2291</v>
@@ -14760,10 +14761,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C61" s="4">
         <v>3534</v>
@@ -14783,10 +14784,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C62" s="4">
         <v>2250</v>
@@ -14806,10 +14807,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C63" s="4">
         <v>2340</v>
@@ -14829,10 +14830,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C64" s="4">
         <v>3533</v>
@@ -14852,10 +14853,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C65" s="4">
         <v>3532</v>
@@ -14875,10 +14876,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C66" s="4">
         <v>2251</v>
@@ -14898,10 +14899,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C67" s="4">
         <v>3081</v>
@@ -14921,10 +14922,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C68" s="4">
         <v>3818</v>
@@ -14944,10 +14945,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C69" s="4">
         <v>2534</v>
@@ -14967,10 +14968,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C70" s="4">
         <v>2234</v>
@@ -14990,10 +14991,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C71" s="4">
         <v>2238</v>
@@ -15013,10 +15014,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C72" s="4">
         <v>2535</v>
@@ -15036,10 +15037,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C73" s="4">
         <v>2512</v>
@@ -15059,10 +15060,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C74" s="4">
         <v>2537</v>
@@ -15082,10 +15083,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="3" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C75" s="4">
         <v>2236</v>
@@ -15105,10 +15106,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C76" s="4">
         <v>2546</v>
@@ -15128,10 +15129,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C77" s="4">
         <v>2232</v>
@@ -15151,10 +15152,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C78" s="4">
         <v>2536</v>
@@ -15174,10 +15175,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C79" s="4">
         <v>3815</v>
@@ -15197,10 +15198,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="3" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C80" s="4">
         <v>3713</v>
@@ -15220,10 +15221,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C81" s="4">
         <v>3712</v>
@@ -15243,10 +15244,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C82" s="4">
         <v>3714</v>
@@ -15266,10 +15267,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C83" s="4">
         <v>3715</v>
@@ -15289,10 +15290,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C84" s="4">
         <v>4021</v>
@@ -15312,10 +15313,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C85" s="4">
         <v>4135</v>
@@ -15335,10 +15336,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C86" s="4">
         <v>2852</v>
@@ -15358,10 +15359,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C87" s="4">
         <v>3601</v>
@@ -15381,10 +15382,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="C88" s="4">
         <v>3093</v>
@@ -15404,10 +15405,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="C89" s="4">
         <v>263</v>
@@ -15427,10 +15428,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="C90" s="4">
         <v>2632</v>
@@ -15450,10 +15451,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C91" s="4">
         <v>2330</v>
@@ -15473,10 +15474,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C92" s="4">
         <v>2385</v>
@@ -15496,10 +15497,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C93" s="4">
         <v>2384</v>
@@ -15519,10 +15520,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C94" s="4">
         <v>3851</v>
@@ -15542,10 +15543,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="3" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C95" s="4">
         <v>2424</v>
@@ -15610,10 +15611,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C2" s="4">
         <v>85</v>
@@ -15633,10 +15634,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C3" s="4">
         <v>2447</v>
@@ -15656,10 +15657,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C4" s="4">
         <v>551</v>
@@ -15679,10 +15680,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C5" s="4">
         <v>2448</v>
@@ -15702,10 +15703,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C6" s="4">
         <v>3559</v>
@@ -15725,10 +15726,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C7" s="4">
         <v>3560</v>
@@ -15748,10 +15749,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C8" s="4">
         <v>255</v>
@@ -15771,10 +15772,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C9" s="4">
         <v>2456</v>
@@ -15794,10 +15795,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C10" s="4">
         <v>80</v>
@@ -15817,10 +15818,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C11" s="4">
         <v>2457</v>
@@ -15840,10 +15841,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C12" s="4">
         <v>94</v>
@@ -15863,10 +15864,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C13" s="4">
         <v>2458</v>
@@ -15886,10 +15887,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C14" s="4">
         <v>2454</v>
@@ -15909,10 +15910,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C15" s="4">
         <v>2455</v>
@@ -15932,10 +15933,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C16" s="4">
         <v>450</v>
@@ -15955,10 +15956,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C17" s="4">
         <v>2459</v>
@@ -16023,10 +16024,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C2" s="4">
         <v>2314</v>
@@ -16046,10 +16047,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C3" s="4">
         <v>2313</v>
@@ -16069,10 +16070,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C4" s="4">
         <v>2316</v>
@@ -16092,10 +16093,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C5" s="4">
         <v>2312</v>
@@ -16115,10 +16116,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C6" s="4">
         <v>3513</v>
@@ -16138,10 +16139,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C7" s="4">
         <v>2315</v>
@@ -16161,10 +16162,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C8" s="4">
         <v>3512</v>
@@ -16184,10 +16185,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C9" s="4">
         <v>2311</v>
@@ -16252,10 +16253,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C2" s="4">
         <v>3440</v>
@@ -16275,10 +16276,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C3" s="4">
         <v>2832</v>
@@ -16298,10 +16299,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C4" s="4">
         <v>4337</v>
@@ -16321,10 +16322,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C5" s="4">
         <v>3045</v>
@@ -16344,10 +16345,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C6" s="4">
         <v>4376</v>
@@ -16367,10 +16368,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C7" s="4">
         <v>2625</v>
@@ -16390,10 +16391,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C8" s="4">
         <v>2717</v>
@@ -16413,10 +16414,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C9" s="4">
         <v>2573</v>
@@ -16436,10 +16437,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C10" s="4">
         <v>2504</v>
@@ -16459,10 +16460,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C11" s="4">
         <v>2505</v>
@@ -16482,10 +16483,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C12" s="4">
         <v>3043</v>
@@ -16505,10 +16506,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C13" s="4">
         <v>2557</v>
@@ -16528,10 +16529,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C14" s="4">
         <v>2540</v>
@@ -16551,10 +16552,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C15" s="4">
         <v>3503</v>
@@ -16574,10 +16575,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C16" s="4">
         <v>2691</v>
@@ -16597,10 +16598,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C17" s="4">
         <v>2692</v>
@@ -16620,10 +16621,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C18" s="4">
         <v>3484</v>
@@ -16643,10 +16644,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C19" s="4">
         <v>3485</v>
@@ -16666,10 +16667,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C20" s="4">
         <v>3976</v>
@@ -16689,10 +16690,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C21" s="4">
         <v>2780</v>
@@ -16712,10 +16713,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C22" s="4">
         <v>3406</v>
@@ -16735,10 +16736,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C23" s="4">
         <v>3040</v>
@@ -16758,10 +16759,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C24" s="4">
         <v>3041</v>
@@ -16781,10 +16782,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C25" s="4">
         <v>2741</v>
@@ -16804,10 +16805,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C26" s="4">
         <v>2559</v>
@@ -16825,12 +16826,12 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C27" s="4">
         <v>2526</v>
@@ -16848,12 +16849,12 @@
         <v>850</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C28" s="4">
         <v>2527</v>
@@ -16871,12 +16872,12 @@
         <v>172.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C29" s="4">
         <v>3063</v>
@@ -16894,12 +16895,12 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C30" s="4">
         <v>4251</v>
@@ -16917,12 +16918,12 @@
         <v>352</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C31" s="4">
         <v>4250</v>
@@ -16940,12 +16941,12 @@
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C32" s="4">
         <v>2739</v>
@@ -16963,12 +16964,12 @@
         <v>290</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C33" s="4">
         <v>2560</v>
@@ -16986,12 +16987,12 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C34" s="4">
         <v>2742</v>
@@ -17009,12 +17010,12 @@
         <v>500</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C35" s="4">
         <v>2744</v>
@@ -17032,12 +17033,12 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C36" s="4">
         <v>4072</v>
@@ -17055,12 +17056,12 @@
         <v>220</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C37" s="4">
         <v>4071</v>
@@ -17078,12 +17079,12 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C38" s="4">
         <v>2696</v>
@@ -17101,12 +17102,12 @@
         <v>660</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C39" s="4">
         <v>2697</v>
@@ -17124,12 +17125,12 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C40" s="4">
         <v>3044</v>
@@ -17147,12 +17148,12 @@
         <v>580</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C41" s="4">
         <v>2746</v>
@@ -17170,12 +17171,12 @@
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C42" s="4">
         <v>2713</v>
@@ -17193,12 +17194,12 @@
         <v>170</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C43" s="4">
         <v>3037</v>
@@ -17216,12 +17217,12 @@
         <v>1125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C44" s="4">
         <v>3038</v>
@@ -17239,12 +17240,12 @@
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C45" s="4">
         <v>2248</v>
@@ -17262,12 +17263,12 @@
         <v>775</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C46" s="4">
         <v>2436</v>
@@ -17285,12 +17286,12 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C47" s="4">
         <v>2466</v>
@@ -17308,12 +17309,12 @@
         <v>775</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C48" s="4">
         <v>2465</v>
@@ -17331,12 +17332,12 @@
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C49" s="4">
         <v>4318</v>
@@ -17354,12 +17355,12 @@
         <v>250</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C50" s="4">
         <v>4319</v>
@@ -17379,10 +17380,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C51" s="4">
         <v>4254</v>
@@ -17402,10 +17403,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C52" s="4">
         <v>2563</v>
@@ -17425,10 +17426,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="3" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C53" s="4">
         <v>2725</v>
@@ -17448,10 +17449,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C54" s="4">
         <v>2562</v>
@@ -17471,10 +17472,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C55" s="4">
         <v>2782</v>
@@ -17494,10 +17495,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C56" s="4">
         <v>2745</v>
@@ -17517,10 +17518,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C57" s="4">
         <v>4207</v>
@@ -17540,10 +17541,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C58" s="4">
         <v>3769</v>
@@ -17563,10 +17564,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C59" s="4">
         <v>3034</v>
@@ -17586,10 +17587,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C60" s="4">
         <v>3039</v>
@@ -17609,10 +17610,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C61" s="4">
         <v>3421</v>
@@ -17632,10 +17633,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C62" s="4">
         <v>2748</v>
@@ -17655,10 +17656,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C63" s="4">
         <v>2576</v>
@@ -17678,10 +17679,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C64" s="4">
         <v>3032</v>
@@ -17701,10 +17702,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C65" s="4">
         <v>2740</v>
@@ -17724,10 +17725,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C66" s="4">
         <v>3098</v>
@@ -17747,10 +17748,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C67" s="4">
         <v>2743</v>
@@ -17770,10 +17771,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C68" s="4">
         <v>3360</v>
@@ -17793,10 +17794,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C69" s="4">
         <v>2611</v>
@@ -17816,10 +17817,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C70" s="4">
         <v>2558</v>
@@ -17839,10 +17840,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C71" s="4">
         <v>3042</v>
@@ -17862,10 +17863,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C72" s="4">
         <v>2561</v>
@@ -17885,10 +17886,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C73" s="4">
         <v>4226</v>
@@ -17908,10 +17909,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C74" s="4">
         <v>4227</v>
@@ -17976,10 +17977,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C2" s="4">
         <v>4295</v>
@@ -17999,10 +18000,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C3" s="4">
         <v>203</v>
@@ -18022,10 +18023,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C4" s="4">
         <v>2490</v>
@@ -18045,10 +18046,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C5" s="4">
         <v>4552</v>
@@ -18068,10 +18069,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C6" s="4">
         <v>3893</v>
@@ -18091,10 +18092,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C7" s="4">
         <v>2242</v>
@@ -18114,10 +18115,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C8" s="4">
         <v>2518</v>
@@ -18137,10 +18138,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C9" s="4">
         <v>845</v>
@@ -18160,10 +18161,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C10" s="4">
         <v>2517</v>
@@ -18183,10 +18184,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C11" s="4">
         <v>2631</v>
@@ -18206,10 +18207,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C12" s="4">
         <v>3088</v>
@@ -18229,10 +18230,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C13" s="4">
         <v>3850</v>
@@ -18252,10 +18253,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C14" s="4">
         <v>2489</v>
@@ -18275,10 +18276,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C15" s="4">
         <v>2437</v>
@@ -18298,10 +18299,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C16" s="4">
         <v>582</v>
@@ -18321,10 +18322,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C17" s="4">
         <v>3415</v>
@@ -18344,10 +18345,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C18" s="4">
         <v>2485</v>
@@ -18367,10 +18368,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C19" s="4">
         <v>583</v>
@@ -18390,10 +18391,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C20" s="4">
         <v>3416</v>
@@ -18413,10 +18414,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C21" s="4">
         <v>564</v>
@@ -18436,10 +18437,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C22" s="4">
         <v>2256</v>
@@ -18459,10 +18460,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C23" s="4">
         <v>3398</v>
@@ -18482,10 +18483,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C24" s="4">
         <v>4025</v>
@@ -18505,10 +18506,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C25" s="4">
         <v>4162</v>
@@ -18528,10 +18529,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C26" s="4">
         <v>3424</v>
@@ -18551,10 +18552,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C27" s="4">
         <v>4161</v>
@@ -18574,10 +18575,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C28" s="4">
         <v>3718</v>
@@ -18597,10 +18598,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C29" s="4">
         <v>4277</v>
@@ -18620,10 +18621,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="3" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C30" s="4">
         <v>4163</v>
@@ -18643,10 +18644,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C31" s="4">
         <v>4117</v>
@@ -18666,10 +18667,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C32" s="4">
         <v>3738</v>
@@ -18689,10 +18690,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C33" s="4">
         <v>4317</v>
@@ -18712,10 +18713,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C34" s="4">
         <v>2924</v>
@@ -18735,10 +18736,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C35" s="4">
         <v>3078</v>
@@ -18758,10 +18759,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C36" s="4">
         <v>2348</v>
@@ -18781,10 +18782,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C37" s="4">
         <v>2538</v>
@@ -18804,10 +18805,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C38" s="4">
         <v>2811</v>
@@ -18827,10 +18828,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="3" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C39" s="4">
         <v>2820</v>
@@ -18850,10 +18851,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C40" s="4">
         <v>3722</v>
@@ -18873,10 +18874,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="3" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C41" s="4">
         <v>4050</v>
@@ -18896,10 +18897,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C42" s="4">
         <v>415</v>
@@ -18919,10 +18920,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C43" s="4">
         <v>93</v>
@@ -18942,10 +18943,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C44" s="4">
         <v>261</v>
@@ -18965,10 +18966,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C45" s="4">
         <v>2475</v>
@@ -18988,10 +18989,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C46" s="4">
         <v>92</v>
@@ -19011,10 +19012,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C47" s="4">
         <v>2476</v>
@@ -19034,10 +19035,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C48" s="4">
         <v>18</v>
@@ -19057,10 +19058,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C49" s="4">
         <v>2477</v>
@@ -19080,10 +19081,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C50" s="4">
         <v>4164</v>
@@ -19103,10 +19104,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C51" s="4">
         <v>3706</v>
@@ -19126,10 +19127,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C52" s="4">
         <v>19</v>
@@ -19149,10 +19150,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C53" s="4">
         <v>2246</v>
@@ -19172,10 +19173,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C54" s="4">
         <v>575</v>
@@ -19195,10 +19196,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C55" s="4">
         <v>221</v>
@@ -19218,10 +19219,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C56" s="4">
         <v>258</v>
@@ -19241,10 +19242,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C57" s="4">
         <v>20</v>
@@ -19264,10 +19265,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C58" s="4">
         <v>2520</v>
@@ -19287,10 +19288,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C59" s="4">
         <v>4089</v>
@@ -19310,10 +19311,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C60" s="4">
         <v>21</v>
@@ -19333,10 +19334,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C61" s="4">
         <v>262</v>
@@ -19356,10 +19357,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C62" s="4">
         <v>2513</v>
@@ -19379,10 +19380,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C63" s="4">
         <v>16</v>
@@ -19402,10 +19403,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C64" s="4">
         <v>3114</v>
@@ -19425,10 +19426,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C65" s="4">
         <v>4086</v>
@@ -19448,10 +19449,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C66" s="4">
         <v>15</v>
@@ -19471,10 +19472,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C67" s="4">
         <v>3115</v>
@@ -19494,10 +19495,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C68" s="4">
         <v>4165</v>
@@ -19517,10 +19518,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C69" s="4">
         <v>4100</v>
@@ -19540,10 +19541,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C70" s="4">
         <v>4280</v>
@@ -19563,10 +19564,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C71" s="4">
         <v>4281</v>
@@ -19594,7 +19595,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -20319,18 +20320,18 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
         <v>792</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="C32" s="4">
-        <v>28</v>
-      </c>
-      <c r="D32" s="4">
-        <v>30</v>
+      <c r="C32" s="10">
+        <v>4664</v>
+      </c>
+      <c r="D32" s="10">
+        <v>25</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -20338,31 +20339,31 @@
       <c r="F32" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G32" s="4">
-        <v>270</v>
+      <c r="G32" s="10">
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C33" s="4">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D33" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G33" s="4">
-        <v>47</v>
+        <v>270</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -20373,7 +20374,7 @@
         <v>795</v>
       </c>
       <c r="C34" s="4">
-        <v>2302</v>
+        <v>68</v>
       </c>
       <c r="D34" s="4">
         <v>5</v>
@@ -20382,24 +20383,24 @@
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G34" s="5">
-        <v>54.5</v>
+        <v>10</v>
+      </c>
+      <c r="G34" s="4">
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C35" s="4">
-        <v>320</v>
+        <v>2302</v>
       </c>
       <c r="D35" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>29</v>
@@ -20407,8 +20408,8 @@
       <c r="F35" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G35" s="4">
-        <v>315</v>
+      <c r="G35" s="5">
+        <v>54.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
@@ -20419,10 +20420,10 @@
         <v>797</v>
       </c>
       <c r="C36" s="4">
-        <v>3479</v>
+        <v>320</v>
       </c>
       <c r="D36" s="4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>29</v>
@@ -20431,21 +20432,21 @@
         <v>158</v>
       </c>
       <c r="G36" s="4">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C37" s="4">
-        <v>130</v>
+        <v>3479</v>
       </c>
       <c r="D37" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>29</v>
@@ -20454,30 +20455,30 @@
         <v>158</v>
       </c>
       <c r="G37" s="4">
-        <v>178</v>
+        <v>356</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C38" s="4">
-        <v>2464</v>
+        <v>130</v>
       </c>
       <c r="D38" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="5">
-        <v>37.5</v>
+        <v>158</v>
+      </c>
+      <c r="G38" s="4">
+        <v>178</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
@@ -20488,42 +20489,42 @@
         <v>799</v>
       </c>
       <c r="C39" s="4">
-        <v>101</v>
+        <v>2464</v>
       </c>
       <c r="D39" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G39" s="4">
-        <v>320</v>
+        <v>10</v>
+      </c>
+      <c r="G39" s="5">
+        <v>37.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C40" s="4">
-        <v>2465</v>
+        <v>101</v>
       </c>
       <c r="D40" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G40" s="4">
-        <v>56.5</v>
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
@@ -20534,7 +20535,7 @@
         <v>801</v>
       </c>
       <c r="C41" s="4">
-        <v>65</v>
+        <v>2465</v>
       </c>
       <c r="D41" s="4">
         <v>5</v>
@@ -20545,45 +20546,45 @@
       <c r="F41" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G41" s="5">
-        <v>30.5</v>
+      <c r="G41" s="4">
+        <v>56.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C42" s="4">
-        <v>2624</v>
+        <v>65</v>
       </c>
       <c r="D42" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G42" s="4">
-        <v>165</v>
+        <v>10</v>
+      </c>
+      <c r="G42" s="5">
+        <v>30.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C43" s="4">
-        <v>119</v>
+        <v>2624</v>
       </c>
       <c r="D43" s="4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>29</v>
@@ -20592,7 +20593,7 @@
         <v>158</v>
       </c>
       <c r="G43" s="4">
-        <v>330</v>
+        <v>165</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
@@ -20603,10 +20604,10 @@
         <v>803</v>
       </c>
       <c r="C44" s="4">
-        <v>2834</v>
+        <v>119</v>
       </c>
       <c r="D44" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>29</v>
@@ -20615,21 +20616,21 @@
         <v>158</v>
       </c>
       <c r="G44" s="4">
-        <v>123</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C45" s="4">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D45" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>29</v>
@@ -20637,22 +20638,22 @@
       <c r="F45" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G45" s="5">
-        <v>102.5</v>
+      <c r="G45" s="4">
+        <v>123</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C46" s="4">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D46" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>29</v>
@@ -20660,8 +20661,8 @@
       <c r="F46" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G46" s="4">
-        <v>23</v>
+      <c r="G46" s="5">
+        <v>102.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
@@ -20672,10 +20673,10 @@
         <v>805</v>
       </c>
       <c r="C47" s="4">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D47" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>29</v>
@@ -20684,33 +20685,33 @@
         <v>158</v>
       </c>
       <c r="G47" s="4">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C48" s="4">
-        <v>2543</v>
+        <v>3025</v>
       </c>
       <c r="D48" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="5">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+        <v>158</v>
+      </c>
+      <c r="G48" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="3" t="s">
         <v>806</v>
       </c>
@@ -20718,33 +20719,33 @@
         <v>807</v>
       </c>
       <c r="C49" s="4">
-        <v>98</v>
+        <v>2543</v>
       </c>
       <c r="D49" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G49" s="4">
-        <v>320</v>
+        <v>10</v>
+      </c>
+      <c r="G49" s="5">
+        <v>35.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C50" s="4">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D50" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>29</v>
@@ -20752,8 +20753,8 @@
       <c r="F50" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G50" s="5">
-        <v>55.5</v>
+      <c r="G50" s="4">
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -20764,10 +20765,10 @@
         <v>809</v>
       </c>
       <c r="C51" s="4">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D51" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>29</v>
@@ -20776,30 +20777,30 @@
         <v>158</v>
       </c>
       <c r="G51" s="5">
-        <v>362.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C52" s="4">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D52" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G52" s="5">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -20810,33 +20811,33 @@
         <v>811</v>
       </c>
       <c r="C53" s="4">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D53" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G53" s="4">
-        <v>255</v>
+        <v>10</v>
+      </c>
+      <c r="G53" s="5">
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C54" s="4">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D54" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>29</v>
@@ -20844,31 +20845,31 @@
       <c r="F54" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G54" s="5">
-        <v>212.5</v>
+      <c r="G54" s="4">
+        <v>255</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C55" s="4">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D55" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G55" s="5">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -20879,33 +20880,33 @@
         <v>813</v>
       </c>
       <c r="C56" s="4">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D56" s="4">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G56" s="4">
-        <v>350</v>
+        <v>10</v>
+      </c>
+      <c r="G56" s="5">
+        <v>44.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C57" s="4">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D57" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>29</v>
@@ -20914,30 +20915,30 @@
         <v>158</v>
       </c>
       <c r="G57" s="4">
-        <v>175</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C58" s="4">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D58" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G58" s="4">
-        <v>31</v>
+        <v>175</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -20948,42 +20949,42 @@
         <v>815</v>
       </c>
       <c r="C59" s="4">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D59" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>275</v>
+        <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C60" s="4">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D60" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G60" s="4">
-        <v>57</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
@@ -20994,33 +20995,33 @@
         <v>817</v>
       </c>
       <c r="C61" s="4">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D61" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G61" s="4">
-        <v>280</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C62" s="4">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D62" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
@@ -21028,8 +21029,8 @@
       <c r="F62" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G62" s="5">
-        <v>48.5</v>
+      <c r="G62" s="4">
+        <v>280</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -21040,10 +21041,10 @@
         <v>819</v>
       </c>
       <c r="C63" s="4">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D63" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
@@ -21051,31 +21052,31 @@
       <c r="F63" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G63" s="4">
-        <v>375</v>
+      <c r="G63" s="5">
+        <v>48.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C64" s="4">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D64" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64" s="5">
-        <v>64.5</v>
+        <v>158</v>
+      </c>
+      <c r="G64" s="4">
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -21086,42 +21087,42 @@
         <v>821</v>
       </c>
       <c r="C65" s="4">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D65" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G65" s="4">
-        <v>330</v>
+        <v>10</v>
+      </c>
+      <c r="G65" s="5">
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C66" s="4">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D66" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G66" s="4">
-        <v>57</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -21132,42 +21133,42 @@
         <v>823</v>
       </c>
       <c r="C67" s="4">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D67" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G67" s="4">
-        <v>225</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C68" s="4">
-        <v>2469</v>
+        <v>3670</v>
       </c>
       <c r="D68" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="5">
-        <v>40.5</v>
+        <v>158</v>
+      </c>
+      <c r="G68" s="4">
+        <v>225</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -21178,42 +21179,42 @@
         <v>825</v>
       </c>
       <c r="C69" s="4">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D69" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G69" s="5">
-        <v>312.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C70" s="4">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D70" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G70" s="5">
-        <v>64.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -21224,42 +21225,42 @@
         <v>827</v>
       </c>
       <c r="C71" s="4">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D71" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G71" s="4">
-        <v>300</v>
+        <v>10</v>
+      </c>
+      <c r="G71" s="5">
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C72" s="4">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D72" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G72" s="4">
-        <v>62</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -21270,42 +21271,42 @@
         <v>829</v>
       </c>
       <c r="C73" s="4">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D73" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G73" s="4">
-        <v>180</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C74" s="4">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D74" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G74" s="4">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -21316,33 +21317,33 @@
         <v>831</v>
       </c>
       <c r="C75" s="4">
-        <v>211</v>
-      </c>
-      <c r="D75" s="5">
-        <v>22.68</v>
+        <v>2321</v>
+      </c>
+      <c r="D75" s="4">
+        <v>5</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G75" s="5">
-        <v>187.5</v>
+        <v>10</v>
+      </c>
+      <c r="G75" s="4">
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C76" s="4">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D76" s="5">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>29</v>
@@ -21350,31 +21351,31 @@
       <c r="F76" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G76" s="4">
-        <v>375</v>
+      <c r="G76" s="5">
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C77" s="4">
-        <v>2322</v>
-      </c>
-      <c r="D77" s="4">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="D77" s="5">
+        <v>45.36</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G77" s="5">
-        <v>43.5</v>
+        <v>158</v>
+      </c>
+      <c r="G77" s="4">
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -21385,33 +21386,33 @@
         <v>833</v>
       </c>
       <c r="C78" s="4">
-        <v>67</v>
-      </c>
-      <c r="D78" s="5">
-        <v>45.36</v>
+        <v>2322</v>
+      </c>
+      <c r="D78" s="4">
+        <v>5</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G78" s="4">
-        <v>626</v>
+        <v>10</v>
+      </c>
+      <c r="G78" s="5">
+        <v>43.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C79" s="4">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D79" s="5">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>29</v>
@@ -21420,30 +21421,30 @@
         <v>158</v>
       </c>
       <c r="G79" s="4">
-        <v>313</v>
+        <v>626</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C80" s="4">
-        <v>2488</v>
-      </c>
-      <c r="D80" s="4">
-        <v>5</v>
+        <v>2244</v>
+      </c>
+      <c r="D80" s="5">
+        <v>22.68</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G80" s="4">
-        <v>71</v>
+        <v>313</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
@@ -21454,19 +21455,19 @@
         <v>835</v>
       </c>
       <c r="C81" s="4">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D81" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
@@ -21477,56 +21478,56 @@
         <v>837</v>
       </c>
       <c r="C82" s="4">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D82" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G82" s="4">
-        <v>182</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C83" s="4">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D83" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G83" s="4">
-        <v>350</v>
+        <v>182</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C84" s="4">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D84" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>29</v>
@@ -21535,30 +21536,30 @@
         <v>158</v>
       </c>
       <c r="G84" s="4">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C85" s="4">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D85" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G85" s="4">
-        <v>106</v>
+        <v>700</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -21569,19 +21570,19 @@
         <v>839</v>
       </c>
       <c r="C86" s="4">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D86" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G86" s="4">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
@@ -21592,10 +21593,10 @@
         <v>841</v>
       </c>
       <c r="C87" s="4">
-        <v>135</v>
-      </c>
-      <c r="D87" s="5">
-        <v>22.68</v>
+        <v>3110</v>
+      </c>
+      <c r="D87" s="4">
+        <v>25</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
@@ -21604,7 +21605,7 @@
         <v>158</v>
       </c>
       <c r="G87" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
@@ -21615,10 +21616,10 @@
         <v>843</v>
       </c>
       <c r="C88" s="4">
-        <v>2463</v>
-      </c>
-      <c r="D88" s="4">
-        <v>5</v>
+        <v>135</v>
+      </c>
+      <c r="D88" s="5">
+        <v>22.68</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
@@ -21627,7 +21628,7 @@
         <v>158</v>
       </c>
       <c r="G88" s="4">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -21638,10 +21639,10 @@
         <v>845</v>
       </c>
       <c r="C89" s="4">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D89" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
@@ -21650,21 +21651,21 @@
         <v>158</v>
       </c>
       <c r="G89" s="4">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C90" s="4">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D90" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
@@ -21673,21 +21674,21 @@
         <v>158</v>
       </c>
       <c r="G90" s="4">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C91" s="4">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D91" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
@@ -21696,7 +21697,7 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>228</v>
+        <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -21707,10 +21708,10 @@
         <v>847</v>
       </c>
       <c r="C92" s="4">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D92" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
@@ -21719,29 +21720,52 @@
         <v>158</v>
       </c>
       <c r="G92" s="4">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C93" s="4">
+        <v>4223</v>
+      </c>
+      <c r="D93" s="4">
+        <v>25</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G93" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="C94" s="4">
         <v>4224</v>
       </c>
-      <c r="D93" s="4">
-        <v>5</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="4">
+      <c r="D94" s="4">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4">
         <v>27</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3722" uniqueCount="1129">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3500,7 +3500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3527,9 +3527,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -4201,10 +4198,10 @@
       <c r="B16" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="4">
         <v>2229</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="4">
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4213,7 +4210,7 @@
       <c r="F16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="4">
         <v>140</v>
       </c>
     </row>
@@ -4588,11 +4585,11 @@
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="11"/>
+      <c r="G33" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3"/>
@@ -6713,7 +6710,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="5">
-        <v>299.5</v>
+        <v>313.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -12573,7 +12570,7 @@
         <v>10</v>
       </c>
       <c r="G110" s="4">
-        <v>414</v>
+        <v>424</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
@@ -12596,7 +12593,7 @@
         <v>10</v>
       </c>
       <c r="G111" s="4">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
@@ -15859,7 +15856,7 @@
         <v>158</v>
       </c>
       <c r="G12" s="4">
-        <v>550</v>
+        <v>650</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
@@ -15882,7 +15879,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="4">
-        <v>113.5</v>
+        <v>133.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
@@ -19595,7 +19592,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -19952,7 +19949,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>776</v>
       </c>
@@ -19975,7 +19972,7 @@
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>778</v>
       </c>
@@ -19998,7 +19995,7 @@
         <v>148</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>778</v>
       </c>
@@ -20021,7 +20018,7 @@
         <v>268.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>778</v>
       </c>
@@ -20044,7 +20041,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>780</v>
       </c>
@@ -20067,7 +20064,7 @@
         <v>590</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>780</v>
       </c>
@@ -20090,7 +20087,7 @@
         <v>100.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>782</v>
       </c>
@@ -20113,7 +20110,7 @@
         <v>540</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>782</v>
       </c>
@@ -20343,27 +20340,25 @@
         <v>350</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="C33" s="4">
-        <v>28</v>
-      </c>
-      <c r="D33" s="4">
-        <v>30</v>
+        <v>793</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10">
+        <v>5</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G33" s="4">
-        <v>270</v>
+        <v>10</v>
+      </c>
+      <c r="G33" s="10">
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -20374,30 +20369,30 @@
         <v>795</v>
       </c>
       <c r="C34" s="4">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D34" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G34" s="4">
-        <v>47</v>
+        <v>270</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C35" s="4">
-        <v>2302</v>
+        <v>68</v>
       </c>
       <c r="D35" s="4">
         <v>5</v>
@@ -20406,10 +20401,10 @@
         <v>29</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G35" s="5">
-        <v>54.5</v>
+        <v>10</v>
+      </c>
+      <c r="G35" s="4">
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
@@ -20420,10 +20415,10 @@
         <v>797</v>
       </c>
       <c r="C36" s="4">
-        <v>320</v>
+        <v>2302</v>
       </c>
       <c r="D36" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>29</v>
@@ -20431,22 +20426,22 @@
       <c r="F36" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G36" s="4">
-        <v>315</v>
+      <c r="G36" s="5">
+        <v>54.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C37" s="4">
-        <v>3479</v>
+        <v>320</v>
       </c>
       <c r="D37" s="4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>29</v>
@@ -20455,7 +20450,7 @@
         <v>158</v>
       </c>
       <c r="G37" s="4">
-        <v>356</v>
+        <v>315</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
@@ -20466,10 +20461,10 @@
         <v>799</v>
       </c>
       <c r="C38" s="4">
-        <v>130</v>
+        <v>3479</v>
       </c>
       <c r="D38" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>29</v>
@@ -20478,7 +20473,7 @@
         <v>158</v>
       </c>
       <c r="G38" s="4">
-        <v>178</v>
+        <v>356</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
@@ -20489,42 +20484,42 @@
         <v>799</v>
       </c>
       <c r="C39" s="4">
-        <v>2464</v>
+        <v>130</v>
       </c>
       <c r="D39" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="5">
-        <v>37.5</v>
+        <v>158</v>
+      </c>
+      <c r="G39" s="4">
+        <v>178</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C40" s="4">
-        <v>101</v>
+        <v>2464</v>
       </c>
       <c r="D40" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G40" s="4">
-        <v>320</v>
+        <v>10</v>
+      </c>
+      <c r="G40" s="5">
+        <v>37.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
@@ -20535,30 +20530,30 @@
         <v>801</v>
       </c>
       <c r="C41" s="4">
-        <v>2465</v>
+        <v>101</v>
       </c>
       <c r="D41" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G41" s="4">
-        <v>56.5</v>
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C42" s="4">
-        <v>65</v>
+        <v>2465</v>
       </c>
       <c r="D42" s="4">
         <v>5</v>
@@ -20569,8 +20564,8 @@
       <c r="F42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="5">
-        <v>30.5</v>
+      <c r="G42" s="4">
+        <v>56.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
@@ -20581,19 +20576,19 @@
         <v>803</v>
       </c>
       <c r="C43" s="4">
-        <v>2624</v>
+        <v>65</v>
       </c>
       <c r="D43" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G43" s="4">
-        <v>165</v>
+        <v>10</v>
+      </c>
+      <c r="G43" s="5">
+        <v>30.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
@@ -20604,10 +20599,10 @@
         <v>803</v>
       </c>
       <c r="C44" s="4">
-        <v>119</v>
+        <v>2624</v>
       </c>
       <c r="D44" s="4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>29</v>
@@ -20616,21 +20611,21 @@
         <v>158</v>
       </c>
       <c r="G44" s="4">
-        <v>330</v>
+        <v>165</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C45" s="4">
-        <v>2834</v>
+        <v>119</v>
       </c>
       <c r="D45" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>29</v>
@@ -20639,7 +20634,7 @@
         <v>158</v>
       </c>
       <c r="G45" s="4">
-        <v>123</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
@@ -20650,10 +20645,10 @@
         <v>805</v>
       </c>
       <c r="C46" s="4">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D46" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>29</v>
@@ -20661,8 +20656,8 @@
       <c r="F46" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G46" s="5">
-        <v>102.5</v>
+      <c r="G46" s="4">
+        <v>123</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
@@ -20673,10 +20668,10 @@
         <v>805</v>
       </c>
       <c r="C47" s="4">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D47" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>29</v>
@@ -20684,22 +20679,22 @@
       <c r="F47" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G47" s="4">
-        <v>23</v>
+      <c r="G47" s="5">
+        <v>102.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C48" s="4">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D48" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>29</v>
@@ -20708,7 +20703,7 @@
         <v>158</v>
       </c>
       <c r="G48" s="4">
-        <v>200</v>
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
@@ -20719,42 +20714,42 @@
         <v>807</v>
       </c>
       <c r="C49" s="4">
+        <v>3025</v>
+      </c>
+      <c r="D49" s="4">
+        <v>30</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G49" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
+      <c r="A50" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="C50" s="4">
         <v>2543</v>
       </c>
-      <c r="D49" s="4">
-        <v>5</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="5">
+      <c r="D50" s="4">
+        <v>5</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="5">
         <v>35.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="C50" s="4">
-        <v>98</v>
-      </c>
-      <c r="D50" s="4">
-        <v>30</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G50" s="4">
-        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -20765,10 +20760,10 @@
         <v>809</v>
       </c>
       <c r="C51" s="4">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D51" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>29</v>
@@ -20776,22 +20771,22 @@
       <c r="F51" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G51" s="5">
-        <v>55.5</v>
+      <c r="G51" s="4">
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C52" s="4">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D52" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>29</v>
@@ -20800,7 +20795,7 @@
         <v>158</v>
       </c>
       <c r="G52" s="5">
-        <v>362.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -20811,42 +20806,42 @@
         <v>811</v>
       </c>
       <c r="C53" s="4">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D53" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G53" s="5">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C54" s="4">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D54" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G54" s="4">
-        <v>255</v>
+        <v>10</v>
+      </c>
+      <c r="G54" s="5">
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
@@ -20857,10 +20852,10 @@
         <v>813</v>
       </c>
       <c r="C55" s="4">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D55" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>29</v>
@@ -20868,8 +20863,8 @@
       <c r="F55" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G55" s="5">
-        <v>212.5</v>
+      <c r="G55" s="4">
+        <v>255</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -20880,42 +20875,42 @@
         <v>813</v>
       </c>
       <c r="C56" s="4">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D56" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G56" s="5">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C57" s="4">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D57" s="4">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G57" s="4">
-        <v>350</v>
+        <v>10</v>
+      </c>
+      <c r="G57" s="5">
+        <v>44.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
@@ -20926,10 +20921,10 @@
         <v>815</v>
       </c>
       <c r="C58" s="4">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D58" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
@@ -20938,7 +20933,7 @@
         <v>158</v>
       </c>
       <c r="G58" s="4">
-        <v>175</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -20949,42 +20944,42 @@
         <v>815</v>
       </c>
       <c r="C59" s="4">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D59" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G59" s="4">
-        <v>31</v>
+        <v>175</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C60" s="4">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D60" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G60" s="4">
-        <v>275</v>
+        <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
@@ -20995,42 +20990,42 @@
         <v>817</v>
       </c>
       <c r="C61" s="4">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D61" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G61" s="4">
-        <v>57</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C62" s="4">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D62" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G62" s="4">
-        <v>280</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -21041,10 +21036,10 @@
         <v>819</v>
       </c>
       <c r="C63" s="4">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D63" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
@@ -21052,22 +21047,22 @@
       <c r="F63" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G63" s="5">
-        <v>48.5</v>
+      <c r="G63" s="4">
+        <v>280</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C64" s="4">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D64" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
@@ -21075,8 +21070,8 @@
       <c r="F64" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G64" s="4">
-        <v>375</v>
+      <c r="G64" s="5">
+        <v>48.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -21087,42 +21082,42 @@
         <v>821</v>
       </c>
       <c r="C65" s="4">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D65" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="5">
-        <v>64.5</v>
+        <v>158</v>
+      </c>
+      <c r="G65" s="4">
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C66" s="4">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D66" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G66" s="4">
-        <v>330</v>
+        <v>10</v>
+      </c>
+      <c r="G66" s="5">
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -21133,42 +21128,42 @@
         <v>823</v>
       </c>
       <c r="C67" s="4">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D67" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G67" s="4">
-        <v>57</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C68" s="4">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D68" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>225</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -21179,42 +21174,42 @@
         <v>825</v>
       </c>
       <c r="C69" s="4">
-        <v>2469</v>
+        <v>3670</v>
       </c>
       <c r="D69" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="5">
-        <v>40.5</v>
+        <v>158</v>
+      </c>
+      <c r="G69" s="4">
+        <v>225</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C70" s="4">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D70" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G70" s="5">
-        <v>312.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -21225,42 +21220,42 @@
         <v>827</v>
       </c>
       <c r="C71" s="4">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D71" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G71" s="5">
-        <v>64.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C72" s="4">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D72" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G72" s="4">
-        <v>300</v>
+        <v>10</v>
+      </c>
+      <c r="G72" s="5">
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -21271,42 +21266,42 @@
         <v>829</v>
       </c>
       <c r="C73" s="4">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D73" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G73" s="4">
-        <v>62</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C74" s="4">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D74" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G74" s="4">
-        <v>180</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -21317,42 +21312,42 @@
         <v>831</v>
       </c>
       <c r="C75" s="4">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D75" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G75" s="4">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C76" s="4">
-        <v>211</v>
-      </c>
-      <c r="D76" s="5">
-        <v>22.68</v>
+        <v>2321</v>
+      </c>
+      <c r="D76" s="4">
+        <v>5</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G76" s="5">
-        <v>187.5</v>
+        <v>10</v>
+      </c>
+      <c r="G76" s="4">
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -21363,10 +21358,10 @@
         <v>833</v>
       </c>
       <c r="C77" s="4">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D77" s="5">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>29</v>
@@ -21374,8 +21369,8 @@
       <c r="F77" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G77" s="4">
-        <v>375</v>
+      <c r="G77" s="5">
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -21386,42 +21381,42 @@
         <v>833</v>
       </c>
       <c r="C78" s="4">
-        <v>2322</v>
-      </c>
-      <c r="D78" s="4">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="D78" s="5">
+        <v>45.36</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="5">
-        <v>43.5</v>
+        <v>158</v>
+      </c>
+      <c r="G78" s="4">
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C79" s="4">
-        <v>67</v>
-      </c>
-      <c r="D79" s="5">
-        <v>45.36</v>
+        <v>2322</v>
+      </c>
+      <c r="D79" s="4">
+        <v>5</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G79" s="4">
-        <v>626</v>
+        <v>10</v>
+      </c>
+      <c r="G79" s="5">
+        <v>43.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
@@ -21432,10 +21427,10 @@
         <v>835</v>
       </c>
       <c r="C80" s="4">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D80" s="5">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>29</v>
@@ -21444,7 +21439,7 @@
         <v>158</v>
       </c>
       <c r="G80" s="4">
-        <v>313</v>
+        <v>626</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
@@ -21455,65 +21450,65 @@
         <v>835</v>
       </c>
       <c r="C81" s="4">
-        <v>2488</v>
-      </c>
-      <c r="D81" s="4">
-        <v>5</v>
+        <v>2244</v>
+      </c>
+      <c r="D81" s="5">
+        <v>22.68</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G81" s="4">
-        <v>71</v>
+        <v>313</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C82" s="4">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D82" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G82" s="4">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C83" s="4">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D83" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G83" s="4">
-        <v>182</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -21524,19 +21519,19 @@
         <v>839</v>
       </c>
       <c r="C84" s="4">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D84" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G84" s="4">
-        <v>350</v>
+        <v>182</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -21547,10 +21542,10 @@
         <v>839</v>
       </c>
       <c r="C85" s="4">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D85" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>29</v>
@@ -21559,7 +21554,7 @@
         <v>158</v>
       </c>
       <c r="G85" s="4">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -21570,56 +21565,56 @@
         <v>839</v>
       </c>
       <c r="C86" s="4">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D86" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G86" s="4">
-        <v>106</v>
+        <v>700</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C87" s="4">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D87" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G87" s="4">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C88" s="4">
-        <v>135</v>
-      </c>
-      <c r="D88" s="5">
-        <v>22.68</v>
+        <v>3110</v>
+      </c>
+      <c r="D88" s="4">
+        <v>25</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
@@ -21628,21 +21623,21 @@
         <v>158</v>
       </c>
       <c r="G88" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C89" s="4">
-        <v>2463</v>
-      </c>
-      <c r="D89" s="4">
-        <v>5</v>
+        <v>135</v>
+      </c>
+      <c r="D89" s="5">
+        <v>22.68</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
@@ -21651,21 +21646,21 @@
         <v>158</v>
       </c>
       <c r="G89" s="4">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C90" s="4">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D90" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
@@ -21674,7 +21669,7 @@
         <v>158</v>
       </c>
       <c r="G90" s="4">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -21685,10 +21680,10 @@
         <v>847</v>
       </c>
       <c r="C91" s="4">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D91" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
@@ -21697,7 +21692,7 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -21708,10 +21703,10 @@
         <v>847</v>
       </c>
       <c r="C92" s="4">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D92" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
@@ -21720,21 +21715,21 @@
         <v>158</v>
       </c>
       <c r="G92" s="4">
-        <v>228</v>
+        <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C93" s="4">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D93" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>29</v>
@@ -21743,7 +21738,7 @@
         <v>158</v>
       </c>
       <c r="G93" s="4">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
@@ -21754,18 +21749,41 @@
         <v>849</v>
       </c>
       <c r="C94" s="4">
+        <v>4223</v>
+      </c>
+      <c r="D94" s="4">
+        <v>25</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G94" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+      <c r="A95" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="C95" s="4">
         <v>4224</v>
       </c>
-      <c r="D94" s="4">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="4">
+      <c r="D95" s="4">
+        <v>5</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="4">
         <v>27</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3425,7 +3425,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3443,12 +3443,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3500,7 +3494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3527,9 +3521,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -5883,7 +5874,7 @@
         <v>158</v>
       </c>
       <c r="G31" s="4">
-        <v>1875</v>
+        <v>1625</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -5906,7 +5897,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>378.5</v>
+        <v>328.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -6437,7 +6428,7 @@
         <v>575</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>352</v>
       </c>
@@ -6460,7 +6451,7 @@
         <v>71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>354</v>
       </c>
@@ -6483,7 +6474,7 @@
         <v>280</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>354</v>
       </c>
@@ -6506,7 +6497,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>356</v>
       </c>
@@ -6736,7 +6727,7 @@
         <v>228.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
         <v>366</v>
       </c>
@@ -20324,10 +20315,10 @@
       <c r="B32" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="4">
         <v>4664</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="4">
         <v>25</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -20336,7 +20327,7 @@
       <c r="F32" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="4">
         <v>350</v>
       </c>
     </row>
@@ -20347,8 +20338,10 @@
       <c r="B33" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10">
+      <c r="C33" s="4">
+        <v>4665</v>
+      </c>
+      <c r="D33" s="4">
         <v>5</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -20357,7 +20350,7 @@
       <c r="F33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="4">
         <v>73</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -5690,7 +5690,7 @@
         <v>158</v>
       </c>
       <c r="G23" s="4">
-        <v>400</v>
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -5713,7 +5713,7 @@
         <v>158</v>
       </c>
       <c r="G24" s="4">
-        <v>363</v>
+        <v>290.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -5920,7 +5920,7 @@
         <v>158</v>
       </c>
       <c r="G33" s="4">
-        <v>287.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -5943,7 +5943,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>60.5</v>
+        <v>66.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
@@ -6126,7 +6126,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="4">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -6149,7 +6149,7 @@
         <v>49</v>
       </c>
       <c r="G7" s="4">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -7644,7 +7644,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="4">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -7667,7 +7667,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="4">
-        <v>117</v>
+        <v>103.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -7690,7 +7690,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="4">
-        <v>210</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -7713,7 +7713,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="4">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -13985,7 +13985,7 @@
         <v>158</v>
       </c>
       <c r="G27" s="4">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
@@ -14008,7 +14008,7 @@
         <v>10</v>
       </c>
       <c r="G28" s="4">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
@@ -14031,7 +14031,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="4">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -14054,7 +14054,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="4">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -14146,7 +14146,7 @@
         <v>158</v>
       </c>
       <c r="G34" s="4">
-        <v>490</v>
+        <v>420</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -14169,7 +14169,7 @@
         <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -15617,7 +15617,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="4">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -15640,7 +15640,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>32</v>
+        <v>32.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -16305,7 +16305,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="4">
-        <v>170</v>
+        <v>120</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -18098,7 +18098,7 @@
         <v>158</v>
       </c>
       <c r="G7" s="4">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -18121,7 +18121,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -18144,7 +18144,7 @@
         <v>158</v>
       </c>
       <c r="G9" s="4">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -18167,7 +18167,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="4">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -19983,7 +19983,7 @@
         <v>158</v>
       </c>
       <c r="G17" s="4">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -20006,7 +20006,7 @@
         <v>158</v>
       </c>
       <c r="G18" s="5">
-        <v>268.5</v>
+        <v>227</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
@@ -20029,7 +20029,7 @@
         <v>158</v>
       </c>
       <c r="G19" s="5">
-        <v>31.5</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -20308,7 +20308,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
         <v>792</v>
       </c>
@@ -20331,7 +20331,7 @@
         <v>350</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
         <v>792</v>
       </c>
@@ -20650,7 +20650,7 @@
         <v>158</v>
       </c>
       <c r="G46" s="4">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
@@ -20696,7 +20696,7 @@
         <v>158</v>
       </c>
       <c r="G48" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
@@ -20719,7 +20719,7 @@
         <v>158</v>
       </c>
       <c r="G49" s="4">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
@@ -20742,7 +20742,7 @@
         <v>10</v>
       </c>
       <c r="G50" s="5">
-        <v>35.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -21432,7 +21432,7 @@
         <v>158</v>
       </c>
       <c r="G80" s="4">
-        <v>626</v>
+        <v>544</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
@@ -21455,7 +21455,7 @@
         <v>158</v>
       </c>
       <c r="G81" s="4">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
@@ -21478,7 +21478,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="4">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
@@ -21960,7 +21960,7 @@
         <v>158</v>
       </c>
       <c r="G7" s="4">
-        <v>350</v>
+        <v>310</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -21983,7 +21983,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4">
-        <v>177</v>
+        <v>158</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -22259,7 +22259,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="4">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -22397,7 +22397,7 @@
         <v>158</v>
       </c>
       <c r="G26" s="4">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
@@ -22420,7 +22420,7 @@
         <v>158</v>
       </c>
       <c r="G27" s="4">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
@@ -22443,7 +22443,7 @@
         <v>158</v>
       </c>
       <c r="G28" s="5">
-        <v>153.5</v>
+        <v>158.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
@@ -22466,7 +22466,7 @@
         <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -22489,7 +22489,7 @@
         <v>158</v>
       </c>
       <c r="G30" s="4">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -22512,7 +22512,7 @@
         <v>158</v>
       </c>
       <c r="G31" s="5">
-        <v>153.5</v>
+        <v>158.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -22581,7 +22581,7 @@
         <v>158</v>
       </c>
       <c r="G34" s="4">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -22925,7 +22925,7 @@
         <v>158</v>
       </c>
       <c r="G11" s="5">
-        <v>132.5</v>
+        <v>130</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
@@ -22948,7 +22948,7 @@
         <v>158</v>
       </c>
       <c r="G12" s="4">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3722" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3738" uniqueCount="1135">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -1737,6 +1737,12 @@
     <t>BICARBONATO DE SODIO SOLVAY</t>
   </si>
   <si>
+    <t>bicarbonato-de-sodio</t>
+  </si>
+  <si>
+    <t>BICARBONATO DE SODIO</t>
+  </si>
+  <si>
     <t>canela-casca-6-cm</t>
   </si>
   <si>
@@ -2313,6 +2319,12 @@
     <t>TAPIOCA GRANULADA</t>
   </si>
   <si>
+    <t>tapioca-granulada-cassava</t>
+  </si>
+  <si>
+    <t>TAPIOCA GRANULADA CASSAVA</t>
+  </si>
+  <si>
     <t>trigo-p-kibe-marrocos</t>
   </si>
   <si>
@@ -2809,6 +2821,12 @@
   </si>
   <si>
     <t>CHÁ ASHWAGANDHA EM PÓ</t>
+  </si>
+  <si>
+    <t>ch-arruda</t>
+  </si>
+  <si>
+    <t>CHÁ ARRUDA</t>
   </si>
   <si>
     <t>ch-barbatimo</t>
@@ -3862,10 +3880,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="C2" s="4">
         <v>109</v>
@@ -3885,10 +3903,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="C3" s="4">
         <v>2419</v>
@@ -3908,10 +3926,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C4" s="4">
         <v>3110</v>
@@ -3931,10 +3949,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C5" s="4">
         <v>3821</v>
@@ -3954,10 +3972,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C6" s="4">
         <v>2263</v>
@@ -3977,10 +3995,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C7" s="4">
         <v>92</v>
@@ -4000,10 +4018,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C8" s="4">
         <v>2476</v>
@@ -4023,10 +4041,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C9" s="4">
         <v>261</v>
@@ -4046,10 +4064,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C10" s="4">
         <v>2475</v>
@@ -4069,10 +4087,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C11" s="4">
         <v>564</v>
@@ -4092,10 +4110,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C12" s="4">
         <v>2256</v>
@@ -4115,10 +4133,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C13" s="4">
         <v>27</v>
@@ -4138,10 +4156,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C14" s="4">
         <v>2255</v>
@@ -5233,7 +5251,7 @@
         <v>281</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>491</v>
       </c>
@@ -5256,7 +5274,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>493</v>
       </c>
@@ -5279,7 +5297,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>493</v>
       </c>
@@ -5302,7 +5320,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>495</v>
       </c>
@@ -5322,10 +5340,10 @@
         <v>10</v>
       </c>
       <c r="G7" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>495</v>
       </c>
@@ -5345,10 +5363,10 @@
         <v>158</v>
       </c>
       <c r="G8" s="5">
-        <v>175</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+        <v>187.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>497</v>
       </c>
@@ -5371,7 +5389,7 @@
         <v>108.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>497</v>
       </c>
@@ -5394,7 +5412,7 @@
         <v>525</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>499</v>
       </c>
@@ -5417,7 +5435,7 @@
         <v>170</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>499</v>
       </c>
@@ -5440,7 +5458,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>501</v>
       </c>
@@ -5463,7 +5481,7 @@
         <v>155</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>501</v>
       </c>
@@ -5486,7 +5504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>503</v>
       </c>
@@ -5509,7 +5527,7 @@
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>503</v>
       </c>
@@ -5532,7 +5550,7 @@
         <v>201</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>505</v>
       </c>
@@ -5555,7 +5573,7 @@
         <v>615</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>505</v>
       </c>
@@ -5578,7 +5596,7 @@
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>507</v>
       </c>
@@ -6724,7 +6742,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="5">
-        <v>228.5</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -13392,10 +13410,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="C2" s="4">
         <v>585</v>
@@ -13415,10 +13433,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="C3" s="4">
         <v>467</v>
@@ -13438,10 +13456,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="C4" s="4">
         <v>3391</v>
@@ -13461,10 +13479,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="C5" s="4">
         <v>3399</v>
@@ -13484,10 +13502,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="C6" s="4">
         <v>2405</v>
@@ -13507,10 +13525,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="C7" s="4">
         <v>3655</v>
@@ -13530,10 +13548,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="C8" s="4">
         <v>2444</v>
@@ -13553,10 +13571,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="C9" s="4">
         <v>3390</v>
@@ -13576,10 +13594,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="C10" s="4">
         <v>3404</v>
@@ -13599,10 +13617,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="C11" s="4">
         <v>3105</v>
@@ -13622,10 +13640,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="C12" s="4">
         <v>2445</v>
@@ -13645,10 +13663,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="C13" s="4">
         <v>2446</v>
@@ -13668,10 +13686,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="C14" s="4">
         <v>2781</v>
@@ -13691,10 +13709,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="C15" s="4">
         <v>3463</v>
@@ -13714,10 +13732,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="C16" s="4">
         <v>4259</v>
@@ -13737,10 +13755,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="C17" s="4">
         <v>3367</v>
@@ -13760,10 +13778,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="C18" s="4">
         <v>3464</v>
@@ -13783,10 +13801,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="C19" s="4">
         <v>4256</v>
@@ -13806,10 +13824,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="C20" s="4">
         <v>3368</v>
@@ -13829,10 +13847,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C21" s="4">
         <v>3465</v>
@@ -13852,10 +13870,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="C22" s="4">
         <v>3372</v>
@@ -13875,10 +13893,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="C23" s="4">
         <v>3466</v>
@@ -13898,10 +13916,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="C24" s="4">
         <v>3380</v>
@@ -13921,10 +13939,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C25" s="4">
         <v>3821</v>
@@ -13944,10 +13962,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C26" s="4">
         <v>2263</v>
@@ -13967,10 +13985,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="3" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="C27" s="4">
         <v>465</v>
@@ -13990,10 +14008,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="C28" s="4">
         <v>2643</v>
@@ -14013,10 +14031,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C29" s="4">
         <v>2644</v>
@@ -14036,10 +14054,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="3" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="C30" s="4">
         <v>2570</v>
@@ -14059,10 +14077,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="C31" s="4">
         <v>3021</v>
@@ -14082,10 +14100,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="C32" s="4">
         <v>109</v>
@@ -14105,10 +14123,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="C33" s="4">
         <v>2419</v>
@@ -14128,10 +14146,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="C34" s="4">
         <v>3505</v>
@@ -14151,10 +14169,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="C35" s="4">
         <v>2443</v>
@@ -14174,10 +14192,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="C36" s="4">
         <v>2283</v>
@@ -14197,10 +14215,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="C37" s="4">
         <v>4255</v>
@@ -14220,10 +14238,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="C38" s="4">
         <v>103</v>
@@ -14243,10 +14261,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="3" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="C39" s="4">
         <v>2629</v>
@@ -14266,10 +14284,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="C40" s="4">
         <v>2452</v>
@@ -14289,10 +14307,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="3" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="C41" s="4">
         <v>150</v>
@@ -14312,10 +14330,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="C42" s="4">
         <v>2453</v>
@@ -14335,10 +14353,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="C43" s="4">
         <v>2450</v>
@@ -14358,10 +14376,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="C44" s="4">
         <v>7</v>
@@ -14381,10 +14399,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="3" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="C45" s="4">
         <v>2451</v>
@@ -14404,10 +14422,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="C46" s="4">
         <v>468</v>
@@ -14427,10 +14445,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="3" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="C47" s="4">
         <v>4138</v>
@@ -14450,10 +14468,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="C48" s="4">
         <v>2508</v>
@@ -14473,10 +14491,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="3" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="C49" s="4">
         <v>2442</v>
@@ -14496,10 +14514,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="C50" s="4">
         <v>2524</v>
@@ -14519,10 +14537,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="C51" s="4">
         <v>3441</v>
@@ -14542,10 +14560,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="C52" s="4">
         <v>2523</v>
@@ -14565,10 +14583,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="3" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C53" s="4">
         <v>3408</v>
@@ -14588,10 +14606,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C54" s="4">
         <v>2273</v>
@@ -14611,10 +14629,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C55" s="4">
         <v>2271</v>
@@ -14634,10 +14652,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="3" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="C56" s="4">
         <v>3409</v>
@@ -14657,10 +14675,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="C57" s="4">
         <v>459</v>
@@ -14680,10 +14698,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="C58" s="4">
         <v>285</v>
@@ -14703,10 +14721,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="C59" s="4">
         <v>2252</v>
@@ -14726,10 +14744,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="C60" s="4">
         <v>2291</v>
@@ -14749,10 +14767,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="C61" s="4">
         <v>3534</v>
@@ -14772,10 +14790,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="C62" s="4">
         <v>2250</v>
@@ -14795,10 +14813,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="C63" s="4">
         <v>2340</v>
@@ -14818,10 +14836,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="C64" s="4">
         <v>3533</v>
@@ -14841,10 +14859,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="C65" s="4">
         <v>3532</v>
@@ -14864,10 +14882,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="C66" s="4">
         <v>2251</v>
@@ -14887,10 +14905,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="C67" s="4">
         <v>3081</v>
@@ -14910,10 +14928,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="C68" s="4">
         <v>3818</v>
@@ -14933,10 +14951,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="C69" s="4">
         <v>2534</v>
@@ -14956,10 +14974,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="C70" s="4">
         <v>2234</v>
@@ -14979,10 +14997,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="C71" s="4">
         <v>2238</v>
@@ -15002,10 +15020,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="C72" s="4">
         <v>2535</v>
@@ -15025,10 +15043,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="C73" s="4">
         <v>2512</v>
@@ -15048,10 +15066,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="C74" s="4">
         <v>2537</v>
@@ -15071,10 +15089,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="3" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="C75" s="4">
         <v>2236</v>
@@ -15094,10 +15112,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="C76" s="4">
         <v>2546</v>
@@ -15117,10 +15135,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="C77" s="4">
         <v>2232</v>
@@ -15140,10 +15158,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="C78" s="4">
         <v>2536</v>
@@ -15163,10 +15181,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="C79" s="4">
         <v>3815</v>
@@ -15186,10 +15204,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="3" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="C80" s="4">
         <v>3713</v>
@@ -15209,10 +15227,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="C81" s="4">
         <v>3712</v>
@@ -15232,10 +15250,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="C82" s="4">
         <v>3714</v>
@@ -15255,10 +15273,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="C83" s="4">
         <v>3715</v>
@@ -15278,10 +15296,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C84" s="4">
         <v>4021</v>
@@ -15301,10 +15319,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C85" s="4">
         <v>4135</v>
@@ -15324,10 +15342,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="C86" s="4">
         <v>2852</v>
@@ -15347,10 +15365,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="C87" s="4">
         <v>3601</v>
@@ -15370,10 +15388,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="C88" s="4">
         <v>3093</v>
@@ -15393,10 +15411,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="C89" s="4">
         <v>263</v>
@@ -15416,10 +15434,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="C90" s="4">
         <v>2632</v>
@@ -15439,10 +15457,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="C91" s="4">
         <v>2330</v>
@@ -15462,10 +15480,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="C92" s="4">
         <v>2385</v>
@@ -15485,10 +15503,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="C93" s="4">
         <v>2384</v>
@@ -15508,10 +15526,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="C94" s="4">
         <v>3851</v>
@@ -15531,10 +15549,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="3" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="C95" s="4">
         <v>2424</v>
@@ -15599,10 +15617,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="C2" s="4">
         <v>85</v>
@@ -15622,10 +15640,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="C3" s="4">
         <v>2447</v>
@@ -15645,10 +15663,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="C4" s="4">
         <v>551</v>
@@ -15668,10 +15686,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="C5" s="4">
         <v>2448</v>
@@ -15691,10 +15709,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="C6" s="4">
         <v>3559</v>
@@ -15714,10 +15732,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="C7" s="4">
         <v>3560</v>
@@ -15737,10 +15755,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C8" s="4">
         <v>255</v>
@@ -15760,10 +15778,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C9" s="4">
         <v>2456</v>
@@ -15783,10 +15801,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="C10" s="4">
         <v>80</v>
@@ -15806,10 +15824,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="C11" s="4">
         <v>2457</v>
@@ -15829,10 +15847,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="C12" s="4">
         <v>94</v>
@@ -15852,10 +15870,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="C13" s="4">
         <v>2458</v>
@@ -15875,10 +15893,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="C14" s="4">
         <v>2454</v>
@@ -15898,10 +15916,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="C15" s="4">
         <v>2455</v>
@@ -15921,10 +15939,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="C16" s="4">
         <v>450</v>
@@ -15944,10 +15962,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="C17" s="4">
         <v>2459</v>
@@ -16012,10 +16030,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="C2" s="4">
         <v>2314</v>
@@ -16035,10 +16053,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="C3" s="4">
         <v>2313</v>
@@ -16058,10 +16076,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="C4" s="4">
         <v>2316</v>
@@ -16081,10 +16099,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C5" s="4">
         <v>2312</v>
@@ -16104,10 +16122,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="C6" s="4">
         <v>3513</v>
@@ -16127,10 +16145,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="C7" s="4">
         <v>2315</v>
@@ -16150,10 +16168,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="C8" s="4">
         <v>3512</v>
@@ -16173,10 +16191,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="C9" s="4">
         <v>2311</v>
@@ -16204,7 +16222,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -16241,10 +16259,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="C2" s="4">
         <v>3440</v>
@@ -16264,10 +16282,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="C3" s="4">
         <v>2832</v>
@@ -16287,10 +16305,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C4" s="4">
         <v>4337</v>
@@ -16310,16 +16328,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="C5" s="4">
-        <v>3045</v>
+        <v>4668</v>
       </c>
       <c r="D5" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>29</v>
@@ -16328,21 +16346,21 @@
         <v>158</v>
       </c>
       <c r="G5" s="4">
-        <v>380</v>
+        <v>770</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="C6" s="4">
-        <v>4376</v>
+        <v>4667</v>
       </c>
       <c r="D6" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>29</v>
@@ -16351,67 +16369,67 @@
         <v>10</v>
       </c>
       <c r="G6" s="4">
-        <v>190</v>
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="C7" s="4">
-        <v>2625</v>
+        <v>3045</v>
       </c>
       <c r="D7" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G7" s="4">
-        <v>57</v>
+        <v>380</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="C8" s="4">
-        <v>2717</v>
+        <v>4376</v>
       </c>
       <c r="D8" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G8" s="4">
-        <v>950</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="C9" s="4">
-        <v>2573</v>
+        <v>2625</v>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>29</v>
@@ -16420,41 +16438,41 @@
         <v>10</v>
       </c>
       <c r="G9" s="4">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="C10" s="4">
-        <v>2504</v>
+        <v>2717</v>
       </c>
       <c r="D10" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="G10" s="4">
-        <v>300</v>
+        <v>950</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="C11" s="4">
-        <v>2505</v>
+        <v>2573</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -16466,41 +16484,41 @@
         <v>10</v>
       </c>
       <c r="G11" s="4">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="C12" s="4">
-        <v>3043</v>
+        <v>2504</v>
       </c>
       <c r="D12" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="G12" s="4">
-        <v>320</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="C13" s="4">
-        <v>2557</v>
+        <v>2505</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -16512,44 +16530,44 @@
         <v>10</v>
       </c>
       <c r="G13" s="4">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="C14" s="4">
-        <v>2540</v>
+        <v>3043</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G14" s="4">
-        <v>17</v>
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="C15" s="4">
-        <v>3503</v>
+        <v>2557</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>29</v>
@@ -16558,44 +16576,44 @@
         <v>10</v>
       </c>
       <c r="G15" s="4">
-        <v>170</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C16" s="4">
-        <v>2691</v>
+        <v>2540</v>
       </c>
       <c r="D16" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G16" s="4">
-        <v>225</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C17" s="4">
-        <v>2692</v>
+        <v>3503</v>
       </c>
       <c r="D17" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
@@ -16604,21 +16622,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="4">
-        <v>15</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C18" s="4">
-        <v>3484</v>
+        <v>2691</v>
       </c>
       <c r="D18" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>29</v>
@@ -16627,21 +16645,21 @@
         <v>158</v>
       </c>
       <c r="G18" s="4">
-        <v>340</v>
+        <v>225</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C19" s="4">
-        <v>3485</v>
+        <v>2692</v>
       </c>
       <c r="D19" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>29</v>
@@ -16650,21 +16668,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="4">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="C20" s="4">
-        <v>3976</v>
+        <v>3484</v>
       </c>
       <c r="D20" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>29</v>
@@ -16673,21 +16691,21 @@
         <v>158</v>
       </c>
       <c r="G20" s="4">
-        <v>530</v>
+        <v>340</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="C21" s="4">
-        <v>2780</v>
+        <v>3485</v>
       </c>
       <c r="D21" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>29</v>
@@ -16696,67 +16714,67 @@
         <v>10</v>
       </c>
       <c r="G21" s="4">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C22" s="4">
-        <v>3406</v>
+        <v>3976</v>
       </c>
       <c r="D22" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G22" s="4">
-        <v>90</v>
+        <v>530</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C23" s="4">
-        <v>3040</v>
+        <v>2780</v>
       </c>
       <c r="D23" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G23" s="4">
-        <v>300</v>
+        <v>53</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="C24" s="4">
-        <v>3041</v>
+        <v>3406</v>
       </c>
       <c r="D24" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>29</v>
@@ -16765,21 +16783,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C25" s="4">
-        <v>2741</v>
+        <v>3040</v>
       </c>
       <c r="D25" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>29</v>
@@ -16788,18 +16806,18 @@
         <v>158</v>
       </c>
       <c r="G25" s="4">
-        <v>660</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+        <v>300</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C26" s="4">
-        <v>2559</v>
+        <v>3041</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
@@ -16811,21 +16829,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="4">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="C27" s="4">
-        <v>2526</v>
+        <v>2741</v>
       </c>
       <c r="D27" s="4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>29</v>
@@ -16834,21 +16852,21 @@
         <v>158</v>
       </c>
       <c r="G27" s="4">
-        <v>850</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
+        <v>660</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="C28" s="4">
-        <v>2527</v>
+        <v>2559</v>
       </c>
       <c r="D28" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>29</v>
@@ -16856,65 +16874,65 @@
       <c r="F28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="5">
-        <v>172.5</v>
+      <c r="G28" s="4">
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="C29" s="4">
-        <v>3063</v>
+        <v>2526</v>
       </c>
       <c r="D29" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>20</v>
+        <v>850</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C30" s="4">
-        <v>4251</v>
+        <v>2527</v>
       </c>
       <c r="D30" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G30" s="4">
-        <v>352</v>
+        <v>10</v>
+      </c>
+      <c r="G30" s="5">
+        <v>172.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="C31" s="4">
-        <v>4250</v>
+        <v>3063</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
@@ -16926,21 +16944,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="4">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C32" s="4">
-        <v>2739</v>
+        <v>4251</v>
       </c>
       <c r="D32" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -16949,18 +16967,18 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>290</v>
+        <v>352</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C33" s="4">
-        <v>2560</v>
+        <v>4250</v>
       </c>
       <c r="D33" s="4">
         <v>1</v>
@@ -16972,21 +16990,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="4">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C34" s="4">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="D34" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>29</v>
@@ -16995,18 +17013,18 @@
         <v>158</v>
       </c>
       <c r="G34" s="4">
-        <v>500</v>
+        <v>290</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C35" s="4">
-        <v>2744</v>
+        <v>2560</v>
       </c>
       <c r="D35" s="4">
         <v>1</v>
@@ -17018,21 +17036,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C36" s="4">
-        <v>4072</v>
+        <v>2742</v>
       </c>
       <c r="D36" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>29</v>
@@ -17041,18 +17059,18 @@
         <v>158</v>
       </c>
       <c r="G36" s="4">
-        <v>220</v>
+        <v>500</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C37" s="4">
-        <v>4071</v>
+        <v>2744</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
@@ -17064,21 +17082,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="4">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C38" s="4">
-        <v>2696</v>
+        <v>4072</v>
       </c>
       <c r="D38" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>29</v>
@@ -17087,18 +17105,18 @@
         <v>158</v>
       </c>
       <c r="G38" s="4">
-        <v>660</v>
+        <v>220</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C39" s="4">
-        <v>2697</v>
+        <v>4071</v>
       </c>
       <c r="D39" s="4">
         <v>1</v>
@@ -17110,18 +17128,18 @@
         <v>10</v>
       </c>
       <c r="G39" s="4">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C40" s="4">
-        <v>3044</v>
+        <v>2696</v>
       </c>
       <c r="D40" s="4">
         <v>20</v>
@@ -17130,21 +17148,21 @@
         <v>29</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G40" s="4">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C41" s="4">
-        <v>2746</v>
+        <v>2697</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
@@ -17156,21 +17174,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="4">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="C42" s="4">
-        <v>2713</v>
+        <v>3044</v>
       </c>
       <c r="D42" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>29</v>
@@ -17179,44 +17197,44 @@
         <v>10</v>
       </c>
       <c r="G42" s="4">
-        <v>170</v>
+        <v>580</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C43" s="4">
-        <v>3037</v>
+        <v>2746</v>
       </c>
       <c r="D43" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G43" s="4">
-        <v>1125</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C44" s="4">
-        <v>3038</v>
+        <v>2713</v>
       </c>
       <c r="D44" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>29</v>
@@ -17225,18 +17243,18 @@
         <v>10</v>
       </c>
       <c r="G44" s="4">
-        <v>45</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="C45" s="4">
-        <v>2248</v>
+        <v>3037</v>
       </c>
       <c r="D45" s="4">
         <v>25</v>
@@ -17248,18 +17266,18 @@
         <v>158</v>
       </c>
       <c r="G45" s="4">
-        <v>775</v>
+        <v>1125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="C46" s="4">
-        <v>2436</v>
+        <v>3038</v>
       </c>
       <c r="D46" s="4">
         <v>1</v>
@@ -17271,18 +17289,18 @@
         <v>10</v>
       </c>
       <c r="G46" s="4">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="C47" s="4">
-        <v>2466</v>
+        <v>2248</v>
       </c>
       <c r="D47" s="4">
         <v>25</v>
@@ -17299,16 +17317,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="C48" s="4">
-        <v>2465</v>
+        <v>2436</v>
       </c>
       <c r="D48" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>29</v>
@@ -17317,110 +17335,110 @@
         <v>10</v>
       </c>
       <c r="G48" s="4">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="3" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C49" s="4">
-        <v>4318</v>
+        <v>2466</v>
       </c>
       <c r="D49" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G49" s="4">
-        <v>250</v>
+        <v>775</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="3" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C50" s="4">
+        <v>2465</v>
+      </c>
+      <c r="D50" s="4">
+        <v>2</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
+      <c r="A51" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="C51" s="4">
+        <v>4318</v>
+      </c>
+      <c r="D51" s="4">
+        <v>10</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
+      <c r="A52" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="C52" s="4">
         <v>4319</v>
       </c>
-      <c r="D50" s="4">
-        <v>5</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="4">
+      <c r="D52" s="4">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="4">
         <v>127</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="3" t="s">
-        <v>974</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="C51" s="4">
-        <v>4254</v>
-      </c>
-      <c r="D51" s="4">
-        <v>10</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="4">
-        <v>150</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="3" t="s">
-        <v>974</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="C52" s="4">
-        <v>2563</v>
-      </c>
-      <c r="D52" s="4">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" s="4">
-        <v>15</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="3" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C53" s="4">
-        <v>2725</v>
+        <v>4254</v>
       </c>
       <c r="D53" s="4">
         <v>10</v>
@@ -17429,21 +17447,21 @@
         <v>29</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G53" s="4">
-        <v>600</v>
+        <v>150</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C54" s="4">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="D54" s="4">
         <v>1</v>
@@ -17455,21 +17473,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="4">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C55" s="4">
-        <v>2782</v>
+        <v>2725</v>
       </c>
       <c r="D55" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>29</v>
@@ -17478,18 +17496,18 @@
         <v>158</v>
       </c>
       <c r="G55" s="4">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="3" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C56" s="4">
-        <v>2745</v>
+        <v>2562</v>
       </c>
       <c r="D56" s="4">
         <v>1</v>
@@ -17501,21 +17519,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="4">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C57" s="4">
-        <v>4207</v>
+        <v>2782</v>
       </c>
       <c r="D57" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>29</v>
@@ -17529,16 +17547,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C58" s="4">
-        <v>3769</v>
+        <v>2745</v>
       </c>
       <c r="D58" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
@@ -17547,90 +17565,90 @@
         <v>10</v>
       </c>
       <c r="G58" s="4">
-        <v>190</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C59" s="4">
-        <v>3034</v>
+        <v>4207</v>
       </c>
       <c r="D59" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G59" s="4">
-        <v>30</v>
+        <v>380</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C60" s="4">
-        <v>3039</v>
+        <v>3769</v>
       </c>
       <c r="D60" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G60" s="4">
-        <v>750</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C61" s="4">
-        <v>3421</v>
+        <v>3034</v>
       </c>
       <c r="D61" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G61" s="4">
-        <v>420</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C62" s="4">
-        <v>2748</v>
+        <v>3039</v>
       </c>
       <c r="D62" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
@@ -17639,136 +17657,136 @@
         <v>158</v>
       </c>
       <c r="G62" s="4">
-        <v>210</v>
+        <v>750</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="C63" s="4">
-        <v>2576</v>
+        <v>3421</v>
       </c>
       <c r="D63" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G63" s="4">
-        <v>21</v>
+        <v>420</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C64" s="4">
-        <v>3032</v>
+        <v>2748</v>
       </c>
       <c r="D64" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G64" s="4">
-        <v>19</v>
+        <v>210</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C65" s="4">
-        <v>2740</v>
+        <v>2576</v>
       </c>
       <c r="D65" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G65" s="4">
-        <v>780</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="C66" s="4">
-        <v>3098</v>
+        <v>3032</v>
       </c>
       <c r="D66" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G66" s="4">
-        <v>390</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="C67" s="4">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="D67" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G67" s="4">
-        <v>39</v>
+        <v>780</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C68" s="4">
-        <v>3360</v>
+        <v>3098</v>
       </c>
       <c r="D68" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
@@ -17777,90 +17795,90 @@
         <v>158</v>
       </c>
       <c r="G68" s="4">
-        <v>300</v>
+        <v>390</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C69" s="4">
-        <v>2611</v>
+        <v>2743</v>
       </c>
       <c r="D69" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G69" s="4">
-        <v>600</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="C70" s="4">
-        <v>2558</v>
+        <v>3360</v>
       </c>
       <c r="D70" s="4">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G70" s="4">
-        <v>24</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C71" s="4">
-        <v>3042</v>
+        <v>2611</v>
       </c>
       <c r="D71" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G71" s="4">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C72" s="4">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="D72" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>29</v>
@@ -17869,21 +17887,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C73" s="4">
-        <v>4226</v>
+        <v>3042</v>
       </c>
       <c r="D73" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>29</v>
@@ -17892,29 +17910,75 @@
         <v>10</v>
       </c>
       <c r="G73" s="4">
-        <v>35</v>
+        <v>400</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C74" s="4">
+        <v>2561</v>
+      </c>
+      <c r="D74" s="4">
+        <v>1</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+      <c r="A75" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C75" s="4">
+        <v>4226</v>
+      </c>
+      <c r="D75" s="4">
+        <v>1</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+      <c r="A76" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C76" s="4">
         <v>4227</v>
       </c>
-      <c r="D74" s="4">
-        <v>10</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G74" s="4">
+      <c r="D76" s="4">
+        <v>10</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G76" s="4">
         <v>350</v>
       </c>
     </row>
@@ -17965,10 +18029,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C2" s="4">
         <v>4295</v>
@@ -17988,10 +18052,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C3" s="4">
         <v>203</v>
@@ -18011,10 +18075,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C4" s="4">
         <v>2490</v>
@@ -18034,10 +18098,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C5" s="4">
         <v>4552</v>
@@ -18057,10 +18121,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C6" s="4">
         <v>3893</v>
@@ -18080,10 +18144,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C7" s="4">
         <v>2242</v>
@@ -18103,10 +18167,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C8" s="4">
         <v>2518</v>
@@ -18126,10 +18190,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C9" s="4">
         <v>845</v>
@@ -18149,10 +18213,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C10" s="4">
         <v>2517</v>
@@ -18172,10 +18236,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C11" s="4">
         <v>2631</v>
@@ -18195,10 +18259,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C12" s="4">
         <v>3088</v>
@@ -18218,10 +18282,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C13" s="4">
         <v>3850</v>
@@ -18241,10 +18305,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C14" s="4">
         <v>2489</v>
@@ -18264,10 +18328,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C15" s="4">
         <v>2437</v>
@@ -18287,10 +18351,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C16" s="4">
         <v>582</v>
@@ -18310,10 +18374,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C17" s="4">
         <v>3415</v>
@@ -18333,10 +18397,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C18" s="4">
         <v>2485</v>
@@ -18356,10 +18420,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C19" s="4">
         <v>583</v>
@@ -18379,10 +18443,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C20" s="4">
         <v>3416</v>
@@ -18402,10 +18466,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C21" s="4">
         <v>564</v>
@@ -18425,10 +18489,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C22" s="4">
         <v>2256</v>
@@ -18448,10 +18512,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C23" s="4">
         <v>3398</v>
@@ -18471,10 +18535,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C24" s="4">
         <v>4025</v>
@@ -18494,10 +18558,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C25" s="4">
         <v>4162</v>
@@ -18517,10 +18581,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C26" s="4">
         <v>3424</v>
@@ -18540,10 +18604,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="3" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C27" s="4">
         <v>4161</v>
@@ -18563,10 +18627,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C28" s="4">
         <v>3718</v>
@@ -18586,10 +18650,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C29" s="4">
         <v>4277</v>
@@ -18609,10 +18673,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="3" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C30" s="4">
         <v>4163</v>
@@ -18632,10 +18696,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C31" s="4">
         <v>4117</v>
@@ -18655,10 +18719,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C32" s="4">
         <v>3738</v>
@@ -18678,10 +18742,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C33" s="4">
         <v>4317</v>
@@ -18701,10 +18765,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C34" s="4">
         <v>2924</v>
@@ -18724,10 +18788,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C35" s="4">
         <v>3078</v>
@@ -18747,10 +18811,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C36" s="4">
         <v>2348</v>
@@ -18770,10 +18834,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C37" s="4">
         <v>2538</v>
@@ -18793,10 +18857,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C38" s="4">
         <v>2811</v>
@@ -18816,10 +18880,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="3" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C39" s="4">
         <v>2820</v>
@@ -18839,10 +18903,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C40" s="4">
         <v>3722</v>
@@ -18862,10 +18926,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="3" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C41" s="4">
         <v>4050</v>
@@ -18885,10 +18949,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C42" s="4">
         <v>415</v>
@@ -18908,10 +18972,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C43" s="4">
         <v>93</v>
@@ -18931,10 +18995,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C44" s="4">
         <v>261</v>
@@ -18954,10 +19018,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="3" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C45" s="4">
         <v>2475</v>
@@ -18977,10 +19041,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C46" s="4">
         <v>92</v>
@@ -19000,10 +19064,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="3" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C47" s="4">
         <v>2476</v>
@@ -19023,10 +19087,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C48" s="4">
         <v>18</v>
@@ -19046,10 +19110,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="3" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C49" s="4">
         <v>2477</v>
@@ -19069,10 +19133,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C50" s="4">
         <v>4164</v>
@@ -19092,10 +19156,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C51" s="4">
         <v>3706</v>
@@ -19115,10 +19179,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C52" s="4">
         <v>19</v>
@@ -19138,10 +19202,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="3" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C53" s="4">
         <v>2246</v>
@@ -19161,10 +19225,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C54" s="4">
         <v>575</v>
@@ -19184,10 +19248,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C55" s="4">
         <v>221</v>
@@ -19207,10 +19271,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="3" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C56" s="4">
         <v>258</v>
@@ -19230,10 +19294,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C57" s="4">
         <v>20</v>
@@ -19253,10 +19317,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C58" s="4">
         <v>2520</v>
@@ -19276,10 +19340,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C59" s="4">
         <v>4089</v>
@@ -19299,10 +19363,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C60" s="4">
         <v>21</v>
@@ -19322,10 +19386,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="C61" s="4">
         <v>262</v>
@@ -19345,10 +19409,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="C62" s="4">
         <v>2513</v>
@@ -19368,10 +19432,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C63" s="4">
         <v>16</v>
@@ -19391,10 +19455,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C64" s="4">
         <v>3114</v>
@@ -19414,10 +19478,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C65" s="4">
         <v>4086</v>
@@ -19437,10 +19501,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C66" s="4">
         <v>15</v>
@@ -19460,10 +19524,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C67" s="4">
         <v>3115</v>
@@ -19483,10 +19547,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C68" s="4">
         <v>4165</v>
@@ -19506,10 +19570,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C69" s="4">
         <v>4100</v>
@@ -19529,10 +19593,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="C70" s="4">
         <v>4280</v>
@@ -19552,10 +19616,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="C71" s="4">
         <v>4281</v>
@@ -19620,10 +19684,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C2" s="4">
         <v>11</v>
@@ -19643,10 +19707,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C3" s="4">
         <v>2471</v>
@@ -19666,10 +19730,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C4" s="4">
         <v>3472</v>
@@ -19689,10 +19753,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C5" s="4">
         <v>2472</v>
@@ -19712,10 +19776,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="C6" s="4">
         <v>133</v>
@@ -19735,10 +19799,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C7" s="4">
         <v>127</v>
@@ -19758,10 +19822,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C8" s="4">
         <v>2637</v>
@@ -19781,10 +19845,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
@@ -19804,10 +19868,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C10" s="4">
         <v>2501</v>
@@ -19827,10 +19891,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C11" s="4">
         <v>24</v>
@@ -19850,10 +19914,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C12" s="4">
         <v>2726</v>
@@ -19873,10 +19937,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C13" s="4">
         <v>4221</v>
@@ -19896,10 +19960,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C14" s="4">
         <v>4222</v>
@@ -19919,10 +19983,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C15" s="4">
         <v>2580</v>
@@ -19942,10 +20006,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C16" s="4">
         <v>123</v>
@@ -19965,10 +20029,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C17" s="4">
         <v>4016</v>
@@ -19988,10 +20052,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C18" s="4">
         <v>4017</v>
@@ -20011,10 +20075,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C19" s="4">
         <v>210</v>
@@ -20034,10 +20098,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C20" s="4">
         <v>4545</v>
@@ -20057,10 +20121,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C21" s="4">
         <v>3363</v>
@@ -20080,10 +20144,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C22" s="4">
         <v>2482</v>
@@ -20103,10 +20167,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C23" s="4">
         <v>34</v>
@@ -20126,10 +20190,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C24" s="4">
         <v>89</v>
@@ -20149,10 +20213,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C25" s="4">
         <v>114</v>
@@ -20172,10 +20236,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="C26" s="4">
         <v>2486</v>
@@ -20195,10 +20259,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="C27" s="4">
         <v>2241</v>
@@ -20218,10 +20282,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C28" s="4">
         <v>2487</v>
@@ -20241,10 +20305,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C29" s="4">
         <v>23</v>
@@ -20264,10 +20328,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C30" s="4">
         <v>2260</v>
@@ -20287,10 +20351,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C31" s="4">
         <v>214</v>
@@ -20310,10 +20374,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C32" s="4">
         <v>4664</v>
@@ -20333,10 +20397,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C33" s="4">
         <v>4665</v>
@@ -20356,10 +20420,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C34" s="4">
         <v>28</v>
@@ -20379,10 +20443,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C35" s="4">
         <v>68</v>
@@ -20402,10 +20466,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C36" s="4">
         <v>2302</v>
@@ -20425,10 +20489,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C37" s="4">
         <v>320</v>
@@ -20448,10 +20512,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C38" s="4">
         <v>3479</v>
@@ -20471,10 +20535,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C39" s="4">
         <v>130</v>
@@ -20494,10 +20558,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C40" s="4">
         <v>2464</v>
@@ -20517,10 +20581,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C41" s="4">
         <v>101</v>
@@ -20540,10 +20604,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C42" s="4">
         <v>2465</v>
@@ -20563,10 +20627,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C43" s="4">
         <v>65</v>
@@ -20586,10 +20650,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C44" s="4">
         <v>2624</v>
@@ -20609,10 +20673,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C45" s="4">
         <v>119</v>
@@ -20632,10 +20696,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C46" s="4">
         <v>2834</v>
@@ -20655,10 +20719,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C47" s="4">
         <v>3621</v>
@@ -20678,10 +20742,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C48" s="4">
         <v>141</v>
@@ -20701,10 +20765,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="3" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C49" s="4">
         <v>3025</v>
@@ -20724,10 +20788,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="3" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C50" s="4">
         <v>2543</v>
@@ -20747,10 +20811,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C51" s="4">
         <v>98</v>
@@ -20770,10 +20834,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C52" s="4">
         <v>35</v>
@@ -20793,10 +20857,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="3" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C53" s="4">
         <v>2353</v>
@@ -20816,10 +20880,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="3" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C54" s="4">
         <v>2466</v>
@@ -20839,10 +20903,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C55" s="4">
         <v>3089</v>
@@ -20862,10 +20926,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C56" s="4">
         <v>2666</v>
@@ -20885,10 +20949,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C57" s="4">
         <v>2667</v>
@@ -20908,10 +20972,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C58" s="4">
         <v>3478</v>
@@ -20931,10 +20995,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C59" s="4">
         <v>190</v>
@@ -20954,10 +21018,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C60" s="4">
         <v>2335</v>
@@ -20977,10 +21041,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C61" s="4">
         <v>3446</v>
@@ -21000,10 +21064,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C62" s="4">
         <v>3447</v>
@@ -21023,10 +21087,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C63" s="4">
         <v>100</v>
@@ -21046,10 +21110,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C64" s="4">
         <v>136</v>
@@ -21069,10 +21133,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C65" s="4">
         <v>259</v>
@@ -21092,10 +21156,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C66" s="4">
         <v>2319</v>
@@ -21115,10 +21179,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C67" s="4">
         <v>125</v>
@@ -21138,10 +21202,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C68" s="4">
         <v>2468</v>
@@ -21161,10 +21225,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C69" s="4">
         <v>3670</v>
@@ -21184,10 +21248,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C70" s="4">
         <v>2469</v>
@@ -21207,10 +21271,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C71" s="4">
         <v>3006</v>
@@ -21230,10 +21294,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C72" s="4">
         <v>3007</v>
@@ -21253,10 +21317,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C73" s="4">
         <v>117</v>
@@ -21276,10 +21340,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C74" s="4">
         <v>2320</v>
@@ -21299,10 +21363,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="3" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C75" s="4">
         <v>60</v>
@@ -21322,10 +21386,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C76" s="4">
         <v>2321</v>
@@ -21345,10 +21409,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C77" s="4">
         <v>211</v>
@@ -21368,10 +21432,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C78" s="4">
         <v>41</v>
@@ -21391,10 +21455,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C79" s="4">
         <v>2322</v>
@@ -21414,10 +21478,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C80" s="4">
         <v>67</v>
@@ -21437,10 +21501,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C81" s="4">
         <v>2244</v>
@@ -21460,10 +21524,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C82" s="4">
         <v>2488</v>
@@ -21483,10 +21547,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C83" s="4">
         <v>520</v>
@@ -21506,10 +21570,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C84" s="4">
         <v>4546</v>
@@ -21529,10 +21593,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C85" s="4">
         <v>3695</v>
@@ -21552,10 +21616,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C86" s="4">
         <v>3097</v>
@@ -21575,10 +21639,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C87" s="4">
         <v>2460</v>
@@ -21598,10 +21662,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C88" s="4">
         <v>3110</v>
@@ -21621,10 +21685,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C89" s="4">
         <v>135</v>
@@ -21644,10 +21708,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C90" s="4">
         <v>2463</v>
@@ -21667,10 +21731,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C91" s="4">
         <v>55</v>
@@ -21690,10 +21754,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C92" s="4">
         <v>51</v>
@@ -21713,10 +21777,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C93" s="4">
         <v>201</v>
@@ -21736,10 +21800,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C94" s="4">
         <v>4223</v>
@@ -21759,10 +21823,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="3" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C95" s="4">
         <v>4224</v>
@@ -21790,7 +21854,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -21827,10 +21891,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C2" s="4">
         <v>8</v>
@@ -21850,10 +21914,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C3" s="4">
         <v>2391</v>
@@ -21873,10 +21937,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C4" s="4">
         <v>2529</v>
@@ -21896,10 +21960,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C5" s="4">
         <v>27</v>
@@ -21919,10 +21983,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C6" s="4">
         <v>2255</v>
@@ -21942,10 +22006,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C7" s="4">
         <v>3649</v>
@@ -21965,10 +22029,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C8" s="4">
         <v>3650</v>
@@ -21988,10 +22052,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C9" s="4">
         <v>3386</v>
@@ -22011,10 +22075,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C10" s="4">
         <v>3385</v>
@@ -22034,10 +22098,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C11" s="4">
         <v>460</v>
@@ -22057,10 +22121,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C12" s="4">
         <v>2473</v>
@@ -22080,10 +22144,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C13" s="4">
         <v>128</v>
@@ -22103,10 +22167,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C14" s="4">
         <v>2474</v>
@@ -22126,10 +22190,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C15" s="4">
         <v>3085</v>
@@ -22149,10 +22213,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C16" s="4">
         <v>3086</v>
@@ -22172,10 +22236,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C17" s="4">
         <v>4558</v>
@@ -22195,10 +22259,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C18" s="4">
         <v>4048</v>
@@ -22218,10 +22282,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C19" s="4">
         <v>2519</v>
@@ -22241,10 +22305,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C20" s="4">
         <v>2525</v>
@@ -22264,10 +22328,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C21" s="4">
         <v>3433</v>
@@ -22287,10 +22351,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C22" s="4">
         <v>3394</v>
@@ -22310,10 +22374,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C23" s="4">
         <v>47</v>
@@ -22333,10 +22397,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C24" s="4">
         <v>46</v>
@@ -22356,10 +22420,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C25" s="4">
         <v>3100</v>
@@ -22379,10 +22443,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C26" s="4">
         <v>3746</v>
@@ -22402,10 +22466,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C27" s="4">
         <v>3639</v>
@@ -22425,10 +22489,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C28" s="4">
         <v>2415</v>
@@ -22448,10 +22512,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C29" s="4">
         <v>3747</v>
@@ -22471,10 +22535,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="3" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C30" s="4">
         <v>3640</v>
@@ -22494,10 +22558,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C31" s="4">
         <v>2416</v>
@@ -22517,10 +22581,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C32" s="4">
         <v>50</v>
@@ -22540,10 +22604,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C33" s="4">
         <v>2533</v>
@@ -22563,10 +22627,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C34" s="4">
         <v>52</v>
@@ -22586,10 +22650,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C35" s="4">
         <v>2470</v>
@@ -22609,13 +22673,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C36" s="4">
-        <v>53</v>
+        <v>4671</v>
       </c>
       <c r="D36" s="4">
         <v>25</v>
@@ -22627,29 +22691,52 @@
         <v>158</v>
       </c>
       <c r="G36" s="4">
-        <v>118</v>
+        <v>164</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C37" s="4">
+        <v>53</v>
+      </c>
+      <c r="D37" s="4">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G37" s="4">
+        <v>118</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C38" s="4">
         <v>2435</v>
       </c>
-      <c r="D37" s="4">
-        <v>5</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="5">
+      <c r="D38" s="4">
+        <v>5</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="5">
         <v>25.5</v>
       </c>
     </row>
@@ -22663,7 +22750,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -22959,42 +23046,42 @@
         <v>569</v>
       </c>
       <c r="C13" s="4">
-        <v>2522</v>
+        <v>4669</v>
       </c>
       <c r="D13" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G13" s="4">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C14" s="4">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="D14" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G14" s="4">
-        <v>490</v>
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -23005,7 +23092,7 @@
         <v>571</v>
       </c>
       <c r="C15" s="4">
-        <v>2571</v>
+        <v>2521</v>
       </c>
       <c r="D15" s="4">
         <v>10</v>
@@ -23014,33 +23101,33 @@
         <v>29</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="G15" s="4">
-        <v>185</v>
+        <v>490</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C16" s="4">
-        <v>4108</v>
+        <v>2571</v>
       </c>
       <c r="D16" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="5">
-        <v>95.5</v>
+        <v>158</v>
+      </c>
+      <c r="G16" s="4">
+        <v>185</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
@@ -23051,42 +23138,42 @@
         <v>573</v>
       </c>
       <c r="C17" s="4">
-        <v>4111</v>
+        <v>4108</v>
       </c>
       <c r="D17" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G17" s="4">
-        <v>180</v>
+        <v>10</v>
+      </c>
+      <c r="G17" s="5">
+        <v>95.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C18" s="4">
-        <v>3499</v>
+        <v>4111</v>
       </c>
       <c r="D18" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G18" s="4">
-        <v>92</v>
+        <v>210</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
@@ -23097,42 +23184,42 @@
         <v>575</v>
       </c>
       <c r="C19" s="4">
-        <v>2616</v>
+        <v>3499</v>
       </c>
       <c r="D19" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G19" s="4">
-        <v>1875</v>
+        <v>108.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C20" s="4">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="D20" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G20" s="4">
-        <v>375</v>
+        <v>1875</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -23143,7 +23230,7 @@
         <v>577</v>
       </c>
       <c r="C21" s="4">
-        <v>4283</v>
+        <v>2615</v>
       </c>
       <c r="D21" s="4">
         <v>5</v>
@@ -23155,7 +23242,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="4">
-        <v>170</v>
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
@@ -23166,42 +23253,42 @@
         <v>579</v>
       </c>
       <c r="C22" s="4">
-        <v>4114</v>
+        <v>4283</v>
       </c>
       <c r="D22" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G22" s="5">
-        <v>62.5</v>
+        <v>10</v>
+      </c>
+      <c r="G22" s="4">
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C23" s="4">
-        <v>3493</v>
+        <v>4114</v>
       </c>
       <c r="D23" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="4">
-        <v>33</v>
+        <v>158</v>
+      </c>
+      <c r="G23" s="5">
+        <v>62.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -23212,10 +23299,10 @@
         <v>581</v>
       </c>
       <c r="C24" s="4">
-        <v>4395</v>
+        <v>3493</v>
       </c>
       <c r="D24" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>29</v>
@@ -23224,21 +23311,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>320</v>
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C25" s="4">
-        <v>4394</v>
+        <v>4395</v>
       </c>
       <c r="D25" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>29</v>
@@ -23247,7 +23334,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="4">
-        <v>97</v>
+        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
@@ -23258,42 +23345,42 @@
         <v>583</v>
       </c>
       <c r="C26" s="4">
-        <v>4115</v>
+        <v>4394</v>
       </c>
       <c r="D26" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G26" s="4">
-        <v>240</v>
+        <v>97</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C27" s="4">
-        <v>3497</v>
+        <v>4115</v>
       </c>
       <c r="D27" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G27" s="4">
-        <v>122</v>
+        <v>240</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
@@ -23304,42 +23391,42 @@
         <v>585</v>
       </c>
       <c r="C28" s="4">
-        <v>2492</v>
+        <v>3497</v>
       </c>
       <c r="D28" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G28" s="4">
-        <v>348</v>
+        <v>122</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C29" s="4">
-        <v>2499</v>
+        <v>2492</v>
       </c>
       <c r="D29" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>29</v>
+        <v>348</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -23350,33 +23437,33 @@
         <v>587</v>
       </c>
       <c r="C30" s="4">
-        <v>3101</v>
+        <v>2499</v>
       </c>
       <c r="D30" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G30" s="5">
-        <v>77.5</v>
+        <v>10</v>
+      </c>
+      <c r="G30" s="4">
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C31" s="4">
-        <v>580</v>
+        <v>3101</v>
       </c>
       <c r="D31" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>29</v>
@@ -23384,8 +23471,8 @@
       <c r="F31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G31" s="4">
-        <v>31</v>
+      <c r="G31" s="5">
+        <v>77.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -23396,10 +23483,10 @@
         <v>589</v>
       </c>
       <c r="C32" s="4">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D32" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -23408,7 +23495,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>112.5</v>
+        <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -23419,19 +23506,19 @@
         <v>591</v>
       </c>
       <c r="C33" s="4">
-        <v>4029</v>
+        <v>581</v>
       </c>
       <c r="D33" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="G33" s="4">
-        <v>122</v>
+        <v>112.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -23442,7 +23529,7 @@
         <v>593</v>
       </c>
       <c r="C34" s="4">
-        <v>4203</v>
+        <v>4029</v>
       </c>
       <c r="D34" s="4">
         <v>20</v>
@@ -23451,10 +23538,10 @@
         <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="G34" s="4">
-        <v>86</v>
+        <v>122</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
@@ -23465,19 +23552,19 @@
         <v>595</v>
       </c>
       <c r="C35" s="4">
-        <v>3936</v>
+        <v>4203</v>
       </c>
       <c r="D35" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G35" s="4">
-        <v>209</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
@@ -23488,10 +23575,10 @@
         <v>597</v>
       </c>
       <c r="C36" s="4">
-        <v>4302</v>
+        <v>3936</v>
       </c>
       <c r="D36" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>38</v>
@@ -23499,8 +23586,8 @@
       <c r="F36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G36" s="5">
-        <v>103.5</v>
+      <c r="G36" s="4">
+        <v>209</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
@@ -23511,42 +23598,42 @@
         <v>599</v>
       </c>
       <c r="C37" s="4">
-        <v>3027</v>
+        <v>4302</v>
       </c>
       <c r="D37" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="G37" s="5">
-        <v>31.5</v>
+        <v>103.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C38" s="4">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="D38" s="4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G38" s="4">
-        <v>44</v>
+        <v>158</v>
+      </c>
+      <c r="G38" s="5">
+        <v>31.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
@@ -23557,42 +23644,42 @@
         <v>601</v>
       </c>
       <c r="C39" s="4">
+        <v>3026</v>
+      </c>
+      <c r="D39" s="4">
+        <v>30</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" s="4">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
+      <c r="A40" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C40" s="4">
         <v>3514</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D40" s="4">
         <v>25</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G39" s="4">
+      <c r="E40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G40" s="4">
         <v>33</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="C40" s="4">
-        <v>3515</v>
-      </c>
-      <c r="D40" s="4">
-        <v>30</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G40" s="4">
-        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -23603,33 +23690,33 @@
         <v>603</v>
       </c>
       <c r="C41" s="4">
-        <v>3139</v>
+        <v>3515</v>
       </c>
       <c r="D41" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G41" s="4">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C42" s="4">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="D42" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>29</v>
@@ -23638,7 +23725,7 @@
         <v>158</v>
       </c>
       <c r="G42" s="4">
-        <v>300</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
@@ -23649,42 +23736,42 @@
         <v>605</v>
       </c>
       <c r="C43" s="4">
-        <v>2592</v>
+        <v>3138</v>
       </c>
       <c r="D43" s="4">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="5">
-        <v>27.5</v>
+        <v>158</v>
+      </c>
+      <c r="G43" s="4">
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C44" s="4">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="D44" s="4">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G44" s="5">
-        <v>337.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
@@ -23695,19 +23782,19 @@
         <v>607</v>
       </c>
       <c r="C45" s="4">
-        <v>2597</v>
+        <v>2591</v>
       </c>
       <c r="D45" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="4">
-        <v>90</v>
+        <v>158</v>
+      </c>
+      <c r="G45" s="5">
+        <v>337.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
@@ -23718,7 +23805,7 @@
         <v>609</v>
       </c>
       <c r="C46" s="4">
-        <v>4174</v>
+        <v>2597</v>
       </c>
       <c r="D46" s="4">
         <v>5</v>
@@ -23730,7 +23817,7 @@
         <v>10</v>
       </c>
       <c r="G46" s="4">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -23741,7 +23828,7 @@
         <v>611</v>
       </c>
       <c r="C47" s="4">
-        <v>4176</v>
+        <v>4174</v>
       </c>
       <c r="D47" s="4">
         <v>5</v>
@@ -23753,7 +23840,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="4">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
@@ -23764,7 +23851,7 @@
         <v>613</v>
       </c>
       <c r="C48" s="4">
-        <v>2686</v>
+        <v>4176</v>
       </c>
       <c r="D48" s="4">
         <v>5</v>
@@ -23775,8 +23862,8 @@
       <c r="F48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G48" s="5">
-        <v>64.5</v>
+      <c r="G48" s="4">
+        <v>140</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
@@ -23787,7 +23874,7 @@
         <v>615</v>
       </c>
       <c r="C49" s="4">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="D49" s="4">
         <v>5</v>
@@ -23810,7 +23897,7 @@
         <v>617</v>
       </c>
       <c r="C50" s="4">
-        <v>4496</v>
+        <v>2687</v>
       </c>
       <c r="D50" s="4">
         <v>5</v>
@@ -23821,8 +23908,8 @@
       <c r="F50" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G50" s="4">
-        <v>125</v>
+      <c r="G50" s="5">
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -23833,7 +23920,7 @@
         <v>619</v>
       </c>
       <c r="C51" s="4">
-        <v>4061</v>
+        <v>4496</v>
       </c>
       <c r="D51" s="4">
         <v>5</v>
@@ -23856,7 +23943,7 @@
         <v>621</v>
       </c>
       <c r="C52" s="4">
-        <v>4166</v>
+        <v>4061</v>
       </c>
       <c r="D52" s="4">
         <v>5</v>
@@ -23879,7 +23966,7 @@
         <v>623</v>
       </c>
       <c r="C53" s="4">
-        <v>2681</v>
+        <v>4166</v>
       </c>
       <c r="D53" s="4">
         <v>5</v>
@@ -23891,7 +23978,7 @@
         <v>10</v>
       </c>
       <c r="G53" s="4">
-        <v>42</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
@@ -23902,7 +23989,7 @@
         <v>625</v>
       </c>
       <c r="C54" s="4">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="D54" s="4">
         <v>5</v>
@@ -23914,7 +24001,7 @@
         <v>10</v>
       </c>
       <c r="G54" s="4">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
@@ -23925,7 +24012,7 @@
         <v>627</v>
       </c>
       <c r="C55" s="4">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="D55" s="4">
         <v>5</v>
@@ -23948,7 +24035,7 @@
         <v>629</v>
       </c>
       <c r="C56" s="4">
-        <v>2600</v>
+        <v>2683</v>
       </c>
       <c r="D56" s="4">
         <v>5</v>
@@ -23960,7 +24047,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="4">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
@@ -23971,7 +24058,7 @@
         <v>631</v>
       </c>
       <c r="C57" s="4">
-        <v>4167</v>
+        <v>2600</v>
       </c>
       <c r="D57" s="4">
         <v>5</v>
@@ -23983,7 +24070,7 @@
         <v>10</v>
       </c>
       <c r="G57" s="4">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
@@ -23994,7 +24081,7 @@
         <v>633</v>
       </c>
       <c r="C58" s="4">
-        <v>2595</v>
+        <v>4167</v>
       </c>
       <c r="D58" s="4">
         <v>5</v>
@@ -24006,7 +24093,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="4">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -24017,7 +24104,7 @@
         <v>635</v>
       </c>
       <c r="C59" s="4">
-        <v>4062</v>
+        <v>2595</v>
       </c>
       <c r="D59" s="4">
         <v>5</v>
@@ -24040,7 +24127,7 @@
         <v>637</v>
       </c>
       <c r="C60" s="4">
-        <v>2707</v>
+        <v>4062</v>
       </c>
       <c r="D60" s="4">
         <v>5</v>
@@ -24063,42 +24150,42 @@
         <v>639</v>
       </c>
       <c r="C61" s="4">
-        <v>3605</v>
+        <v>2707</v>
       </c>
       <c r="D61" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G61" s="5">
-        <v>212.5</v>
+        <v>10</v>
+      </c>
+      <c r="G61" s="4">
+        <v>140</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C62" s="4">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="D62" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="4">
-        <v>27</v>
+        <v>158</v>
+      </c>
+      <c r="G62" s="5">
+        <v>212.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -24109,10 +24196,10 @@
         <v>641</v>
       </c>
       <c r="C63" s="4">
-        <v>4402</v>
+        <v>3606</v>
       </c>
       <c r="D63" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
@@ -24121,21 +24208,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="4">
-        <v>160</v>
+        <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C64" s="4">
-        <v>4401</v>
+        <v>4402</v>
       </c>
       <c r="D64" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
@@ -24144,7 +24231,7 @@
         <v>10</v>
       </c>
       <c r="G64" s="4">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -24155,7 +24242,7 @@
         <v>643</v>
       </c>
       <c r="C65" s="4">
-        <v>2684</v>
+        <v>4401</v>
       </c>
       <c r="D65" s="4">
         <v>5</v>
@@ -24166,8 +24253,8 @@
       <c r="F65" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G65" s="5">
-        <v>50.5</v>
+      <c r="G65" s="4">
+        <v>82</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -24178,7 +24265,7 @@
         <v>645</v>
       </c>
       <c r="C66" s="4">
-        <v>2723</v>
+        <v>2684</v>
       </c>
       <c r="D66" s="4">
         <v>5</v>
@@ -24189,31 +24276,31 @@
       <c r="F66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G66" s="4">
-        <v>105</v>
+      <c r="G66" s="5">
+        <v>50.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C67" s="4">
-        <v>2734</v>
+        <v>2723</v>
       </c>
       <c r="D67" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>339</v>
+        <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="4">
-        <v>630</v>
+        <v>105</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -24224,19 +24311,19 @@
         <v>647</v>
       </c>
       <c r="C68" s="4">
-        <v>4168</v>
+        <v>2734</v>
       </c>
       <c r="D68" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>29</v>
+        <v>339</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>125</v>
+        <v>630</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -24247,42 +24334,42 @@
         <v>649</v>
       </c>
       <c r="C69" s="4">
-        <v>2718</v>
+        <v>4168</v>
       </c>
       <c r="D69" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G69" s="4">
-        <v>750</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C70" s="4">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="D70" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70" s="5">
-        <v>172.5</v>
+        <v>158</v>
+      </c>
+      <c r="G70" s="4">
+        <v>750</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -24293,7 +24380,7 @@
         <v>651</v>
       </c>
       <c r="C71" s="4">
-        <v>3094</v>
+        <v>2719</v>
       </c>
       <c r="D71" s="4">
         <v>5</v>
@@ -24304,8 +24391,8 @@
       <c r="F71" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G71" s="4">
-        <v>64</v>
+      <c r="G71" s="5">
+        <v>172.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
@@ -24316,7 +24403,7 @@
         <v>653</v>
       </c>
       <c r="C72" s="4">
-        <v>4169</v>
+        <v>3094</v>
       </c>
       <c r="D72" s="4">
         <v>5</v>
@@ -24328,7 +24415,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="4">
-        <v>140</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -24339,7 +24426,7 @@
         <v>655</v>
       </c>
       <c r="C73" s="4">
-        <v>2685</v>
+        <v>4169</v>
       </c>
       <c r="D73" s="4">
         <v>5</v>
@@ -24351,7 +24438,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="4">
-        <v>72</v>
+        <v>140</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -24362,42 +24449,42 @@
         <v>657</v>
       </c>
       <c r="C74" s="4">
-        <v>4113</v>
+        <v>2685</v>
       </c>
       <c r="D74" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G74" s="4">
-        <v>189</v>
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C75" s="4">
-        <v>4106</v>
+        <v>4113</v>
       </c>
       <c r="D75" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G75" s="4">
-        <v>96</v>
+        <v>189</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -24408,7 +24495,7 @@
         <v>659</v>
       </c>
       <c r="C76" s="4">
-        <v>2596</v>
+        <v>4106</v>
       </c>
       <c r="D76" s="4">
         <v>5</v>
@@ -24420,7 +24507,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="4">
-        <v>125</v>
+        <v>96</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -24431,10 +24518,10 @@
         <v>661</v>
       </c>
       <c r="C77" s="4">
-        <v>4457</v>
+        <v>2596</v>
       </c>
       <c r="D77" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>29</v>
@@ -24443,21 +24530,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="4">
-        <v>224</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C78" s="4">
-        <v>4458</v>
+        <v>4457</v>
       </c>
       <c r="D78" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>29</v>
@@ -24466,7 +24553,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="4">
-        <v>114</v>
+        <v>224</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
@@ -24477,65 +24564,65 @@
         <v>663</v>
       </c>
       <c r="C79" s="4">
-        <v>2602</v>
+        <v>4458</v>
       </c>
       <c r="D79" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G79" s="4">
-        <v>330</v>
+        <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C80" s="4">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="D80" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G80" s="4">
-        <v>33</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C81" s="4">
-        <v>3894</v>
+        <v>2605</v>
       </c>
       <c r="D81" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4">
-        <v>825</v>
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
@@ -24546,10 +24633,10 @@
         <v>665</v>
       </c>
       <c r="C82" s="4">
-        <v>4109</v>
+        <v>3894</v>
       </c>
       <c r="D82" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>29</v>
@@ -24558,21 +24645,21 @@
         <v>158</v>
       </c>
       <c r="G82" s="4">
-        <v>148</v>
+        <v>825</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C83" s="4">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D83" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
@@ -24581,7 +24668,7 @@
         <v>158</v>
       </c>
       <c r="G83" s="4">
-        <v>76</v>
+        <v>148</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -24592,7 +24679,7 @@
         <v>667</v>
       </c>
       <c r="C84" s="4">
-        <v>4171</v>
+        <v>4110</v>
       </c>
       <c r="D84" s="4">
         <v>5</v>
@@ -24601,10 +24688,10 @@
         <v>29</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G84" s="4">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -24615,7 +24702,7 @@
         <v>669</v>
       </c>
       <c r="C85" s="4">
-        <v>2653</v>
+        <v>4171</v>
       </c>
       <c r="D85" s="4">
         <v>5</v>
@@ -24627,7 +24714,7 @@
         <v>10</v>
       </c>
       <c r="G85" s="4">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -24638,10 +24725,10 @@
         <v>671</v>
       </c>
       <c r="C86" s="4">
-        <v>3675</v>
+        <v>2653</v>
       </c>
       <c r="D86" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>29</v>
@@ -24650,7 +24737,7 @@
         <v>10</v>
       </c>
       <c r="G86" s="4">
-        <v>132</v>
+        <v>160</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
@@ -24661,42 +24748,42 @@
         <v>673</v>
       </c>
       <c r="C87" s="4">
-        <v>2417</v>
+        <v>3675</v>
       </c>
       <c r="D87" s="4">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G87" s="4">
-        <v>182</v>
+        <v>132</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C88" s="4">
-        <v>3109</v>
+        <v>2417</v>
       </c>
       <c r="D88" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G88" s="5">
-        <v>38.5</v>
+        <v>158</v>
+      </c>
+      <c r="G88" s="4">
+        <v>182</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -24707,10 +24794,10 @@
         <v>675</v>
       </c>
       <c r="C89" s="4">
-        <v>2777</v>
+        <v>3109</v>
       </c>
       <c r="D89" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
@@ -24718,22 +24805,22 @@
       <c r="F89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G89" s="4">
-        <v>180</v>
+      <c r="G89" s="5">
+        <v>38.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C90" s="4">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="D90" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
@@ -24742,7 +24829,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="4">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -24753,7 +24840,7 @@
         <v>677</v>
       </c>
       <c r="C91" s="4">
-        <v>4173</v>
+        <v>2776</v>
       </c>
       <c r="D91" s="4">
         <v>5</v>
@@ -24765,7 +24852,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="4">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -24776,7 +24863,7 @@
         <v>679</v>
       </c>
       <c r="C92" s="4">
-        <v>2689</v>
+        <v>4173</v>
       </c>
       <c r="D92" s="4">
         <v>5</v>
@@ -24788,7 +24875,7 @@
         <v>10</v>
       </c>
       <c r="G92" s="4">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -24799,7 +24886,7 @@
         <v>681</v>
       </c>
       <c r="C93" s="4">
-        <v>4170</v>
+        <v>2689</v>
       </c>
       <c r="D93" s="4">
         <v>5</v>
@@ -24811,7 +24898,7 @@
         <v>10</v>
       </c>
       <c r="G93" s="4">
-        <v>125</v>
+        <v>85</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
@@ -24822,42 +24909,42 @@
         <v>683</v>
       </c>
       <c r="C94" s="4">
-        <v>4494</v>
+        <v>4170</v>
       </c>
       <c r="D94" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G94" s="4">
-        <v>300</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C95" s="4">
-        <v>4495</v>
+        <v>4494</v>
       </c>
       <c r="D95" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G95" s="4">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
@@ -24868,7 +24955,7 @@
         <v>685</v>
       </c>
       <c r="C96" s="4">
-        <v>2785</v>
+        <v>4495</v>
       </c>
       <c r="D96" s="4">
         <v>5</v>
@@ -24879,31 +24966,31 @@
       <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="5">
-        <v>47.5</v>
+      <c r="G96" s="4">
+        <v>150</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C97" s="4">
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="D97" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G97" s="4">
-        <v>95</v>
+        <v>10</v>
+      </c>
+      <c r="G97" s="5">
+        <v>47.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
@@ -24914,7 +25001,7 @@
         <v>687</v>
       </c>
       <c r="C98" s="4">
-        <v>2788</v>
+        <v>2784</v>
       </c>
       <c r="D98" s="4">
         <v>10</v>
@@ -24926,30 +25013,30 @@
         <v>158</v>
       </c>
       <c r="G98" s="4">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="3" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C99" s="4">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="D99" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G99" s="4">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
@@ -24960,42 +25047,42 @@
         <v>689</v>
       </c>
       <c r="C100" s="4">
-        <v>4539</v>
+        <v>2789</v>
       </c>
       <c r="D100" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G100" s="4">
-        <v>95</v>
+        <v>45</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="3" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C101" s="4">
-        <v>3495</v>
+        <v>4539</v>
       </c>
       <c r="D101" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="5">
-        <v>47.5</v>
+        <v>158</v>
+      </c>
+      <c r="G101" s="4">
+        <v>95</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
@@ -25006,42 +25093,42 @@
         <v>691</v>
       </c>
       <c r="C102" s="4">
-        <v>2786</v>
+        <v>3495</v>
       </c>
       <c r="D102" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G102" s="4">
-        <v>90</v>
+        <v>10</v>
+      </c>
+      <c r="G102" s="5">
+        <v>47.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="3" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C103" s="4">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="D103" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G103" s="4">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
@@ -25052,7 +25139,7 @@
         <v>693</v>
       </c>
       <c r="C104" s="4">
-        <v>2598</v>
+        <v>2787</v>
       </c>
       <c r="D104" s="4">
         <v>5</v>
@@ -25064,7 +25151,7 @@
         <v>10</v>
       </c>
       <c r="G104" s="4">
-        <v>130</v>
+        <v>45</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
@@ -25075,7 +25162,7 @@
         <v>695</v>
       </c>
       <c r="C105" s="4">
-        <v>4060</v>
+        <v>2598</v>
       </c>
       <c r="D105" s="4">
         <v>5</v>
@@ -25087,7 +25174,7 @@
         <v>10</v>
       </c>
       <c r="G105" s="4">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
@@ -25098,7 +25185,7 @@
         <v>697</v>
       </c>
       <c r="C106" s="4">
-        <v>2690</v>
+        <v>4060</v>
       </c>
       <c r="D106" s="4">
         <v>5</v>
@@ -25110,7 +25197,7 @@
         <v>10</v>
       </c>
       <c r="G106" s="4">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
@@ -25121,42 +25208,42 @@
         <v>699</v>
       </c>
       <c r="C107" s="4">
-        <v>3355</v>
+        <v>2690</v>
       </c>
       <c r="D107" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G107" s="4">
-        <v>315</v>
+        <v>135</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="3" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C108" s="4">
-        <v>3066</v>
+        <v>3355</v>
       </c>
       <c r="D108" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G108" s="4">
-        <v>65</v>
+        <v>315</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
@@ -25167,42 +25254,42 @@
         <v>701</v>
       </c>
       <c r="C109" s="4">
-        <v>1515</v>
+        <v>3066</v>
       </c>
       <c r="D109" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G109" s="4">
-        <v>1175</v>
+        <v>65</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C110" s="4">
-        <v>2552</v>
+        <v>1515</v>
       </c>
       <c r="D110" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G110" s="4">
-        <v>235</v>
+        <v>1175</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
@@ -25213,7 +25300,7 @@
         <v>703</v>
       </c>
       <c r="C111" s="4">
-        <v>3092</v>
+        <v>2552</v>
       </c>
       <c r="D111" s="4">
         <v>5</v>
@@ -25224,8 +25311,8 @@
       <c r="F111" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G111" s="5">
-        <v>73.5</v>
+      <c r="G111" s="4">
+        <v>235</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
@@ -25236,10 +25323,10 @@
         <v>705</v>
       </c>
       <c r="C112" s="4">
-        <v>2589</v>
+        <v>3092</v>
       </c>
       <c r="D112" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>29</v>
@@ -25247,22 +25334,22 @@
       <c r="F112" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G112" s="4">
-        <v>200</v>
+      <c r="G112" s="5">
+        <v>73.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="3" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C113" s="4">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="D113" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>29</v>
@@ -25271,7 +25358,7 @@
         <v>10</v>
       </c>
       <c r="G113" s="4">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
@@ -25282,10 +25369,10 @@
         <v>707</v>
       </c>
       <c r="C114" s="4">
-        <v>2688</v>
+        <v>2588</v>
       </c>
       <c r="D114" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>29</v>
@@ -25294,7 +25381,7 @@
         <v>10</v>
       </c>
       <c r="G114" s="4">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
@@ -25305,18 +25392,41 @@
         <v>709</v>
       </c>
       <c r="C115" s="4">
+        <v>2688</v>
+      </c>
+      <c r="D115" s="4">
+        <v>5</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+      <c r="A116" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C116" s="4">
         <v>2599</v>
       </c>
-      <c r="D115" s="4">
+      <c r="D116" s="4">
         <v>3</v>
       </c>
-      <c r="E115" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G115" s="4">
+      <c r="E116" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" s="4">
         <v>84</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3734" uniqueCount="1131">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3394,36 +3394,6 @@
   </si>
   <si>
     <t>CROCANTE NATURAL BALSAMO</t>
-  </si>
-  <si>
-    <t>crocante-vp-bacon</t>
-  </si>
-  <si>
-    <t>CROCANTE VP BACON</t>
-  </si>
-  <si>
-    <t>crocante-vp-com-pimenta</t>
-  </si>
-  <si>
-    <t>CROCANTE VP COM PIMENTA</t>
-  </si>
-  <si>
-    <t>crocante-vp-com-salsa</t>
-  </si>
-  <si>
-    <t>CROCANTE VP COM SALSA</t>
-  </si>
-  <si>
-    <t>crocante-vp-japones</t>
-  </si>
-  <si>
-    <t>CROCANTE VP JAPONES</t>
-  </si>
-  <si>
-    <t>crocante-vp-natural</t>
-  </si>
-  <si>
-    <t>CROCANTE VP NATURAL</t>
   </si>
   <si>
     <t>macadamia-torrada-ssal</t>
@@ -5510,7 +5480,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="5">
-        <v>22.68</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>29</v>
@@ -5519,7 +5489,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="4">
-        <v>155</v>
+        <v>136.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
@@ -5887,7 +5857,7 @@
         <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -5910,7 +5880,7 @@
         <v>158</v>
       </c>
       <c r="G30" s="4">
-        <v>500</v>
+        <v>425</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
@@ -13460,7 +13430,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -14895,7 +14865,7 @@
         <v>15</v>
       </c>
       <c r="G62" s="4">
-        <v>1820</v>
+        <v>1950</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -14918,7 +14888,7 @@
         <v>15</v>
       </c>
       <c r="G63" s="4">
-        <v>1560</v>
+        <v>1670</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -14941,7 +14911,7 @@
         <v>10</v>
       </c>
       <c r="G64" s="4">
-        <v>393.5</v>
+        <v>421</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -14964,7 +14934,7 @@
         <v>10</v>
       </c>
       <c r="G65" s="4">
-        <v>373.5</v>
+        <v>398.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -14987,7 +14957,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="4">
-        <v>1480</v>
+        <v>1580</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -15010,7 +14980,7 @@
         <v>15</v>
       </c>
       <c r="G67" s="4">
-        <v>1040</v>
+        <v>1110</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -15033,7 +15003,7 @@
         <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>263.5</v>
+        <v>281</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -15320,16 +15290,16 @@
         <v>1122</v>
       </c>
       <c r="C81" s="4">
-        <v>3815</v>
+        <v>4021</v>
       </c>
       <c r="D81" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4">
         <v>125</v>
@@ -15337,13 +15307,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C82" s="4">
-        <v>3713</v>
+        <v>4135</v>
       </c>
       <c r="D82" s="4">
         <v>10</v>
@@ -15352,44 +15322,44 @@
         <v>29</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G82" s="4">
-        <v>125</v>
+        <v>1250</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C83" s="4">
-        <v>3712</v>
+        <v>2852</v>
       </c>
       <c r="D83" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G83" s="4">
-        <v>125</v>
+        <v>325</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="C84" s="4">
-        <v>3714</v>
+        <v>3601</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -15401,113 +15371,113 @@
         <v>10</v>
       </c>
       <c r="G84" s="4">
-        <v>125</v>
+        <v>650</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="C85" s="4">
-        <v>3715</v>
+        <v>3093</v>
       </c>
       <c r="D85" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="G85" s="4">
-        <v>125</v>
+        <v>583</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="C86" s="4">
-        <v>4021</v>
+        <v>263</v>
       </c>
       <c r="D86" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G86" s="4">
-        <v>125</v>
+        <v>530</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="C87" s="4">
-        <v>4135</v>
+        <v>2632</v>
       </c>
       <c r="D87" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G87" s="4">
-        <v>1250</v>
+        <v>267</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="C88" s="4">
-        <v>2852</v>
+        <v>2330</v>
       </c>
       <c r="D88" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G88" s="4">
-        <v>325</v>
+        <v>480</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="C89" s="4">
-        <v>3601</v>
+        <v>2385</v>
       </c>
       <c r="D89" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
@@ -15516,21 +15486,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="4">
-        <v>650</v>
+        <v>242</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C90" s="4">
-        <v>3093</v>
+        <v>2384</v>
       </c>
       <c r="D90" s="4">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
@@ -15538,19 +15508,19 @@
       <c r="F90" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G90" s="4">
-        <v>583</v>
+      <c r="G90" s="5">
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C91" s="4">
-        <v>263</v>
+        <v>3851</v>
       </c>
       <c r="D91" s="4">
         <v>10</v>
@@ -15559,21 +15529,21 @@
         <v>29</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>530</v>
+        <v>75</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C92" s="4">
-        <v>2632</v>
+        <v>2424</v>
       </c>
       <c r="D92" s="4">
         <v>5</v>
@@ -15584,122 +15554,7 @@
       <c r="F92" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G92" s="4">
-        <v>267</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="3" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C93" s="4">
-        <v>2330</v>
-      </c>
-      <c r="D93" s="4">
-        <v>10</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" s="4">
-        <v>480</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="3" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C94" s="4">
-        <v>2385</v>
-      </c>
-      <c r="D94" s="4">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="4">
-        <v>242</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="3" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C95" s="4">
-        <v>2384</v>
-      </c>
-      <c r="D95" s="4">
-        <v>25</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G95" s="5">
-        <v>187.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="3" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C96" s="4">
-        <v>3851</v>
-      </c>
-      <c r="D96" s="4">
-        <v>10</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G96" s="4">
-        <v>75</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="3" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C97" s="4">
-        <v>2424</v>
-      </c>
-      <c r="D97" s="4">
-        <v>5</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="5">
+      <c r="G92" s="5">
         <v>39.5</v>
       </c>
     </row>
@@ -17091,7 +16946,7 @@
         <v>4251</v>
       </c>
       <c r="D32" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -17100,7 +16955,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>352</v>
+        <v>440</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -17629,7 +17484,7 @@
         <v>158</v>
       </c>
       <c r="G55" s="4">
-        <v>600</v>
+        <v>550</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -17652,7 +17507,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="4">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
@@ -19238,7 +19093,7 @@
         <v>158</v>
       </c>
       <c r="G48" s="4">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
@@ -19261,7 +19116,7 @@
         <v>10</v>
       </c>
       <c r="G49" s="4">
-        <v>24</v>
+        <v>22.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
@@ -19815,7 +19670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>770</v>
       </c>
@@ -19838,7 +19693,7 @@
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>770</v>
       </c>
@@ -19861,7 +19716,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>772</v>
       </c>
@@ -19884,7 +19739,7 @@
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>772</v>
       </c>
@@ -19907,7 +19762,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>774</v>
       </c>
@@ -19930,7 +19785,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>776</v>
       </c>
@@ -19953,7 +19808,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>776</v>
       </c>
@@ -19976,7 +19831,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>778</v>
       </c>
@@ -19999,7 +19854,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>778</v>
       </c>
@@ -20022,7 +19877,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>780</v>
       </c>
@@ -20045,7 +19900,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>780</v>
       </c>
@@ -20068,7 +19923,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>782</v>
       </c>
@@ -20091,7 +19946,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>782</v>
       </c>
@@ -20114,7 +19969,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>784</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Documents\lista-bourached\Lista-de-Produtos-Bourached\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D3E2BE-25E8-4B64-8D4C-0DA9093B747A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728AD734-514A-44E5-8791-927F937D2641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -8983,7 +8983,7 @@
         <v>49</v>
       </c>
       <c r="G8" s="3">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9006,7 +9006,7 @@
         <v>49</v>
       </c>
       <c r="G9" s="4">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4191,7 +4191,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="4">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -4237,7 +4237,7 @@
         <v>158</v>
       </c>
       <c r="G17" s="4">
-        <v>1875</v>
+        <v>1850</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
@@ -4260,7 +4260,7 @@
         <v>158</v>
       </c>
       <c r="G18" s="4">
-        <v>378.5</v>
+        <v>373.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
